--- a/terminboard/vorlagen/termine_modell2.xlsx
+++ b/terminboard/vorlagen/termine_modell2.xlsx
@@ -15,7 +15,6 @@
   </sheets>
   <definedNames>
     <definedName name="Pruefstaende">'Prüfstände'!$C$2:$C$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Termine'!$A$1:$G$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -37,61 +36,28 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F3864"/>
       <sz val="14"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="002E74B5"/>
-      <sz val="11"/>
+      <i val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E74B5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00595959"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -99,64 +65,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -520,23 +440,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002E74B5"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Nr</t>
@@ -574,199 +493,2170 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Wartung</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>P03 NRA</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="2" t="n">
         <v>46328.29166666666</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="2" t="n">
         <v>46328.625</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Jahreswartung Hydraulik</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>abgeschlossen</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Kalibrierung</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>P10 PTU TESTFUCHS</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="2" t="n">
         <v>46342.33333333334</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="2" t="n">
         <v>46347.66666666666</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Kalibrierung Druckmessung, unterbrochen</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>abgeschlossen</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Ausfall</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>P21 NRC HYCOM</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="2" t="n">
         <v>46344.25</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="2" t="n">
         <v>46345.75</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Steuerung ausgefallen, Ersatzteil</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>offen</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Kalibrierung</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>P31 THSA</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="2" t="n">
         <v>46350.375</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="2" t="n">
         <v>46350.54166666666</v>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Halbtag, Rest des Tages freigegeben</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>offen</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Audit</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>P40 AKKU/HOCHDRUCK-RAUM</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="2" t="n">
         <v>46353.41666666666</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="2" t="n">
         <v>46353.5</v>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>interner Audit</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>offen</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>P07 EHSV NRA</t>
         </is>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="2" t="n">
         <v>46357.33333333334</v>
       </c>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Hinweis Software-Update</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>offen</t>
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="D25" s="2" t="n"/>
+      <c r="E25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="D26" s="2" t="n"/>
+      <c r="E26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="D27" s="2" t="n"/>
+      <c r="E27" s="2" t="n"/>
+    </row>
+    <row r="28">
+      <c r="D28" s="2" t="n"/>
+      <c r="E28" s="2" t="n"/>
+    </row>
+    <row r="29">
+      <c r="D29" s="2" t="n"/>
+      <c r="E29" s="2" t="n"/>
+    </row>
+    <row r="30">
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="D31" s="2" t="n"/>
+      <c r="E31" s="2" t="n"/>
+    </row>
+    <row r="32">
+      <c r="D32" s="2" t="n"/>
+      <c r="E32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="D33" s="2" t="n"/>
+      <c r="E33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="D34" s="2" t="n"/>
+      <c r="E34" s="2" t="n"/>
+    </row>
+    <row r="35">
+      <c r="D35" s="2" t="n"/>
+      <c r="E35" s="2" t="n"/>
+    </row>
+    <row r="36">
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="2" t="n"/>
+    </row>
+    <row r="37">
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="n"/>
+    </row>
+    <row r="38">
+      <c r="D38" s="2" t="n"/>
+      <c r="E38" s="2" t="n"/>
+    </row>
+    <row r="39">
+      <c r="D39" s="2" t="n"/>
+      <c r="E39" s="2" t="n"/>
+    </row>
+    <row r="40">
+      <c r="D40" s="2" t="n"/>
+      <c r="E40" s="2" t="n"/>
+    </row>
+    <row r="41">
+      <c r="D41" s="2" t="n"/>
+      <c r="E41" s="2" t="n"/>
+    </row>
+    <row r="42">
+      <c r="D42" s="2" t="n"/>
+      <c r="E42" s="2" t="n"/>
+    </row>
+    <row r="43">
+      <c r="D43" s="2" t="n"/>
+      <c r="E43" s="2" t="n"/>
+    </row>
+    <row r="44">
+      <c r="D44" s="2" t="n"/>
+      <c r="E44" s="2" t="n"/>
+    </row>
+    <row r="45">
+      <c r="D45" s="2" t="n"/>
+      <c r="E45" s="2" t="n"/>
+    </row>
+    <row r="46">
+      <c r="D46" s="2" t="n"/>
+      <c r="E46" s="2" t="n"/>
+    </row>
+    <row r="47">
+      <c r="D47" s="2" t="n"/>
+      <c r="E47" s="2" t="n"/>
+    </row>
+    <row r="48">
+      <c r="D48" s="2" t="n"/>
+      <c r="E48" s="2" t="n"/>
+    </row>
+    <row r="49">
+      <c r="D49" s="2" t="n"/>
+      <c r="E49" s="2" t="n"/>
+    </row>
+    <row r="50">
+      <c r="D50" s="2" t="n"/>
+      <c r="E50" s="2" t="n"/>
+    </row>
+    <row r="51">
+      <c r="D51" s="2" t="n"/>
+      <c r="E51" s="2" t="n"/>
+    </row>
+    <row r="52">
+      <c r="D52" s="2" t="n"/>
+      <c r="E52" s="2" t="n"/>
+    </row>
+    <row r="53">
+      <c r="D53" s="2" t="n"/>
+      <c r="E53" s="2" t="n"/>
+    </row>
+    <row r="54">
+      <c r="D54" s="2" t="n"/>
+      <c r="E54" s="2" t="n"/>
+    </row>
+    <row r="55">
+      <c r="D55" s="2" t="n"/>
+      <c r="E55" s="2" t="n"/>
+    </row>
+    <row r="56">
+      <c r="D56" s="2" t="n"/>
+      <c r="E56" s="2" t="n"/>
+    </row>
+    <row r="57">
+      <c r="D57" s="2" t="n"/>
+      <c r="E57" s="2" t="n"/>
+    </row>
+    <row r="58">
+      <c r="D58" s="2" t="n"/>
+      <c r="E58" s="2" t="n"/>
+    </row>
+    <row r="59">
+      <c r="D59" s="2" t="n"/>
+      <c r="E59" s="2" t="n"/>
+    </row>
+    <row r="60">
+      <c r="D60" s="2" t="n"/>
+      <c r="E60" s="2" t="n"/>
+    </row>
+    <row r="61">
+      <c r="D61" s="2" t="n"/>
+      <c r="E61" s="2" t="n"/>
+    </row>
+    <row r="62">
+      <c r="D62" s="2" t="n"/>
+      <c r="E62" s="2" t="n"/>
+    </row>
+    <row r="63">
+      <c r="D63" s="2" t="n"/>
+      <c r="E63" s="2" t="n"/>
+    </row>
+    <row r="64">
+      <c r="D64" s="2" t="n"/>
+      <c r="E64" s="2" t="n"/>
+    </row>
+    <row r="65">
+      <c r="D65" s="2" t="n"/>
+      <c r="E65" s="2" t="n"/>
+    </row>
+    <row r="66">
+      <c r="D66" s="2" t="n"/>
+      <c r="E66" s="2" t="n"/>
+    </row>
+    <row r="67">
+      <c r="D67" s="2" t="n"/>
+      <c r="E67" s="2" t="n"/>
+    </row>
+    <row r="68">
+      <c r="D68" s="2" t="n"/>
+      <c r="E68" s="2" t="n"/>
+    </row>
+    <row r="69">
+      <c r="D69" s="2" t="n"/>
+      <c r="E69" s="2" t="n"/>
+    </row>
+    <row r="70">
+      <c r="D70" s="2" t="n"/>
+      <c r="E70" s="2" t="n"/>
+    </row>
+    <row r="71">
+      <c r="D71" s="2" t="n"/>
+      <c r="E71" s="2" t="n"/>
+    </row>
+    <row r="72">
+      <c r="D72" s="2" t="n"/>
+      <c r="E72" s="2" t="n"/>
+    </row>
+    <row r="73">
+      <c r="D73" s="2" t="n"/>
+      <c r="E73" s="2" t="n"/>
+    </row>
+    <row r="74">
+      <c r="D74" s="2" t="n"/>
+      <c r="E74" s="2" t="n"/>
+    </row>
+    <row r="75">
+      <c r="D75" s="2" t="n"/>
+      <c r="E75" s="2" t="n"/>
+    </row>
+    <row r="76">
+      <c r="D76" s="2" t="n"/>
+      <c r="E76" s="2" t="n"/>
+    </row>
+    <row r="77">
+      <c r="D77" s="2" t="n"/>
+      <c r="E77" s="2" t="n"/>
+    </row>
+    <row r="78">
+      <c r="D78" s="2" t="n"/>
+      <c r="E78" s="2" t="n"/>
+    </row>
+    <row r="79">
+      <c r="D79" s="2" t="n"/>
+      <c r="E79" s="2" t="n"/>
+    </row>
+    <row r="80">
+      <c r="D80" s="2" t="n"/>
+      <c r="E80" s="2" t="n"/>
+    </row>
+    <row r="81">
+      <c r="D81" s="2" t="n"/>
+      <c r="E81" s="2" t="n"/>
+    </row>
+    <row r="82">
+      <c r="D82" s="2" t="n"/>
+      <c r="E82" s="2" t="n"/>
+    </row>
+    <row r="83">
+      <c r="D83" s="2" t="n"/>
+      <c r="E83" s="2" t="n"/>
+    </row>
+    <row r="84">
+      <c r="D84" s="2" t="n"/>
+      <c r="E84" s="2" t="n"/>
+    </row>
+    <row r="85">
+      <c r="D85" s="2" t="n"/>
+      <c r="E85" s="2" t="n"/>
+    </row>
+    <row r="86">
+      <c r="D86" s="2" t="n"/>
+      <c r="E86" s="2" t="n"/>
+    </row>
+    <row r="87">
+      <c r="D87" s="2" t="n"/>
+      <c r="E87" s="2" t="n"/>
+    </row>
+    <row r="88">
+      <c r="D88" s="2" t="n"/>
+      <c r="E88" s="2" t="n"/>
+    </row>
+    <row r="89">
+      <c r="D89" s="2" t="n"/>
+      <c r="E89" s="2" t="n"/>
+    </row>
+    <row r="90">
+      <c r="D90" s="2" t="n"/>
+      <c r="E90" s="2" t="n"/>
+    </row>
+    <row r="91">
+      <c r="D91" s="2" t="n"/>
+      <c r="E91" s="2" t="n"/>
+    </row>
+    <row r="92">
+      <c r="D92" s="2" t="n"/>
+      <c r="E92" s="2" t="n"/>
+    </row>
+    <row r="93">
+      <c r="D93" s="2" t="n"/>
+      <c r="E93" s="2" t="n"/>
+    </row>
+    <row r="94">
+      <c r="D94" s="2" t="n"/>
+      <c r="E94" s="2" t="n"/>
+    </row>
+    <row r="95">
+      <c r="D95" s="2" t="n"/>
+      <c r="E95" s="2" t="n"/>
+    </row>
+    <row r="96">
+      <c r="D96" s="2" t="n"/>
+      <c r="E96" s="2" t="n"/>
+    </row>
+    <row r="97">
+      <c r="D97" s="2" t="n"/>
+      <c r="E97" s="2" t="n"/>
+    </row>
+    <row r="98">
+      <c r="D98" s="2" t="n"/>
+      <c r="E98" s="2" t="n"/>
+    </row>
+    <row r="99">
+      <c r="D99" s="2" t="n"/>
+      <c r="E99" s="2" t="n"/>
+    </row>
+    <row r="100">
+      <c r="D100" s="2" t="n"/>
+      <c r="E100" s="2" t="n"/>
+    </row>
+    <row r="101">
+      <c r="D101" s="2" t="n"/>
+      <c r="E101" s="2" t="n"/>
+    </row>
+    <row r="102">
+      <c r="D102" s="2" t="n"/>
+      <c r="E102" s="2" t="n"/>
+    </row>
+    <row r="103">
+      <c r="D103" s="2" t="n"/>
+      <c r="E103" s="2" t="n"/>
+    </row>
+    <row r="104">
+      <c r="D104" s="2" t="n"/>
+      <c r="E104" s="2" t="n"/>
+    </row>
+    <row r="105">
+      <c r="D105" s="2" t="n"/>
+      <c r="E105" s="2" t="n"/>
+    </row>
+    <row r="106">
+      <c r="D106" s="2" t="n"/>
+      <c r="E106" s="2" t="n"/>
+    </row>
+    <row r="107">
+      <c r="D107" s="2" t="n"/>
+      <c r="E107" s="2" t="n"/>
+    </row>
+    <row r="108">
+      <c r="D108" s="2" t="n"/>
+      <c r="E108" s="2" t="n"/>
+    </row>
+    <row r="109">
+      <c r="D109" s="2" t="n"/>
+      <c r="E109" s="2" t="n"/>
+    </row>
+    <row r="110">
+      <c r="D110" s="2" t="n"/>
+      <c r="E110" s="2" t="n"/>
+    </row>
+    <row r="111">
+      <c r="D111" s="2" t="n"/>
+      <c r="E111" s="2" t="n"/>
+    </row>
+    <row r="112">
+      <c r="D112" s="2" t="n"/>
+      <c r="E112" s="2" t="n"/>
+    </row>
+    <row r="113">
+      <c r="D113" s="2" t="n"/>
+      <c r="E113" s="2" t="n"/>
+    </row>
+    <row r="114">
+      <c r="D114" s="2" t="n"/>
+      <c r="E114" s="2" t="n"/>
+    </row>
+    <row r="115">
+      <c r="D115" s="2" t="n"/>
+      <c r="E115" s="2" t="n"/>
+    </row>
+    <row r="116">
+      <c r="D116" s="2" t="n"/>
+      <c r="E116" s="2" t="n"/>
+    </row>
+    <row r="117">
+      <c r="D117" s="2" t="n"/>
+      <c r="E117" s="2" t="n"/>
+    </row>
+    <row r="118">
+      <c r="D118" s="2" t="n"/>
+      <c r="E118" s="2" t="n"/>
+    </row>
+    <row r="119">
+      <c r="D119" s="2" t="n"/>
+      <c r="E119" s="2" t="n"/>
+    </row>
+    <row r="120">
+      <c r="D120" s="2" t="n"/>
+      <c r="E120" s="2" t="n"/>
+    </row>
+    <row r="121">
+      <c r="D121" s="2" t="n"/>
+      <c r="E121" s="2" t="n"/>
+    </row>
+    <row r="122">
+      <c r="D122" s="2" t="n"/>
+      <c r="E122" s="2" t="n"/>
+    </row>
+    <row r="123">
+      <c r="D123" s="2" t="n"/>
+      <c r="E123" s="2" t="n"/>
+    </row>
+    <row r="124">
+      <c r="D124" s="2" t="n"/>
+      <c r="E124" s="2" t="n"/>
+    </row>
+    <row r="125">
+      <c r="D125" s="2" t="n"/>
+      <c r="E125" s="2" t="n"/>
+    </row>
+    <row r="126">
+      <c r="D126" s="2" t="n"/>
+      <c r="E126" s="2" t="n"/>
+    </row>
+    <row r="127">
+      <c r="D127" s="2" t="n"/>
+      <c r="E127" s="2" t="n"/>
+    </row>
+    <row r="128">
+      <c r="D128" s="2" t="n"/>
+      <c r="E128" s="2" t="n"/>
+    </row>
+    <row r="129">
+      <c r="D129" s="2" t="n"/>
+      <c r="E129" s="2" t="n"/>
+    </row>
+    <row r="130">
+      <c r="D130" s="2" t="n"/>
+      <c r="E130" s="2" t="n"/>
+    </row>
+    <row r="131">
+      <c r="D131" s="2" t="n"/>
+      <c r="E131" s="2" t="n"/>
+    </row>
+    <row r="132">
+      <c r="D132" s="2" t="n"/>
+      <c r="E132" s="2" t="n"/>
+    </row>
+    <row r="133">
+      <c r="D133" s="2" t="n"/>
+      <c r="E133" s="2" t="n"/>
+    </row>
+    <row r="134">
+      <c r="D134" s="2" t="n"/>
+      <c r="E134" s="2" t="n"/>
+    </row>
+    <row r="135">
+      <c r="D135" s="2" t="n"/>
+      <c r="E135" s="2" t="n"/>
+    </row>
+    <row r="136">
+      <c r="D136" s="2" t="n"/>
+      <c r="E136" s="2" t="n"/>
+    </row>
+    <row r="137">
+      <c r="D137" s="2" t="n"/>
+      <c r="E137" s="2" t="n"/>
+    </row>
+    <row r="138">
+      <c r="D138" s="2" t="n"/>
+      <c r="E138" s="2" t="n"/>
+    </row>
+    <row r="139">
+      <c r="D139" s="2" t="n"/>
+      <c r="E139" s="2" t="n"/>
+    </row>
+    <row r="140">
+      <c r="D140" s="2" t="n"/>
+      <c r="E140" s="2" t="n"/>
+    </row>
+    <row r="141">
+      <c r="D141" s="2" t="n"/>
+      <c r="E141" s="2" t="n"/>
+    </row>
+    <row r="142">
+      <c r="D142" s="2" t="n"/>
+      <c r="E142" s="2" t="n"/>
+    </row>
+    <row r="143">
+      <c r="D143" s="2" t="n"/>
+      <c r="E143" s="2" t="n"/>
+    </row>
+    <row r="144">
+      <c r="D144" s="2" t="n"/>
+      <c r="E144" s="2" t="n"/>
+    </row>
+    <row r="145">
+      <c r="D145" s="2" t="n"/>
+      <c r="E145" s="2" t="n"/>
+    </row>
+    <row r="146">
+      <c r="D146" s="2" t="n"/>
+      <c r="E146" s="2" t="n"/>
+    </row>
+    <row r="147">
+      <c r="D147" s="2" t="n"/>
+      <c r="E147" s="2" t="n"/>
+    </row>
+    <row r="148">
+      <c r="D148" s="2" t="n"/>
+      <c r="E148" s="2" t="n"/>
+    </row>
+    <row r="149">
+      <c r="D149" s="2" t="n"/>
+      <c r="E149" s="2" t="n"/>
+    </row>
+    <row r="150">
+      <c r="D150" s="2" t="n"/>
+      <c r="E150" s="2" t="n"/>
+    </row>
+    <row r="151">
+      <c r="D151" s="2" t="n"/>
+      <c r="E151" s="2" t="n"/>
+    </row>
+    <row r="152">
+      <c r="D152" s="2" t="n"/>
+      <c r="E152" s="2" t="n"/>
+    </row>
+    <row r="153">
+      <c r="D153" s="2" t="n"/>
+      <c r="E153" s="2" t="n"/>
+    </row>
+    <row r="154">
+      <c r="D154" s="2" t="n"/>
+      <c r="E154" s="2" t="n"/>
+    </row>
+    <row r="155">
+      <c r="D155" s="2" t="n"/>
+      <c r="E155" s="2" t="n"/>
+    </row>
+    <row r="156">
+      <c r="D156" s="2" t="n"/>
+      <c r="E156" s="2" t="n"/>
+    </row>
+    <row r="157">
+      <c r="D157" s="2" t="n"/>
+      <c r="E157" s="2" t="n"/>
+    </row>
+    <row r="158">
+      <c r="D158" s="2" t="n"/>
+      <c r="E158" s="2" t="n"/>
+    </row>
+    <row r="159">
+      <c r="D159" s="2" t="n"/>
+      <c r="E159" s="2" t="n"/>
+    </row>
+    <row r="160">
+      <c r="D160" s="2" t="n"/>
+      <c r="E160" s="2" t="n"/>
+    </row>
+    <row r="161">
+      <c r="D161" s="2" t="n"/>
+      <c r="E161" s="2" t="n"/>
+    </row>
+    <row r="162">
+      <c r="D162" s="2" t="n"/>
+      <c r="E162" s="2" t="n"/>
+    </row>
+    <row r="163">
+      <c r="D163" s="2" t="n"/>
+      <c r="E163" s="2" t="n"/>
+    </row>
+    <row r="164">
+      <c r="D164" s="2" t="n"/>
+      <c r="E164" s="2" t="n"/>
+    </row>
+    <row r="165">
+      <c r="D165" s="2" t="n"/>
+      <c r="E165" s="2" t="n"/>
+    </row>
+    <row r="166">
+      <c r="D166" s="2" t="n"/>
+      <c r="E166" s="2" t="n"/>
+    </row>
+    <row r="167">
+      <c r="D167" s="2" t="n"/>
+      <c r="E167" s="2" t="n"/>
+    </row>
+    <row r="168">
+      <c r="D168" s="2" t="n"/>
+      <c r="E168" s="2" t="n"/>
+    </row>
+    <row r="169">
+      <c r="D169" s="2" t="n"/>
+      <c r="E169" s="2" t="n"/>
+    </row>
+    <row r="170">
+      <c r="D170" s="2" t="n"/>
+      <c r="E170" s="2" t="n"/>
+    </row>
+    <row r="171">
+      <c r="D171" s="2" t="n"/>
+      <c r="E171" s="2" t="n"/>
+    </row>
+    <row r="172">
+      <c r="D172" s="2" t="n"/>
+      <c r="E172" s="2" t="n"/>
+    </row>
+    <row r="173">
+      <c r="D173" s="2" t="n"/>
+      <c r="E173" s="2" t="n"/>
+    </row>
+    <row r="174">
+      <c r="D174" s="2" t="n"/>
+      <c r="E174" s="2" t="n"/>
+    </row>
+    <row r="175">
+      <c r="D175" s="2" t="n"/>
+      <c r="E175" s="2" t="n"/>
+    </row>
+    <row r="176">
+      <c r="D176" s="2" t="n"/>
+      <c r="E176" s="2" t="n"/>
+    </row>
+    <row r="177">
+      <c r="D177" s="2" t="n"/>
+      <c r="E177" s="2" t="n"/>
+    </row>
+    <row r="178">
+      <c r="D178" s="2" t="n"/>
+      <c r="E178" s="2" t="n"/>
+    </row>
+    <row r="179">
+      <c r="D179" s="2" t="n"/>
+      <c r="E179" s="2" t="n"/>
+    </row>
+    <row r="180">
+      <c r="D180" s="2" t="n"/>
+      <c r="E180" s="2" t="n"/>
+    </row>
+    <row r="181">
+      <c r="D181" s="2" t="n"/>
+      <c r="E181" s="2" t="n"/>
+    </row>
+    <row r="182">
+      <c r="D182" s="2" t="n"/>
+      <c r="E182" s="2" t="n"/>
+    </row>
+    <row r="183">
+      <c r="D183" s="2" t="n"/>
+      <c r="E183" s="2" t="n"/>
+    </row>
+    <row r="184">
+      <c r="D184" s="2" t="n"/>
+      <c r="E184" s="2" t="n"/>
+    </row>
+    <row r="185">
+      <c r="D185" s="2" t="n"/>
+      <c r="E185" s="2" t="n"/>
+    </row>
+    <row r="186">
+      <c r="D186" s="2" t="n"/>
+      <c r="E186" s="2" t="n"/>
+    </row>
+    <row r="187">
+      <c r="D187" s="2" t="n"/>
+      <c r="E187" s="2" t="n"/>
+    </row>
+    <row r="188">
+      <c r="D188" s="2" t="n"/>
+      <c r="E188" s="2" t="n"/>
+    </row>
+    <row r="189">
+      <c r="D189" s="2" t="n"/>
+      <c r="E189" s="2" t="n"/>
+    </row>
+    <row r="190">
+      <c r="D190" s="2" t="n"/>
+      <c r="E190" s="2" t="n"/>
+    </row>
+    <row r="191">
+      <c r="D191" s="2" t="n"/>
+      <c r="E191" s="2" t="n"/>
+    </row>
+    <row r="192">
+      <c r="D192" s="2" t="n"/>
+      <c r="E192" s="2" t="n"/>
+    </row>
+    <row r="193">
+      <c r="D193" s="2" t="n"/>
+      <c r="E193" s="2" t="n"/>
+    </row>
+    <row r="194">
+      <c r="D194" s="2" t="n"/>
+      <c r="E194" s="2" t="n"/>
+    </row>
+    <row r="195">
+      <c r="D195" s="2" t="n"/>
+      <c r="E195" s="2" t="n"/>
+    </row>
+    <row r="196">
+      <c r="D196" s="2" t="n"/>
+      <c r="E196" s="2" t="n"/>
+    </row>
+    <row r="197">
+      <c r="D197" s="2" t="n"/>
+      <c r="E197" s="2" t="n"/>
+    </row>
+    <row r="198">
+      <c r="D198" s="2" t="n"/>
+      <c r="E198" s="2" t="n"/>
+    </row>
+    <row r="199">
+      <c r="D199" s="2" t="n"/>
+      <c r="E199" s="2" t="n"/>
+    </row>
+    <row r="200">
+      <c r="D200" s="2" t="n"/>
+      <c r="E200" s="2" t="n"/>
+    </row>
+    <row r="201">
+      <c r="D201" s="2" t="n"/>
+      <c r="E201" s="2" t="n"/>
+    </row>
+    <row r="202">
+      <c r="D202" s="2" t="n"/>
+      <c r="E202" s="2" t="n"/>
+    </row>
+    <row r="203">
+      <c r="D203" s="2" t="n"/>
+      <c r="E203" s="2" t="n"/>
+    </row>
+    <row r="204">
+      <c r="D204" s="2" t="n"/>
+      <c r="E204" s="2" t="n"/>
+    </row>
+    <row r="205">
+      <c r="D205" s="2" t="n"/>
+      <c r="E205" s="2" t="n"/>
+    </row>
+    <row r="206">
+      <c r="D206" s="2" t="n"/>
+      <c r="E206" s="2" t="n"/>
+    </row>
+    <row r="207">
+      <c r="D207" s="2" t="n"/>
+      <c r="E207" s="2" t="n"/>
+    </row>
+    <row r="208">
+      <c r="D208" s="2" t="n"/>
+      <c r="E208" s="2" t="n"/>
+    </row>
+    <row r="209">
+      <c r="D209" s="2" t="n"/>
+      <c r="E209" s="2" t="n"/>
+    </row>
+    <row r="210">
+      <c r="D210" s="2" t="n"/>
+      <c r="E210" s="2" t="n"/>
+    </row>
+    <row r="211">
+      <c r="D211" s="2" t="n"/>
+      <c r="E211" s="2" t="n"/>
+    </row>
+    <row r="212">
+      <c r="D212" s="2" t="n"/>
+      <c r="E212" s="2" t="n"/>
+    </row>
+    <row r="213">
+      <c r="D213" s="2" t="n"/>
+      <c r="E213" s="2" t="n"/>
+    </row>
+    <row r="214">
+      <c r="D214" s="2" t="n"/>
+      <c r="E214" s="2" t="n"/>
+    </row>
+    <row r="215">
+      <c r="D215" s="2" t="n"/>
+      <c r="E215" s="2" t="n"/>
+    </row>
+    <row r="216">
+      <c r="D216" s="2" t="n"/>
+      <c r="E216" s="2" t="n"/>
+    </row>
+    <row r="217">
+      <c r="D217" s="2" t="n"/>
+      <c r="E217" s="2" t="n"/>
+    </row>
+    <row r="218">
+      <c r="D218" s="2" t="n"/>
+      <c r="E218" s="2" t="n"/>
+    </row>
+    <row r="219">
+      <c r="D219" s="2" t="n"/>
+      <c r="E219" s="2" t="n"/>
+    </row>
+    <row r="220">
+      <c r="D220" s="2" t="n"/>
+      <c r="E220" s="2" t="n"/>
+    </row>
+    <row r="221">
+      <c r="D221" s="2" t="n"/>
+      <c r="E221" s="2" t="n"/>
+    </row>
+    <row r="222">
+      <c r="D222" s="2" t="n"/>
+      <c r="E222" s="2" t="n"/>
+    </row>
+    <row r="223">
+      <c r="D223" s="2" t="n"/>
+      <c r="E223" s="2" t="n"/>
+    </row>
+    <row r="224">
+      <c r="D224" s="2" t="n"/>
+      <c r="E224" s="2" t="n"/>
+    </row>
+    <row r="225">
+      <c r="D225" s="2" t="n"/>
+      <c r="E225" s="2" t="n"/>
+    </row>
+    <row r="226">
+      <c r="D226" s="2" t="n"/>
+      <c r="E226" s="2" t="n"/>
+    </row>
+    <row r="227">
+      <c r="D227" s="2" t="n"/>
+      <c r="E227" s="2" t="n"/>
+    </row>
+    <row r="228">
+      <c r="D228" s="2" t="n"/>
+      <c r="E228" s="2" t="n"/>
+    </row>
+    <row r="229">
+      <c r="D229" s="2" t="n"/>
+      <c r="E229" s="2" t="n"/>
+    </row>
+    <row r="230">
+      <c r="D230" s="2" t="n"/>
+      <c r="E230" s="2" t="n"/>
+    </row>
+    <row r="231">
+      <c r="D231" s="2" t="n"/>
+      <c r="E231" s="2" t="n"/>
+    </row>
+    <row r="232">
+      <c r="D232" s="2" t="n"/>
+      <c r="E232" s="2" t="n"/>
+    </row>
+    <row r="233">
+      <c r="D233" s="2" t="n"/>
+      <c r="E233" s="2" t="n"/>
+    </row>
+    <row r="234">
+      <c r="D234" s="2" t="n"/>
+      <c r="E234" s="2" t="n"/>
+    </row>
+    <row r="235">
+      <c r="D235" s="2" t="n"/>
+      <c r="E235" s="2" t="n"/>
+    </row>
+    <row r="236">
+      <c r="D236" s="2" t="n"/>
+      <c r="E236" s="2" t="n"/>
+    </row>
+    <row r="237">
+      <c r="D237" s="2" t="n"/>
+      <c r="E237" s="2" t="n"/>
+    </row>
+    <row r="238">
+      <c r="D238" s="2" t="n"/>
+      <c r="E238" s="2" t="n"/>
+    </row>
+    <row r="239">
+      <c r="D239" s="2" t="n"/>
+      <c r="E239" s="2" t="n"/>
+    </row>
+    <row r="240">
+      <c r="D240" s="2" t="n"/>
+      <c r="E240" s="2" t="n"/>
+    </row>
+    <row r="241">
+      <c r="D241" s="2" t="n"/>
+      <c r="E241" s="2" t="n"/>
+    </row>
+    <row r="242">
+      <c r="D242" s="2" t="n"/>
+      <c r="E242" s="2" t="n"/>
+    </row>
+    <row r="243">
+      <c r="D243" s="2" t="n"/>
+      <c r="E243" s="2" t="n"/>
+    </row>
+    <row r="244">
+      <c r="D244" s="2" t="n"/>
+      <c r="E244" s="2" t="n"/>
+    </row>
+    <row r="245">
+      <c r="D245" s="2" t="n"/>
+      <c r="E245" s="2" t="n"/>
+    </row>
+    <row r="246">
+      <c r="D246" s="2" t="n"/>
+      <c r="E246" s="2" t="n"/>
+    </row>
+    <row r="247">
+      <c r="D247" s="2" t="n"/>
+      <c r="E247" s="2" t="n"/>
+    </row>
+    <row r="248">
+      <c r="D248" s="2" t="n"/>
+      <c r="E248" s="2" t="n"/>
+    </row>
+    <row r="249">
+      <c r="D249" s="2" t="n"/>
+      <c r="E249" s="2" t="n"/>
+    </row>
+    <row r="250">
+      <c r="D250" s="2" t="n"/>
+      <c r="E250" s="2" t="n"/>
+    </row>
+    <row r="251">
+      <c r="D251" s="2" t="n"/>
+      <c r="E251" s="2" t="n"/>
+    </row>
+    <row r="252">
+      <c r="D252" s="2" t="n"/>
+      <c r="E252" s="2" t="n"/>
+    </row>
+    <row r="253">
+      <c r="D253" s="2" t="n"/>
+      <c r="E253" s="2" t="n"/>
+    </row>
+    <row r="254">
+      <c r="D254" s="2" t="n"/>
+      <c r="E254" s="2" t="n"/>
+    </row>
+    <row r="255">
+      <c r="D255" s="2" t="n"/>
+      <c r="E255" s="2" t="n"/>
+    </row>
+    <row r="256">
+      <c r="D256" s="2" t="n"/>
+      <c r="E256" s="2" t="n"/>
+    </row>
+    <row r="257">
+      <c r="D257" s="2" t="n"/>
+      <c r="E257" s="2" t="n"/>
+    </row>
+    <row r="258">
+      <c r="D258" s="2" t="n"/>
+      <c r="E258" s="2" t="n"/>
+    </row>
+    <row r="259">
+      <c r="D259" s="2" t="n"/>
+      <c r="E259" s="2" t="n"/>
+    </row>
+    <row r="260">
+      <c r="D260" s="2" t="n"/>
+      <c r="E260" s="2" t="n"/>
+    </row>
+    <row r="261">
+      <c r="D261" s="2" t="n"/>
+      <c r="E261" s="2" t="n"/>
+    </row>
+    <row r="262">
+      <c r="D262" s="2" t="n"/>
+      <c r="E262" s="2" t="n"/>
+    </row>
+    <row r="263">
+      <c r="D263" s="2" t="n"/>
+      <c r="E263" s="2" t="n"/>
+    </row>
+    <row r="264">
+      <c r="D264" s="2" t="n"/>
+      <c r="E264" s="2" t="n"/>
+    </row>
+    <row r="265">
+      <c r="D265" s="2" t="n"/>
+      <c r="E265" s="2" t="n"/>
+    </row>
+    <row r="266">
+      <c r="D266" s="2" t="n"/>
+      <c r="E266" s="2" t="n"/>
+    </row>
+    <row r="267">
+      <c r="D267" s="2" t="n"/>
+      <c r="E267" s="2" t="n"/>
+    </row>
+    <row r="268">
+      <c r="D268" s="2" t="n"/>
+      <c r="E268" s="2" t="n"/>
+    </row>
+    <row r="269">
+      <c r="D269" s="2" t="n"/>
+      <c r="E269" s="2" t="n"/>
+    </row>
+    <row r="270">
+      <c r="D270" s="2" t="n"/>
+      <c r="E270" s="2" t="n"/>
+    </row>
+    <row r="271">
+      <c r="D271" s="2" t="n"/>
+      <c r="E271" s="2" t="n"/>
+    </row>
+    <row r="272">
+      <c r="D272" s="2" t="n"/>
+      <c r="E272" s="2" t="n"/>
+    </row>
+    <row r="273">
+      <c r="D273" s="2" t="n"/>
+      <c r="E273" s="2" t="n"/>
+    </row>
+    <row r="274">
+      <c r="D274" s="2" t="n"/>
+      <c r="E274" s="2" t="n"/>
+    </row>
+    <row r="275">
+      <c r="D275" s="2" t="n"/>
+      <c r="E275" s="2" t="n"/>
+    </row>
+    <row r="276">
+      <c r="D276" s="2" t="n"/>
+      <c r="E276" s="2" t="n"/>
+    </row>
+    <row r="277">
+      <c r="D277" s="2" t="n"/>
+      <c r="E277" s="2" t="n"/>
+    </row>
+    <row r="278">
+      <c r="D278" s="2" t="n"/>
+      <c r="E278" s="2" t="n"/>
+    </row>
+    <row r="279">
+      <c r="D279" s="2" t="n"/>
+      <c r="E279" s="2" t="n"/>
+    </row>
+    <row r="280">
+      <c r="D280" s="2" t="n"/>
+      <c r="E280" s="2" t="n"/>
+    </row>
+    <row r="281">
+      <c r="D281" s="2" t="n"/>
+      <c r="E281" s="2" t="n"/>
+    </row>
+    <row r="282">
+      <c r="D282" s="2" t="n"/>
+      <c r="E282" s="2" t="n"/>
+    </row>
+    <row r="283">
+      <c r="D283" s="2" t="n"/>
+      <c r="E283" s="2" t="n"/>
+    </row>
+    <row r="284">
+      <c r="D284" s="2" t="n"/>
+      <c r="E284" s="2" t="n"/>
+    </row>
+    <row r="285">
+      <c r="D285" s="2" t="n"/>
+      <c r="E285" s="2" t="n"/>
+    </row>
+    <row r="286">
+      <c r="D286" s="2" t="n"/>
+      <c r="E286" s="2" t="n"/>
+    </row>
+    <row r="287">
+      <c r="D287" s="2" t="n"/>
+      <c r="E287" s="2" t="n"/>
+    </row>
+    <row r="288">
+      <c r="D288" s="2" t="n"/>
+      <c r="E288" s="2" t="n"/>
+    </row>
+    <row r="289">
+      <c r="D289" s="2" t="n"/>
+      <c r="E289" s="2" t="n"/>
+    </row>
+    <row r="290">
+      <c r="D290" s="2" t="n"/>
+      <c r="E290" s="2" t="n"/>
+    </row>
+    <row r="291">
+      <c r="D291" s="2" t="n"/>
+      <c r="E291" s="2" t="n"/>
+    </row>
+    <row r="292">
+      <c r="D292" s="2" t="n"/>
+      <c r="E292" s="2" t="n"/>
+    </row>
+    <row r="293">
+      <c r="D293" s="2" t="n"/>
+      <c r="E293" s="2" t="n"/>
+    </row>
+    <row r="294">
+      <c r="D294" s="2" t="n"/>
+      <c r="E294" s="2" t="n"/>
+    </row>
+    <row r="295">
+      <c r="D295" s="2" t="n"/>
+      <c r="E295" s="2" t="n"/>
+    </row>
+    <row r="296">
+      <c r="D296" s="2" t="n"/>
+      <c r="E296" s="2" t="n"/>
+    </row>
+    <row r="297">
+      <c r="D297" s="2" t="n"/>
+      <c r="E297" s="2" t="n"/>
+    </row>
+    <row r="298">
+      <c r="D298" s="2" t="n"/>
+      <c r="E298" s="2" t="n"/>
+    </row>
+    <row r="299">
+      <c r="D299" s="2" t="n"/>
+      <c r="E299" s="2" t="n"/>
+    </row>
+    <row r="300">
+      <c r="D300" s="2" t="n"/>
+      <c r="E300" s="2" t="n"/>
+    </row>
+    <row r="301">
+      <c r="D301" s="2" t="n"/>
+      <c r="E301" s="2" t="n"/>
+    </row>
+    <row r="302">
+      <c r="D302" s="2" t="n"/>
+      <c r="E302" s="2" t="n"/>
+    </row>
+    <row r="303">
+      <c r="D303" s="2" t="n"/>
+      <c r="E303" s="2" t="n"/>
+    </row>
+    <row r="304">
+      <c r="D304" s="2" t="n"/>
+      <c r="E304" s="2" t="n"/>
+    </row>
+    <row r="305">
+      <c r="D305" s="2" t="n"/>
+      <c r="E305" s="2" t="n"/>
+    </row>
+    <row r="306">
+      <c r="D306" s="2" t="n"/>
+      <c r="E306" s="2" t="n"/>
+    </row>
+    <row r="307">
+      <c r="D307" s="2" t="n"/>
+      <c r="E307" s="2" t="n"/>
+    </row>
+    <row r="308">
+      <c r="D308" s="2" t="n"/>
+      <c r="E308" s="2" t="n"/>
+    </row>
+    <row r="309">
+      <c r="D309" s="2" t="n"/>
+      <c r="E309" s="2" t="n"/>
+    </row>
+    <row r="310">
+      <c r="D310" s="2" t="n"/>
+      <c r="E310" s="2" t="n"/>
+    </row>
+    <row r="311">
+      <c r="D311" s="2" t="n"/>
+      <c r="E311" s="2" t="n"/>
+    </row>
+    <row r="312">
+      <c r="D312" s="2" t="n"/>
+      <c r="E312" s="2" t="n"/>
+    </row>
+    <row r="313">
+      <c r="D313" s="2" t="n"/>
+      <c r="E313" s="2" t="n"/>
+    </row>
+    <row r="314">
+      <c r="D314" s="2" t="n"/>
+      <c r="E314" s="2" t="n"/>
+    </row>
+    <row r="315">
+      <c r="D315" s="2" t="n"/>
+      <c r="E315" s="2" t="n"/>
+    </row>
+    <row r="316">
+      <c r="D316" s="2" t="n"/>
+      <c r="E316" s="2" t="n"/>
+    </row>
+    <row r="317">
+      <c r="D317" s="2" t="n"/>
+      <c r="E317" s="2" t="n"/>
+    </row>
+    <row r="318">
+      <c r="D318" s="2" t="n"/>
+      <c r="E318" s="2" t="n"/>
+    </row>
+    <row r="319">
+      <c r="D319" s="2" t="n"/>
+      <c r="E319" s="2" t="n"/>
+    </row>
+    <row r="320">
+      <c r="D320" s="2" t="n"/>
+      <c r="E320" s="2" t="n"/>
+    </row>
+    <row r="321">
+      <c r="D321" s="2" t="n"/>
+      <c r="E321" s="2" t="n"/>
+    </row>
+    <row r="322">
+      <c r="D322" s="2" t="n"/>
+      <c r="E322" s="2" t="n"/>
+    </row>
+    <row r="323">
+      <c r="D323" s="2" t="n"/>
+      <c r="E323" s="2" t="n"/>
+    </row>
+    <row r="324">
+      <c r="D324" s="2" t="n"/>
+      <c r="E324" s="2" t="n"/>
+    </row>
+    <row r="325">
+      <c r="D325" s="2" t="n"/>
+      <c r="E325" s="2" t="n"/>
+    </row>
+    <row r="326">
+      <c r="D326" s="2" t="n"/>
+      <c r="E326" s="2" t="n"/>
+    </row>
+    <row r="327">
+      <c r="D327" s="2" t="n"/>
+      <c r="E327" s="2" t="n"/>
+    </row>
+    <row r="328">
+      <c r="D328" s="2" t="n"/>
+      <c r="E328" s="2" t="n"/>
+    </row>
+    <row r="329">
+      <c r="D329" s="2" t="n"/>
+      <c r="E329" s="2" t="n"/>
+    </row>
+    <row r="330">
+      <c r="D330" s="2" t="n"/>
+      <c r="E330" s="2" t="n"/>
+    </row>
+    <row r="331">
+      <c r="D331" s="2" t="n"/>
+      <c r="E331" s="2" t="n"/>
+    </row>
+    <row r="332">
+      <c r="D332" s="2" t="n"/>
+      <c r="E332" s="2" t="n"/>
+    </row>
+    <row r="333">
+      <c r="D333" s="2" t="n"/>
+      <c r="E333" s="2" t="n"/>
+    </row>
+    <row r="334">
+      <c r="D334" s="2" t="n"/>
+      <c r="E334" s="2" t="n"/>
+    </row>
+    <row r="335">
+      <c r="D335" s="2" t="n"/>
+      <c r="E335" s="2" t="n"/>
+    </row>
+    <row r="336">
+      <c r="D336" s="2" t="n"/>
+      <c r="E336" s="2" t="n"/>
+    </row>
+    <row r="337">
+      <c r="D337" s="2" t="n"/>
+      <c r="E337" s="2" t="n"/>
+    </row>
+    <row r="338">
+      <c r="D338" s="2" t="n"/>
+      <c r="E338" s="2" t="n"/>
+    </row>
+    <row r="339">
+      <c r="D339" s="2" t="n"/>
+      <c r="E339" s="2" t="n"/>
+    </row>
+    <row r="340">
+      <c r="D340" s="2" t="n"/>
+      <c r="E340" s="2" t="n"/>
+    </row>
+    <row r="341">
+      <c r="D341" s="2" t="n"/>
+      <c r="E341" s="2" t="n"/>
+    </row>
+    <row r="342">
+      <c r="D342" s="2" t="n"/>
+      <c r="E342" s="2" t="n"/>
+    </row>
+    <row r="343">
+      <c r="D343" s="2" t="n"/>
+      <c r="E343" s="2" t="n"/>
+    </row>
+    <row r="344">
+      <c r="D344" s="2" t="n"/>
+      <c r="E344" s="2" t="n"/>
+    </row>
+    <row r="345">
+      <c r="D345" s="2" t="n"/>
+      <c r="E345" s="2" t="n"/>
+    </row>
+    <row r="346">
+      <c r="D346" s="2" t="n"/>
+      <c r="E346" s="2" t="n"/>
+    </row>
+    <row r="347">
+      <c r="D347" s="2" t="n"/>
+      <c r="E347" s="2" t="n"/>
+    </row>
+    <row r="348">
+      <c r="D348" s="2" t="n"/>
+      <c r="E348" s="2" t="n"/>
+    </row>
+    <row r="349">
+      <c r="D349" s="2" t="n"/>
+      <c r="E349" s="2" t="n"/>
+    </row>
+    <row r="350">
+      <c r="D350" s="2" t="n"/>
+      <c r="E350" s="2" t="n"/>
+    </row>
+    <row r="351">
+      <c r="D351" s="2" t="n"/>
+      <c r="E351" s="2" t="n"/>
+    </row>
+    <row r="352">
+      <c r="D352" s="2" t="n"/>
+      <c r="E352" s="2" t="n"/>
+    </row>
+    <row r="353">
+      <c r="D353" s="2" t="n"/>
+      <c r="E353" s="2" t="n"/>
+    </row>
+    <row r="354">
+      <c r="D354" s="2" t="n"/>
+      <c r="E354" s="2" t="n"/>
+    </row>
+    <row r="355">
+      <c r="D355" s="2" t="n"/>
+      <c r="E355" s="2" t="n"/>
+    </row>
+    <row r="356">
+      <c r="D356" s="2" t="n"/>
+      <c r="E356" s="2" t="n"/>
+    </row>
+    <row r="357">
+      <c r="D357" s="2" t="n"/>
+      <c r="E357" s="2" t="n"/>
+    </row>
+    <row r="358">
+      <c r="D358" s="2" t="n"/>
+      <c r="E358" s="2" t="n"/>
+    </row>
+    <row r="359">
+      <c r="D359" s="2" t="n"/>
+      <c r="E359" s="2" t="n"/>
+    </row>
+    <row r="360">
+      <c r="D360" s="2" t="n"/>
+      <c r="E360" s="2" t="n"/>
+    </row>
+    <row r="361">
+      <c r="D361" s="2" t="n"/>
+      <c r="E361" s="2" t="n"/>
+    </row>
+    <row r="362">
+      <c r="D362" s="2" t="n"/>
+      <c r="E362" s="2" t="n"/>
+    </row>
+    <row r="363">
+      <c r="D363" s="2" t="n"/>
+      <c r="E363" s="2" t="n"/>
+    </row>
+    <row r="364">
+      <c r="D364" s="2" t="n"/>
+      <c r="E364" s="2" t="n"/>
+    </row>
+    <row r="365">
+      <c r="D365" s="2" t="n"/>
+      <c r="E365" s="2" t="n"/>
+    </row>
+    <row r="366">
+      <c r="D366" s="2" t="n"/>
+      <c r="E366" s="2" t="n"/>
+    </row>
+    <row r="367">
+      <c r="D367" s="2" t="n"/>
+      <c r="E367" s="2" t="n"/>
+    </row>
+    <row r="368">
+      <c r="D368" s="2" t="n"/>
+      <c r="E368" s="2" t="n"/>
+    </row>
+    <row r="369">
+      <c r="D369" s="2" t="n"/>
+      <c r="E369" s="2" t="n"/>
+    </row>
+    <row r="370">
+      <c r="D370" s="2" t="n"/>
+      <c r="E370" s="2" t="n"/>
+    </row>
+    <row r="371">
+      <c r="D371" s="2" t="n"/>
+      <c r="E371" s="2" t="n"/>
+    </row>
+    <row r="372">
+      <c r="D372" s="2" t="n"/>
+      <c r="E372" s="2" t="n"/>
+    </row>
+    <row r="373">
+      <c r="D373" s="2" t="n"/>
+      <c r="E373" s="2" t="n"/>
+    </row>
+    <row r="374">
+      <c r="D374" s="2" t="n"/>
+      <c r="E374" s="2" t="n"/>
+    </row>
+    <row r="375">
+      <c r="D375" s="2" t="n"/>
+      <c r="E375" s="2" t="n"/>
+    </row>
+    <row r="376">
+      <c r="D376" s="2" t="n"/>
+      <c r="E376" s="2" t="n"/>
+    </row>
+    <row r="377">
+      <c r="D377" s="2" t="n"/>
+      <c r="E377" s="2" t="n"/>
+    </row>
+    <row r="378">
+      <c r="D378" s="2" t="n"/>
+      <c r="E378" s="2" t="n"/>
+    </row>
+    <row r="379">
+      <c r="D379" s="2" t="n"/>
+      <c r="E379" s="2" t="n"/>
+    </row>
+    <row r="380">
+      <c r="D380" s="2" t="n"/>
+      <c r="E380" s="2" t="n"/>
+    </row>
+    <row r="381">
+      <c r="D381" s="2" t="n"/>
+      <c r="E381" s="2" t="n"/>
+    </row>
+    <row r="382">
+      <c r="D382" s="2" t="n"/>
+      <c r="E382" s="2" t="n"/>
+    </row>
+    <row r="383">
+      <c r="D383" s="2" t="n"/>
+      <c r="E383" s="2" t="n"/>
+    </row>
+    <row r="384">
+      <c r="D384" s="2" t="n"/>
+      <c r="E384" s="2" t="n"/>
+    </row>
+    <row r="385">
+      <c r="D385" s="2" t="n"/>
+      <c r="E385" s="2" t="n"/>
+    </row>
+    <row r="386">
+      <c r="D386" s="2" t="n"/>
+      <c r="E386" s="2" t="n"/>
+    </row>
+    <row r="387">
+      <c r="D387" s="2" t="n"/>
+      <c r="E387" s="2" t="n"/>
+    </row>
+    <row r="388">
+      <c r="D388" s="2" t="n"/>
+      <c r="E388" s="2" t="n"/>
+    </row>
+    <row r="389">
+      <c r="D389" s="2" t="n"/>
+      <c r="E389" s="2" t="n"/>
+    </row>
+    <row r="390">
+      <c r="D390" s="2" t="n"/>
+      <c r="E390" s="2" t="n"/>
+    </row>
+    <row r="391">
+      <c r="D391" s="2" t="n"/>
+      <c r="E391" s="2" t="n"/>
+    </row>
+    <row r="392">
+      <c r="D392" s="2" t="n"/>
+      <c r="E392" s="2" t="n"/>
+    </row>
+    <row r="393">
+      <c r="D393" s="2" t="n"/>
+      <c r="E393" s="2" t="n"/>
+    </row>
+    <row r="394">
+      <c r="D394" s="2" t="n"/>
+      <c r="E394" s="2" t="n"/>
+    </row>
+    <row r="395">
+      <c r="D395" s="2" t="n"/>
+      <c r="E395" s="2" t="n"/>
+    </row>
+    <row r="396">
+      <c r="D396" s="2" t="n"/>
+      <c r="E396" s="2" t="n"/>
+    </row>
+    <row r="397">
+      <c r="D397" s="2" t="n"/>
+      <c r="E397" s="2" t="n"/>
+    </row>
+    <row r="398">
+      <c r="D398" s="2" t="n"/>
+      <c r="E398" s="2" t="n"/>
+    </row>
+    <row r="399">
+      <c r="D399" s="2" t="n"/>
+      <c r="E399" s="2" t="n"/>
+    </row>
+    <row r="400">
+      <c r="D400" s="2" t="n"/>
+      <c r="E400" s="2" t="n"/>
+    </row>
+    <row r="401">
+      <c r="D401" s="2" t="n"/>
+      <c r="E401" s="2" t="n"/>
+    </row>
+    <row r="402">
+      <c r="D402" s="2" t="n"/>
+      <c r="E402" s="2" t="n"/>
+    </row>
+    <row r="403">
+      <c r="D403" s="2" t="n"/>
+      <c r="E403" s="2" t="n"/>
+    </row>
+    <row r="404">
+      <c r="D404" s="2" t="n"/>
+      <c r="E404" s="2" t="n"/>
+    </row>
+    <row r="405">
+      <c r="D405" s="2" t="n"/>
+      <c r="E405" s="2" t="n"/>
+    </row>
+    <row r="406">
+      <c r="D406" s="2" t="n"/>
+      <c r="E406" s="2" t="n"/>
+    </row>
+    <row r="407">
+      <c r="D407" s="2" t="n"/>
+      <c r="E407" s="2" t="n"/>
+    </row>
+    <row r="408">
+      <c r="D408" s="2" t="n"/>
+      <c r="E408" s="2" t="n"/>
+    </row>
+    <row r="409">
+      <c r="D409" s="2" t="n"/>
+      <c r="E409" s="2" t="n"/>
+    </row>
+    <row r="410">
+      <c r="D410" s="2" t="n"/>
+      <c r="E410" s="2" t="n"/>
+    </row>
+    <row r="411">
+      <c r="D411" s="2" t="n"/>
+      <c r="E411" s="2" t="n"/>
+    </row>
+    <row r="412">
+      <c r="D412" s="2" t="n"/>
+      <c r="E412" s="2" t="n"/>
+    </row>
+    <row r="413">
+      <c r="D413" s="2" t="n"/>
+      <c r="E413" s="2" t="n"/>
+    </row>
+    <row r="414">
+      <c r="D414" s="2" t="n"/>
+      <c r="E414" s="2" t="n"/>
+    </row>
+    <row r="415">
+      <c r="D415" s="2" t="n"/>
+      <c r="E415" s="2" t="n"/>
+    </row>
+    <row r="416">
+      <c r="D416" s="2" t="n"/>
+      <c r="E416" s="2" t="n"/>
+    </row>
+    <row r="417">
+      <c r="D417" s="2" t="n"/>
+      <c r="E417" s="2" t="n"/>
+    </row>
+    <row r="418">
+      <c r="D418" s="2" t="n"/>
+      <c r="E418" s="2" t="n"/>
+    </row>
+    <row r="419">
+      <c r="D419" s="2" t="n"/>
+      <c r="E419" s="2" t="n"/>
+    </row>
+    <row r="420">
+      <c r="D420" s="2" t="n"/>
+      <c r="E420" s="2" t="n"/>
+    </row>
+    <row r="421">
+      <c r="D421" s="2" t="n"/>
+      <c r="E421" s="2" t="n"/>
+    </row>
+    <row r="422">
+      <c r="D422" s="2" t="n"/>
+      <c r="E422" s="2" t="n"/>
+    </row>
+    <row r="423">
+      <c r="D423" s="2" t="n"/>
+      <c r="E423" s="2" t="n"/>
+    </row>
+    <row r="424">
+      <c r="D424" s="2" t="n"/>
+      <c r="E424" s="2" t="n"/>
+    </row>
+    <row r="425">
+      <c r="D425" s="2" t="n"/>
+      <c r="E425" s="2" t="n"/>
+    </row>
+    <row r="426">
+      <c r="D426" s="2" t="n"/>
+      <c r="E426" s="2" t="n"/>
+    </row>
+    <row r="427">
+      <c r="D427" s="2" t="n"/>
+      <c r="E427" s="2" t="n"/>
+    </row>
+    <row r="428">
+      <c r="D428" s="2" t="n"/>
+      <c r="E428" s="2" t="n"/>
+    </row>
+    <row r="429">
+      <c r="D429" s="2" t="n"/>
+      <c r="E429" s="2" t="n"/>
+    </row>
+    <row r="430">
+      <c r="D430" s="2" t="n"/>
+      <c r="E430" s="2" t="n"/>
+    </row>
+    <row r="431">
+      <c r="D431" s="2" t="n"/>
+      <c r="E431" s="2" t="n"/>
+    </row>
+    <row r="432">
+      <c r="D432" s="2" t="n"/>
+      <c r="E432" s="2" t="n"/>
+    </row>
+    <row r="433">
+      <c r="D433" s="2" t="n"/>
+      <c r="E433" s="2" t="n"/>
+    </row>
+    <row r="434">
+      <c r="D434" s="2" t="n"/>
+      <c r="E434" s="2" t="n"/>
+    </row>
+    <row r="435">
+      <c r="D435" s="2" t="n"/>
+      <c r="E435" s="2" t="n"/>
+    </row>
+    <row r="436">
+      <c r="D436" s="2" t="n"/>
+      <c r="E436" s="2" t="n"/>
+    </row>
+    <row r="437">
+      <c r="D437" s="2" t="n"/>
+      <c r="E437" s="2" t="n"/>
+    </row>
+    <row r="438">
+      <c r="D438" s="2" t="n"/>
+      <c r="E438" s="2" t="n"/>
+    </row>
+    <row r="439">
+      <c r="D439" s="2" t="n"/>
+      <c r="E439" s="2" t="n"/>
+    </row>
+    <row r="440">
+      <c r="D440" s="2" t="n"/>
+      <c r="E440" s="2" t="n"/>
+    </row>
+    <row r="441">
+      <c r="D441" s="2" t="n"/>
+      <c r="E441" s="2" t="n"/>
+    </row>
+    <row r="442">
+      <c r="D442" s="2" t="n"/>
+      <c r="E442" s="2" t="n"/>
+    </row>
+    <row r="443">
+      <c r="D443" s="2" t="n"/>
+      <c r="E443" s="2" t="n"/>
+    </row>
+    <row r="444">
+      <c r="D444" s="2" t="n"/>
+      <c r="E444" s="2" t="n"/>
+    </row>
+    <row r="445">
+      <c r="D445" s="2" t="n"/>
+      <c r="E445" s="2" t="n"/>
+    </row>
+    <row r="446">
+      <c r="D446" s="2" t="n"/>
+      <c r="E446" s="2" t="n"/>
+    </row>
+    <row r="447">
+      <c r="D447" s="2" t="n"/>
+      <c r="E447" s="2" t="n"/>
+    </row>
+    <row r="448">
+      <c r="D448" s="2" t="n"/>
+      <c r="E448" s="2" t="n"/>
+    </row>
+    <row r="449">
+      <c r="D449" s="2" t="n"/>
+      <c r="E449" s="2" t="n"/>
+    </row>
+    <row r="450">
+      <c r="D450" s="2" t="n"/>
+      <c r="E450" s="2" t="n"/>
+    </row>
+    <row r="451">
+      <c r="D451" s="2" t="n"/>
+      <c r="E451" s="2" t="n"/>
+    </row>
+    <row r="452">
+      <c r="D452" s="2" t="n"/>
+      <c r="E452" s="2" t="n"/>
+    </row>
+    <row r="453">
+      <c r="D453" s="2" t="n"/>
+      <c r="E453" s="2" t="n"/>
+    </row>
+    <row r="454">
+      <c r="D454" s="2" t="n"/>
+      <c r="E454" s="2" t="n"/>
+    </row>
+    <row r="455">
+      <c r="D455" s="2" t="n"/>
+      <c r="E455" s="2" t="n"/>
+    </row>
+    <row r="456">
+      <c r="D456" s="2" t="n"/>
+      <c r="E456" s="2" t="n"/>
+    </row>
+    <row r="457">
+      <c r="D457" s="2" t="n"/>
+      <c r="E457" s="2" t="n"/>
+    </row>
+    <row r="458">
+      <c r="D458" s="2" t="n"/>
+      <c r="E458" s="2" t="n"/>
+    </row>
+    <row r="459">
+      <c r="D459" s="2" t="n"/>
+      <c r="E459" s="2" t="n"/>
+    </row>
+    <row r="460">
+      <c r="D460" s="2" t="n"/>
+      <c r="E460" s="2" t="n"/>
+    </row>
+    <row r="461">
+      <c r="D461" s="2" t="n"/>
+      <c r="E461" s="2" t="n"/>
+    </row>
+    <row r="462">
+      <c r="D462" s="2" t="n"/>
+      <c r="E462" s="2" t="n"/>
+    </row>
+    <row r="463">
+      <c r="D463" s="2" t="n"/>
+      <c r="E463" s="2" t="n"/>
+    </row>
+    <row r="464">
+      <c r="D464" s="2" t="n"/>
+      <c r="E464" s="2" t="n"/>
+    </row>
+    <row r="465">
+      <c r="D465" s="2" t="n"/>
+      <c r="E465" s="2" t="n"/>
+    </row>
+    <row r="466">
+      <c r="D466" s="2" t="n"/>
+      <c r="E466" s="2" t="n"/>
+    </row>
+    <row r="467">
+      <c r="D467" s="2" t="n"/>
+      <c r="E467" s="2" t="n"/>
+    </row>
+    <row r="468">
+      <c r="D468" s="2" t="n"/>
+      <c r="E468" s="2" t="n"/>
+    </row>
+    <row r="469">
+      <c r="D469" s="2" t="n"/>
+      <c r="E469" s="2" t="n"/>
+    </row>
+    <row r="470">
+      <c r="D470" s="2" t="n"/>
+      <c r="E470" s="2" t="n"/>
+    </row>
+    <row r="471">
+      <c r="D471" s="2" t="n"/>
+      <c r="E471" s="2" t="n"/>
+    </row>
+    <row r="472">
+      <c r="D472" s="2" t="n"/>
+      <c r="E472" s="2" t="n"/>
+    </row>
+    <row r="473">
+      <c r="D473" s="2" t="n"/>
+      <c r="E473" s="2" t="n"/>
+    </row>
+    <row r="474">
+      <c r="D474" s="2" t="n"/>
+      <c r="E474" s="2" t="n"/>
+    </row>
+    <row r="475">
+      <c r="D475" s="2" t="n"/>
+      <c r="E475" s="2" t="n"/>
+    </row>
+    <row r="476">
+      <c r="D476" s="2" t="n"/>
+      <c r="E476" s="2" t="n"/>
+    </row>
+    <row r="477">
+      <c r="D477" s="2" t="n"/>
+      <c r="E477" s="2" t="n"/>
+    </row>
+    <row r="478">
+      <c r="D478" s="2" t="n"/>
+      <c r="E478" s="2" t="n"/>
+    </row>
+    <row r="479">
+      <c r="D479" s="2" t="n"/>
+      <c r="E479" s="2" t="n"/>
+    </row>
+    <row r="480">
+      <c r="D480" s="2" t="n"/>
+      <c r="E480" s="2" t="n"/>
+    </row>
+    <row r="481">
+      <c r="D481" s="2" t="n"/>
+      <c r="E481" s="2" t="n"/>
+    </row>
+    <row r="482">
+      <c r="D482" s="2" t="n"/>
+      <c r="E482" s="2" t="n"/>
+    </row>
+    <row r="483">
+      <c r="D483" s="2" t="n"/>
+      <c r="E483" s="2" t="n"/>
+    </row>
+    <row r="484">
+      <c r="D484" s="2" t="n"/>
+      <c r="E484" s="2" t="n"/>
+    </row>
+    <row r="485">
+      <c r="D485" s="2" t="n"/>
+      <c r="E485" s="2" t="n"/>
+    </row>
+    <row r="486">
+      <c r="D486" s="2" t="n"/>
+      <c r="E486" s="2" t="n"/>
+    </row>
+    <row r="487">
+      <c r="D487" s="2" t="n"/>
+      <c r="E487" s="2" t="n"/>
+    </row>
+    <row r="488">
+      <c r="D488" s="2" t="n"/>
+      <c r="E488" s="2" t="n"/>
+    </row>
+    <row r="489">
+      <c r="D489" s="2" t="n"/>
+      <c r="E489" s="2" t="n"/>
+    </row>
+    <row r="490">
+      <c r="D490" s="2" t="n"/>
+      <c r="E490" s="2" t="n"/>
+    </row>
+    <row r="491">
+      <c r="D491" s="2" t="n"/>
+      <c r="E491" s="2" t="n"/>
+    </row>
+    <row r="492">
+      <c r="D492" s="2" t="n"/>
+      <c r="E492" s="2" t="n"/>
+    </row>
+    <row r="493">
+      <c r="D493" s="2" t="n"/>
+      <c r="E493" s="2" t="n"/>
+    </row>
+    <row r="494">
+      <c r="D494" s="2" t="n"/>
+      <c r="E494" s="2" t="n"/>
+    </row>
+    <row r="495">
+      <c r="D495" s="2" t="n"/>
+      <c r="E495" s="2" t="n"/>
+    </row>
+    <row r="496">
+      <c r="D496" s="2" t="n"/>
+      <c r="E496" s="2" t="n"/>
+    </row>
+    <row r="497">
+      <c r="D497" s="2" t="n"/>
+      <c r="E497" s="2" t="n"/>
+    </row>
+    <row r="498">
+      <c r="D498" s="2" t="n"/>
+      <c r="E498" s="2" t="n"/>
+    </row>
+    <row r="499">
+      <c r="D499" s="2" t="n"/>
+      <c r="E499" s="2" t="n"/>
+    </row>
+    <row r="500">
+      <c r="D500" s="2" t="n"/>
+      <c r="E500" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G7"/>
   <dataValidations count="3">
-    <dataValidation sqref="B2:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Ungültige Art" error="Bitte eine Art aus der Liste wählen." type="list">
+    <dataValidation sqref="B2:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Ungültiger Wert" error="Bitte einen Wert aus der Liste wählen." promptTitle="Art" prompt="Art des Termins wählen." type="list">
       <formula1>"Kalibrierung,Wartung,Ausfall,Audit,Info"</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Unbekannter Prüfstand" error="Bitte einen Prüfstand aus der Liste wählen." type="list">
+    <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Ungültiger Wert" error="Bitte einen Wert aus der Liste wählen." promptTitle="Prüfstand" prompt="Prüfstand aus dem Blatt „Prüfstände“ wählen." type="list">
       <formula1>=Pruefstaende</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Ungültiger Wert" error="Bitte einen Wert aus der Liste wählen." promptTitle="Status" prompt="offen / abgeschlossen / storniert." type="list">
       <formula1>"offen,abgeschlossen,storniert"</formula1>
     </dataValidation>
   </dataValidations>
@@ -777,110 +2667,2088 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="0070AD47"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Termin (Nr)</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Von</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Bis</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Notiz</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="n">
+      <c r="A2" t="n">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="2" t="n">
         <v>46342.33333333334</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="2" t="n">
         <v>46342.5</v>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Tag 1, vormittags</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="n">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" s="2" t="n">
         <v>46343.33333333334</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="2" t="n">
         <v>46343.66666666666</v>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Tag 2, ganztags</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="n">
+      <c r="A4" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="2" t="n">
         <v>46345.29166666666</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="2" t="n">
         <v>46345.45833333334</v>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Tag 4, vormittags</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n">
+      <c r="A5" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="2" t="n">
         <v>46346.33333333334</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="2" t="n">
         <v>46346.58333333334</v>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Tag 5, 6 Stunden</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+    </row>
+    <row r="37">
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+    </row>
+    <row r="38">
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+    </row>
+    <row r="39">
+      <c r="B39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+    </row>
+    <row r="41">
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+    </row>
+    <row r="42">
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+    </row>
+    <row r="43">
+      <c r="B43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+    </row>
+    <row r="44">
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+    </row>
+    <row r="45">
+      <c r="B45" s="2" t="n"/>
+      <c r="C45" s="2" t="n"/>
+    </row>
+    <row r="46">
+      <c r="B46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+    </row>
+    <row r="47">
+      <c r="B47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+    </row>
+    <row r="48">
+      <c r="B48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+    </row>
+    <row r="49">
+      <c r="B49" s="2" t="n"/>
+      <c r="C49" s="2" t="n"/>
+    </row>
+    <row r="50">
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+    </row>
+    <row r="51">
+      <c r="B51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+    </row>
+    <row r="52">
+      <c r="B52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+    </row>
+    <row r="53">
+      <c r="B53" s="2" t="n"/>
+      <c r="C53" s="2" t="n"/>
+    </row>
+    <row r="54">
+      <c r="B54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+    </row>
+    <row r="55">
+      <c r="B55" s="2" t="n"/>
+      <c r="C55" s="2" t="n"/>
+    </row>
+    <row r="56">
+      <c r="B56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+    </row>
+    <row r="57">
+      <c r="B57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+    </row>
+    <row r="58">
+      <c r="B58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+    </row>
+    <row r="59">
+      <c r="B59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+    </row>
+    <row r="60">
+      <c r="B60" s="2" t="n"/>
+      <c r="C60" s="2" t="n"/>
+    </row>
+    <row r="61">
+      <c r="B61" s="2" t="n"/>
+      <c r="C61" s="2" t="n"/>
+    </row>
+    <row r="62">
+      <c r="B62" s="2" t="n"/>
+      <c r="C62" s="2" t="n"/>
+    </row>
+    <row r="63">
+      <c r="B63" s="2" t="n"/>
+      <c r="C63" s="2" t="n"/>
+    </row>
+    <row r="64">
+      <c r="B64" s="2" t="n"/>
+      <c r="C64" s="2" t="n"/>
+    </row>
+    <row r="65">
+      <c r="B65" s="2" t="n"/>
+      <c r="C65" s="2" t="n"/>
+    </row>
+    <row r="66">
+      <c r="B66" s="2" t="n"/>
+      <c r="C66" s="2" t="n"/>
+    </row>
+    <row r="67">
+      <c r="B67" s="2" t="n"/>
+      <c r="C67" s="2" t="n"/>
+    </row>
+    <row r="68">
+      <c r="B68" s="2" t="n"/>
+      <c r="C68" s="2" t="n"/>
+    </row>
+    <row r="69">
+      <c r="B69" s="2" t="n"/>
+      <c r="C69" s="2" t="n"/>
+    </row>
+    <row r="70">
+      <c r="B70" s="2" t="n"/>
+      <c r="C70" s="2" t="n"/>
+    </row>
+    <row r="71">
+      <c r="B71" s="2" t="n"/>
+      <c r="C71" s="2" t="n"/>
+    </row>
+    <row r="72">
+      <c r="B72" s="2" t="n"/>
+      <c r="C72" s="2" t="n"/>
+    </row>
+    <row r="73">
+      <c r="B73" s="2" t="n"/>
+      <c r="C73" s="2" t="n"/>
+    </row>
+    <row r="74">
+      <c r="B74" s="2" t="n"/>
+      <c r="C74" s="2" t="n"/>
+    </row>
+    <row r="75">
+      <c r="B75" s="2" t="n"/>
+      <c r="C75" s="2" t="n"/>
+    </row>
+    <row r="76">
+      <c r="B76" s="2" t="n"/>
+      <c r="C76" s="2" t="n"/>
+    </row>
+    <row r="77">
+      <c r="B77" s="2" t="n"/>
+      <c r="C77" s="2" t="n"/>
+    </row>
+    <row r="78">
+      <c r="B78" s="2" t="n"/>
+      <c r="C78" s="2" t="n"/>
+    </row>
+    <row r="79">
+      <c r="B79" s="2" t="n"/>
+      <c r="C79" s="2" t="n"/>
+    </row>
+    <row r="80">
+      <c r="B80" s="2" t="n"/>
+      <c r="C80" s="2" t="n"/>
+    </row>
+    <row r="81">
+      <c r="B81" s="2" t="n"/>
+      <c r="C81" s="2" t="n"/>
+    </row>
+    <row r="82">
+      <c r="B82" s="2" t="n"/>
+      <c r="C82" s="2" t="n"/>
+    </row>
+    <row r="83">
+      <c r="B83" s="2" t="n"/>
+      <c r="C83" s="2" t="n"/>
+    </row>
+    <row r="84">
+      <c r="B84" s="2" t="n"/>
+      <c r="C84" s="2" t="n"/>
+    </row>
+    <row r="85">
+      <c r="B85" s="2" t="n"/>
+      <c r="C85" s="2" t="n"/>
+    </row>
+    <row r="86">
+      <c r="B86" s="2" t="n"/>
+      <c r="C86" s="2" t="n"/>
+    </row>
+    <row r="87">
+      <c r="B87" s="2" t="n"/>
+      <c r="C87" s="2" t="n"/>
+    </row>
+    <row r="88">
+      <c r="B88" s="2" t="n"/>
+      <c r="C88" s="2" t="n"/>
+    </row>
+    <row r="89">
+      <c r="B89" s="2" t="n"/>
+      <c r="C89" s="2" t="n"/>
+    </row>
+    <row r="90">
+      <c r="B90" s="2" t="n"/>
+      <c r="C90" s="2" t="n"/>
+    </row>
+    <row r="91">
+      <c r="B91" s="2" t="n"/>
+      <c r="C91" s="2" t="n"/>
+    </row>
+    <row r="92">
+      <c r="B92" s="2" t="n"/>
+      <c r="C92" s="2" t="n"/>
+    </row>
+    <row r="93">
+      <c r="B93" s="2" t="n"/>
+      <c r="C93" s="2" t="n"/>
+    </row>
+    <row r="94">
+      <c r="B94" s="2" t="n"/>
+      <c r="C94" s="2" t="n"/>
+    </row>
+    <row r="95">
+      <c r="B95" s="2" t="n"/>
+      <c r="C95" s="2" t="n"/>
+    </row>
+    <row r="96">
+      <c r="B96" s="2" t="n"/>
+      <c r="C96" s="2" t="n"/>
+    </row>
+    <row r="97">
+      <c r="B97" s="2" t="n"/>
+      <c r="C97" s="2" t="n"/>
+    </row>
+    <row r="98">
+      <c r="B98" s="2" t="n"/>
+      <c r="C98" s="2" t="n"/>
+    </row>
+    <row r="99">
+      <c r="B99" s="2" t="n"/>
+      <c r="C99" s="2" t="n"/>
+    </row>
+    <row r="100">
+      <c r="B100" s="2" t="n"/>
+      <c r="C100" s="2" t="n"/>
+    </row>
+    <row r="101">
+      <c r="B101" s="2" t="n"/>
+      <c r="C101" s="2" t="n"/>
+    </row>
+    <row r="102">
+      <c r="B102" s="2" t="n"/>
+      <c r="C102" s="2" t="n"/>
+    </row>
+    <row r="103">
+      <c r="B103" s="2" t="n"/>
+      <c r="C103" s="2" t="n"/>
+    </row>
+    <row r="104">
+      <c r="B104" s="2" t="n"/>
+      <c r="C104" s="2" t="n"/>
+    </row>
+    <row r="105">
+      <c r="B105" s="2" t="n"/>
+      <c r="C105" s="2" t="n"/>
+    </row>
+    <row r="106">
+      <c r="B106" s="2" t="n"/>
+      <c r="C106" s="2" t="n"/>
+    </row>
+    <row r="107">
+      <c r="B107" s="2" t="n"/>
+      <c r="C107" s="2" t="n"/>
+    </row>
+    <row r="108">
+      <c r="B108" s="2" t="n"/>
+      <c r="C108" s="2" t="n"/>
+    </row>
+    <row r="109">
+      <c r="B109" s="2" t="n"/>
+      <c r="C109" s="2" t="n"/>
+    </row>
+    <row r="110">
+      <c r="B110" s="2" t="n"/>
+      <c r="C110" s="2" t="n"/>
+    </row>
+    <row r="111">
+      <c r="B111" s="2" t="n"/>
+      <c r="C111" s="2" t="n"/>
+    </row>
+    <row r="112">
+      <c r="B112" s="2" t="n"/>
+      <c r="C112" s="2" t="n"/>
+    </row>
+    <row r="113">
+      <c r="B113" s="2" t="n"/>
+      <c r="C113" s="2" t="n"/>
+    </row>
+    <row r="114">
+      <c r="B114" s="2" t="n"/>
+      <c r="C114" s="2" t="n"/>
+    </row>
+    <row r="115">
+      <c r="B115" s="2" t="n"/>
+      <c r="C115" s="2" t="n"/>
+    </row>
+    <row r="116">
+      <c r="B116" s="2" t="n"/>
+      <c r="C116" s="2" t="n"/>
+    </row>
+    <row r="117">
+      <c r="B117" s="2" t="n"/>
+      <c r="C117" s="2" t="n"/>
+    </row>
+    <row r="118">
+      <c r="B118" s="2" t="n"/>
+      <c r="C118" s="2" t="n"/>
+    </row>
+    <row r="119">
+      <c r="B119" s="2" t="n"/>
+      <c r="C119" s="2" t="n"/>
+    </row>
+    <row r="120">
+      <c r="B120" s="2" t="n"/>
+      <c r="C120" s="2" t="n"/>
+    </row>
+    <row r="121">
+      <c r="B121" s="2" t="n"/>
+      <c r="C121" s="2" t="n"/>
+    </row>
+    <row r="122">
+      <c r="B122" s="2" t="n"/>
+      <c r="C122" s="2" t="n"/>
+    </row>
+    <row r="123">
+      <c r="B123" s="2" t="n"/>
+      <c r="C123" s="2" t="n"/>
+    </row>
+    <row r="124">
+      <c r="B124" s="2" t="n"/>
+      <c r="C124" s="2" t="n"/>
+    </row>
+    <row r="125">
+      <c r="B125" s="2" t="n"/>
+      <c r="C125" s="2" t="n"/>
+    </row>
+    <row r="126">
+      <c r="B126" s="2" t="n"/>
+      <c r="C126" s="2" t="n"/>
+    </row>
+    <row r="127">
+      <c r="B127" s="2" t="n"/>
+      <c r="C127" s="2" t="n"/>
+    </row>
+    <row r="128">
+      <c r="B128" s="2" t="n"/>
+      <c r="C128" s="2" t="n"/>
+    </row>
+    <row r="129">
+      <c r="B129" s="2" t="n"/>
+      <c r="C129" s="2" t="n"/>
+    </row>
+    <row r="130">
+      <c r="B130" s="2" t="n"/>
+      <c r="C130" s="2" t="n"/>
+    </row>
+    <row r="131">
+      <c r="B131" s="2" t="n"/>
+      <c r="C131" s="2" t="n"/>
+    </row>
+    <row r="132">
+      <c r="B132" s="2" t="n"/>
+      <c r="C132" s="2" t="n"/>
+    </row>
+    <row r="133">
+      <c r="B133" s="2" t="n"/>
+      <c r="C133" s="2" t="n"/>
+    </row>
+    <row r="134">
+      <c r="B134" s="2" t="n"/>
+      <c r="C134" s="2" t="n"/>
+    </row>
+    <row r="135">
+      <c r="B135" s="2" t="n"/>
+      <c r="C135" s="2" t="n"/>
+    </row>
+    <row r="136">
+      <c r="B136" s="2" t="n"/>
+      <c r="C136" s="2" t="n"/>
+    </row>
+    <row r="137">
+      <c r="B137" s="2" t="n"/>
+      <c r="C137" s="2" t="n"/>
+    </row>
+    <row r="138">
+      <c r="B138" s="2" t="n"/>
+      <c r="C138" s="2" t="n"/>
+    </row>
+    <row r="139">
+      <c r="B139" s="2" t="n"/>
+      <c r="C139" s="2" t="n"/>
+    </row>
+    <row r="140">
+      <c r="B140" s="2" t="n"/>
+      <c r="C140" s="2" t="n"/>
+    </row>
+    <row r="141">
+      <c r="B141" s="2" t="n"/>
+      <c r="C141" s="2" t="n"/>
+    </row>
+    <row r="142">
+      <c r="B142" s="2" t="n"/>
+      <c r="C142" s="2" t="n"/>
+    </row>
+    <row r="143">
+      <c r="B143" s="2" t="n"/>
+      <c r="C143" s="2" t="n"/>
+    </row>
+    <row r="144">
+      <c r="B144" s="2" t="n"/>
+      <c r="C144" s="2" t="n"/>
+    </row>
+    <row r="145">
+      <c r="B145" s="2" t="n"/>
+      <c r="C145" s="2" t="n"/>
+    </row>
+    <row r="146">
+      <c r="B146" s="2" t="n"/>
+      <c r="C146" s="2" t="n"/>
+    </row>
+    <row r="147">
+      <c r="B147" s="2" t="n"/>
+      <c r="C147" s="2" t="n"/>
+    </row>
+    <row r="148">
+      <c r="B148" s="2" t="n"/>
+      <c r="C148" s="2" t="n"/>
+    </row>
+    <row r="149">
+      <c r="B149" s="2" t="n"/>
+      <c r="C149" s="2" t="n"/>
+    </row>
+    <row r="150">
+      <c r="B150" s="2" t="n"/>
+      <c r="C150" s="2" t="n"/>
+    </row>
+    <row r="151">
+      <c r="B151" s="2" t="n"/>
+      <c r="C151" s="2" t="n"/>
+    </row>
+    <row r="152">
+      <c r="B152" s="2" t="n"/>
+      <c r="C152" s="2" t="n"/>
+    </row>
+    <row r="153">
+      <c r="B153" s="2" t="n"/>
+      <c r="C153" s="2" t="n"/>
+    </row>
+    <row r="154">
+      <c r="B154" s="2" t="n"/>
+      <c r="C154" s="2" t="n"/>
+    </row>
+    <row r="155">
+      <c r="B155" s="2" t="n"/>
+      <c r="C155" s="2" t="n"/>
+    </row>
+    <row r="156">
+      <c r="B156" s="2" t="n"/>
+      <c r="C156" s="2" t="n"/>
+    </row>
+    <row r="157">
+      <c r="B157" s="2" t="n"/>
+      <c r="C157" s="2" t="n"/>
+    </row>
+    <row r="158">
+      <c r="B158" s="2" t="n"/>
+      <c r="C158" s="2" t="n"/>
+    </row>
+    <row r="159">
+      <c r="B159" s="2" t="n"/>
+      <c r="C159" s="2" t="n"/>
+    </row>
+    <row r="160">
+      <c r="B160" s="2" t="n"/>
+      <c r="C160" s="2" t="n"/>
+    </row>
+    <row r="161">
+      <c r="B161" s="2" t="n"/>
+      <c r="C161" s="2" t="n"/>
+    </row>
+    <row r="162">
+      <c r="B162" s="2" t="n"/>
+      <c r="C162" s="2" t="n"/>
+    </row>
+    <row r="163">
+      <c r="B163" s="2" t="n"/>
+      <c r="C163" s="2" t="n"/>
+    </row>
+    <row r="164">
+      <c r="B164" s="2" t="n"/>
+      <c r="C164" s="2" t="n"/>
+    </row>
+    <row r="165">
+      <c r="B165" s="2" t="n"/>
+      <c r="C165" s="2" t="n"/>
+    </row>
+    <row r="166">
+      <c r="B166" s="2" t="n"/>
+      <c r="C166" s="2" t="n"/>
+    </row>
+    <row r="167">
+      <c r="B167" s="2" t="n"/>
+      <c r="C167" s="2" t="n"/>
+    </row>
+    <row r="168">
+      <c r="B168" s="2" t="n"/>
+      <c r="C168" s="2" t="n"/>
+    </row>
+    <row r="169">
+      <c r="B169" s="2" t="n"/>
+      <c r="C169" s="2" t="n"/>
+    </row>
+    <row r="170">
+      <c r="B170" s="2" t="n"/>
+      <c r="C170" s="2" t="n"/>
+    </row>
+    <row r="171">
+      <c r="B171" s="2" t="n"/>
+      <c r="C171" s="2" t="n"/>
+    </row>
+    <row r="172">
+      <c r="B172" s="2" t="n"/>
+      <c r="C172" s="2" t="n"/>
+    </row>
+    <row r="173">
+      <c r="B173" s="2" t="n"/>
+      <c r="C173" s="2" t="n"/>
+    </row>
+    <row r="174">
+      <c r="B174" s="2" t="n"/>
+      <c r="C174" s="2" t="n"/>
+    </row>
+    <row r="175">
+      <c r="B175" s="2" t="n"/>
+      <c r="C175" s="2" t="n"/>
+    </row>
+    <row r="176">
+      <c r="B176" s="2" t="n"/>
+      <c r="C176" s="2" t="n"/>
+    </row>
+    <row r="177">
+      <c r="B177" s="2" t="n"/>
+      <c r="C177" s="2" t="n"/>
+    </row>
+    <row r="178">
+      <c r="B178" s="2" t="n"/>
+      <c r="C178" s="2" t="n"/>
+    </row>
+    <row r="179">
+      <c r="B179" s="2" t="n"/>
+      <c r="C179" s="2" t="n"/>
+    </row>
+    <row r="180">
+      <c r="B180" s="2" t="n"/>
+      <c r="C180" s="2" t="n"/>
+    </row>
+    <row r="181">
+      <c r="B181" s="2" t="n"/>
+      <c r="C181" s="2" t="n"/>
+    </row>
+    <row r="182">
+      <c r="B182" s="2" t="n"/>
+      <c r="C182" s="2" t="n"/>
+    </row>
+    <row r="183">
+      <c r="B183" s="2" t="n"/>
+      <c r="C183" s="2" t="n"/>
+    </row>
+    <row r="184">
+      <c r="B184" s="2" t="n"/>
+      <c r="C184" s="2" t="n"/>
+    </row>
+    <row r="185">
+      <c r="B185" s="2" t="n"/>
+      <c r="C185" s="2" t="n"/>
+    </row>
+    <row r="186">
+      <c r="B186" s="2" t="n"/>
+      <c r="C186" s="2" t="n"/>
+    </row>
+    <row r="187">
+      <c r="B187" s="2" t="n"/>
+      <c r="C187" s="2" t="n"/>
+    </row>
+    <row r="188">
+      <c r="B188" s="2" t="n"/>
+      <c r="C188" s="2" t="n"/>
+    </row>
+    <row r="189">
+      <c r="B189" s="2" t="n"/>
+      <c r="C189" s="2" t="n"/>
+    </row>
+    <row r="190">
+      <c r="B190" s="2" t="n"/>
+      <c r="C190" s="2" t="n"/>
+    </row>
+    <row r="191">
+      <c r="B191" s="2" t="n"/>
+      <c r="C191" s="2" t="n"/>
+    </row>
+    <row r="192">
+      <c r="B192" s="2" t="n"/>
+      <c r="C192" s="2" t="n"/>
+    </row>
+    <row r="193">
+      <c r="B193" s="2" t="n"/>
+      <c r="C193" s="2" t="n"/>
+    </row>
+    <row r="194">
+      <c r="B194" s="2" t="n"/>
+      <c r="C194" s="2" t="n"/>
+    </row>
+    <row r="195">
+      <c r="B195" s="2" t="n"/>
+      <c r="C195" s="2" t="n"/>
+    </row>
+    <row r="196">
+      <c r="B196" s="2" t="n"/>
+      <c r="C196" s="2" t="n"/>
+    </row>
+    <row r="197">
+      <c r="B197" s="2" t="n"/>
+      <c r="C197" s="2" t="n"/>
+    </row>
+    <row r="198">
+      <c r="B198" s="2" t="n"/>
+      <c r="C198" s="2" t="n"/>
+    </row>
+    <row r="199">
+      <c r="B199" s="2" t="n"/>
+      <c r="C199" s="2" t="n"/>
+    </row>
+    <row r="200">
+      <c r="B200" s="2" t="n"/>
+      <c r="C200" s="2" t="n"/>
+    </row>
+    <row r="201">
+      <c r="B201" s="2" t="n"/>
+      <c r="C201" s="2" t="n"/>
+    </row>
+    <row r="202">
+      <c r="B202" s="2" t="n"/>
+      <c r="C202" s="2" t="n"/>
+    </row>
+    <row r="203">
+      <c r="B203" s="2" t="n"/>
+      <c r="C203" s="2" t="n"/>
+    </row>
+    <row r="204">
+      <c r="B204" s="2" t="n"/>
+      <c r="C204" s="2" t="n"/>
+    </row>
+    <row r="205">
+      <c r="B205" s="2" t="n"/>
+      <c r="C205" s="2" t="n"/>
+    </row>
+    <row r="206">
+      <c r="B206" s="2" t="n"/>
+      <c r="C206" s="2" t="n"/>
+    </row>
+    <row r="207">
+      <c r="B207" s="2" t="n"/>
+      <c r="C207" s="2" t="n"/>
+    </row>
+    <row r="208">
+      <c r="B208" s="2" t="n"/>
+      <c r="C208" s="2" t="n"/>
+    </row>
+    <row r="209">
+      <c r="B209" s="2" t="n"/>
+      <c r="C209" s="2" t="n"/>
+    </row>
+    <row r="210">
+      <c r="B210" s="2" t="n"/>
+      <c r="C210" s="2" t="n"/>
+    </row>
+    <row r="211">
+      <c r="B211" s="2" t="n"/>
+      <c r="C211" s="2" t="n"/>
+    </row>
+    <row r="212">
+      <c r="B212" s="2" t="n"/>
+      <c r="C212" s="2" t="n"/>
+    </row>
+    <row r="213">
+      <c r="B213" s="2" t="n"/>
+      <c r="C213" s="2" t="n"/>
+    </row>
+    <row r="214">
+      <c r="B214" s="2" t="n"/>
+      <c r="C214" s="2" t="n"/>
+    </row>
+    <row r="215">
+      <c r="B215" s="2" t="n"/>
+      <c r="C215" s="2" t="n"/>
+    </row>
+    <row r="216">
+      <c r="B216" s="2" t="n"/>
+      <c r="C216" s="2" t="n"/>
+    </row>
+    <row r="217">
+      <c r="B217" s="2" t="n"/>
+      <c r="C217" s="2" t="n"/>
+    </row>
+    <row r="218">
+      <c r="B218" s="2" t="n"/>
+      <c r="C218" s="2" t="n"/>
+    </row>
+    <row r="219">
+      <c r="B219" s="2" t="n"/>
+      <c r="C219" s="2" t="n"/>
+    </row>
+    <row r="220">
+      <c r="B220" s="2" t="n"/>
+      <c r="C220" s="2" t="n"/>
+    </row>
+    <row r="221">
+      <c r="B221" s="2" t="n"/>
+      <c r="C221" s="2" t="n"/>
+    </row>
+    <row r="222">
+      <c r="B222" s="2" t="n"/>
+      <c r="C222" s="2" t="n"/>
+    </row>
+    <row r="223">
+      <c r="B223" s="2" t="n"/>
+      <c r="C223" s="2" t="n"/>
+    </row>
+    <row r="224">
+      <c r="B224" s="2" t="n"/>
+      <c r="C224" s="2" t="n"/>
+    </row>
+    <row r="225">
+      <c r="B225" s="2" t="n"/>
+      <c r="C225" s="2" t="n"/>
+    </row>
+    <row r="226">
+      <c r="B226" s="2" t="n"/>
+      <c r="C226" s="2" t="n"/>
+    </row>
+    <row r="227">
+      <c r="B227" s="2" t="n"/>
+      <c r="C227" s="2" t="n"/>
+    </row>
+    <row r="228">
+      <c r="B228" s="2" t="n"/>
+      <c r="C228" s="2" t="n"/>
+    </row>
+    <row r="229">
+      <c r="B229" s="2" t="n"/>
+      <c r="C229" s="2" t="n"/>
+    </row>
+    <row r="230">
+      <c r="B230" s="2" t="n"/>
+      <c r="C230" s="2" t="n"/>
+    </row>
+    <row r="231">
+      <c r="B231" s="2" t="n"/>
+      <c r="C231" s="2" t="n"/>
+    </row>
+    <row r="232">
+      <c r="B232" s="2" t="n"/>
+      <c r="C232" s="2" t="n"/>
+    </row>
+    <row r="233">
+      <c r="B233" s="2" t="n"/>
+      <c r="C233" s="2" t="n"/>
+    </row>
+    <row r="234">
+      <c r="B234" s="2" t="n"/>
+      <c r="C234" s="2" t="n"/>
+    </row>
+    <row r="235">
+      <c r="B235" s="2" t="n"/>
+      <c r="C235" s="2" t="n"/>
+    </row>
+    <row r="236">
+      <c r="B236" s="2" t="n"/>
+      <c r="C236" s="2" t="n"/>
+    </row>
+    <row r="237">
+      <c r="B237" s="2" t="n"/>
+      <c r="C237" s="2" t="n"/>
+    </row>
+    <row r="238">
+      <c r="B238" s="2" t="n"/>
+      <c r="C238" s="2" t="n"/>
+    </row>
+    <row r="239">
+      <c r="B239" s="2" t="n"/>
+      <c r="C239" s="2" t="n"/>
+    </row>
+    <row r="240">
+      <c r="B240" s="2" t="n"/>
+      <c r="C240" s="2" t="n"/>
+    </row>
+    <row r="241">
+      <c r="B241" s="2" t="n"/>
+      <c r="C241" s="2" t="n"/>
+    </row>
+    <row r="242">
+      <c r="B242" s="2" t="n"/>
+      <c r="C242" s="2" t="n"/>
+    </row>
+    <row r="243">
+      <c r="B243" s="2" t="n"/>
+      <c r="C243" s="2" t="n"/>
+    </row>
+    <row r="244">
+      <c r="B244" s="2" t="n"/>
+      <c r="C244" s="2" t="n"/>
+    </row>
+    <row r="245">
+      <c r="B245" s="2" t="n"/>
+      <c r="C245" s="2" t="n"/>
+    </row>
+    <row r="246">
+      <c r="B246" s="2" t="n"/>
+      <c r="C246" s="2" t="n"/>
+    </row>
+    <row r="247">
+      <c r="B247" s="2" t="n"/>
+      <c r="C247" s="2" t="n"/>
+    </row>
+    <row r="248">
+      <c r="B248" s="2" t="n"/>
+      <c r="C248" s="2" t="n"/>
+    </row>
+    <row r="249">
+      <c r="B249" s="2" t="n"/>
+      <c r="C249" s="2" t="n"/>
+    </row>
+    <row r="250">
+      <c r="B250" s="2" t="n"/>
+      <c r="C250" s="2" t="n"/>
+    </row>
+    <row r="251">
+      <c r="B251" s="2" t="n"/>
+      <c r="C251" s="2" t="n"/>
+    </row>
+    <row r="252">
+      <c r="B252" s="2" t="n"/>
+      <c r="C252" s="2" t="n"/>
+    </row>
+    <row r="253">
+      <c r="B253" s="2" t="n"/>
+      <c r="C253" s="2" t="n"/>
+    </row>
+    <row r="254">
+      <c r="B254" s="2" t="n"/>
+      <c r="C254" s="2" t="n"/>
+    </row>
+    <row r="255">
+      <c r="B255" s="2" t="n"/>
+      <c r="C255" s="2" t="n"/>
+    </row>
+    <row r="256">
+      <c r="B256" s="2" t="n"/>
+      <c r="C256" s="2" t="n"/>
+    </row>
+    <row r="257">
+      <c r="B257" s="2" t="n"/>
+      <c r="C257" s="2" t="n"/>
+    </row>
+    <row r="258">
+      <c r="B258" s="2" t="n"/>
+      <c r="C258" s="2" t="n"/>
+    </row>
+    <row r="259">
+      <c r="B259" s="2" t="n"/>
+      <c r="C259" s="2" t="n"/>
+    </row>
+    <row r="260">
+      <c r="B260" s="2" t="n"/>
+      <c r="C260" s="2" t="n"/>
+    </row>
+    <row r="261">
+      <c r="B261" s="2" t="n"/>
+      <c r="C261" s="2" t="n"/>
+    </row>
+    <row r="262">
+      <c r="B262" s="2" t="n"/>
+      <c r="C262" s="2" t="n"/>
+    </row>
+    <row r="263">
+      <c r="B263" s="2" t="n"/>
+      <c r="C263" s="2" t="n"/>
+    </row>
+    <row r="264">
+      <c r="B264" s="2" t="n"/>
+      <c r="C264" s="2" t="n"/>
+    </row>
+    <row r="265">
+      <c r="B265" s="2" t="n"/>
+      <c r="C265" s="2" t="n"/>
+    </row>
+    <row r="266">
+      <c r="B266" s="2" t="n"/>
+      <c r="C266" s="2" t="n"/>
+    </row>
+    <row r="267">
+      <c r="B267" s="2" t="n"/>
+      <c r="C267" s="2" t="n"/>
+    </row>
+    <row r="268">
+      <c r="B268" s="2" t="n"/>
+      <c r="C268" s="2" t="n"/>
+    </row>
+    <row r="269">
+      <c r="B269" s="2" t="n"/>
+      <c r="C269" s="2" t="n"/>
+    </row>
+    <row r="270">
+      <c r="B270" s="2" t="n"/>
+      <c r="C270" s="2" t="n"/>
+    </row>
+    <row r="271">
+      <c r="B271" s="2" t="n"/>
+      <c r="C271" s="2" t="n"/>
+    </row>
+    <row r="272">
+      <c r="B272" s="2" t="n"/>
+      <c r="C272" s="2" t="n"/>
+    </row>
+    <row r="273">
+      <c r="B273" s="2" t="n"/>
+      <c r="C273" s="2" t="n"/>
+    </row>
+    <row r="274">
+      <c r="B274" s="2" t="n"/>
+      <c r="C274" s="2" t="n"/>
+    </row>
+    <row r="275">
+      <c r="B275" s="2" t="n"/>
+      <c r="C275" s="2" t="n"/>
+    </row>
+    <row r="276">
+      <c r="B276" s="2" t="n"/>
+      <c r="C276" s="2" t="n"/>
+    </row>
+    <row r="277">
+      <c r="B277" s="2" t="n"/>
+      <c r="C277" s="2" t="n"/>
+    </row>
+    <row r="278">
+      <c r="B278" s="2" t="n"/>
+      <c r="C278" s="2" t="n"/>
+    </row>
+    <row r="279">
+      <c r="B279" s="2" t="n"/>
+      <c r="C279" s="2" t="n"/>
+    </row>
+    <row r="280">
+      <c r="B280" s="2" t="n"/>
+      <c r="C280" s="2" t="n"/>
+    </row>
+    <row r="281">
+      <c r="B281" s="2" t="n"/>
+      <c r="C281" s="2" t="n"/>
+    </row>
+    <row r="282">
+      <c r="B282" s="2" t="n"/>
+      <c r="C282" s="2" t="n"/>
+    </row>
+    <row r="283">
+      <c r="B283" s="2" t="n"/>
+      <c r="C283" s="2" t="n"/>
+    </row>
+    <row r="284">
+      <c r="B284" s="2" t="n"/>
+      <c r="C284" s="2" t="n"/>
+    </row>
+    <row r="285">
+      <c r="B285" s="2" t="n"/>
+      <c r="C285" s="2" t="n"/>
+    </row>
+    <row r="286">
+      <c r="B286" s="2" t="n"/>
+      <c r="C286" s="2" t="n"/>
+    </row>
+    <row r="287">
+      <c r="B287" s="2" t="n"/>
+      <c r="C287" s="2" t="n"/>
+    </row>
+    <row r="288">
+      <c r="B288" s="2" t="n"/>
+      <c r="C288" s="2" t="n"/>
+    </row>
+    <row r="289">
+      <c r="B289" s="2" t="n"/>
+      <c r="C289" s="2" t="n"/>
+    </row>
+    <row r="290">
+      <c r="B290" s="2" t="n"/>
+      <c r="C290" s="2" t="n"/>
+    </row>
+    <row r="291">
+      <c r="B291" s="2" t="n"/>
+      <c r="C291" s="2" t="n"/>
+    </row>
+    <row r="292">
+      <c r="B292" s="2" t="n"/>
+      <c r="C292" s="2" t="n"/>
+    </row>
+    <row r="293">
+      <c r="B293" s="2" t="n"/>
+      <c r="C293" s="2" t="n"/>
+    </row>
+    <row r="294">
+      <c r="B294" s="2" t="n"/>
+      <c r="C294" s="2" t="n"/>
+    </row>
+    <row r="295">
+      <c r="B295" s="2" t="n"/>
+      <c r="C295" s="2" t="n"/>
+    </row>
+    <row r="296">
+      <c r="B296" s="2" t="n"/>
+      <c r="C296" s="2" t="n"/>
+    </row>
+    <row r="297">
+      <c r="B297" s="2" t="n"/>
+      <c r="C297" s="2" t="n"/>
+    </row>
+    <row r="298">
+      <c r="B298" s="2" t="n"/>
+      <c r="C298" s="2" t="n"/>
+    </row>
+    <row r="299">
+      <c r="B299" s="2" t="n"/>
+      <c r="C299" s="2" t="n"/>
+    </row>
+    <row r="300">
+      <c r="B300" s="2" t="n"/>
+      <c r="C300" s="2" t="n"/>
+    </row>
+    <row r="301">
+      <c r="B301" s="2" t="n"/>
+      <c r="C301" s="2" t="n"/>
+    </row>
+    <row r="302">
+      <c r="B302" s="2" t="n"/>
+      <c r="C302" s="2" t="n"/>
+    </row>
+    <row r="303">
+      <c r="B303" s="2" t="n"/>
+      <c r="C303" s="2" t="n"/>
+    </row>
+    <row r="304">
+      <c r="B304" s="2" t="n"/>
+      <c r="C304" s="2" t="n"/>
+    </row>
+    <row r="305">
+      <c r="B305" s="2" t="n"/>
+      <c r="C305" s="2" t="n"/>
+    </row>
+    <row r="306">
+      <c r="B306" s="2" t="n"/>
+      <c r="C306" s="2" t="n"/>
+    </row>
+    <row r="307">
+      <c r="B307" s="2" t="n"/>
+      <c r="C307" s="2" t="n"/>
+    </row>
+    <row r="308">
+      <c r="B308" s="2" t="n"/>
+      <c r="C308" s="2" t="n"/>
+    </row>
+    <row r="309">
+      <c r="B309" s="2" t="n"/>
+      <c r="C309" s="2" t="n"/>
+    </row>
+    <row r="310">
+      <c r="B310" s="2" t="n"/>
+      <c r="C310" s="2" t="n"/>
+    </row>
+    <row r="311">
+      <c r="B311" s="2" t="n"/>
+      <c r="C311" s="2" t="n"/>
+    </row>
+    <row r="312">
+      <c r="B312" s="2" t="n"/>
+      <c r="C312" s="2" t="n"/>
+    </row>
+    <row r="313">
+      <c r="B313" s="2" t="n"/>
+      <c r="C313" s="2" t="n"/>
+    </row>
+    <row r="314">
+      <c r="B314" s="2" t="n"/>
+      <c r="C314" s="2" t="n"/>
+    </row>
+    <row r="315">
+      <c r="B315" s="2" t="n"/>
+      <c r="C315" s="2" t="n"/>
+    </row>
+    <row r="316">
+      <c r="B316" s="2" t="n"/>
+      <c r="C316" s="2" t="n"/>
+    </row>
+    <row r="317">
+      <c r="B317" s="2" t="n"/>
+      <c r="C317" s="2" t="n"/>
+    </row>
+    <row r="318">
+      <c r="B318" s="2" t="n"/>
+      <c r="C318" s="2" t="n"/>
+    </row>
+    <row r="319">
+      <c r="B319" s="2" t="n"/>
+      <c r="C319" s="2" t="n"/>
+    </row>
+    <row r="320">
+      <c r="B320" s="2" t="n"/>
+      <c r="C320" s="2" t="n"/>
+    </row>
+    <row r="321">
+      <c r="B321" s="2" t="n"/>
+      <c r="C321" s="2" t="n"/>
+    </row>
+    <row r="322">
+      <c r="B322" s="2" t="n"/>
+      <c r="C322" s="2" t="n"/>
+    </row>
+    <row r="323">
+      <c r="B323" s="2" t="n"/>
+      <c r="C323" s="2" t="n"/>
+    </row>
+    <row r="324">
+      <c r="B324" s="2" t="n"/>
+      <c r="C324" s="2" t="n"/>
+    </row>
+    <row r="325">
+      <c r="B325" s="2" t="n"/>
+      <c r="C325" s="2" t="n"/>
+    </row>
+    <row r="326">
+      <c r="B326" s="2" t="n"/>
+      <c r="C326" s="2" t="n"/>
+    </row>
+    <row r="327">
+      <c r="B327" s="2" t="n"/>
+      <c r="C327" s="2" t="n"/>
+    </row>
+    <row r="328">
+      <c r="B328" s="2" t="n"/>
+      <c r="C328" s="2" t="n"/>
+    </row>
+    <row r="329">
+      <c r="B329" s="2" t="n"/>
+      <c r="C329" s="2" t="n"/>
+    </row>
+    <row r="330">
+      <c r="B330" s="2" t="n"/>
+      <c r="C330" s="2" t="n"/>
+    </row>
+    <row r="331">
+      <c r="B331" s="2" t="n"/>
+      <c r="C331" s="2" t="n"/>
+    </row>
+    <row r="332">
+      <c r="B332" s="2" t="n"/>
+      <c r="C332" s="2" t="n"/>
+    </row>
+    <row r="333">
+      <c r="B333" s="2" t="n"/>
+      <c r="C333" s="2" t="n"/>
+    </row>
+    <row r="334">
+      <c r="B334" s="2" t="n"/>
+      <c r="C334" s="2" t="n"/>
+    </row>
+    <row r="335">
+      <c r="B335" s="2" t="n"/>
+      <c r="C335" s="2" t="n"/>
+    </row>
+    <row r="336">
+      <c r="B336" s="2" t="n"/>
+      <c r="C336" s="2" t="n"/>
+    </row>
+    <row r="337">
+      <c r="B337" s="2" t="n"/>
+      <c r="C337" s="2" t="n"/>
+    </row>
+    <row r="338">
+      <c r="B338" s="2" t="n"/>
+      <c r="C338" s="2" t="n"/>
+    </row>
+    <row r="339">
+      <c r="B339" s="2" t="n"/>
+      <c r="C339" s="2" t="n"/>
+    </row>
+    <row r="340">
+      <c r="B340" s="2" t="n"/>
+      <c r="C340" s="2" t="n"/>
+    </row>
+    <row r="341">
+      <c r="B341" s="2" t="n"/>
+      <c r="C341" s="2" t="n"/>
+    </row>
+    <row r="342">
+      <c r="B342" s="2" t="n"/>
+      <c r="C342" s="2" t="n"/>
+    </row>
+    <row r="343">
+      <c r="B343" s="2" t="n"/>
+      <c r="C343" s="2" t="n"/>
+    </row>
+    <row r="344">
+      <c r="B344" s="2" t="n"/>
+      <c r="C344" s="2" t="n"/>
+    </row>
+    <row r="345">
+      <c r="B345" s="2" t="n"/>
+      <c r="C345" s="2" t="n"/>
+    </row>
+    <row r="346">
+      <c r="B346" s="2" t="n"/>
+      <c r="C346" s="2" t="n"/>
+    </row>
+    <row r="347">
+      <c r="B347" s="2" t="n"/>
+      <c r="C347" s="2" t="n"/>
+    </row>
+    <row r="348">
+      <c r="B348" s="2" t="n"/>
+      <c r="C348" s="2" t="n"/>
+    </row>
+    <row r="349">
+      <c r="B349" s="2" t="n"/>
+      <c r="C349" s="2" t="n"/>
+    </row>
+    <row r="350">
+      <c r="B350" s="2" t="n"/>
+      <c r="C350" s="2" t="n"/>
+    </row>
+    <row r="351">
+      <c r="B351" s="2" t="n"/>
+      <c r="C351" s="2" t="n"/>
+    </row>
+    <row r="352">
+      <c r="B352" s="2" t="n"/>
+      <c r="C352" s="2" t="n"/>
+    </row>
+    <row r="353">
+      <c r="B353" s="2" t="n"/>
+      <c r="C353" s="2" t="n"/>
+    </row>
+    <row r="354">
+      <c r="B354" s="2" t="n"/>
+      <c r="C354" s="2" t="n"/>
+    </row>
+    <row r="355">
+      <c r="B355" s="2" t="n"/>
+      <c r="C355" s="2" t="n"/>
+    </row>
+    <row r="356">
+      <c r="B356" s="2" t="n"/>
+      <c r="C356" s="2" t="n"/>
+    </row>
+    <row r="357">
+      <c r="B357" s="2" t="n"/>
+      <c r="C357" s="2" t="n"/>
+    </row>
+    <row r="358">
+      <c r="B358" s="2" t="n"/>
+      <c r="C358" s="2" t="n"/>
+    </row>
+    <row r="359">
+      <c r="B359" s="2" t="n"/>
+      <c r="C359" s="2" t="n"/>
+    </row>
+    <row r="360">
+      <c r="B360" s="2" t="n"/>
+      <c r="C360" s="2" t="n"/>
+    </row>
+    <row r="361">
+      <c r="B361" s="2" t="n"/>
+      <c r="C361" s="2" t="n"/>
+    </row>
+    <row r="362">
+      <c r="B362" s="2" t="n"/>
+      <c r="C362" s="2" t="n"/>
+    </row>
+    <row r="363">
+      <c r="B363" s="2" t="n"/>
+      <c r="C363" s="2" t="n"/>
+    </row>
+    <row r="364">
+      <c r="B364" s="2" t="n"/>
+      <c r="C364" s="2" t="n"/>
+    </row>
+    <row r="365">
+      <c r="B365" s="2" t="n"/>
+      <c r="C365" s="2" t="n"/>
+    </row>
+    <row r="366">
+      <c r="B366" s="2" t="n"/>
+      <c r="C366" s="2" t="n"/>
+    </row>
+    <row r="367">
+      <c r="B367" s="2" t="n"/>
+      <c r="C367" s="2" t="n"/>
+    </row>
+    <row r="368">
+      <c r="B368" s="2" t="n"/>
+      <c r="C368" s="2" t="n"/>
+    </row>
+    <row r="369">
+      <c r="B369" s="2" t="n"/>
+      <c r="C369" s="2" t="n"/>
+    </row>
+    <row r="370">
+      <c r="B370" s="2" t="n"/>
+      <c r="C370" s="2" t="n"/>
+    </row>
+    <row r="371">
+      <c r="B371" s="2" t="n"/>
+      <c r="C371" s="2" t="n"/>
+    </row>
+    <row r="372">
+      <c r="B372" s="2" t="n"/>
+      <c r="C372" s="2" t="n"/>
+    </row>
+    <row r="373">
+      <c r="B373" s="2" t="n"/>
+      <c r="C373" s="2" t="n"/>
+    </row>
+    <row r="374">
+      <c r="B374" s="2" t="n"/>
+      <c r="C374" s="2" t="n"/>
+    </row>
+    <row r="375">
+      <c r="B375" s="2" t="n"/>
+      <c r="C375" s="2" t="n"/>
+    </row>
+    <row r="376">
+      <c r="B376" s="2" t="n"/>
+      <c r="C376" s="2" t="n"/>
+    </row>
+    <row r="377">
+      <c r="B377" s="2" t="n"/>
+      <c r="C377" s="2" t="n"/>
+    </row>
+    <row r="378">
+      <c r="B378" s="2" t="n"/>
+      <c r="C378" s="2" t="n"/>
+    </row>
+    <row r="379">
+      <c r="B379" s="2" t="n"/>
+      <c r="C379" s="2" t="n"/>
+    </row>
+    <row r="380">
+      <c r="B380" s="2" t="n"/>
+      <c r="C380" s="2" t="n"/>
+    </row>
+    <row r="381">
+      <c r="B381" s="2" t="n"/>
+      <c r="C381" s="2" t="n"/>
+    </row>
+    <row r="382">
+      <c r="B382" s="2" t="n"/>
+      <c r="C382" s="2" t="n"/>
+    </row>
+    <row r="383">
+      <c r="B383" s="2" t="n"/>
+      <c r="C383" s="2" t="n"/>
+    </row>
+    <row r="384">
+      <c r="B384" s="2" t="n"/>
+      <c r="C384" s="2" t="n"/>
+    </row>
+    <row r="385">
+      <c r="B385" s="2" t="n"/>
+      <c r="C385" s="2" t="n"/>
+    </row>
+    <row r="386">
+      <c r="B386" s="2" t="n"/>
+      <c r="C386" s="2" t="n"/>
+    </row>
+    <row r="387">
+      <c r="B387" s="2" t="n"/>
+      <c r="C387" s="2" t="n"/>
+    </row>
+    <row r="388">
+      <c r="B388" s="2" t="n"/>
+      <c r="C388" s="2" t="n"/>
+    </row>
+    <row r="389">
+      <c r="B389" s="2" t="n"/>
+      <c r="C389" s="2" t="n"/>
+    </row>
+    <row r="390">
+      <c r="B390" s="2" t="n"/>
+      <c r="C390" s="2" t="n"/>
+    </row>
+    <row r="391">
+      <c r="B391" s="2" t="n"/>
+      <c r="C391" s="2" t="n"/>
+    </row>
+    <row r="392">
+      <c r="B392" s="2" t="n"/>
+      <c r="C392" s="2" t="n"/>
+    </row>
+    <row r="393">
+      <c r="B393" s="2" t="n"/>
+      <c r="C393" s="2" t="n"/>
+    </row>
+    <row r="394">
+      <c r="B394" s="2" t="n"/>
+      <c r="C394" s="2" t="n"/>
+    </row>
+    <row r="395">
+      <c r="B395" s="2" t="n"/>
+      <c r="C395" s="2" t="n"/>
+    </row>
+    <row r="396">
+      <c r="B396" s="2" t="n"/>
+      <c r="C396" s="2" t="n"/>
+    </row>
+    <row r="397">
+      <c r="B397" s="2" t="n"/>
+      <c r="C397" s="2" t="n"/>
+    </row>
+    <row r="398">
+      <c r="B398" s="2" t="n"/>
+      <c r="C398" s="2" t="n"/>
+    </row>
+    <row r="399">
+      <c r="B399" s="2" t="n"/>
+      <c r="C399" s="2" t="n"/>
+    </row>
+    <row r="400">
+      <c r="B400" s="2" t="n"/>
+      <c r="C400" s="2" t="n"/>
+    </row>
+    <row r="401">
+      <c r="B401" s="2" t="n"/>
+      <c r="C401" s="2" t="n"/>
+    </row>
+    <row r="402">
+      <c r="B402" s="2" t="n"/>
+      <c r="C402" s="2" t="n"/>
+    </row>
+    <row r="403">
+      <c r="B403" s="2" t="n"/>
+      <c r="C403" s="2" t="n"/>
+    </row>
+    <row r="404">
+      <c r="B404" s="2" t="n"/>
+      <c r="C404" s="2" t="n"/>
+    </row>
+    <row r="405">
+      <c r="B405" s="2" t="n"/>
+      <c r="C405" s="2" t="n"/>
+    </row>
+    <row r="406">
+      <c r="B406" s="2" t="n"/>
+      <c r="C406" s="2" t="n"/>
+    </row>
+    <row r="407">
+      <c r="B407" s="2" t="n"/>
+      <c r="C407" s="2" t="n"/>
+    </row>
+    <row r="408">
+      <c r="B408" s="2" t="n"/>
+      <c r="C408" s="2" t="n"/>
+    </row>
+    <row r="409">
+      <c r="B409" s="2" t="n"/>
+      <c r="C409" s="2" t="n"/>
+    </row>
+    <row r="410">
+      <c r="B410" s="2" t="n"/>
+      <c r="C410" s="2" t="n"/>
+    </row>
+    <row r="411">
+      <c r="B411" s="2" t="n"/>
+      <c r="C411" s="2" t="n"/>
+    </row>
+    <row r="412">
+      <c r="B412" s="2" t="n"/>
+      <c r="C412" s="2" t="n"/>
+    </row>
+    <row r="413">
+      <c r="B413" s="2" t="n"/>
+      <c r="C413" s="2" t="n"/>
+    </row>
+    <row r="414">
+      <c r="B414" s="2" t="n"/>
+      <c r="C414" s="2" t="n"/>
+    </row>
+    <row r="415">
+      <c r="B415" s="2" t="n"/>
+      <c r="C415" s="2" t="n"/>
+    </row>
+    <row r="416">
+      <c r="B416" s="2" t="n"/>
+      <c r="C416" s="2" t="n"/>
+    </row>
+    <row r="417">
+      <c r="B417" s="2" t="n"/>
+      <c r="C417" s="2" t="n"/>
+    </row>
+    <row r="418">
+      <c r="B418" s="2" t="n"/>
+      <c r="C418" s="2" t="n"/>
+    </row>
+    <row r="419">
+      <c r="B419" s="2" t="n"/>
+      <c r="C419" s="2" t="n"/>
+    </row>
+    <row r="420">
+      <c r="B420" s="2" t="n"/>
+      <c r="C420" s="2" t="n"/>
+    </row>
+    <row r="421">
+      <c r="B421" s="2" t="n"/>
+      <c r="C421" s="2" t="n"/>
+    </row>
+    <row r="422">
+      <c r="B422" s="2" t="n"/>
+      <c r="C422" s="2" t="n"/>
+    </row>
+    <row r="423">
+      <c r="B423" s="2" t="n"/>
+      <c r="C423" s="2" t="n"/>
+    </row>
+    <row r="424">
+      <c r="B424" s="2" t="n"/>
+      <c r="C424" s="2" t="n"/>
+    </row>
+    <row r="425">
+      <c r="B425" s="2" t="n"/>
+      <c r="C425" s="2" t="n"/>
+    </row>
+    <row r="426">
+      <c r="B426" s="2" t="n"/>
+      <c r="C426" s="2" t="n"/>
+    </row>
+    <row r="427">
+      <c r="B427" s="2" t="n"/>
+      <c r="C427" s="2" t="n"/>
+    </row>
+    <row r="428">
+      <c r="B428" s="2" t="n"/>
+      <c r="C428" s="2" t="n"/>
+    </row>
+    <row r="429">
+      <c r="B429" s="2" t="n"/>
+      <c r="C429" s="2" t="n"/>
+    </row>
+    <row r="430">
+      <c r="B430" s="2" t="n"/>
+      <c r="C430" s="2" t="n"/>
+    </row>
+    <row r="431">
+      <c r="B431" s="2" t="n"/>
+      <c r="C431" s="2" t="n"/>
+    </row>
+    <row r="432">
+      <c r="B432" s="2" t="n"/>
+      <c r="C432" s="2" t="n"/>
+    </row>
+    <row r="433">
+      <c r="B433" s="2" t="n"/>
+      <c r="C433" s="2" t="n"/>
+    </row>
+    <row r="434">
+      <c r="B434" s="2" t="n"/>
+      <c r="C434" s="2" t="n"/>
+    </row>
+    <row r="435">
+      <c r="B435" s="2" t="n"/>
+      <c r="C435" s="2" t="n"/>
+    </row>
+    <row r="436">
+      <c r="B436" s="2" t="n"/>
+      <c r="C436" s="2" t="n"/>
+    </row>
+    <row r="437">
+      <c r="B437" s="2" t="n"/>
+      <c r="C437" s="2" t="n"/>
+    </row>
+    <row r="438">
+      <c r="B438" s="2" t="n"/>
+      <c r="C438" s="2" t="n"/>
+    </row>
+    <row r="439">
+      <c r="B439" s="2" t="n"/>
+      <c r="C439" s="2" t="n"/>
+    </row>
+    <row r="440">
+      <c r="B440" s="2" t="n"/>
+      <c r="C440" s="2" t="n"/>
+    </row>
+    <row r="441">
+      <c r="B441" s="2" t="n"/>
+      <c r="C441" s="2" t="n"/>
+    </row>
+    <row r="442">
+      <c r="B442" s="2" t="n"/>
+      <c r="C442" s="2" t="n"/>
+    </row>
+    <row r="443">
+      <c r="B443" s="2" t="n"/>
+      <c r="C443" s="2" t="n"/>
+    </row>
+    <row r="444">
+      <c r="B444" s="2" t="n"/>
+      <c r="C444" s="2" t="n"/>
+    </row>
+    <row r="445">
+      <c r="B445" s="2" t="n"/>
+      <c r="C445" s="2" t="n"/>
+    </row>
+    <row r="446">
+      <c r="B446" s="2" t="n"/>
+      <c r="C446" s="2" t="n"/>
+    </row>
+    <row r="447">
+      <c r="B447" s="2" t="n"/>
+      <c r="C447" s="2" t="n"/>
+    </row>
+    <row r="448">
+      <c r="B448" s="2" t="n"/>
+      <c r="C448" s="2" t="n"/>
+    </row>
+    <row r="449">
+      <c r="B449" s="2" t="n"/>
+      <c r="C449" s="2" t="n"/>
+    </row>
+    <row r="450">
+      <c r="B450" s="2" t="n"/>
+      <c r="C450" s="2" t="n"/>
+    </row>
+    <row r="451">
+      <c r="B451" s="2" t="n"/>
+      <c r="C451" s="2" t="n"/>
+    </row>
+    <row r="452">
+      <c r="B452" s="2" t="n"/>
+      <c r="C452" s="2" t="n"/>
+    </row>
+    <row r="453">
+      <c r="B453" s="2" t="n"/>
+      <c r="C453" s="2" t="n"/>
+    </row>
+    <row r="454">
+      <c r="B454" s="2" t="n"/>
+      <c r="C454" s="2" t="n"/>
+    </row>
+    <row r="455">
+      <c r="B455" s="2" t="n"/>
+      <c r="C455" s="2" t="n"/>
+    </row>
+    <row r="456">
+      <c r="B456" s="2" t="n"/>
+      <c r="C456" s="2" t="n"/>
+    </row>
+    <row r="457">
+      <c r="B457" s="2" t="n"/>
+      <c r="C457" s="2" t="n"/>
+    </row>
+    <row r="458">
+      <c r="B458" s="2" t="n"/>
+      <c r="C458" s="2" t="n"/>
+    </row>
+    <row r="459">
+      <c r="B459" s="2" t="n"/>
+      <c r="C459" s="2" t="n"/>
+    </row>
+    <row r="460">
+      <c r="B460" s="2" t="n"/>
+      <c r="C460" s="2" t="n"/>
+    </row>
+    <row r="461">
+      <c r="B461" s="2" t="n"/>
+      <c r="C461" s="2" t="n"/>
+    </row>
+    <row r="462">
+      <c r="B462" s="2" t="n"/>
+      <c r="C462" s="2" t="n"/>
+    </row>
+    <row r="463">
+      <c r="B463" s="2" t="n"/>
+      <c r="C463" s="2" t="n"/>
+    </row>
+    <row r="464">
+      <c r="B464" s="2" t="n"/>
+      <c r="C464" s="2" t="n"/>
+    </row>
+    <row r="465">
+      <c r="B465" s="2" t="n"/>
+      <c r="C465" s="2" t="n"/>
+    </row>
+    <row r="466">
+      <c r="B466" s="2" t="n"/>
+      <c r="C466" s="2" t="n"/>
+    </row>
+    <row r="467">
+      <c r="B467" s="2" t="n"/>
+      <c r="C467" s="2" t="n"/>
+    </row>
+    <row r="468">
+      <c r="B468" s="2" t="n"/>
+      <c r="C468" s="2" t="n"/>
+    </row>
+    <row r="469">
+      <c r="B469" s="2" t="n"/>
+      <c r="C469" s="2" t="n"/>
+    </row>
+    <row r="470">
+      <c r="B470" s="2" t="n"/>
+      <c r="C470" s="2" t="n"/>
+    </row>
+    <row r="471">
+      <c r="B471" s="2" t="n"/>
+      <c r="C471" s="2" t="n"/>
+    </row>
+    <row r="472">
+      <c r="B472" s="2" t="n"/>
+      <c r="C472" s="2" t="n"/>
+    </row>
+    <row r="473">
+      <c r="B473" s="2" t="n"/>
+      <c r="C473" s="2" t="n"/>
+    </row>
+    <row r="474">
+      <c r="B474" s="2" t="n"/>
+      <c r="C474" s="2" t="n"/>
+    </row>
+    <row r="475">
+      <c r="B475" s="2" t="n"/>
+      <c r="C475" s="2" t="n"/>
+    </row>
+    <row r="476">
+      <c r="B476" s="2" t="n"/>
+      <c r="C476" s="2" t="n"/>
+    </row>
+    <row r="477">
+      <c r="B477" s="2" t="n"/>
+      <c r="C477" s="2" t="n"/>
+    </row>
+    <row r="478">
+      <c r="B478" s="2" t="n"/>
+      <c r="C478" s="2" t="n"/>
+    </row>
+    <row r="479">
+      <c r="B479" s="2" t="n"/>
+      <c r="C479" s="2" t="n"/>
+    </row>
+    <row r="480">
+      <c r="B480" s="2" t="n"/>
+      <c r="C480" s="2" t="n"/>
+    </row>
+    <row r="481">
+      <c r="B481" s="2" t="n"/>
+      <c r="C481" s="2" t="n"/>
+    </row>
+    <row r="482">
+      <c r="B482" s="2" t="n"/>
+      <c r="C482" s="2" t="n"/>
+    </row>
+    <row r="483">
+      <c r="B483" s="2" t="n"/>
+      <c r="C483" s="2" t="n"/>
+    </row>
+    <row r="484">
+      <c r="B484" s="2" t="n"/>
+      <c r="C484" s="2" t="n"/>
+    </row>
+    <row r="485">
+      <c r="B485" s="2" t="n"/>
+      <c r="C485" s="2" t="n"/>
+    </row>
+    <row r="486">
+      <c r="B486" s="2" t="n"/>
+      <c r="C486" s="2" t="n"/>
+    </row>
+    <row r="487">
+      <c r="B487" s="2" t="n"/>
+      <c r="C487" s="2" t="n"/>
+    </row>
+    <row r="488">
+      <c r="B488" s="2" t="n"/>
+      <c r="C488" s="2" t="n"/>
+    </row>
+    <row r="489">
+      <c r="B489" s="2" t="n"/>
+      <c r="C489" s="2" t="n"/>
+    </row>
+    <row r="490">
+      <c r="B490" s="2" t="n"/>
+      <c r="C490" s="2" t="n"/>
+    </row>
+    <row r="491">
+      <c r="B491" s="2" t="n"/>
+      <c r="C491" s="2" t="n"/>
+    </row>
+    <row r="492">
+      <c r="B492" s="2" t="n"/>
+      <c r="C492" s="2" t="n"/>
+    </row>
+    <row r="493">
+      <c r="B493" s="2" t="n"/>
+      <c r="C493" s="2" t="n"/>
+    </row>
+    <row r="494">
+      <c r="B494" s="2" t="n"/>
+      <c r="C494" s="2" t="n"/>
+    </row>
+    <row r="495">
+      <c r="B495" s="2" t="n"/>
+      <c r="C495" s="2" t="n"/>
+    </row>
+    <row r="496">
+      <c r="B496" s="2" t="n"/>
+      <c r="C496" s="2" t="n"/>
+    </row>
+    <row r="497">
+      <c r="B497" s="2" t="n"/>
+      <c r="C497" s="2" t="n"/>
+    </row>
+    <row r="498">
+      <c r="B498" s="2" t="n"/>
+      <c r="C498" s="2" t="n"/>
+    </row>
+    <row r="499">
+      <c r="B499" s="2" t="n"/>
+      <c r="C499" s="2" t="n"/>
+    </row>
+    <row r="500">
+      <c r="B500" s="2" t="n"/>
+      <c r="C500" s="2" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="A2:A500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Ungültige Termin-Nr" error="Hier steht die Nummer aus Spalte A im Blatt Termine." type="whole" operator="between">
-      <formula1>1</formula1>
-      <formula2>500</formula2>
+    <dataValidation sqref="A2:A500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Ungültiger Wert" error="Bitte einen Wert aus der Liste wählen." promptTitle="Termin" prompt="Nummer des Termins aus dem Blatt „Termine“." type="list">
+      <formula1>=Termine!$A$2:$A$500</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -890,285 +4758,284 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00808080"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Kennung</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Bezeichnung</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Auswahl (für Dropdown)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>P01</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>NRA</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>P01 NRA</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>P02</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>NRA</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>P02 NRA</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>P03</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>NRA</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>P03 NRA</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>P04</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>NRA</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>P04 NRA</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>P06</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>EHSV NRA</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>P06 EHSV NRA</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>P07</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>EHSV NRA</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>P07 EHSV NRA</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>P10</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>PTU TESTFUCHS</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>P10 PTU TESTFUCHS</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>PUMO HYCOM</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>P11 PUMO HYCOM</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>P12</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>PUMO TESTFUCHS</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>P12 PUMO TESTFUCHS</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>P20</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>THRUST-REVERSER</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>P20 THRUST-REVERSER</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>P21</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>NRC HYCOM</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>P21 NRC HYCOM</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>P31</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>THSA</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>P31 THSA</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>P40</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>AKKU/HOCHDRUCK-RAUM</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>P40 AKKU/HOCHDRUCK-RAUM</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>P41</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>P41 MIL</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>P43</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>LOW-PRESSURE</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>P43 LOW-PRESSURE</t>
         </is>
@@ -1182,122 +5049,2120 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00A6A6A6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Nr</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Art</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Prüfstand</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Von</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Bis</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="n">
+      <c r="A2" t="n">
         <v>7</v>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Ausfall</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>P02 NRA</t>
         </is>
       </c>
-      <c r="D2" s="12" t="n">
+      <c r="D2" s="2" t="n">
         <v>46300.25</v>
       </c>
-      <c r="E2" s="12" t="n">
+      <c r="E2" s="2" t="n">
         <v>46302.91666666666</v>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Kühlmittelverlust, Reparatur</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>abgeschlossen</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="n">
+      <c r="A3" t="n">
         <v>8</v>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Wartung</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>P41 MIL</t>
         </is>
       </c>
-      <c r="D3" s="12" t="n">
+      <c r="D3" s="2" t="n">
         <v>46307.29166666666</v>
       </c>
-      <c r="E3" s="12" t="n">
+      <c r="E3" s="2" t="n">
         <v>46307.66666666666</v>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Dichtungen getauscht</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>abgeschlossen</t>
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="D25" s="2" t="n"/>
+      <c r="E25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="D26" s="2" t="n"/>
+      <c r="E26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="D27" s="2" t="n"/>
+      <c r="E27" s="2" t="n"/>
+    </row>
+    <row r="28">
+      <c r="D28" s="2" t="n"/>
+      <c r="E28" s="2" t="n"/>
+    </row>
+    <row r="29">
+      <c r="D29" s="2" t="n"/>
+      <c r="E29" s="2" t="n"/>
+    </row>
+    <row r="30">
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="D31" s="2" t="n"/>
+      <c r="E31" s="2" t="n"/>
+    </row>
+    <row r="32">
+      <c r="D32" s="2" t="n"/>
+      <c r="E32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="D33" s="2" t="n"/>
+      <c r="E33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="D34" s="2" t="n"/>
+      <c r="E34" s="2" t="n"/>
+    </row>
+    <row r="35">
+      <c r="D35" s="2" t="n"/>
+      <c r="E35" s="2" t="n"/>
+    </row>
+    <row r="36">
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="2" t="n"/>
+    </row>
+    <row r="37">
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="n"/>
+    </row>
+    <row r="38">
+      <c r="D38" s="2" t="n"/>
+      <c r="E38" s="2" t="n"/>
+    </row>
+    <row r="39">
+      <c r="D39" s="2" t="n"/>
+      <c r="E39" s="2" t="n"/>
+    </row>
+    <row r="40">
+      <c r="D40" s="2" t="n"/>
+      <c r="E40" s="2" t="n"/>
+    </row>
+    <row r="41">
+      <c r="D41" s="2" t="n"/>
+      <c r="E41" s="2" t="n"/>
+    </row>
+    <row r="42">
+      <c r="D42" s="2" t="n"/>
+      <c r="E42" s="2" t="n"/>
+    </row>
+    <row r="43">
+      <c r="D43" s="2" t="n"/>
+      <c r="E43" s="2" t="n"/>
+    </row>
+    <row r="44">
+      <c r="D44" s="2" t="n"/>
+      <c r="E44" s="2" t="n"/>
+    </row>
+    <row r="45">
+      <c r="D45" s="2" t="n"/>
+      <c r="E45" s="2" t="n"/>
+    </row>
+    <row r="46">
+      <c r="D46" s="2" t="n"/>
+      <c r="E46" s="2" t="n"/>
+    </row>
+    <row r="47">
+      <c r="D47" s="2" t="n"/>
+      <c r="E47" s="2" t="n"/>
+    </row>
+    <row r="48">
+      <c r="D48" s="2" t="n"/>
+      <c r="E48" s="2" t="n"/>
+    </row>
+    <row r="49">
+      <c r="D49" s="2" t="n"/>
+      <c r="E49" s="2" t="n"/>
+    </row>
+    <row r="50">
+      <c r="D50" s="2" t="n"/>
+      <c r="E50" s="2" t="n"/>
+    </row>
+    <row r="51">
+      <c r="D51" s="2" t="n"/>
+      <c r="E51" s="2" t="n"/>
+    </row>
+    <row r="52">
+      <c r="D52" s="2" t="n"/>
+      <c r="E52" s="2" t="n"/>
+    </row>
+    <row r="53">
+      <c r="D53" s="2" t="n"/>
+      <c r="E53" s="2" t="n"/>
+    </row>
+    <row r="54">
+      <c r="D54" s="2" t="n"/>
+      <c r="E54" s="2" t="n"/>
+    </row>
+    <row r="55">
+      <c r="D55" s="2" t="n"/>
+      <c r="E55" s="2" t="n"/>
+    </row>
+    <row r="56">
+      <c r="D56" s="2" t="n"/>
+      <c r="E56" s="2" t="n"/>
+    </row>
+    <row r="57">
+      <c r="D57" s="2" t="n"/>
+      <c r="E57" s="2" t="n"/>
+    </row>
+    <row r="58">
+      <c r="D58" s="2" t="n"/>
+      <c r="E58" s="2" t="n"/>
+    </row>
+    <row r="59">
+      <c r="D59" s="2" t="n"/>
+      <c r="E59" s="2" t="n"/>
+    </row>
+    <row r="60">
+      <c r="D60" s="2" t="n"/>
+      <c r="E60" s="2" t="n"/>
+    </row>
+    <row r="61">
+      <c r="D61" s="2" t="n"/>
+      <c r="E61" s="2" t="n"/>
+    </row>
+    <row r="62">
+      <c r="D62" s="2" t="n"/>
+      <c r="E62" s="2" t="n"/>
+    </row>
+    <row r="63">
+      <c r="D63" s="2" t="n"/>
+      <c r="E63" s="2" t="n"/>
+    </row>
+    <row r="64">
+      <c r="D64" s="2" t="n"/>
+      <c r="E64" s="2" t="n"/>
+    </row>
+    <row r="65">
+      <c r="D65" s="2" t="n"/>
+      <c r="E65" s="2" t="n"/>
+    </row>
+    <row r="66">
+      <c r="D66" s="2" t="n"/>
+      <c r="E66" s="2" t="n"/>
+    </row>
+    <row r="67">
+      <c r="D67" s="2" t="n"/>
+      <c r="E67" s="2" t="n"/>
+    </row>
+    <row r="68">
+      <c r="D68" s="2" t="n"/>
+      <c r="E68" s="2" t="n"/>
+    </row>
+    <row r="69">
+      <c r="D69" s="2" t="n"/>
+      <c r="E69" s="2" t="n"/>
+    </row>
+    <row r="70">
+      <c r="D70" s="2" t="n"/>
+      <c r="E70" s="2" t="n"/>
+    </row>
+    <row r="71">
+      <c r="D71" s="2" t="n"/>
+      <c r="E71" s="2" t="n"/>
+    </row>
+    <row r="72">
+      <c r="D72" s="2" t="n"/>
+      <c r="E72" s="2" t="n"/>
+    </row>
+    <row r="73">
+      <c r="D73" s="2" t="n"/>
+      <c r="E73" s="2" t="n"/>
+    </row>
+    <row r="74">
+      <c r="D74" s="2" t="n"/>
+      <c r="E74" s="2" t="n"/>
+    </row>
+    <row r="75">
+      <c r="D75" s="2" t="n"/>
+      <c r="E75" s="2" t="n"/>
+    </row>
+    <row r="76">
+      <c r="D76" s="2" t="n"/>
+      <c r="E76" s="2" t="n"/>
+    </row>
+    <row r="77">
+      <c r="D77" s="2" t="n"/>
+      <c r="E77" s="2" t="n"/>
+    </row>
+    <row r="78">
+      <c r="D78" s="2" t="n"/>
+      <c r="E78" s="2" t="n"/>
+    </row>
+    <row r="79">
+      <c r="D79" s="2" t="n"/>
+      <c r="E79" s="2" t="n"/>
+    </row>
+    <row r="80">
+      <c r="D80" s="2" t="n"/>
+      <c r="E80" s="2" t="n"/>
+    </row>
+    <row r="81">
+      <c r="D81" s="2" t="n"/>
+      <c r="E81" s="2" t="n"/>
+    </row>
+    <row r="82">
+      <c r="D82" s="2" t="n"/>
+      <c r="E82" s="2" t="n"/>
+    </row>
+    <row r="83">
+      <c r="D83" s="2" t="n"/>
+      <c r="E83" s="2" t="n"/>
+    </row>
+    <row r="84">
+      <c r="D84" s="2" t="n"/>
+      <c r="E84" s="2" t="n"/>
+    </row>
+    <row r="85">
+      <c r="D85" s="2" t="n"/>
+      <c r="E85" s="2" t="n"/>
+    </row>
+    <row r="86">
+      <c r="D86" s="2" t="n"/>
+      <c r="E86" s="2" t="n"/>
+    </row>
+    <row r="87">
+      <c r="D87" s="2" t="n"/>
+      <c r="E87" s="2" t="n"/>
+    </row>
+    <row r="88">
+      <c r="D88" s="2" t="n"/>
+      <c r="E88" s="2" t="n"/>
+    </row>
+    <row r="89">
+      <c r="D89" s="2" t="n"/>
+      <c r="E89" s="2" t="n"/>
+    </row>
+    <row r="90">
+      <c r="D90" s="2" t="n"/>
+      <c r="E90" s="2" t="n"/>
+    </row>
+    <row r="91">
+      <c r="D91" s="2" t="n"/>
+      <c r="E91" s="2" t="n"/>
+    </row>
+    <row r="92">
+      <c r="D92" s="2" t="n"/>
+      <c r="E92" s="2" t="n"/>
+    </row>
+    <row r="93">
+      <c r="D93" s="2" t="n"/>
+      <c r="E93" s="2" t="n"/>
+    </row>
+    <row r="94">
+      <c r="D94" s="2" t="n"/>
+      <c r="E94" s="2" t="n"/>
+    </row>
+    <row r="95">
+      <c r="D95" s="2" t="n"/>
+      <c r="E95" s="2" t="n"/>
+    </row>
+    <row r="96">
+      <c r="D96" s="2" t="n"/>
+      <c r="E96" s="2" t="n"/>
+    </row>
+    <row r="97">
+      <c r="D97" s="2" t="n"/>
+      <c r="E97" s="2" t="n"/>
+    </row>
+    <row r="98">
+      <c r="D98" s="2" t="n"/>
+      <c r="E98" s="2" t="n"/>
+    </row>
+    <row r="99">
+      <c r="D99" s="2" t="n"/>
+      <c r="E99" s="2" t="n"/>
+    </row>
+    <row r="100">
+      <c r="D100" s="2" t="n"/>
+      <c r="E100" s="2" t="n"/>
+    </row>
+    <row r="101">
+      <c r="D101" s="2" t="n"/>
+      <c r="E101" s="2" t="n"/>
+    </row>
+    <row r="102">
+      <c r="D102" s="2" t="n"/>
+      <c r="E102" s="2" t="n"/>
+    </row>
+    <row r="103">
+      <c r="D103" s="2" t="n"/>
+      <c r="E103" s="2" t="n"/>
+    </row>
+    <row r="104">
+      <c r="D104" s="2" t="n"/>
+      <c r="E104" s="2" t="n"/>
+    </row>
+    <row r="105">
+      <c r="D105" s="2" t="n"/>
+      <c r="E105" s="2" t="n"/>
+    </row>
+    <row r="106">
+      <c r="D106" s="2" t="n"/>
+      <c r="E106" s="2" t="n"/>
+    </row>
+    <row r="107">
+      <c r="D107" s="2" t="n"/>
+      <c r="E107" s="2" t="n"/>
+    </row>
+    <row r="108">
+      <c r="D108" s="2" t="n"/>
+      <c r="E108" s="2" t="n"/>
+    </row>
+    <row r="109">
+      <c r="D109" s="2" t="n"/>
+      <c r="E109" s="2" t="n"/>
+    </row>
+    <row r="110">
+      <c r="D110" s="2" t="n"/>
+      <c r="E110" s="2" t="n"/>
+    </row>
+    <row r="111">
+      <c r="D111" s="2" t="n"/>
+      <c r="E111" s="2" t="n"/>
+    </row>
+    <row r="112">
+      <c r="D112" s="2" t="n"/>
+      <c r="E112" s="2" t="n"/>
+    </row>
+    <row r="113">
+      <c r="D113" s="2" t="n"/>
+      <c r="E113" s="2" t="n"/>
+    </row>
+    <row r="114">
+      <c r="D114" s="2" t="n"/>
+      <c r="E114" s="2" t="n"/>
+    </row>
+    <row r="115">
+      <c r="D115" s="2" t="n"/>
+      <c r="E115" s="2" t="n"/>
+    </row>
+    <row r="116">
+      <c r="D116" s="2" t="n"/>
+      <c r="E116" s="2" t="n"/>
+    </row>
+    <row r="117">
+      <c r="D117" s="2" t="n"/>
+      <c r="E117" s="2" t="n"/>
+    </row>
+    <row r="118">
+      <c r="D118" s="2" t="n"/>
+      <c r="E118" s="2" t="n"/>
+    </row>
+    <row r="119">
+      <c r="D119" s="2" t="n"/>
+      <c r="E119" s="2" t="n"/>
+    </row>
+    <row r="120">
+      <c r="D120" s="2" t="n"/>
+      <c r="E120" s="2" t="n"/>
+    </row>
+    <row r="121">
+      <c r="D121" s="2" t="n"/>
+      <c r="E121" s="2" t="n"/>
+    </row>
+    <row r="122">
+      <c r="D122" s="2" t="n"/>
+      <c r="E122" s="2" t="n"/>
+    </row>
+    <row r="123">
+      <c r="D123" s="2" t="n"/>
+      <c r="E123" s="2" t="n"/>
+    </row>
+    <row r="124">
+      <c r="D124" s="2" t="n"/>
+      <c r="E124" s="2" t="n"/>
+    </row>
+    <row r="125">
+      <c r="D125" s="2" t="n"/>
+      <c r="E125" s="2" t="n"/>
+    </row>
+    <row r="126">
+      <c r="D126" s="2" t="n"/>
+      <c r="E126" s="2" t="n"/>
+    </row>
+    <row r="127">
+      <c r="D127" s="2" t="n"/>
+      <c r="E127" s="2" t="n"/>
+    </row>
+    <row r="128">
+      <c r="D128" s="2" t="n"/>
+      <c r="E128" s="2" t="n"/>
+    </row>
+    <row r="129">
+      <c r="D129" s="2" t="n"/>
+      <c r="E129" s="2" t="n"/>
+    </row>
+    <row r="130">
+      <c r="D130" s="2" t="n"/>
+      <c r="E130" s="2" t="n"/>
+    </row>
+    <row r="131">
+      <c r="D131" s="2" t="n"/>
+      <c r="E131" s="2" t="n"/>
+    </row>
+    <row r="132">
+      <c r="D132" s="2" t="n"/>
+      <c r="E132" s="2" t="n"/>
+    </row>
+    <row r="133">
+      <c r="D133" s="2" t="n"/>
+      <c r="E133" s="2" t="n"/>
+    </row>
+    <row r="134">
+      <c r="D134" s="2" t="n"/>
+      <c r="E134" s="2" t="n"/>
+    </row>
+    <row r="135">
+      <c r="D135" s="2" t="n"/>
+      <c r="E135" s="2" t="n"/>
+    </row>
+    <row r="136">
+      <c r="D136" s="2" t="n"/>
+      <c r="E136" s="2" t="n"/>
+    </row>
+    <row r="137">
+      <c r="D137" s="2" t="n"/>
+      <c r="E137" s="2" t="n"/>
+    </row>
+    <row r="138">
+      <c r="D138" s="2" t="n"/>
+      <c r="E138" s="2" t="n"/>
+    </row>
+    <row r="139">
+      <c r="D139" s="2" t="n"/>
+      <c r="E139" s="2" t="n"/>
+    </row>
+    <row r="140">
+      <c r="D140" s="2" t="n"/>
+      <c r="E140" s="2" t="n"/>
+    </row>
+    <row r="141">
+      <c r="D141" s="2" t="n"/>
+      <c r="E141" s="2" t="n"/>
+    </row>
+    <row r="142">
+      <c r="D142" s="2" t="n"/>
+      <c r="E142" s="2" t="n"/>
+    </row>
+    <row r="143">
+      <c r="D143" s="2" t="n"/>
+      <c r="E143" s="2" t="n"/>
+    </row>
+    <row r="144">
+      <c r="D144" s="2" t="n"/>
+      <c r="E144" s="2" t="n"/>
+    </row>
+    <row r="145">
+      <c r="D145" s="2" t="n"/>
+      <c r="E145" s="2" t="n"/>
+    </row>
+    <row r="146">
+      <c r="D146" s="2" t="n"/>
+      <c r="E146" s="2" t="n"/>
+    </row>
+    <row r="147">
+      <c r="D147" s="2" t="n"/>
+      <c r="E147" s="2" t="n"/>
+    </row>
+    <row r="148">
+      <c r="D148" s="2" t="n"/>
+      <c r="E148" s="2" t="n"/>
+    </row>
+    <row r="149">
+      <c r="D149" s="2" t="n"/>
+      <c r="E149" s="2" t="n"/>
+    </row>
+    <row r="150">
+      <c r="D150" s="2" t="n"/>
+      <c r="E150" s="2" t="n"/>
+    </row>
+    <row r="151">
+      <c r="D151" s="2" t="n"/>
+      <c r="E151" s="2" t="n"/>
+    </row>
+    <row r="152">
+      <c r="D152" s="2" t="n"/>
+      <c r="E152" s="2" t="n"/>
+    </row>
+    <row r="153">
+      <c r="D153" s="2" t="n"/>
+      <c r="E153" s="2" t="n"/>
+    </row>
+    <row r="154">
+      <c r="D154" s="2" t="n"/>
+      <c r="E154" s="2" t="n"/>
+    </row>
+    <row r="155">
+      <c r="D155" s="2" t="n"/>
+      <c r="E155" s="2" t="n"/>
+    </row>
+    <row r="156">
+      <c r="D156" s="2" t="n"/>
+      <c r="E156" s="2" t="n"/>
+    </row>
+    <row r="157">
+      <c r="D157" s="2" t="n"/>
+      <c r="E157" s="2" t="n"/>
+    </row>
+    <row r="158">
+      <c r="D158" s="2" t="n"/>
+      <c r="E158" s="2" t="n"/>
+    </row>
+    <row r="159">
+      <c r="D159" s="2" t="n"/>
+      <c r="E159" s="2" t="n"/>
+    </row>
+    <row r="160">
+      <c r="D160" s="2" t="n"/>
+      <c r="E160" s="2" t="n"/>
+    </row>
+    <row r="161">
+      <c r="D161" s="2" t="n"/>
+      <c r="E161" s="2" t="n"/>
+    </row>
+    <row r="162">
+      <c r="D162" s="2" t="n"/>
+      <c r="E162" s="2" t="n"/>
+    </row>
+    <row r="163">
+      <c r="D163" s="2" t="n"/>
+      <c r="E163" s="2" t="n"/>
+    </row>
+    <row r="164">
+      <c r="D164" s="2" t="n"/>
+      <c r="E164" s="2" t="n"/>
+    </row>
+    <row r="165">
+      <c r="D165" s="2" t="n"/>
+      <c r="E165" s="2" t="n"/>
+    </row>
+    <row r="166">
+      <c r="D166" s="2" t="n"/>
+      <c r="E166" s="2" t="n"/>
+    </row>
+    <row r="167">
+      <c r="D167" s="2" t="n"/>
+      <c r="E167" s="2" t="n"/>
+    </row>
+    <row r="168">
+      <c r="D168" s="2" t="n"/>
+      <c r="E168" s="2" t="n"/>
+    </row>
+    <row r="169">
+      <c r="D169" s="2" t="n"/>
+      <c r="E169" s="2" t="n"/>
+    </row>
+    <row r="170">
+      <c r="D170" s="2" t="n"/>
+      <c r="E170" s="2" t="n"/>
+    </row>
+    <row r="171">
+      <c r="D171" s="2" t="n"/>
+      <c r="E171" s="2" t="n"/>
+    </row>
+    <row r="172">
+      <c r="D172" s="2" t="n"/>
+      <c r="E172" s="2" t="n"/>
+    </row>
+    <row r="173">
+      <c r="D173" s="2" t="n"/>
+      <c r="E173" s="2" t="n"/>
+    </row>
+    <row r="174">
+      <c r="D174" s="2" t="n"/>
+      <c r="E174" s="2" t="n"/>
+    </row>
+    <row r="175">
+      <c r="D175" s="2" t="n"/>
+      <c r="E175" s="2" t="n"/>
+    </row>
+    <row r="176">
+      <c r="D176" s="2" t="n"/>
+      <c r="E176" s="2" t="n"/>
+    </row>
+    <row r="177">
+      <c r="D177" s="2" t="n"/>
+      <c r="E177" s="2" t="n"/>
+    </row>
+    <row r="178">
+      <c r="D178" s="2" t="n"/>
+      <c r="E178" s="2" t="n"/>
+    </row>
+    <row r="179">
+      <c r="D179" s="2" t="n"/>
+      <c r="E179" s="2" t="n"/>
+    </row>
+    <row r="180">
+      <c r="D180" s="2" t="n"/>
+      <c r="E180" s="2" t="n"/>
+    </row>
+    <row r="181">
+      <c r="D181" s="2" t="n"/>
+      <c r="E181" s="2" t="n"/>
+    </row>
+    <row r="182">
+      <c r="D182" s="2" t="n"/>
+      <c r="E182" s="2" t="n"/>
+    </row>
+    <row r="183">
+      <c r="D183" s="2" t="n"/>
+      <c r="E183" s="2" t="n"/>
+    </row>
+    <row r="184">
+      <c r="D184" s="2" t="n"/>
+      <c r="E184" s="2" t="n"/>
+    </row>
+    <row r="185">
+      <c r="D185" s="2" t="n"/>
+      <c r="E185" s="2" t="n"/>
+    </row>
+    <row r="186">
+      <c r="D186" s="2" t="n"/>
+      <c r="E186" s="2" t="n"/>
+    </row>
+    <row r="187">
+      <c r="D187" s="2" t="n"/>
+      <c r="E187" s="2" t="n"/>
+    </row>
+    <row r="188">
+      <c r="D188" s="2" t="n"/>
+      <c r="E188" s="2" t="n"/>
+    </row>
+    <row r="189">
+      <c r="D189" s="2" t="n"/>
+      <c r="E189" s="2" t="n"/>
+    </row>
+    <row r="190">
+      <c r="D190" s="2" t="n"/>
+      <c r="E190" s="2" t="n"/>
+    </row>
+    <row r="191">
+      <c r="D191" s="2" t="n"/>
+      <c r="E191" s="2" t="n"/>
+    </row>
+    <row r="192">
+      <c r="D192" s="2" t="n"/>
+      <c r="E192" s="2" t="n"/>
+    </row>
+    <row r="193">
+      <c r="D193" s="2" t="n"/>
+      <c r="E193" s="2" t="n"/>
+    </row>
+    <row r="194">
+      <c r="D194" s="2" t="n"/>
+      <c r="E194" s="2" t="n"/>
+    </row>
+    <row r="195">
+      <c r="D195" s="2" t="n"/>
+      <c r="E195" s="2" t="n"/>
+    </row>
+    <row r="196">
+      <c r="D196" s="2" t="n"/>
+      <c r="E196" s="2" t="n"/>
+    </row>
+    <row r="197">
+      <c r="D197" s="2" t="n"/>
+      <c r="E197" s="2" t="n"/>
+    </row>
+    <row r="198">
+      <c r="D198" s="2" t="n"/>
+      <c r="E198" s="2" t="n"/>
+    </row>
+    <row r="199">
+      <c r="D199" s="2" t="n"/>
+      <c r="E199" s="2" t="n"/>
+    </row>
+    <row r="200">
+      <c r="D200" s="2" t="n"/>
+      <c r="E200" s="2" t="n"/>
+    </row>
+    <row r="201">
+      <c r="D201" s="2" t="n"/>
+      <c r="E201" s="2" t="n"/>
+    </row>
+    <row r="202">
+      <c r="D202" s="2" t="n"/>
+      <c r="E202" s="2" t="n"/>
+    </row>
+    <row r="203">
+      <c r="D203" s="2" t="n"/>
+      <c r="E203" s="2" t="n"/>
+    </row>
+    <row r="204">
+      <c r="D204" s="2" t="n"/>
+      <c r="E204" s="2" t="n"/>
+    </row>
+    <row r="205">
+      <c r="D205" s="2" t="n"/>
+      <c r="E205" s="2" t="n"/>
+    </row>
+    <row r="206">
+      <c r="D206" s="2" t="n"/>
+      <c r="E206" s="2" t="n"/>
+    </row>
+    <row r="207">
+      <c r="D207" s="2" t="n"/>
+      <c r="E207" s="2" t="n"/>
+    </row>
+    <row r="208">
+      <c r="D208" s="2" t="n"/>
+      <c r="E208" s="2" t="n"/>
+    </row>
+    <row r="209">
+      <c r="D209" s="2" t="n"/>
+      <c r="E209" s="2" t="n"/>
+    </row>
+    <row r="210">
+      <c r="D210" s="2" t="n"/>
+      <c r="E210" s="2" t="n"/>
+    </row>
+    <row r="211">
+      <c r="D211" s="2" t="n"/>
+      <c r="E211" s="2" t="n"/>
+    </row>
+    <row r="212">
+      <c r="D212" s="2" t="n"/>
+      <c r="E212" s="2" t="n"/>
+    </row>
+    <row r="213">
+      <c r="D213" s="2" t="n"/>
+      <c r="E213" s="2" t="n"/>
+    </row>
+    <row r="214">
+      <c r="D214" s="2" t="n"/>
+      <c r="E214" s="2" t="n"/>
+    </row>
+    <row r="215">
+      <c r="D215" s="2" t="n"/>
+      <c r="E215" s="2" t="n"/>
+    </row>
+    <row r="216">
+      <c r="D216" s="2" t="n"/>
+      <c r="E216" s="2" t="n"/>
+    </row>
+    <row r="217">
+      <c r="D217" s="2" t="n"/>
+      <c r="E217" s="2" t="n"/>
+    </row>
+    <row r="218">
+      <c r="D218" s="2" t="n"/>
+      <c r="E218" s="2" t="n"/>
+    </row>
+    <row r="219">
+      <c r="D219" s="2" t="n"/>
+      <c r="E219" s="2" t="n"/>
+    </row>
+    <row r="220">
+      <c r="D220" s="2" t="n"/>
+      <c r="E220" s="2" t="n"/>
+    </row>
+    <row r="221">
+      <c r="D221" s="2" t="n"/>
+      <c r="E221" s="2" t="n"/>
+    </row>
+    <row r="222">
+      <c r="D222" s="2" t="n"/>
+      <c r="E222" s="2" t="n"/>
+    </row>
+    <row r="223">
+      <c r="D223" s="2" t="n"/>
+      <c r="E223" s="2" t="n"/>
+    </row>
+    <row r="224">
+      <c r="D224" s="2" t="n"/>
+      <c r="E224" s="2" t="n"/>
+    </row>
+    <row r="225">
+      <c r="D225" s="2" t="n"/>
+      <c r="E225" s="2" t="n"/>
+    </row>
+    <row r="226">
+      <c r="D226" s="2" t="n"/>
+      <c r="E226" s="2" t="n"/>
+    </row>
+    <row r="227">
+      <c r="D227" s="2" t="n"/>
+      <c r="E227" s="2" t="n"/>
+    </row>
+    <row r="228">
+      <c r="D228" s="2" t="n"/>
+      <c r="E228" s="2" t="n"/>
+    </row>
+    <row r="229">
+      <c r="D229" s="2" t="n"/>
+      <c r="E229" s="2" t="n"/>
+    </row>
+    <row r="230">
+      <c r="D230" s="2" t="n"/>
+      <c r="E230" s="2" t="n"/>
+    </row>
+    <row r="231">
+      <c r="D231" s="2" t="n"/>
+      <c r="E231" s="2" t="n"/>
+    </row>
+    <row r="232">
+      <c r="D232" s="2" t="n"/>
+      <c r="E232" s="2" t="n"/>
+    </row>
+    <row r="233">
+      <c r="D233" s="2" t="n"/>
+      <c r="E233" s="2" t="n"/>
+    </row>
+    <row r="234">
+      <c r="D234" s="2" t="n"/>
+      <c r="E234" s="2" t="n"/>
+    </row>
+    <row r="235">
+      <c r="D235" s="2" t="n"/>
+      <c r="E235" s="2" t="n"/>
+    </row>
+    <row r="236">
+      <c r="D236" s="2" t="n"/>
+      <c r="E236" s="2" t="n"/>
+    </row>
+    <row r="237">
+      <c r="D237" s="2" t="n"/>
+      <c r="E237" s="2" t="n"/>
+    </row>
+    <row r="238">
+      <c r="D238" s="2" t="n"/>
+      <c r="E238" s="2" t="n"/>
+    </row>
+    <row r="239">
+      <c r="D239" s="2" t="n"/>
+      <c r="E239" s="2" t="n"/>
+    </row>
+    <row r="240">
+      <c r="D240" s="2" t="n"/>
+      <c r="E240" s="2" t="n"/>
+    </row>
+    <row r="241">
+      <c r="D241" s="2" t="n"/>
+      <c r="E241" s="2" t="n"/>
+    </row>
+    <row r="242">
+      <c r="D242" s="2" t="n"/>
+      <c r="E242" s="2" t="n"/>
+    </row>
+    <row r="243">
+      <c r="D243" s="2" t="n"/>
+      <c r="E243" s="2" t="n"/>
+    </row>
+    <row r="244">
+      <c r="D244" s="2" t="n"/>
+      <c r="E244" s="2" t="n"/>
+    </row>
+    <row r="245">
+      <c r="D245" s="2" t="n"/>
+      <c r="E245" s="2" t="n"/>
+    </row>
+    <row r="246">
+      <c r="D246" s="2" t="n"/>
+      <c r="E246" s="2" t="n"/>
+    </row>
+    <row r="247">
+      <c r="D247" s="2" t="n"/>
+      <c r="E247" s="2" t="n"/>
+    </row>
+    <row r="248">
+      <c r="D248" s="2" t="n"/>
+      <c r="E248" s="2" t="n"/>
+    </row>
+    <row r="249">
+      <c r="D249" s="2" t="n"/>
+      <c r="E249" s="2" t="n"/>
+    </row>
+    <row r="250">
+      <c r="D250" s="2" t="n"/>
+      <c r="E250" s="2" t="n"/>
+    </row>
+    <row r="251">
+      <c r="D251" s="2" t="n"/>
+      <c r="E251" s="2" t="n"/>
+    </row>
+    <row r="252">
+      <c r="D252" s="2" t="n"/>
+      <c r="E252" s="2" t="n"/>
+    </row>
+    <row r="253">
+      <c r="D253" s="2" t="n"/>
+      <c r="E253" s="2" t="n"/>
+    </row>
+    <row r="254">
+      <c r="D254" s="2" t="n"/>
+      <c r="E254" s="2" t="n"/>
+    </row>
+    <row r="255">
+      <c r="D255" s="2" t="n"/>
+      <c r="E255" s="2" t="n"/>
+    </row>
+    <row r="256">
+      <c r="D256" s="2" t="n"/>
+      <c r="E256" s="2" t="n"/>
+    </row>
+    <row r="257">
+      <c r="D257" s="2" t="n"/>
+      <c r="E257" s="2" t="n"/>
+    </row>
+    <row r="258">
+      <c r="D258" s="2" t="n"/>
+      <c r="E258" s="2" t="n"/>
+    </row>
+    <row r="259">
+      <c r="D259" s="2" t="n"/>
+      <c r="E259" s="2" t="n"/>
+    </row>
+    <row r="260">
+      <c r="D260" s="2" t="n"/>
+      <c r="E260" s="2" t="n"/>
+    </row>
+    <row r="261">
+      <c r="D261" s="2" t="n"/>
+      <c r="E261" s="2" t="n"/>
+    </row>
+    <row r="262">
+      <c r="D262" s="2" t="n"/>
+      <c r="E262" s="2" t="n"/>
+    </row>
+    <row r="263">
+      <c r="D263" s="2" t="n"/>
+      <c r="E263" s="2" t="n"/>
+    </row>
+    <row r="264">
+      <c r="D264" s="2" t="n"/>
+      <c r="E264" s="2" t="n"/>
+    </row>
+    <row r="265">
+      <c r="D265" s="2" t="n"/>
+      <c r="E265" s="2" t="n"/>
+    </row>
+    <row r="266">
+      <c r="D266" s="2" t="n"/>
+      <c r="E266" s="2" t="n"/>
+    </row>
+    <row r="267">
+      <c r="D267" s="2" t="n"/>
+      <c r="E267" s="2" t="n"/>
+    </row>
+    <row r="268">
+      <c r="D268" s="2" t="n"/>
+      <c r="E268" s="2" t="n"/>
+    </row>
+    <row r="269">
+      <c r="D269" s="2" t="n"/>
+      <c r="E269" s="2" t="n"/>
+    </row>
+    <row r="270">
+      <c r="D270" s="2" t="n"/>
+      <c r="E270" s="2" t="n"/>
+    </row>
+    <row r="271">
+      <c r="D271" s="2" t="n"/>
+      <c r="E271" s="2" t="n"/>
+    </row>
+    <row r="272">
+      <c r="D272" s="2" t="n"/>
+      <c r="E272" s="2" t="n"/>
+    </row>
+    <row r="273">
+      <c r="D273" s="2" t="n"/>
+      <c r="E273" s="2" t="n"/>
+    </row>
+    <row r="274">
+      <c r="D274" s="2" t="n"/>
+      <c r="E274" s="2" t="n"/>
+    </row>
+    <row r="275">
+      <c r="D275" s="2" t="n"/>
+      <c r="E275" s="2" t="n"/>
+    </row>
+    <row r="276">
+      <c r="D276" s="2" t="n"/>
+      <c r="E276" s="2" t="n"/>
+    </row>
+    <row r="277">
+      <c r="D277" s="2" t="n"/>
+      <c r="E277" s="2" t="n"/>
+    </row>
+    <row r="278">
+      <c r="D278" s="2" t="n"/>
+      <c r="E278" s="2" t="n"/>
+    </row>
+    <row r="279">
+      <c r="D279" s="2" t="n"/>
+      <c r="E279" s="2" t="n"/>
+    </row>
+    <row r="280">
+      <c r="D280" s="2" t="n"/>
+      <c r="E280" s="2" t="n"/>
+    </row>
+    <row r="281">
+      <c r="D281" s="2" t="n"/>
+      <c r="E281" s="2" t="n"/>
+    </row>
+    <row r="282">
+      <c r="D282" s="2" t="n"/>
+      <c r="E282" s="2" t="n"/>
+    </row>
+    <row r="283">
+      <c r="D283" s="2" t="n"/>
+      <c r="E283" s="2" t="n"/>
+    </row>
+    <row r="284">
+      <c r="D284" s="2" t="n"/>
+      <c r="E284" s="2" t="n"/>
+    </row>
+    <row r="285">
+      <c r="D285" s="2" t="n"/>
+      <c r="E285" s="2" t="n"/>
+    </row>
+    <row r="286">
+      <c r="D286" s="2" t="n"/>
+      <c r="E286" s="2" t="n"/>
+    </row>
+    <row r="287">
+      <c r="D287" s="2" t="n"/>
+      <c r="E287" s="2" t="n"/>
+    </row>
+    <row r="288">
+      <c r="D288" s="2" t="n"/>
+      <c r="E288" s="2" t="n"/>
+    </row>
+    <row r="289">
+      <c r="D289" s="2" t="n"/>
+      <c r="E289" s="2" t="n"/>
+    </row>
+    <row r="290">
+      <c r="D290" s="2" t="n"/>
+      <c r="E290" s="2" t="n"/>
+    </row>
+    <row r="291">
+      <c r="D291" s="2" t="n"/>
+      <c r="E291" s="2" t="n"/>
+    </row>
+    <row r="292">
+      <c r="D292" s="2" t="n"/>
+      <c r="E292" s="2" t="n"/>
+    </row>
+    <row r="293">
+      <c r="D293" s="2" t="n"/>
+      <c r="E293" s="2" t="n"/>
+    </row>
+    <row r="294">
+      <c r="D294" s="2" t="n"/>
+      <c r="E294" s="2" t="n"/>
+    </row>
+    <row r="295">
+      <c r="D295" s="2" t="n"/>
+      <c r="E295" s="2" t="n"/>
+    </row>
+    <row r="296">
+      <c r="D296" s="2" t="n"/>
+      <c r="E296" s="2" t="n"/>
+    </row>
+    <row r="297">
+      <c r="D297" s="2" t="n"/>
+      <c r="E297" s="2" t="n"/>
+    </row>
+    <row r="298">
+      <c r="D298" s="2" t="n"/>
+      <c r="E298" s="2" t="n"/>
+    </row>
+    <row r="299">
+      <c r="D299" s="2" t="n"/>
+      <c r="E299" s="2" t="n"/>
+    </row>
+    <row r="300">
+      <c r="D300" s="2" t="n"/>
+      <c r="E300" s="2" t="n"/>
+    </row>
+    <row r="301">
+      <c r="D301" s="2" t="n"/>
+      <c r="E301" s="2" t="n"/>
+    </row>
+    <row r="302">
+      <c r="D302" s="2" t="n"/>
+      <c r="E302" s="2" t="n"/>
+    </row>
+    <row r="303">
+      <c r="D303" s="2" t="n"/>
+      <c r="E303" s="2" t="n"/>
+    </row>
+    <row r="304">
+      <c r="D304" s="2" t="n"/>
+      <c r="E304" s="2" t="n"/>
+    </row>
+    <row r="305">
+      <c r="D305" s="2" t="n"/>
+      <c r="E305" s="2" t="n"/>
+    </row>
+    <row r="306">
+      <c r="D306" s="2" t="n"/>
+      <c r="E306" s="2" t="n"/>
+    </row>
+    <row r="307">
+      <c r="D307" s="2" t="n"/>
+      <c r="E307" s="2" t="n"/>
+    </row>
+    <row r="308">
+      <c r="D308" s="2" t="n"/>
+      <c r="E308" s="2" t="n"/>
+    </row>
+    <row r="309">
+      <c r="D309" s="2" t="n"/>
+      <c r="E309" s="2" t="n"/>
+    </row>
+    <row r="310">
+      <c r="D310" s="2" t="n"/>
+      <c r="E310" s="2" t="n"/>
+    </row>
+    <row r="311">
+      <c r="D311" s="2" t="n"/>
+      <c r="E311" s="2" t="n"/>
+    </row>
+    <row r="312">
+      <c r="D312" s="2" t="n"/>
+      <c r="E312" s="2" t="n"/>
+    </row>
+    <row r="313">
+      <c r="D313" s="2" t="n"/>
+      <c r="E313" s="2" t="n"/>
+    </row>
+    <row r="314">
+      <c r="D314" s="2" t="n"/>
+      <c r="E314" s="2" t="n"/>
+    </row>
+    <row r="315">
+      <c r="D315" s="2" t="n"/>
+      <c r="E315" s="2" t="n"/>
+    </row>
+    <row r="316">
+      <c r="D316" s="2" t="n"/>
+      <c r="E316" s="2" t="n"/>
+    </row>
+    <row r="317">
+      <c r="D317" s="2" t="n"/>
+      <c r="E317" s="2" t="n"/>
+    </row>
+    <row r="318">
+      <c r="D318" s="2" t="n"/>
+      <c r="E318" s="2" t="n"/>
+    </row>
+    <row r="319">
+      <c r="D319" s="2" t="n"/>
+      <c r="E319" s="2" t="n"/>
+    </row>
+    <row r="320">
+      <c r="D320" s="2" t="n"/>
+      <c r="E320" s="2" t="n"/>
+    </row>
+    <row r="321">
+      <c r="D321" s="2" t="n"/>
+      <c r="E321" s="2" t="n"/>
+    </row>
+    <row r="322">
+      <c r="D322" s="2" t="n"/>
+      <c r="E322" s="2" t="n"/>
+    </row>
+    <row r="323">
+      <c r="D323" s="2" t="n"/>
+      <c r="E323" s="2" t="n"/>
+    </row>
+    <row r="324">
+      <c r="D324" s="2" t="n"/>
+      <c r="E324" s="2" t="n"/>
+    </row>
+    <row r="325">
+      <c r="D325" s="2" t="n"/>
+      <c r="E325" s="2" t="n"/>
+    </row>
+    <row r="326">
+      <c r="D326" s="2" t="n"/>
+      <c r="E326" s="2" t="n"/>
+    </row>
+    <row r="327">
+      <c r="D327" s="2" t="n"/>
+      <c r="E327" s="2" t="n"/>
+    </row>
+    <row r="328">
+      <c r="D328" s="2" t="n"/>
+      <c r="E328" s="2" t="n"/>
+    </row>
+    <row r="329">
+      <c r="D329" s="2" t="n"/>
+      <c r="E329" s="2" t="n"/>
+    </row>
+    <row r="330">
+      <c r="D330" s="2" t="n"/>
+      <c r="E330" s="2" t="n"/>
+    </row>
+    <row r="331">
+      <c r="D331" s="2" t="n"/>
+      <c r="E331" s="2" t="n"/>
+    </row>
+    <row r="332">
+      <c r="D332" s="2" t="n"/>
+      <c r="E332" s="2" t="n"/>
+    </row>
+    <row r="333">
+      <c r="D333" s="2" t="n"/>
+      <c r="E333" s="2" t="n"/>
+    </row>
+    <row r="334">
+      <c r="D334" s="2" t="n"/>
+      <c r="E334" s="2" t="n"/>
+    </row>
+    <row r="335">
+      <c r="D335" s="2" t="n"/>
+      <c r="E335" s="2" t="n"/>
+    </row>
+    <row r="336">
+      <c r="D336" s="2" t="n"/>
+      <c r="E336" s="2" t="n"/>
+    </row>
+    <row r="337">
+      <c r="D337" s="2" t="n"/>
+      <c r="E337" s="2" t="n"/>
+    </row>
+    <row r="338">
+      <c r="D338" s="2" t="n"/>
+      <c r="E338" s="2" t="n"/>
+    </row>
+    <row r="339">
+      <c r="D339" s="2" t="n"/>
+      <c r="E339" s="2" t="n"/>
+    </row>
+    <row r="340">
+      <c r="D340" s="2" t="n"/>
+      <c r="E340" s="2" t="n"/>
+    </row>
+    <row r="341">
+      <c r="D341" s="2" t="n"/>
+      <c r="E341" s="2" t="n"/>
+    </row>
+    <row r="342">
+      <c r="D342" s="2" t="n"/>
+      <c r="E342" s="2" t="n"/>
+    </row>
+    <row r="343">
+      <c r="D343" s="2" t="n"/>
+      <c r="E343" s="2" t="n"/>
+    </row>
+    <row r="344">
+      <c r="D344" s="2" t="n"/>
+      <c r="E344" s="2" t="n"/>
+    </row>
+    <row r="345">
+      <c r="D345" s="2" t="n"/>
+      <c r="E345" s="2" t="n"/>
+    </row>
+    <row r="346">
+      <c r="D346" s="2" t="n"/>
+      <c r="E346" s="2" t="n"/>
+    </row>
+    <row r="347">
+      <c r="D347" s="2" t="n"/>
+      <c r="E347" s="2" t="n"/>
+    </row>
+    <row r="348">
+      <c r="D348" s="2" t="n"/>
+      <c r="E348" s="2" t="n"/>
+    </row>
+    <row r="349">
+      <c r="D349" s="2" t="n"/>
+      <c r="E349" s="2" t="n"/>
+    </row>
+    <row r="350">
+      <c r="D350" s="2" t="n"/>
+      <c r="E350" s="2" t="n"/>
+    </row>
+    <row r="351">
+      <c r="D351" s="2" t="n"/>
+      <c r="E351" s="2" t="n"/>
+    </row>
+    <row r="352">
+      <c r="D352" s="2" t="n"/>
+      <c r="E352" s="2" t="n"/>
+    </row>
+    <row r="353">
+      <c r="D353" s="2" t="n"/>
+      <c r="E353" s="2" t="n"/>
+    </row>
+    <row r="354">
+      <c r="D354" s="2" t="n"/>
+      <c r="E354" s="2" t="n"/>
+    </row>
+    <row r="355">
+      <c r="D355" s="2" t="n"/>
+      <c r="E355" s="2" t="n"/>
+    </row>
+    <row r="356">
+      <c r="D356" s="2" t="n"/>
+      <c r="E356" s="2" t="n"/>
+    </row>
+    <row r="357">
+      <c r="D357" s="2" t="n"/>
+      <c r="E357" s="2" t="n"/>
+    </row>
+    <row r="358">
+      <c r="D358" s="2" t="n"/>
+      <c r="E358" s="2" t="n"/>
+    </row>
+    <row r="359">
+      <c r="D359" s="2" t="n"/>
+      <c r="E359" s="2" t="n"/>
+    </row>
+    <row r="360">
+      <c r="D360" s="2" t="n"/>
+      <c r="E360" s="2" t="n"/>
+    </row>
+    <row r="361">
+      <c r="D361" s="2" t="n"/>
+      <c r="E361" s="2" t="n"/>
+    </row>
+    <row r="362">
+      <c r="D362" s="2" t="n"/>
+      <c r="E362" s="2" t="n"/>
+    </row>
+    <row r="363">
+      <c r="D363" s="2" t="n"/>
+      <c r="E363" s="2" t="n"/>
+    </row>
+    <row r="364">
+      <c r="D364" s="2" t="n"/>
+      <c r="E364" s="2" t="n"/>
+    </row>
+    <row r="365">
+      <c r="D365" s="2" t="n"/>
+      <c r="E365" s="2" t="n"/>
+    </row>
+    <row r="366">
+      <c r="D366" s="2" t="n"/>
+      <c r="E366" s="2" t="n"/>
+    </row>
+    <row r="367">
+      <c r="D367" s="2" t="n"/>
+      <c r="E367" s="2" t="n"/>
+    </row>
+    <row r="368">
+      <c r="D368" s="2" t="n"/>
+      <c r="E368" s="2" t="n"/>
+    </row>
+    <row r="369">
+      <c r="D369" s="2" t="n"/>
+      <c r="E369" s="2" t="n"/>
+    </row>
+    <row r="370">
+      <c r="D370" s="2" t="n"/>
+      <c r="E370" s="2" t="n"/>
+    </row>
+    <row r="371">
+      <c r="D371" s="2" t="n"/>
+      <c r="E371" s="2" t="n"/>
+    </row>
+    <row r="372">
+      <c r="D372" s="2" t="n"/>
+      <c r="E372" s="2" t="n"/>
+    </row>
+    <row r="373">
+      <c r="D373" s="2" t="n"/>
+      <c r="E373" s="2" t="n"/>
+    </row>
+    <row r="374">
+      <c r="D374" s="2" t="n"/>
+      <c r="E374" s="2" t="n"/>
+    </row>
+    <row r="375">
+      <c r="D375" s="2" t="n"/>
+      <c r="E375" s="2" t="n"/>
+    </row>
+    <row r="376">
+      <c r="D376" s="2" t="n"/>
+      <c r="E376" s="2" t="n"/>
+    </row>
+    <row r="377">
+      <c r="D377" s="2" t="n"/>
+      <c r="E377" s="2" t="n"/>
+    </row>
+    <row r="378">
+      <c r="D378" s="2" t="n"/>
+      <c r="E378" s="2" t="n"/>
+    </row>
+    <row r="379">
+      <c r="D379" s="2" t="n"/>
+      <c r="E379" s="2" t="n"/>
+    </row>
+    <row r="380">
+      <c r="D380" s="2" t="n"/>
+      <c r="E380" s="2" t="n"/>
+    </row>
+    <row r="381">
+      <c r="D381" s="2" t="n"/>
+      <c r="E381" s="2" t="n"/>
+    </row>
+    <row r="382">
+      <c r="D382" s="2" t="n"/>
+      <c r="E382" s="2" t="n"/>
+    </row>
+    <row r="383">
+      <c r="D383" s="2" t="n"/>
+      <c r="E383" s="2" t="n"/>
+    </row>
+    <row r="384">
+      <c r="D384" s="2" t="n"/>
+      <c r="E384" s="2" t="n"/>
+    </row>
+    <row r="385">
+      <c r="D385" s="2" t="n"/>
+      <c r="E385" s="2" t="n"/>
+    </row>
+    <row r="386">
+      <c r="D386" s="2" t="n"/>
+      <c r="E386" s="2" t="n"/>
+    </row>
+    <row r="387">
+      <c r="D387" s="2" t="n"/>
+      <c r="E387" s="2" t="n"/>
+    </row>
+    <row r="388">
+      <c r="D388" s="2" t="n"/>
+      <c r="E388" s="2" t="n"/>
+    </row>
+    <row r="389">
+      <c r="D389" s="2" t="n"/>
+      <c r="E389" s="2" t="n"/>
+    </row>
+    <row r="390">
+      <c r="D390" s="2" t="n"/>
+      <c r="E390" s="2" t="n"/>
+    </row>
+    <row r="391">
+      <c r="D391" s="2" t="n"/>
+      <c r="E391" s="2" t="n"/>
+    </row>
+    <row r="392">
+      <c r="D392" s="2" t="n"/>
+      <c r="E392" s="2" t="n"/>
+    </row>
+    <row r="393">
+      <c r="D393" s="2" t="n"/>
+      <c r="E393" s="2" t="n"/>
+    </row>
+    <row r="394">
+      <c r="D394" s="2" t="n"/>
+      <c r="E394" s="2" t="n"/>
+    </row>
+    <row r="395">
+      <c r="D395" s="2" t="n"/>
+      <c r="E395" s="2" t="n"/>
+    </row>
+    <row r="396">
+      <c r="D396" s="2" t="n"/>
+      <c r="E396" s="2" t="n"/>
+    </row>
+    <row r="397">
+      <c r="D397" s="2" t="n"/>
+      <c r="E397" s="2" t="n"/>
+    </row>
+    <row r="398">
+      <c r="D398" s="2" t="n"/>
+      <c r="E398" s="2" t="n"/>
+    </row>
+    <row r="399">
+      <c r="D399" s="2" t="n"/>
+      <c r="E399" s="2" t="n"/>
+    </row>
+    <row r="400">
+      <c r="D400" s="2" t="n"/>
+      <c r="E400" s="2" t="n"/>
+    </row>
+    <row r="401">
+      <c r="D401" s="2" t="n"/>
+      <c r="E401" s="2" t="n"/>
+    </row>
+    <row r="402">
+      <c r="D402" s="2" t="n"/>
+      <c r="E402" s="2" t="n"/>
+    </row>
+    <row r="403">
+      <c r="D403" s="2" t="n"/>
+      <c r="E403" s="2" t="n"/>
+    </row>
+    <row r="404">
+      <c r="D404" s="2" t="n"/>
+      <c r="E404" s="2" t="n"/>
+    </row>
+    <row r="405">
+      <c r="D405" s="2" t="n"/>
+      <c r="E405" s="2" t="n"/>
+    </row>
+    <row r="406">
+      <c r="D406" s="2" t="n"/>
+      <c r="E406" s="2" t="n"/>
+    </row>
+    <row r="407">
+      <c r="D407" s="2" t="n"/>
+      <c r="E407" s="2" t="n"/>
+    </row>
+    <row r="408">
+      <c r="D408" s="2" t="n"/>
+      <c r="E408" s="2" t="n"/>
+    </row>
+    <row r="409">
+      <c r="D409" s="2" t="n"/>
+      <c r="E409" s="2" t="n"/>
+    </row>
+    <row r="410">
+      <c r="D410" s="2" t="n"/>
+      <c r="E410" s="2" t="n"/>
+    </row>
+    <row r="411">
+      <c r="D411" s="2" t="n"/>
+      <c r="E411" s="2" t="n"/>
+    </row>
+    <row r="412">
+      <c r="D412" s="2" t="n"/>
+      <c r="E412" s="2" t="n"/>
+    </row>
+    <row r="413">
+      <c r="D413" s="2" t="n"/>
+      <c r="E413" s="2" t="n"/>
+    </row>
+    <row r="414">
+      <c r="D414" s="2" t="n"/>
+      <c r="E414" s="2" t="n"/>
+    </row>
+    <row r="415">
+      <c r="D415" s="2" t="n"/>
+      <c r="E415" s="2" t="n"/>
+    </row>
+    <row r="416">
+      <c r="D416" s="2" t="n"/>
+      <c r="E416" s="2" t="n"/>
+    </row>
+    <row r="417">
+      <c r="D417" s="2" t="n"/>
+      <c r="E417" s="2" t="n"/>
+    </row>
+    <row r="418">
+      <c r="D418" s="2" t="n"/>
+      <c r="E418" s="2" t="n"/>
+    </row>
+    <row r="419">
+      <c r="D419" s="2" t="n"/>
+      <c r="E419" s="2" t="n"/>
+    </row>
+    <row r="420">
+      <c r="D420" s="2" t="n"/>
+      <c r="E420" s="2" t="n"/>
+    </row>
+    <row r="421">
+      <c r="D421" s="2" t="n"/>
+      <c r="E421" s="2" t="n"/>
+    </row>
+    <row r="422">
+      <c r="D422" s="2" t="n"/>
+      <c r="E422" s="2" t="n"/>
+    </row>
+    <row r="423">
+      <c r="D423" s="2" t="n"/>
+      <c r="E423" s="2" t="n"/>
+    </row>
+    <row r="424">
+      <c r="D424" s="2" t="n"/>
+      <c r="E424" s="2" t="n"/>
+    </row>
+    <row r="425">
+      <c r="D425" s="2" t="n"/>
+      <c r="E425" s="2" t="n"/>
+    </row>
+    <row r="426">
+      <c r="D426" s="2" t="n"/>
+      <c r="E426" s="2" t="n"/>
+    </row>
+    <row r="427">
+      <c r="D427" s="2" t="n"/>
+      <c r="E427" s="2" t="n"/>
+    </row>
+    <row r="428">
+      <c r="D428" s="2" t="n"/>
+      <c r="E428" s="2" t="n"/>
+    </row>
+    <row r="429">
+      <c r="D429" s="2" t="n"/>
+      <c r="E429" s="2" t="n"/>
+    </row>
+    <row r="430">
+      <c r="D430" s="2" t="n"/>
+      <c r="E430" s="2" t="n"/>
+    </row>
+    <row r="431">
+      <c r="D431" s="2" t="n"/>
+      <c r="E431" s="2" t="n"/>
+    </row>
+    <row r="432">
+      <c r="D432" s="2" t="n"/>
+      <c r="E432" s="2" t="n"/>
+    </row>
+    <row r="433">
+      <c r="D433" s="2" t="n"/>
+      <c r="E433" s="2" t="n"/>
+    </row>
+    <row r="434">
+      <c r="D434" s="2" t="n"/>
+      <c r="E434" s="2" t="n"/>
+    </row>
+    <row r="435">
+      <c r="D435" s="2" t="n"/>
+      <c r="E435" s="2" t="n"/>
+    </row>
+    <row r="436">
+      <c r="D436" s="2" t="n"/>
+      <c r="E436" s="2" t="n"/>
+    </row>
+    <row r="437">
+      <c r="D437" s="2" t="n"/>
+      <c r="E437" s="2" t="n"/>
+    </row>
+    <row r="438">
+      <c r="D438" s="2" t="n"/>
+      <c r="E438" s="2" t="n"/>
+    </row>
+    <row r="439">
+      <c r="D439" s="2" t="n"/>
+      <c r="E439" s="2" t="n"/>
+    </row>
+    <row r="440">
+      <c r="D440" s="2" t="n"/>
+      <c r="E440" s="2" t="n"/>
+    </row>
+    <row r="441">
+      <c r="D441" s="2" t="n"/>
+      <c r="E441" s="2" t="n"/>
+    </row>
+    <row r="442">
+      <c r="D442" s="2" t="n"/>
+      <c r="E442" s="2" t="n"/>
+    </row>
+    <row r="443">
+      <c r="D443" s="2" t="n"/>
+      <c r="E443" s="2" t="n"/>
+    </row>
+    <row r="444">
+      <c r="D444" s="2" t="n"/>
+      <c r="E444" s="2" t="n"/>
+    </row>
+    <row r="445">
+      <c r="D445" s="2" t="n"/>
+      <c r="E445" s="2" t="n"/>
+    </row>
+    <row r="446">
+      <c r="D446" s="2" t="n"/>
+      <c r="E446" s="2" t="n"/>
+    </row>
+    <row r="447">
+      <c r="D447" s="2" t="n"/>
+      <c r="E447" s="2" t="n"/>
+    </row>
+    <row r="448">
+      <c r="D448" s="2" t="n"/>
+      <c r="E448" s="2" t="n"/>
+    </row>
+    <row r="449">
+      <c r="D449" s="2" t="n"/>
+      <c r="E449" s="2" t="n"/>
+    </row>
+    <row r="450">
+      <c r="D450" s="2" t="n"/>
+      <c r="E450" s="2" t="n"/>
+    </row>
+    <row r="451">
+      <c r="D451" s="2" t="n"/>
+      <c r="E451" s="2" t="n"/>
+    </row>
+    <row r="452">
+      <c r="D452" s="2" t="n"/>
+      <c r="E452" s="2" t="n"/>
+    </row>
+    <row r="453">
+      <c r="D453" s="2" t="n"/>
+      <c r="E453" s="2" t="n"/>
+    </row>
+    <row r="454">
+      <c r="D454" s="2" t="n"/>
+      <c r="E454" s="2" t="n"/>
+    </row>
+    <row r="455">
+      <c r="D455" s="2" t="n"/>
+      <c r="E455" s="2" t="n"/>
+    </row>
+    <row r="456">
+      <c r="D456" s="2" t="n"/>
+      <c r="E456" s="2" t="n"/>
+    </row>
+    <row r="457">
+      <c r="D457" s="2" t="n"/>
+      <c r="E457" s="2" t="n"/>
+    </row>
+    <row r="458">
+      <c r="D458" s="2" t="n"/>
+      <c r="E458" s="2" t="n"/>
+    </row>
+    <row r="459">
+      <c r="D459" s="2" t="n"/>
+      <c r="E459" s="2" t="n"/>
+    </row>
+    <row r="460">
+      <c r="D460" s="2" t="n"/>
+      <c r="E460" s="2" t="n"/>
+    </row>
+    <row r="461">
+      <c r="D461" s="2" t="n"/>
+      <c r="E461" s="2" t="n"/>
+    </row>
+    <row r="462">
+      <c r="D462" s="2" t="n"/>
+      <c r="E462" s="2" t="n"/>
+    </row>
+    <row r="463">
+      <c r="D463" s="2" t="n"/>
+      <c r="E463" s="2" t="n"/>
+    </row>
+    <row r="464">
+      <c r="D464" s="2" t="n"/>
+      <c r="E464" s="2" t="n"/>
+    </row>
+    <row r="465">
+      <c r="D465" s="2" t="n"/>
+      <c r="E465" s="2" t="n"/>
+    </row>
+    <row r="466">
+      <c r="D466" s="2" t="n"/>
+      <c r="E466" s="2" t="n"/>
+    </row>
+    <row r="467">
+      <c r="D467" s="2" t="n"/>
+      <c r="E467" s="2" t="n"/>
+    </row>
+    <row r="468">
+      <c r="D468" s="2" t="n"/>
+      <c r="E468" s="2" t="n"/>
+    </row>
+    <row r="469">
+      <c r="D469" s="2" t="n"/>
+      <c r="E469" s="2" t="n"/>
+    </row>
+    <row r="470">
+      <c r="D470" s="2" t="n"/>
+      <c r="E470" s="2" t="n"/>
+    </row>
+    <row r="471">
+      <c r="D471" s="2" t="n"/>
+      <c r="E471" s="2" t="n"/>
+    </row>
+    <row r="472">
+      <c r="D472" s="2" t="n"/>
+      <c r="E472" s="2" t="n"/>
+    </row>
+    <row r="473">
+      <c r="D473" s="2" t="n"/>
+      <c r="E473" s="2" t="n"/>
+    </row>
+    <row r="474">
+      <c r="D474" s="2" t="n"/>
+      <c r="E474" s="2" t="n"/>
+    </row>
+    <row r="475">
+      <c r="D475" s="2" t="n"/>
+      <c r="E475" s="2" t="n"/>
+    </row>
+    <row r="476">
+      <c r="D476" s="2" t="n"/>
+      <c r="E476" s="2" t="n"/>
+    </row>
+    <row r="477">
+      <c r="D477" s="2" t="n"/>
+      <c r="E477" s="2" t="n"/>
+    </row>
+    <row r="478">
+      <c r="D478" s="2" t="n"/>
+      <c r="E478" s="2" t="n"/>
+    </row>
+    <row r="479">
+      <c r="D479" s="2" t="n"/>
+      <c r="E479" s="2" t="n"/>
+    </row>
+    <row r="480">
+      <c r="D480" s="2" t="n"/>
+      <c r="E480" s="2" t="n"/>
+    </row>
+    <row r="481">
+      <c r="D481" s="2" t="n"/>
+      <c r="E481" s="2" t="n"/>
+    </row>
+    <row r="482">
+      <c r="D482" s="2" t="n"/>
+      <c r="E482" s="2" t="n"/>
+    </row>
+    <row r="483">
+      <c r="D483" s="2" t="n"/>
+      <c r="E483" s="2" t="n"/>
+    </row>
+    <row r="484">
+      <c r="D484" s="2" t="n"/>
+      <c r="E484" s="2" t="n"/>
+    </row>
+    <row r="485">
+      <c r="D485" s="2" t="n"/>
+      <c r="E485" s="2" t="n"/>
+    </row>
+    <row r="486">
+      <c r="D486" s="2" t="n"/>
+      <c r="E486" s="2" t="n"/>
+    </row>
+    <row r="487">
+      <c r="D487" s="2" t="n"/>
+      <c r="E487" s="2" t="n"/>
+    </row>
+    <row r="488">
+      <c r="D488" s="2" t="n"/>
+      <c r="E488" s="2" t="n"/>
+    </row>
+    <row r="489">
+      <c r="D489" s="2" t="n"/>
+      <c r="E489" s="2" t="n"/>
+    </row>
+    <row r="490">
+      <c r="D490" s="2" t="n"/>
+      <c r="E490" s="2" t="n"/>
+    </row>
+    <row r="491">
+      <c r="D491" s="2" t="n"/>
+      <c r="E491" s="2" t="n"/>
+    </row>
+    <row r="492">
+      <c r="D492" s="2" t="n"/>
+      <c r="E492" s="2" t="n"/>
+    </row>
+    <row r="493">
+      <c r="D493" s="2" t="n"/>
+      <c r="E493" s="2" t="n"/>
+    </row>
+    <row r="494">
+      <c r="D494" s="2" t="n"/>
+      <c r="E494" s="2" t="n"/>
+    </row>
+    <row r="495">
+      <c r="D495" s="2" t="n"/>
+      <c r="E495" s="2" t="n"/>
+    </row>
+    <row r="496">
+      <c r="D496" s="2" t="n"/>
+      <c r="E496" s="2" t="n"/>
+    </row>
+    <row r="497">
+      <c r="D497" s="2" t="n"/>
+      <c r="E497" s="2" t="n"/>
+    </row>
+    <row r="498">
+      <c r="D498" s="2" t="n"/>
+      <c r="E498" s="2" t="n"/>
+    </row>
+    <row r="499">
+      <c r="D499" s="2" t="n"/>
+      <c r="E499" s="2" t="n"/>
+    </row>
+    <row r="500">
+      <c r="D500" s="2" t="n"/>
+      <c r="E500" s="2" t="n"/>
+    </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="B2:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Ungültiger Wert" error="Bitte einen Wert aus der Liste wählen." promptTitle="Art" prompt="Art des Termins wählen." type="list">
+      <formula1>"Kalibrierung,Wartung,Ausfall,Audit,Info"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Ungültiger Wert" error="Bitte einen Wert aus der Liste wählen." promptTitle="Prüfstand" prompt="Prüfstand aus dem Blatt „Prüfstände“ wählen." type="list">
+      <formula1>=Pruefstaende</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Ungültiger Wert" error="Bitte einen Wert aus der Liste wählen." promptTitle="Status" prompt="offen / abgeschlossen / storniert." type="list">
+      <formula1>"offen,abgeschlossen,storniert"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1308,220 +7173,249 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B34"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="110" customWidth="1" min="2" max="2"/>
+    <col width="96" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="13" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Terminübersicht – so wird sie ausgefüllt</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="B2" s="14" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Blatt „Termine“ – hier wird alles eingetragen</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>A  Nr        – fortlaufende Nummer, wird für das Blatt „Zeiten“ gebraucht</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>B  Art       – Auswahl: Kalibrierung / Wartung / Ausfall / Audit / Info</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>C  Prüfstand – Auswahl aus der Liste (Blatt „Prüfstände“)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>D  Von       – Datum und Uhrzeit, z. B. 16.11.2026 08:00</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>E  Bis       – Datum und Uhrzeit, bei „Info“ darf das Feld leer bleiben</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>F  Info      – kurze Beschreibung</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>G  Status    – offen / abgeschlossen / storniert</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" s="14" t="inlineStr"/>
-    </row>
+    <row r="11"/>
     <row r="12">
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Die Spalten Art, Prüfstand, Status und Termin-Nr haben ein Drop-Down:</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>in die Zelle klicken, dann rechts am Zellrand auf den Pfeil klicken.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>So kann kein Tippfehler und kein unbekannter Prüfstand entstehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Wann ist das Blatt „Zeiten“ nötig?</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="14" t="inlineStr">
+    <row r="17">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Nur wenn der Prüfstand NICHT durchgehend außer Betrieb ist.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="14" t="inlineStr">
+    <row r="18">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Beispiel: Kalibrierung von Montag bis Samstag, aber täglich nur 4–8 Stunden,</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="14" t="inlineStr">
+    <row r="19">
+      <c r="B19" t="inlineStr">
         <is>
           <t>und zwischendurch zwei Tage gar nicht.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="14" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="B17" s="14" t="inlineStr">
+    <row r="20"/>
+    <row r="21">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Dann für jeden Zeitraum, in dem wirklich gearbeitet wurde, eine Zeile:</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="14" t="inlineStr">
+    <row r="22">
+      <c r="B22" t="inlineStr">
         <is>
           <t xml:space="preserve">   Termin-Nr | Von | Bis | Notiz</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="14" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="14" t="inlineStr">
+    <row r="23"/>
+    <row r="24">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Kein Eintrag im Blatt „Zeiten“ = Prüfstand war durchgehend außer Betrieb.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="14" t="inlineStr">
+    <row r="25">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Bei Wartung und Ausfall ist das der Normalfall – das Blatt bleibt dann leer.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="14" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="15" t="inlineStr">
+    <row r="26"/>
+    <row r="27">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="14" t="inlineStr">
+    <row r="28">
+      <c r="B28" t="inlineStr">
         <is>
           <t>offen         – Termin läuft bzw. steht noch aus, wird am Kiosk angezeigt</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="14" t="inlineStr">
+    <row r="29">
+      <c r="B29" t="inlineStr">
         <is>
           <t>abgeschlossen – erledigt, geht in die Historie und in die Ausfallstatistik</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="14" t="inlineStr">
+    <row r="30">
+      <c r="B30" t="inlineStr">
         <is>
           <t>storniert     – versehentlich eingetragen, zählt NICHT als Ausfall</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="14" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="B28" s="15" t="inlineStr">
+    <row r="31"/>
+    <row r="32">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>Nach dem Abschluss</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="14" t="inlineStr">
+    <row r="33">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Abgeschlossene Zeilen aus „Termine“ in das Blatt „Archiv“ verschieben.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="14" t="inlineStr">
+    <row r="34">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Die Historie bleibt im Gerät erhalten, auch wenn die Zeile hier verschwindet.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="14" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="B32" s="15" t="inlineStr">
+    <row r="35"/>
+    <row r="36">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>Neue Prüfstände</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="14" t="inlineStr">
+    <row r="37">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Im Blatt „Prüfstände“ unten eine Zeile ergänzen (Kennung, Bezeichnung, Auswahl).</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="14" t="inlineStr">
+    <row r="38">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Das Dropdown im Blatt „Termine“ zieht automatisch nach.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Beispiele</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Die Zeilen in dieser Vorlage sind Muster zum Ansehen. Vor dem ersten</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>echten Eintrag löschen – sonst werden sie als echte Termine importiert.</t>
         </is>
       </c>
     </row>

--- a/terminboard/vorlagen/termine_modell2.xlsx
+++ b/terminboard/vorlagen/termine_modell2.xlsx
@@ -22,9 +22,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="DD.MM.YYYY HH:MM"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="DD.MM.YYYY"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="167" formatCode="DD.MM.YYYY HH:MM"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -69,12 +71,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -507,10 +510,10 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>46328.29166666666</v>
+        <v>46328</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>46328.625</v>
+        <v>46328</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -538,10 +541,10 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>46342.33333333334</v>
+        <v>46342</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>46347.66666666666</v>
+        <v>46347</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -569,10 +572,10 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>46344.25</v>
+        <v>46344</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>46345.75</v>
+        <v>46345</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -600,10 +603,10 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>46350.375</v>
+        <v>46350</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>46350.54166666666</v>
+        <v>46350</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -631,10 +634,10 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>46353.41666666666</v>
+        <v>46353</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>46353.5</v>
+        <v>46353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -662,7 +665,7 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>46357.33333333334</v>
+        <v>46357</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" t="inlineStr">
@@ -2703,17 +2706,17 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>46342.33333333334</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>46342.5</v>
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>46350.375</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>46350.54166666666</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Tag 1, vormittags</t>
+          <t>Halbtag, Rest des Tages freigegeben</t>
         </is>
       </c>
     </row>
@@ -2721,15 +2724,15 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>46343.33333333334</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>46343.66666666666</v>
+      <c r="B3" s="3" t="n">
+        <v>46342.33333333334</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>46342.5</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Tag 2, ganztags</t>
+          <t>Tag 1, vormittags</t>
         </is>
       </c>
     </row>
@@ -2737,15 +2740,15 @@
       <c r="A4" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>46345.29166666666</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>46345.45833333334</v>
+      <c r="B4" s="3" t="n">
+        <v>46343.33333333334</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>46343.66666666666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Tag 4, vormittags</t>
+          <t>Tag 2, ganztags</t>
         </is>
       </c>
     </row>
@@ -2753,1997 +2756,2009 @@
       <c r="A5" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="3" t="n">
+        <v>46345.29166666666</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>46345.45833333334</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Tag 4, vormittags</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="3" t="n">
         <v>46346.33333333334</v>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C6" s="3" t="n">
         <v>46346.58333333334</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Tag 5, 6 Stunden</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-    </row>
     <row r="7">
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="3" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="n"/>
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="3" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="2" t="n"/>
-      <c r="C11" s="2" t="n"/>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n"/>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="3" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="2" t="n"/>
-      <c r="C15" s="2" t="n"/>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="2" t="n"/>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="2" t="n"/>
-      <c r="C17" s="2" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="2" t="n"/>
-      <c r="C18" s="2" t="n"/>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="2" t="n"/>
-      <c r="C19" s="2" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="2" t="n"/>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="2" t="n"/>
-      <c r="C21" s="2" t="n"/>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="2" t="n"/>
-      <c r="C22" s="2" t="n"/>
+      <c r="B22" s="3" t="n"/>
+      <c r="C22" s="3" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="2" t="n"/>
-      <c r="C23" s="2" t="n"/>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="2" t="n"/>
-      <c r="C24" s="2" t="n"/>
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="3" t="n"/>
     </row>
     <row r="25">
-      <c r="B25" s="2" t="n"/>
-      <c r="C25" s="2" t="n"/>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
     </row>
     <row r="26">
-      <c r="B26" s="2" t="n"/>
-      <c r="C26" s="2" t="n"/>
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="3" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="2" t="n"/>
-      <c r="C27" s="2" t="n"/>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n"/>
     </row>
     <row r="28">
-      <c r="B28" s="2" t="n"/>
-      <c r="C28" s="2" t="n"/>
+      <c r="B28" s="3" t="n"/>
+      <c r="C28" s="3" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="2" t="n"/>
-      <c r="C29" s="2" t="n"/>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="2" t="n"/>
-      <c r="C30" s="2" t="n"/>
+      <c r="B30" s="3" t="n"/>
+      <c r="C30" s="3" t="n"/>
     </row>
     <row r="31">
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="n"/>
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="2" t="n"/>
-      <c r="C32" s="2" t="n"/>
+      <c r="B32" s="3" t="n"/>
+      <c r="C32" s="3" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="2" t="n"/>
-      <c r="C33" s="2" t="n"/>
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="3" t="n"/>
     </row>
     <row r="34">
-      <c r="B34" s="2" t="n"/>
-      <c r="C34" s="2" t="n"/>
+      <c r="B34" s="3" t="n"/>
+      <c r="C34" s="3" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="2" t="n"/>
-      <c r="C35" s="2" t="n"/>
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="3" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" s="2" t="n"/>
-      <c r="C36" s="2" t="n"/>
+      <c r="B36" s="3" t="n"/>
+      <c r="C36" s="3" t="n"/>
     </row>
     <row r="37">
-      <c r="B37" s="2" t="n"/>
-      <c r="C37" s="2" t="n"/>
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="3" t="n"/>
     </row>
     <row r="38">
-      <c r="B38" s="2" t="n"/>
-      <c r="C38" s="2" t="n"/>
+      <c r="B38" s="3" t="n"/>
+      <c r="C38" s="3" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" s="2" t="n"/>
-      <c r="C39" s="2" t="n"/>
+      <c r="B39" s="3" t="n"/>
+      <c r="C39" s="3" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" s="2" t="n"/>
-      <c r="C40" s="2" t="n"/>
+      <c r="B40" s="3" t="n"/>
+      <c r="C40" s="3" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="2" t="n"/>
-      <c r="C41" s="2" t="n"/>
+      <c r="B41" s="3" t="n"/>
+      <c r="C41" s="3" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" s="2" t="n"/>
-      <c r="C42" s="2" t="n"/>
+      <c r="B42" s="3" t="n"/>
+      <c r="C42" s="3" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" s="2" t="n"/>
-      <c r="C43" s="2" t="n"/>
+      <c r="B43" s="3" t="n"/>
+      <c r="C43" s="3" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" s="2" t="n"/>
-      <c r="C44" s="2" t="n"/>
+      <c r="B44" s="3" t="n"/>
+      <c r="C44" s="3" t="n"/>
     </row>
     <row r="45">
-      <c r="B45" s="2" t="n"/>
-      <c r="C45" s="2" t="n"/>
+      <c r="B45" s="3" t="n"/>
+      <c r="C45" s="3" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="2" t="n"/>
-      <c r="C46" s="2" t="n"/>
+      <c r="B46" s="3" t="n"/>
+      <c r="C46" s="3" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="2" t="n"/>
-      <c r="C47" s="2" t="n"/>
+      <c r="B47" s="3" t="n"/>
+      <c r="C47" s="3" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="2" t="n"/>
-      <c r="C48" s="2" t="n"/>
+      <c r="B48" s="3" t="n"/>
+      <c r="C48" s="3" t="n"/>
     </row>
     <row r="49">
-      <c r="B49" s="2" t="n"/>
-      <c r="C49" s="2" t="n"/>
+      <c r="B49" s="3" t="n"/>
+      <c r="C49" s="3" t="n"/>
     </row>
     <row r="50">
-      <c r="B50" s="2" t="n"/>
-      <c r="C50" s="2" t="n"/>
+      <c r="B50" s="3" t="n"/>
+      <c r="C50" s="3" t="n"/>
     </row>
     <row r="51">
-      <c r="B51" s="2" t="n"/>
-      <c r="C51" s="2" t="n"/>
+      <c r="B51" s="3" t="n"/>
+      <c r="C51" s="3" t="n"/>
     </row>
     <row r="52">
-      <c r="B52" s="2" t="n"/>
-      <c r="C52" s="2" t="n"/>
+      <c r="B52" s="3" t="n"/>
+      <c r="C52" s="3" t="n"/>
     </row>
     <row r="53">
-      <c r="B53" s="2" t="n"/>
-      <c r="C53" s="2" t="n"/>
+      <c r="B53" s="3" t="n"/>
+      <c r="C53" s="3" t="n"/>
     </row>
     <row r="54">
-      <c r="B54" s="2" t="n"/>
-      <c r="C54" s="2" t="n"/>
+      <c r="B54" s="3" t="n"/>
+      <c r="C54" s="3" t="n"/>
     </row>
     <row r="55">
-      <c r="B55" s="2" t="n"/>
-      <c r="C55" s="2" t="n"/>
+      <c r="B55" s="3" t="n"/>
+      <c r="C55" s="3" t="n"/>
     </row>
     <row r="56">
-      <c r="B56" s="2" t="n"/>
-      <c r="C56" s="2" t="n"/>
+      <c r="B56" s="3" t="n"/>
+      <c r="C56" s="3" t="n"/>
     </row>
     <row r="57">
-      <c r="B57" s="2" t="n"/>
-      <c r="C57" s="2" t="n"/>
+      <c r="B57" s="3" t="n"/>
+      <c r="C57" s="3" t="n"/>
     </row>
     <row r="58">
-      <c r="B58" s="2" t="n"/>
-      <c r="C58" s="2" t="n"/>
+      <c r="B58" s="3" t="n"/>
+      <c r="C58" s="3" t="n"/>
     </row>
     <row r="59">
-      <c r="B59" s="2" t="n"/>
-      <c r="C59" s="2" t="n"/>
+      <c r="B59" s="3" t="n"/>
+      <c r="C59" s="3" t="n"/>
     </row>
     <row r="60">
-      <c r="B60" s="2" t="n"/>
-      <c r="C60" s="2" t="n"/>
+      <c r="B60" s="3" t="n"/>
+      <c r="C60" s="3" t="n"/>
     </row>
     <row r="61">
-      <c r="B61" s="2" t="n"/>
-      <c r="C61" s="2" t="n"/>
+      <c r="B61" s="3" t="n"/>
+      <c r="C61" s="3" t="n"/>
     </row>
     <row r="62">
-      <c r="B62" s="2" t="n"/>
-      <c r="C62" s="2" t="n"/>
+      <c r="B62" s="3" t="n"/>
+      <c r="C62" s="3" t="n"/>
     </row>
     <row r="63">
-      <c r="B63" s="2" t="n"/>
-      <c r="C63" s="2" t="n"/>
+      <c r="B63" s="3" t="n"/>
+      <c r="C63" s="3" t="n"/>
     </row>
     <row r="64">
-      <c r="B64" s="2" t="n"/>
-      <c r="C64" s="2" t="n"/>
+      <c r="B64" s="3" t="n"/>
+      <c r="C64" s="3" t="n"/>
     </row>
     <row r="65">
-      <c r="B65" s="2" t="n"/>
-      <c r="C65" s="2" t="n"/>
+      <c r="B65" s="3" t="n"/>
+      <c r="C65" s="3" t="n"/>
     </row>
     <row r="66">
-      <c r="B66" s="2" t="n"/>
-      <c r="C66" s="2" t="n"/>
+      <c r="B66" s="3" t="n"/>
+      <c r="C66" s="3" t="n"/>
     </row>
     <row r="67">
-      <c r="B67" s="2" t="n"/>
-      <c r="C67" s="2" t="n"/>
+      <c r="B67" s="3" t="n"/>
+      <c r="C67" s="3" t="n"/>
     </row>
     <row r="68">
-      <c r="B68" s="2" t="n"/>
-      <c r="C68" s="2" t="n"/>
+      <c r="B68" s="3" t="n"/>
+      <c r="C68" s="3" t="n"/>
     </row>
     <row r="69">
-      <c r="B69" s="2" t="n"/>
-      <c r="C69" s="2" t="n"/>
+      <c r="B69" s="3" t="n"/>
+      <c r="C69" s="3" t="n"/>
     </row>
     <row r="70">
-      <c r="B70" s="2" t="n"/>
-      <c r="C70" s="2" t="n"/>
+      <c r="B70" s="3" t="n"/>
+      <c r="C70" s="3" t="n"/>
     </row>
     <row r="71">
-      <c r="B71" s="2" t="n"/>
-      <c r="C71" s="2" t="n"/>
+      <c r="B71" s="3" t="n"/>
+      <c r="C71" s="3" t="n"/>
     </row>
     <row r="72">
-      <c r="B72" s="2" t="n"/>
-      <c r="C72" s="2" t="n"/>
+      <c r="B72" s="3" t="n"/>
+      <c r="C72" s="3" t="n"/>
     </row>
     <row r="73">
-      <c r="B73" s="2" t="n"/>
-      <c r="C73" s="2" t="n"/>
+      <c r="B73" s="3" t="n"/>
+      <c r="C73" s="3" t="n"/>
     </row>
     <row r="74">
-      <c r="B74" s="2" t="n"/>
-      <c r="C74" s="2" t="n"/>
+      <c r="B74" s="3" t="n"/>
+      <c r="C74" s="3" t="n"/>
     </row>
     <row r="75">
-      <c r="B75" s="2" t="n"/>
-      <c r="C75" s="2" t="n"/>
+      <c r="B75" s="3" t="n"/>
+      <c r="C75" s="3" t="n"/>
     </row>
     <row r="76">
-      <c r="B76" s="2" t="n"/>
-      <c r="C76" s="2" t="n"/>
+      <c r="B76" s="3" t="n"/>
+      <c r="C76" s="3" t="n"/>
     </row>
     <row r="77">
-      <c r="B77" s="2" t="n"/>
-      <c r="C77" s="2" t="n"/>
+      <c r="B77" s="3" t="n"/>
+      <c r="C77" s="3" t="n"/>
     </row>
     <row r="78">
-      <c r="B78" s="2" t="n"/>
-      <c r="C78" s="2" t="n"/>
+      <c r="B78" s="3" t="n"/>
+      <c r="C78" s="3" t="n"/>
     </row>
     <row r="79">
-      <c r="B79" s="2" t="n"/>
-      <c r="C79" s="2" t="n"/>
+      <c r="B79" s="3" t="n"/>
+      <c r="C79" s="3" t="n"/>
     </row>
     <row r="80">
-      <c r="B80" s="2" t="n"/>
-      <c r="C80" s="2" t="n"/>
+      <c r="B80" s="3" t="n"/>
+      <c r="C80" s="3" t="n"/>
     </row>
     <row r="81">
-      <c r="B81" s="2" t="n"/>
-      <c r="C81" s="2" t="n"/>
+      <c r="B81" s="3" t="n"/>
+      <c r="C81" s="3" t="n"/>
     </row>
     <row r="82">
-      <c r="B82" s="2" t="n"/>
-      <c r="C82" s="2" t="n"/>
+      <c r="B82" s="3" t="n"/>
+      <c r="C82" s="3" t="n"/>
     </row>
     <row r="83">
-      <c r="B83" s="2" t="n"/>
-      <c r="C83" s="2" t="n"/>
+      <c r="B83" s="3" t="n"/>
+      <c r="C83" s="3" t="n"/>
     </row>
     <row r="84">
-      <c r="B84" s="2" t="n"/>
-      <c r="C84" s="2" t="n"/>
+      <c r="B84" s="3" t="n"/>
+      <c r="C84" s="3" t="n"/>
     </row>
     <row r="85">
-      <c r="B85" s="2" t="n"/>
-      <c r="C85" s="2" t="n"/>
+      <c r="B85" s="3" t="n"/>
+      <c r="C85" s="3" t="n"/>
     </row>
     <row r="86">
-      <c r="B86" s="2" t="n"/>
-      <c r="C86" s="2" t="n"/>
+      <c r="B86" s="3" t="n"/>
+      <c r="C86" s="3" t="n"/>
     </row>
     <row r="87">
-      <c r="B87" s="2" t="n"/>
-      <c r="C87" s="2" t="n"/>
+      <c r="B87" s="3" t="n"/>
+      <c r="C87" s="3" t="n"/>
     </row>
     <row r="88">
-      <c r="B88" s="2" t="n"/>
-      <c r="C88" s="2" t="n"/>
+      <c r="B88" s="3" t="n"/>
+      <c r="C88" s="3" t="n"/>
     </row>
     <row r="89">
-      <c r="B89" s="2" t="n"/>
-      <c r="C89" s="2" t="n"/>
+      <c r="B89" s="3" t="n"/>
+      <c r="C89" s="3" t="n"/>
     </row>
     <row r="90">
-      <c r="B90" s="2" t="n"/>
-      <c r="C90" s="2" t="n"/>
+      <c r="B90" s="3" t="n"/>
+      <c r="C90" s="3" t="n"/>
     </row>
     <row r="91">
-      <c r="B91" s="2" t="n"/>
-      <c r="C91" s="2" t="n"/>
+      <c r="B91" s="3" t="n"/>
+      <c r="C91" s="3" t="n"/>
     </row>
     <row r="92">
-      <c r="B92" s="2" t="n"/>
-      <c r="C92" s="2" t="n"/>
+      <c r="B92" s="3" t="n"/>
+      <c r="C92" s="3" t="n"/>
     </row>
     <row r="93">
-      <c r="B93" s="2" t="n"/>
-      <c r="C93" s="2" t="n"/>
+      <c r="B93" s="3" t="n"/>
+      <c r="C93" s="3" t="n"/>
     </row>
     <row r="94">
-      <c r="B94" s="2" t="n"/>
-      <c r="C94" s="2" t="n"/>
+      <c r="B94" s="3" t="n"/>
+      <c r="C94" s="3" t="n"/>
     </row>
     <row r="95">
-      <c r="B95" s="2" t="n"/>
-      <c r="C95" s="2" t="n"/>
+      <c r="B95" s="3" t="n"/>
+      <c r="C95" s="3" t="n"/>
     </row>
     <row r="96">
-      <c r="B96" s="2" t="n"/>
-      <c r="C96" s="2" t="n"/>
+      <c r="B96" s="3" t="n"/>
+      <c r="C96" s="3" t="n"/>
     </row>
     <row r="97">
-      <c r="B97" s="2" t="n"/>
-      <c r="C97" s="2" t="n"/>
+      <c r="B97" s="3" t="n"/>
+      <c r="C97" s="3" t="n"/>
     </row>
     <row r="98">
-      <c r="B98" s="2" t="n"/>
-      <c r="C98" s="2" t="n"/>
+      <c r="B98" s="3" t="n"/>
+      <c r="C98" s="3" t="n"/>
     </row>
     <row r="99">
-      <c r="B99" s="2" t="n"/>
-      <c r="C99" s="2" t="n"/>
+      <c r="B99" s="3" t="n"/>
+      <c r="C99" s="3" t="n"/>
     </row>
     <row r="100">
-      <c r="B100" s="2" t="n"/>
-      <c r="C100" s="2" t="n"/>
+      <c r="B100" s="3" t="n"/>
+      <c r="C100" s="3" t="n"/>
     </row>
     <row r="101">
-      <c r="B101" s="2" t="n"/>
-      <c r="C101" s="2" t="n"/>
+      <c r="B101" s="3" t="n"/>
+      <c r="C101" s="3" t="n"/>
     </row>
     <row r="102">
-      <c r="B102" s="2" t="n"/>
-      <c r="C102" s="2" t="n"/>
+      <c r="B102" s="3" t="n"/>
+      <c r="C102" s="3" t="n"/>
     </row>
     <row r="103">
-      <c r="B103" s="2" t="n"/>
-      <c r="C103" s="2" t="n"/>
+      <c r="B103" s="3" t="n"/>
+      <c r="C103" s="3" t="n"/>
     </row>
     <row r="104">
-      <c r="B104" s="2" t="n"/>
-      <c r="C104" s="2" t="n"/>
+      <c r="B104" s="3" t="n"/>
+      <c r="C104" s="3" t="n"/>
     </row>
     <row r="105">
-      <c r="B105" s="2" t="n"/>
-      <c r="C105" s="2" t="n"/>
+      <c r="B105" s="3" t="n"/>
+      <c r="C105" s="3" t="n"/>
     </row>
     <row r="106">
-      <c r="B106" s="2" t="n"/>
-      <c r="C106" s="2" t="n"/>
+      <c r="B106" s="3" t="n"/>
+      <c r="C106" s="3" t="n"/>
     </row>
     <row r="107">
-      <c r="B107" s="2" t="n"/>
-      <c r="C107" s="2" t="n"/>
+      <c r="B107" s="3" t="n"/>
+      <c r="C107" s="3" t="n"/>
     </row>
     <row r="108">
-      <c r="B108" s="2" t="n"/>
-      <c r="C108" s="2" t="n"/>
+      <c r="B108" s="3" t="n"/>
+      <c r="C108" s="3" t="n"/>
     </row>
     <row r="109">
-      <c r="B109" s="2" t="n"/>
-      <c r="C109" s="2" t="n"/>
+      <c r="B109" s="3" t="n"/>
+      <c r="C109" s="3" t="n"/>
     </row>
     <row r="110">
-      <c r="B110" s="2" t="n"/>
-      <c r="C110" s="2" t="n"/>
+      <c r="B110" s="3" t="n"/>
+      <c r="C110" s="3" t="n"/>
     </row>
     <row r="111">
-      <c r="B111" s="2" t="n"/>
-      <c r="C111" s="2" t="n"/>
+      <c r="B111" s="3" t="n"/>
+      <c r="C111" s="3" t="n"/>
     </row>
     <row r="112">
-      <c r="B112" s="2" t="n"/>
-      <c r="C112" s="2" t="n"/>
+      <c r="B112" s="3" t="n"/>
+      <c r="C112" s="3" t="n"/>
     </row>
     <row r="113">
-      <c r="B113" s="2" t="n"/>
-      <c r="C113" s="2" t="n"/>
+      <c r="B113" s="3" t="n"/>
+      <c r="C113" s="3" t="n"/>
     </row>
     <row r="114">
-      <c r="B114" s="2" t="n"/>
-      <c r="C114" s="2" t="n"/>
+      <c r="B114" s="3" t="n"/>
+      <c r="C114" s="3" t="n"/>
     </row>
     <row r="115">
-      <c r="B115" s="2" t="n"/>
-      <c r="C115" s="2" t="n"/>
+      <c r="B115" s="3" t="n"/>
+      <c r="C115" s="3" t="n"/>
     </row>
     <row r="116">
-      <c r="B116" s="2" t="n"/>
-      <c r="C116" s="2" t="n"/>
+      <c r="B116" s="3" t="n"/>
+      <c r="C116" s="3" t="n"/>
     </row>
     <row r="117">
-      <c r="B117" s="2" t="n"/>
-      <c r="C117" s="2" t="n"/>
+      <c r="B117" s="3" t="n"/>
+      <c r="C117" s="3" t="n"/>
     </row>
     <row r="118">
-      <c r="B118" s="2" t="n"/>
-      <c r="C118" s="2" t="n"/>
+      <c r="B118" s="3" t="n"/>
+      <c r="C118" s="3" t="n"/>
     </row>
     <row r="119">
-      <c r="B119" s="2" t="n"/>
-      <c r="C119" s="2" t="n"/>
+      <c r="B119" s="3" t="n"/>
+      <c r="C119" s="3" t="n"/>
     </row>
     <row r="120">
-      <c r="B120" s="2" t="n"/>
-      <c r="C120" s="2" t="n"/>
+      <c r="B120" s="3" t="n"/>
+      <c r="C120" s="3" t="n"/>
     </row>
     <row r="121">
-      <c r="B121" s="2" t="n"/>
-      <c r="C121" s="2" t="n"/>
+      <c r="B121" s="3" t="n"/>
+      <c r="C121" s="3" t="n"/>
     </row>
     <row r="122">
-      <c r="B122" s="2" t="n"/>
-      <c r="C122" s="2" t="n"/>
+      <c r="B122" s="3" t="n"/>
+      <c r="C122" s="3" t="n"/>
     </row>
     <row r="123">
-      <c r="B123" s="2" t="n"/>
-      <c r="C123" s="2" t="n"/>
+      <c r="B123" s="3" t="n"/>
+      <c r="C123" s="3" t="n"/>
     </row>
     <row r="124">
-      <c r="B124" s="2" t="n"/>
-      <c r="C124" s="2" t="n"/>
+      <c r="B124" s="3" t="n"/>
+      <c r="C124" s="3" t="n"/>
     </row>
     <row r="125">
-      <c r="B125" s="2" t="n"/>
-      <c r="C125" s="2" t="n"/>
+      <c r="B125" s="3" t="n"/>
+      <c r="C125" s="3" t="n"/>
     </row>
     <row r="126">
-      <c r="B126" s="2" t="n"/>
-      <c r="C126" s="2" t="n"/>
+      <c r="B126" s="3" t="n"/>
+      <c r="C126" s="3" t="n"/>
     </row>
     <row r="127">
-      <c r="B127" s="2" t="n"/>
-      <c r="C127" s="2" t="n"/>
+      <c r="B127" s="3" t="n"/>
+      <c r="C127" s="3" t="n"/>
     </row>
     <row r="128">
-      <c r="B128" s="2" t="n"/>
-      <c r="C128" s="2" t="n"/>
+      <c r="B128" s="3" t="n"/>
+      <c r="C128" s="3" t="n"/>
     </row>
     <row r="129">
-      <c r="B129" s="2" t="n"/>
-      <c r="C129" s="2" t="n"/>
+      <c r="B129" s="3" t="n"/>
+      <c r="C129" s="3" t="n"/>
     </row>
     <row r="130">
-      <c r="B130" s="2" t="n"/>
-      <c r="C130" s="2" t="n"/>
+      <c r="B130" s="3" t="n"/>
+      <c r="C130" s="3" t="n"/>
     </row>
     <row r="131">
-      <c r="B131" s="2" t="n"/>
-      <c r="C131" s="2" t="n"/>
+      <c r="B131" s="3" t="n"/>
+      <c r="C131" s="3" t="n"/>
     </row>
     <row r="132">
-      <c r="B132" s="2" t="n"/>
-      <c r="C132" s="2" t="n"/>
+      <c r="B132" s="3" t="n"/>
+      <c r="C132" s="3" t="n"/>
     </row>
     <row r="133">
-      <c r="B133" s="2" t="n"/>
-      <c r="C133" s="2" t="n"/>
+      <c r="B133" s="3" t="n"/>
+      <c r="C133" s="3" t="n"/>
     </row>
     <row r="134">
-      <c r="B134" s="2" t="n"/>
-      <c r="C134" s="2" t="n"/>
+      <c r="B134" s="3" t="n"/>
+      <c r="C134" s="3" t="n"/>
     </row>
     <row r="135">
-      <c r="B135" s="2" t="n"/>
-      <c r="C135" s="2" t="n"/>
+      <c r="B135" s="3" t="n"/>
+      <c r="C135" s="3" t="n"/>
     </row>
     <row r="136">
-      <c r="B136" s="2" t="n"/>
-      <c r="C136" s="2" t="n"/>
+      <c r="B136" s="3" t="n"/>
+      <c r="C136" s="3" t="n"/>
     </row>
     <row r="137">
-      <c r="B137" s="2" t="n"/>
-      <c r="C137" s="2" t="n"/>
+      <c r="B137" s="3" t="n"/>
+      <c r="C137" s="3" t="n"/>
     </row>
     <row r="138">
-      <c r="B138" s="2" t="n"/>
-      <c r="C138" s="2" t="n"/>
+      <c r="B138" s="3" t="n"/>
+      <c r="C138" s="3" t="n"/>
     </row>
     <row r="139">
-      <c r="B139" s="2" t="n"/>
-      <c r="C139" s="2" t="n"/>
+      <c r="B139" s="3" t="n"/>
+      <c r="C139" s="3" t="n"/>
     </row>
     <row r="140">
-      <c r="B140" s="2" t="n"/>
-      <c r="C140" s="2" t="n"/>
+      <c r="B140" s="3" t="n"/>
+      <c r="C140" s="3" t="n"/>
     </row>
     <row r="141">
-      <c r="B141" s="2" t="n"/>
-      <c r="C141" s="2" t="n"/>
+      <c r="B141" s="3" t="n"/>
+      <c r="C141" s="3" t="n"/>
     </row>
     <row r="142">
-      <c r="B142" s="2" t="n"/>
-      <c r="C142" s="2" t="n"/>
+      <c r="B142" s="3" t="n"/>
+      <c r="C142" s="3" t="n"/>
     </row>
     <row r="143">
-      <c r="B143" s="2" t="n"/>
-      <c r="C143" s="2" t="n"/>
+      <c r="B143" s="3" t="n"/>
+      <c r="C143" s="3" t="n"/>
     </row>
     <row r="144">
-      <c r="B144" s="2" t="n"/>
-      <c r="C144" s="2" t="n"/>
+      <c r="B144" s="3" t="n"/>
+      <c r="C144" s="3" t="n"/>
     </row>
     <row r="145">
-      <c r="B145" s="2" t="n"/>
-      <c r="C145" s="2" t="n"/>
+      <c r="B145" s="3" t="n"/>
+      <c r="C145" s="3" t="n"/>
     </row>
     <row r="146">
-      <c r="B146" s="2" t="n"/>
-      <c r="C146" s="2" t="n"/>
+      <c r="B146" s="3" t="n"/>
+      <c r="C146" s="3" t="n"/>
     </row>
     <row r="147">
-      <c r="B147" s="2" t="n"/>
-      <c r="C147" s="2" t="n"/>
+      <c r="B147" s="3" t="n"/>
+      <c r="C147" s="3" t="n"/>
     </row>
     <row r="148">
-      <c r="B148" s="2" t="n"/>
-      <c r="C148" s="2" t="n"/>
+      <c r="B148" s="3" t="n"/>
+      <c r="C148" s="3" t="n"/>
     </row>
     <row r="149">
-      <c r="B149" s="2" t="n"/>
-      <c r="C149" s="2" t="n"/>
+      <c r="B149" s="3" t="n"/>
+      <c r="C149" s="3" t="n"/>
     </row>
     <row r="150">
-      <c r="B150" s="2" t="n"/>
-      <c r="C150" s="2" t="n"/>
+      <c r="B150" s="3" t="n"/>
+      <c r="C150" s="3" t="n"/>
     </row>
     <row r="151">
-      <c r="B151" s="2" t="n"/>
-      <c r="C151" s="2" t="n"/>
+      <c r="B151" s="3" t="n"/>
+      <c r="C151" s="3" t="n"/>
     </row>
     <row r="152">
-      <c r="B152" s="2" t="n"/>
-      <c r="C152" s="2" t="n"/>
+      <c r="B152" s="3" t="n"/>
+      <c r="C152" s="3" t="n"/>
     </row>
     <row r="153">
-      <c r="B153" s="2" t="n"/>
-      <c r="C153" s="2" t="n"/>
+      <c r="B153" s="3" t="n"/>
+      <c r="C153" s="3" t="n"/>
     </row>
     <row r="154">
-      <c r="B154" s="2" t="n"/>
-      <c r="C154" s="2" t="n"/>
+      <c r="B154" s="3" t="n"/>
+      <c r="C154" s="3" t="n"/>
     </row>
     <row r="155">
-      <c r="B155" s="2" t="n"/>
-      <c r="C155" s="2" t="n"/>
+      <c r="B155" s="3" t="n"/>
+      <c r="C155" s="3" t="n"/>
     </row>
     <row r="156">
-      <c r="B156" s="2" t="n"/>
-      <c r="C156" s="2" t="n"/>
+      <c r="B156" s="3" t="n"/>
+      <c r="C156" s="3" t="n"/>
     </row>
     <row r="157">
-      <c r="B157" s="2" t="n"/>
-      <c r="C157" s="2" t="n"/>
+      <c r="B157" s="3" t="n"/>
+      <c r="C157" s="3" t="n"/>
     </row>
     <row r="158">
-      <c r="B158" s="2" t="n"/>
-      <c r="C158" s="2" t="n"/>
+      <c r="B158" s="3" t="n"/>
+      <c r="C158" s="3" t="n"/>
     </row>
     <row r="159">
-      <c r="B159" s="2" t="n"/>
-      <c r="C159" s="2" t="n"/>
+      <c r="B159" s="3" t="n"/>
+      <c r="C159" s="3" t="n"/>
     </row>
     <row r="160">
-      <c r="B160" s="2" t="n"/>
-      <c r="C160" s="2" t="n"/>
+      <c r="B160" s="3" t="n"/>
+      <c r="C160" s="3" t="n"/>
     </row>
     <row r="161">
-      <c r="B161" s="2" t="n"/>
-      <c r="C161" s="2" t="n"/>
+      <c r="B161" s="3" t="n"/>
+      <c r="C161" s="3" t="n"/>
     </row>
     <row r="162">
-      <c r="B162" s="2" t="n"/>
-      <c r="C162" s="2" t="n"/>
+      <c r="B162" s="3" t="n"/>
+      <c r="C162" s="3" t="n"/>
     </row>
     <row r="163">
-      <c r="B163" s="2" t="n"/>
-      <c r="C163" s="2" t="n"/>
+      <c r="B163" s="3" t="n"/>
+      <c r="C163" s="3" t="n"/>
     </row>
     <row r="164">
-      <c r="B164" s="2" t="n"/>
-      <c r="C164" s="2" t="n"/>
+      <c r="B164" s="3" t="n"/>
+      <c r="C164" s="3" t="n"/>
     </row>
     <row r="165">
-      <c r="B165" s="2" t="n"/>
-      <c r="C165" s="2" t="n"/>
+      <c r="B165" s="3" t="n"/>
+      <c r="C165" s="3" t="n"/>
     </row>
     <row r="166">
-      <c r="B166" s="2" t="n"/>
-      <c r="C166" s="2" t="n"/>
+      <c r="B166" s="3" t="n"/>
+      <c r="C166" s="3" t="n"/>
     </row>
     <row r="167">
-      <c r="B167" s="2" t="n"/>
-      <c r="C167" s="2" t="n"/>
+      <c r="B167" s="3" t="n"/>
+      <c r="C167" s="3" t="n"/>
     </row>
     <row r="168">
-      <c r="B168" s="2" t="n"/>
-      <c r="C168" s="2" t="n"/>
+      <c r="B168" s="3" t="n"/>
+      <c r="C168" s="3" t="n"/>
     </row>
     <row r="169">
-      <c r="B169" s="2" t="n"/>
-      <c r="C169" s="2" t="n"/>
+      <c r="B169" s="3" t="n"/>
+      <c r="C169" s="3" t="n"/>
     </row>
     <row r="170">
-      <c r="B170" s="2" t="n"/>
-      <c r="C170" s="2" t="n"/>
+      <c r="B170" s="3" t="n"/>
+      <c r="C170" s="3" t="n"/>
     </row>
     <row r="171">
-      <c r="B171" s="2" t="n"/>
-      <c r="C171" s="2" t="n"/>
+      <c r="B171" s="3" t="n"/>
+      <c r="C171" s="3" t="n"/>
     </row>
     <row r="172">
-      <c r="B172" s="2" t="n"/>
-      <c r="C172" s="2" t="n"/>
+      <c r="B172" s="3" t="n"/>
+      <c r="C172" s="3" t="n"/>
     </row>
     <row r="173">
-      <c r="B173" s="2" t="n"/>
-      <c r="C173" s="2" t="n"/>
+      <c r="B173" s="3" t="n"/>
+      <c r="C173" s="3" t="n"/>
     </row>
     <row r="174">
-      <c r="B174" s="2" t="n"/>
-      <c r="C174" s="2" t="n"/>
+      <c r="B174" s="3" t="n"/>
+      <c r="C174" s="3" t="n"/>
     </row>
     <row r="175">
-      <c r="B175" s="2" t="n"/>
-      <c r="C175" s="2" t="n"/>
+      <c r="B175" s="3" t="n"/>
+      <c r="C175" s="3" t="n"/>
     </row>
     <row r="176">
-      <c r="B176" s="2" t="n"/>
-      <c r="C176" s="2" t="n"/>
+      <c r="B176" s="3" t="n"/>
+      <c r="C176" s="3" t="n"/>
     </row>
     <row r="177">
-      <c r="B177" s="2" t="n"/>
-      <c r="C177" s="2" t="n"/>
+      <c r="B177" s="3" t="n"/>
+      <c r="C177" s="3" t="n"/>
     </row>
     <row r="178">
-      <c r="B178" s="2" t="n"/>
-      <c r="C178" s="2" t="n"/>
+      <c r="B178" s="3" t="n"/>
+      <c r="C178" s="3" t="n"/>
     </row>
     <row r="179">
-      <c r="B179" s="2" t="n"/>
-      <c r="C179" s="2" t="n"/>
+      <c r="B179" s="3" t="n"/>
+      <c r="C179" s="3" t="n"/>
     </row>
     <row r="180">
-      <c r="B180" s="2" t="n"/>
-      <c r="C180" s="2" t="n"/>
+      <c r="B180" s="3" t="n"/>
+      <c r="C180" s="3" t="n"/>
     </row>
     <row r="181">
-      <c r="B181" s="2" t="n"/>
-      <c r="C181" s="2" t="n"/>
+      <c r="B181" s="3" t="n"/>
+      <c r="C181" s="3" t="n"/>
     </row>
     <row r="182">
-      <c r="B182" s="2" t="n"/>
-      <c r="C182" s="2" t="n"/>
+      <c r="B182" s="3" t="n"/>
+      <c r="C182" s="3" t="n"/>
     </row>
     <row r="183">
-      <c r="B183" s="2" t="n"/>
-      <c r="C183" s="2" t="n"/>
+      <c r="B183" s="3" t="n"/>
+      <c r="C183" s="3" t="n"/>
     </row>
     <row r="184">
-      <c r="B184" s="2" t="n"/>
-      <c r="C184" s="2" t="n"/>
+      <c r="B184" s="3" t="n"/>
+      <c r="C184" s="3" t="n"/>
     </row>
     <row r="185">
-      <c r="B185" s="2" t="n"/>
-      <c r="C185" s="2" t="n"/>
+      <c r="B185" s="3" t="n"/>
+      <c r="C185" s="3" t="n"/>
     </row>
     <row r="186">
-      <c r="B186" s="2" t="n"/>
-      <c r="C186" s="2" t="n"/>
+      <c r="B186" s="3" t="n"/>
+      <c r="C186" s="3" t="n"/>
     </row>
     <row r="187">
-      <c r="B187" s="2" t="n"/>
-      <c r="C187" s="2" t="n"/>
+      <c r="B187" s="3" t="n"/>
+      <c r="C187" s="3" t="n"/>
     </row>
     <row r="188">
-      <c r="B188" s="2" t="n"/>
-      <c r="C188" s="2" t="n"/>
+      <c r="B188" s="3" t="n"/>
+      <c r="C188" s="3" t="n"/>
     </row>
     <row r="189">
-      <c r="B189" s="2" t="n"/>
-      <c r="C189" s="2" t="n"/>
+      <c r="B189" s="3" t="n"/>
+      <c r="C189" s="3" t="n"/>
     </row>
     <row r="190">
-      <c r="B190" s="2" t="n"/>
-      <c r="C190" s="2" t="n"/>
+      <c r="B190" s="3" t="n"/>
+      <c r="C190" s="3" t="n"/>
     </row>
     <row r="191">
-      <c r="B191" s="2" t="n"/>
-      <c r="C191" s="2" t="n"/>
+      <c r="B191" s="3" t="n"/>
+      <c r="C191" s="3" t="n"/>
     </row>
     <row r="192">
-      <c r="B192" s="2" t="n"/>
-      <c r="C192" s="2" t="n"/>
+      <c r="B192" s="3" t="n"/>
+      <c r="C192" s="3" t="n"/>
     </row>
     <row r="193">
-      <c r="B193" s="2" t="n"/>
-      <c r="C193" s="2" t="n"/>
+      <c r="B193" s="3" t="n"/>
+      <c r="C193" s="3" t="n"/>
     </row>
     <row r="194">
-      <c r="B194" s="2" t="n"/>
-      <c r="C194" s="2" t="n"/>
+      <c r="B194" s="3" t="n"/>
+      <c r="C194" s="3" t="n"/>
     </row>
     <row r="195">
-      <c r="B195" s="2" t="n"/>
-      <c r="C195" s="2" t="n"/>
+      <c r="B195" s="3" t="n"/>
+      <c r="C195" s="3" t="n"/>
     </row>
     <row r="196">
-      <c r="B196" s="2" t="n"/>
-      <c r="C196" s="2" t="n"/>
+      <c r="B196" s="3" t="n"/>
+      <c r="C196" s="3" t="n"/>
     </row>
     <row r="197">
-      <c r="B197" s="2" t="n"/>
-      <c r="C197" s="2" t="n"/>
+      <c r="B197" s="3" t="n"/>
+      <c r="C197" s="3" t="n"/>
     </row>
     <row r="198">
-      <c r="B198" s="2" t="n"/>
-      <c r="C198" s="2" t="n"/>
+      <c r="B198" s="3" t="n"/>
+      <c r="C198" s="3" t="n"/>
     </row>
     <row r="199">
-      <c r="B199" s="2" t="n"/>
-      <c r="C199" s="2" t="n"/>
+      <c r="B199" s="3" t="n"/>
+      <c r="C199" s="3" t="n"/>
     </row>
     <row r="200">
-      <c r="B200" s="2" t="n"/>
-      <c r="C200" s="2" t="n"/>
+      <c r="B200" s="3" t="n"/>
+      <c r="C200" s="3" t="n"/>
     </row>
     <row r="201">
-      <c r="B201" s="2" t="n"/>
-      <c r="C201" s="2" t="n"/>
+      <c r="B201" s="3" t="n"/>
+      <c r="C201" s="3" t="n"/>
     </row>
     <row r="202">
-      <c r="B202" s="2" t="n"/>
-      <c r="C202" s="2" t="n"/>
+      <c r="B202" s="3" t="n"/>
+      <c r="C202" s="3" t="n"/>
     </row>
     <row r="203">
-      <c r="B203" s="2" t="n"/>
-      <c r="C203" s="2" t="n"/>
+      <c r="B203" s="3" t="n"/>
+      <c r="C203" s="3" t="n"/>
     </row>
     <row r="204">
-      <c r="B204" s="2" t="n"/>
-      <c r="C204" s="2" t="n"/>
+      <c r="B204" s="3" t="n"/>
+      <c r="C204" s="3" t="n"/>
     </row>
     <row r="205">
-      <c r="B205" s="2" t="n"/>
-      <c r="C205" s="2" t="n"/>
+      <c r="B205" s="3" t="n"/>
+      <c r="C205" s="3" t="n"/>
     </row>
     <row r="206">
-      <c r="B206" s="2" t="n"/>
-      <c r="C206" s="2" t="n"/>
+      <c r="B206" s="3" t="n"/>
+      <c r="C206" s="3" t="n"/>
     </row>
     <row r="207">
-      <c r="B207" s="2" t="n"/>
-      <c r="C207" s="2" t="n"/>
+      <c r="B207" s="3" t="n"/>
+      <c r="C207" s="3" t="n"/>
     </row>
     <row r="208">
-      <c r="B208" s="2" t="n"/>
-      <c r="C208" s="2" t="n"/>
+      <c r="B208" s="3" t="n"/>
+      <c r="C208" s="3" t="n"/>
     </row>
     <row r="209">
-      <c r="B209" s="2" t="n"/>
-      <c r="C209" s="2" t="n"/>
+      <c r="B209" s="3" t="n"/>
+      <c r="C209" s="3" t="n"/>
     </row>
     <row r="210">
-      <c r="B210" s="2" t="n"/>
-      <c r="C210" s="2" t="n"/>
+      <c r="B210" s="3" t="n"/>
+      <c r="C210" s="3" t="n"/>
     </row>
     <row r="211">
-      <c r="B211" s="2" t="n"/>
-      <c r="C211" s="2" t="n"/>
+      <c r="B211" s="3" t="n"/>
+      <c r="C211" s="3" t="n"/>
     </row>
     <row r="212">
-      <c r="B212" s="2" t="n"/>
-      <c r="C212" s="2" t="n"/>
+      <c r="B212" s="3" t="n"/>
+      <c r="C212" s="3" t="n"/>
     </row>
     <row r="213">
-      <c r="B213" s="2" t="n"/>
-      <c r="C213" s="2" t="n"/>
+      <c r="B213" s="3" t="n"/>
+      <c r="C213" s="3" t="n"/>
     </row>
     <row r="214">
-      <c r="B214" s="2" t="n"/>
-      <c r="C214" s="2" t="n"/>
+      <c r="B214" s="3" t="n"/>
+      <c r="C214" s="3" t="n"/>
     </row>
     <row r="215">
-      <c r="B215" s="2" t="n"/>
-      <c r="C215" s="2" t="n"/>
+      <c r="B215" s="3" t="n"/>
+      <c r="C215" s="3" t="n"/>
     </row>
     <row r="216">
-      <c r="B216" s="2" t="n"/>
-      <c r="C216" s="2" t="n"/>
+      <c r="B216" s="3" t="n"/>
+      <c r="C216" s="3" t="n"/>
     </row>
     <row r="217">
-      <c r="B217" s="2" t="n"/>
-      <c r="C217" s="2" t="n"/>
+      <c r="B217" s="3" t="n"/>
+      <c r="C217" s="3" t="n"/>
     </row>
     <row r="218">
-      <c r="B218" s="2" t="n"/>
-      <c r="C218" s="2" t="n"/>
+      <c r="B218" s="3" t="n"/>
+      <c r="C218" s="3" t="n"/>
     </row>
     <row r="219">
-      <c r="B219" s="2" t="n"/>
-      <c r="C219" s="2" t="n"/>
+      <c r="B219" s="3" t="n"/>
+      <c r="C219" s="3" t="n"/>
     </row>
     <row r="220">
-      <c r="B220" s="2" t="n"/>
-      <c r="C220" s="2" t="n"/>
+      <c r="B220" s="3" t="n"/>
+      <c r="C220" s="3" t="n"/>
     </row>
     <row r="221">
-      <c r="B221" s="2" t="n"/>
-      <c r="C221" s="2" t="n"/>
+      <c r="B221" s="3" t="n"/>
+      <c r="C221" s="3" t="n"/>
     </row>
     <row r="222">
-      <c r="B222" s="2" t="n"/>
-      <c r="C222" s="2" t="n"/>
+      <c r="B222" s="3" t="n"/>
+      <c r="C222" s="3" t="n"/>
     </row>
     <row r="223">
-      <c r="B223" s="2" t="n"/>
-      <c r="C223" s="2" t="n"/>
+      <c r="B223" s="3" t="n"/>
+      <c r="C223" s="3" t="n"/>
     </row>
     <row r="224">
-      <c r="B224" s="2" t="n"/>
-      <c r="C224" s="2" t="n"/>
+      <c r="B224" s="3" t="n"/>
+      <c r="C224" s="3" t="n"/>
     </row>
     <row r="225">
-      <c r="B225" s="2" t="n"/>
-      <c r="C225" s="2" t="n"/>
+      <c r="B225" s="3" t="n"/>
+      <c r="C225" s="3" t="n"/>
     </row>
     <row r="226">
-      <c r="B226" s="2" t="n"/>
-      <c r="C226" s="2" t="n"/>
+      <c r="B226" s="3" t="n"/>
+      <c r="C226" s="3" t="n"/>
     </row>
     <row r="227">
-      <c r="B227" s="2" t="n"/>
-      <c r="C227" s="2" t="n"/>
+      <c r="B227" s="3" t="n"/>
+      <c r="C227" s="3" t="n"/>
     </row>
     <row r="228">
-      <c r="B228" s="2" t="n"/>
-      <c r="C228" s="2" t="n"/>
+      <c r="B228" s="3" t="n"/>
+      <c r="C228" s="3" t="n"/>
     </row>
     <row r="229">
-      <c r="B229" s="2" t="n"/>
-      <c r="C229" s="2" t="n"/>
+      <c r="B229" s="3" t="n"/>
+      <c r="C229" s="3" t="n"/>
     </row>
     <row r="230">
-      <c r="B230" s="2" t="n"/>
-      <c r="C230" s="2" t="n"/>
+      <c r="B230" s="3" t="n"/>
+      <c r="C230" s="3" t="n"/>
     </row>
     <row r="231">
-      <c r="B231" s="2" t="n"/>
-      <c r="C231" s="2" t="n"/>
+      <c r="B231" s="3" t="n"/>
+      <c r="C231" s="3" t="n"/>
     </row>
     <row r="232">
-      <c r="B232" s="2" t="n"/>
-      <c r="C232" s="2" t="n"/>
+      <c r="B232" s="3" t="n"/>
+      <c r="C232" s="3" t="n"/>
     </row>
     <row r="233">
-      <c r="B233" s="2" t="n"/>
-      <c r="C233" s="2" t="n"/>
+      <c r="B233" s="3" t="n"/>
+      <c r="C233" s="3" t="n"/>
     </row>
     <row r="234">
-      <c r="B234" s="2" t="n"/>
-      <c r="C234" s="2" t="n"/>
+      <c r="B234" s="3" t="n"/>
+      <c r="C234" s="3" t="n"/>
     </row>
     <row r="235">
-      <c r="B235" s="2" t="n"/>
-      <c r="C235" s="2" t="n"/>
+      <c r="B235" s="3" t="n"/>
+      <c r="C235" s="3" t="n"/>
     </row>
     <row r="236">
-      <c r="B236" s="2" t="n"/>
-      <c r="C236" s="2" t="n"/>
+      <c r="B236" s="3" t="n"/>
+      <c r="C236" s="3" t="n"/>
     </row>
     <row r="237">
-      <c r="B237" s="2" t="n"/>
-      <c r="C237" s="2" t="n"/>
+      <c r="B237" s="3" t="n"/>
+      <c r="C237" s="3" t="n"/>
     </row>
     <row r="238">
-      <c r="B238" s="2" t="n"/>
-      <c r="C238" s="2" t="n"/>
+      <c r="B238" s="3" t="n"/>
+      <c r="C238" s="3" t="n"/>
     </row>
     <row r="239">
-      <c r="B239" s="2" t="n"/>
-      <c r="C239" s="2" t="n"/>
+      <c r="B239" s="3" t="n"/>
+      <c r="C239" s="3" t="n"/>
     </row>
     <row r="240">
-      <c r="B240" s="2" t="n"/>
-      <c r="C240" s="2" t="n"/>
+      <c r="B240" s="3" t="n"/>
+      <c r="C240" s="3" t="n"/>
     </row>
     <row r="241">
-      <c r="B241" s="2" t="n"/>
-      <c r="C241" s="2" t="n"/>
+      <c r="B241" s="3" t="n"/>
+      <c r="C241" s="3" t="n"/>
     </row>
     <row r="242">
-      <c r="B242" s="2" t="n"/>
-      <c r="C242" s="2" t="n"/>
+      <c r="B242" s="3" t="n"/>
+      <c r="C242" s="3" t="n"/>
     </row>
     <row r="243">
-      <c r="B243" s="2" t="n"/>
-      <c r="C243" s="2" t="n"/>
+      <c r="B243" s="3" t="n"/>
+      <c r="C243" s="3" t="n"/>
     </row>
     <row r="244">
-      <c r="B244" s="2" t="n"/>
-      <c r="C244" s="2" t="n"/>
+      <c r="B244" s="3" t="n"/>
+      <c r="C244" s="3" t="n"/>
     </row>
     <row r="245">
-      <c r="B245" s="2" t="n"/>
-      <c r="C245" s="2" t="n"/>
+      <c r="B245" s="3" t="n"/>
+      <c r="C245" s="3" t="n"/>
     </row>
     <row r="246">
-      <c r="B246" s="2" t="n"/>
-      <c r="C246" s="2" t="n"/>
+      <c r="B246" s="3" t="n"/>
+      <c r="C246" s="3" t="n"/>
     </row>
     <row r="247">
-      <c r="B247" s="2" t="n"/>
-      <c r="C247" s="2" t="n"/>
+      <c r="B247" s="3" t="n"/>
+      <c r="C247" s="3" t="n"/>
     </row>
     <row r="248">
-      <c r="B248" s="2" t="n"/>
-      <c r="C248" s="2" t="n"/>
+      <c r="B248" s="3" t="n"/>
+      <c r="C248" s="3" t="n"/>
     </row>
     <row r="249">
-      <c r="B249" s="2" t="n"/>
-      <c r="C249" s="2" t="n"/>
+      <c r="B249" s="3" t="n"/>
+      <c r="C249" s="3" t="n"/>
     </row>
     <row r="250">
-      <c r="B250" s="2" t="n"/>
-      <c r="C250" s="2" t="n"/>
+      <c r="B250" s="3" t="n"/>
+      <c r="C250" s="3" t="n"/>
     </row>
     <row r="251">
-      <c r="B251" s="2" t="n"/>
-      <c r="C251" s="2" t="n"/>
+      <c r="B251" s="3" t="n"/>
+      <c r="C251" s="3" t="n"/>
     </row>
     <row r="252">
-      <c r="B252" s="2" t="n"/>
-      <c r="C252" s="2" t="n"/>
+      <c r="B252" s="3" t="n"/>
+      <c r="C252" s="3" t="n"/>
     </row>
     <row r="253">
-      <c r="B253" s="2" t="n"/>
-      <c r="C253" s="2" t="n"/>
+      <c r="B253" s="3" t="n"/>
+      <c r="C253" s="3" t="n"/>
     </row>
     <row r="254">
-      <c r="B254" s="2" t="n"/>
-      <c r="C254" s="2" t="n"/>
+      <c r="B254" s="3" t="n"/>
+      <c r="C254" s="3" t="n"/>
     </row>
     <row r="255">
-      <c r="B255" s="2" t="n"/>
-      <c r="C255" s="2" t="n"/>
+      <c r="B255" s="3" t="n"/>
+      <c r="C255" s="3" t="n"/>
     </row>
     <row r="256">
-      <c r="B256" s="2" t="n"/>
-      <c r="C256" s="2" t="n"/>
+      <c r="B256" s="3" t="n"/>
+      <c r="C256" s="3" t="n"/>
     </row>
     <row r="257">
-      <c r="B257" s="2" t="n"/>
-      <c r="C257" s="2" t="n"/>
+      <c r="B257" s="3" t="n"/>
+      <c r="C257" s="3" t="n"/>
     </row>
     <row r="258">
-      <c r="B258" s="2" t="n"/>
-      <c r="C258" s="2" t="n"/>
+      <c r="B258" s="3" t="n"/>
+      <c r="C258" s="3" t="n"/>
     </row>
     <row r="259">
-      <c r="B259" s="2" t="n"/>
-      <c r="C259" s="2" t="n"/>
+      <c r="B259" s="3" t="n"/>
+      <c r="C259" s="3" t="n"/>
     </row>
     <row r="260">
-      <c r="B260" s="2" t="n"/>
-      <c r="C260" s="2" t="n"/>
+      <c r="B260" s="3" t="n"/>
+      <c r="C260" s="3" t="n"/>
     </row>
     <row r="261">
-      <c r="B261" s="2" t="n"/>
-      <c r="C261" s="2" t="n"/>
+      <c r="B261" s="3" t="n"/>
+      <c r="C261" s="3" t="n"/>
     </row>
     <row r="262">
-      <c r="B262" s="2" t="n"/>
-      <c r="C262" s="2" t="n"/>
+      <c r="B262" s="3" t="n"/>
+      <c r="C262" s="3" t="n"/>
     </row>
     <row r="263">
-      <c r="B263" s="2" t="n"/>
-      <c r="C263" s="2" t="n"/>
+      <c r="B263" s="3" t="n"/>
+      <c r="C263" s="3" t="n"/>
     </row>
     <row r="264">
-      <c r="B264" s="2" t="n"/>
-      <c r="C264" s="2" t="n"/>
+      <c r="B264" s="3" t="n"/>
+      <c r="C264" s="3" t="n"/>
     </row>
     <row r="265">
-      <c r="B265" s="2" t="n"/>
-      <c r="C265" s="2" t="n"/>
+      <c r="B265" s="3" t="n"/>
+      <c r="C265" s="3" t="n"/>
     </row>
     <row r="266">
-      <c r="B266" s="2" t="n"/>
-      <c r="C266" s="2" t="n"/>
+      <c r="B266" s="3" t="n"/>
+      <c r="C266" s="3" t="n"/>
     </row>
     <row r="267">
-      <c r="B267" s="2" t="n"/>
-      <c r="C267" s="2" t="n"/>
+      <c r="B267" s="3" t="n"/>
+      <c r="C267" s="3" t="n"/>
     </row>
     <row r="268">
-      <c r="B268" s="2" t="n"/>
-      <c r="C268" s="2" t="n"/>
+      <c r="B268" s="3" t="n"/>
+      <c r="C268" s="3" t="n"/>
     </row>
     <row r="269">
-      <c r="B269" s="2" t="n"/>
-      <c r="C269" s="2" t="n"/>
+      <c r="B269" s="3" t="n"/>
+      <c r="C269" s="3" t="n"/>
     </row>
     <row r="270">
-      <c r="B270" s="2" t="n"/>
-      <c r="C270" s="2" t="n"/>
+      <c r="B270" s="3" t="n"/>
+      <c r="C270" s="3" t="n"/>
     </row>
     <row r="271">
-      <c r="B271" s="2" t="n"/>
-      <c r="C271" s="2" t="n"/>
+      <c r="B271" s="3" t="n"/>
+      <c r="C271" s="3" t="n"/>
     </row>
     <row r="272">
-      <c r="B272" s="2" t="n"/>
-      <c r="C272" s="2" t="n"/>
+      <c r="B272" s="3" t="n"/>
+      <c r="C272" s="3" t="n"/>
     </row>
     <row r="273">
-      <c r="B273" s="2" t="n"/>
-      <c r="C273" s="2" t="n"/>
+      <c r="B273" s="3" t="n"/>
+      <c r="C273" s="3" t="n"/>
     </row>
     <row r="274">
-      <c r="B274" s="2" t="n"/>
-      <c r="C274" s="2" t="n"/>
+      <c r="B274" s="3" t="n"/>
+      <c r="C274" s="3" t="n"/>
     </row>
     <row r="275">
-      <c r="B275" s="2" t="n"/>
-      <c r="C275" s="2" t="n"/>
+      <c r="B275" s="3" t="n"/>
+      <c r="C275" s="3" t="n"/>
     </row>
     <row r="276">
-      <c r="B276" s="2" t="n"/>
-      <c r="C276" s="2" t="n"/>
+      <c r="B276" s="3" t="n"/>
+      <c r="C276" s="3" t="n"/>
     </row>
     <row r="277">
-      <c r="B277" s="2" t="n"/>
-      <c r="C277" s="2" t="n"/>
+      <c r="B277" s="3" t="n"/>
+      <c r="C277" s="3" t="n"/>
     </row>
     <row r="278">
-      <c r="B278" s="2" t="n"/>
-      <c r="C278" s="2" t="n"/>
+      <c r="B278" s="3" t="n"/>
+      <c r="C278" s="3" t="n"/>
     </row>
     <row r="279">
-      <c r="B279" s="2" t="n"/>
-      <c r="C279" s="2" t="n"/>
+      <c r="B279" s="3" t="n"/>
+      <c r="C279" s="3" t="n"/>
     </row>
     <row r="280">
-      <c r="B280" s="2" t="n"/>
-      <c r="C280" s="2" t="n"/>
+      <c r="B280" s="3" t="n"/>
+      <c r="C280" s="3" t="n"/>
     </row>
     <row r="281">
-      <c r="B281" s="2" t="n"/>
-      <c r="C281" s="2" t="n"/>
+      <c r="B281" s="3" t="n"/>
+      <c r="C281" s="3" t="n"/>
     </row>
     <row r="282">
-      <c r="B282" s="2" t="n"/>
-      <c r="C282" s="2" t="n"/>
+      <c r="B282" s="3" t="n"/>
+      <c r="C282" s="3" t="n"/>
     </row>
     <row r="283">
-      <c r="B283" s="2" t="n"/>
-      <c r="C283" s="2" t="n"/>
+      <c r="B283" s="3" t="n"/>
+      <c r="C283" s="3" t="n"/>
     </row>
     <row r="284">
-      <c r="B284" s="2" t="n"/>
-      <c r="C284" s="2" t="n"/>
+      <c r="B284" s="3" t="n"/>
+      <c r="C284" s="3" t="n"/>
     </row>
     <row r="285">
-      <c r="B285" s="2" t="n"/>
-      <c r="C285" s="2" t="n"/>
+      <c r="B285" s="3" t="n"/>
+      <c r="C285" s="3" t="n"/>
     </row>
     <row r="286">
-      <c r="B286" s="2" t="n"/>
-      <c r="C286" s="2" t="n"/>
+      <c r="B286" s="3" t="n"/>
+      <c r="C286" s="3" t="n"/>
     </row>
     <row r="287">
-      <c r="B287" s="2" t="n"/>
-      <c r="C287" s="2" t="n"/>
+      <c r="B287" s="3" t="n"/>
+      <c r="C287" s="3" t="n"/>
     </row>
     <row r="288">
-      <c r="B288" s="2" t="n"/>
-      <c r="C288" s="2" t="n"/>
+      <c r="B288" s="3" t="n"/>
+      <c r="C288" s="3" t="n"/>
     </row>
     <row r="289">
-      <c r="B289" s="2" t="n"/>
-      <c r="C289" s="2" t="n"/>
+      <c r="B289" s="3" t="n"/>
+      <c r="C289" s="3" t="n"/>
     </row>
     <row r="290">
-      <c r="B290" s="2" t="n"/>
-      <c r="C290" s="2" t="n"/>
+      <c r="B290" s="3" t="n"/>
+      <c r="C290" s="3" t="n"/>
     </row>
     <row r="291">
-      <c r="B291" s="2" t="n"/>
-      <c r="C291" s="2" t="n"/>
+      <c r="B291" s="3" t="n"/>
+      <c r="C291" s="3" t="n"/>
     </row>
     <row r="292">
-      <c r="B292" s="2" t="n"/>
-      <c r="C292" s="2" t="n"/>
+      <c r="B292" s="3" t="n"/>
+      <c r="C292" s="3" t="n"/>
     </row>
     <row r="293">
-      <c r="B293" s="2" t="n"/>
-      <c r="C293" s="2" t="n"/>
+      <c r="B293" s="3" t="n"/>
+      <c r="C293" s="3" t="n"/>
     </row>
     <row r="294">
-      <c r="B294" s="2" t="n"/>
-      <c r="C294" s="2" t="n"/>
+      <c r="B294" s="3" t="n"/>
+      <c r="C294" s="3" t="n"/>
     </row>
     <row r="295">
-      <c r="B295" s="2" t="n"/>
-      <c r="C295" s="2" t="n"/>
+      <c r="B295" s="3" t="n"/>
+      <c r="C295" s="3" t="n"/>
     </row>
     <row r="296">
-      <c r="B296" s="2" t="n"/>
-      <c r="C296" s="2" t="n"/>
+      <c r="B296" s="3" t="n"/>
+      <c r="C296" s="3" t="n"/>
     </row>
     <row r="297">
-      <c r="B297" s="2" t="n"/>
-      <c r="C297" s="2" t="n"/>
+      <c r="B297" s="3" t="n"/>
+      <c r="C297" s="3" t="n"/>
     </row>
     <row r="298">
-      <c r="B298" s="2" t="n"/>
-      <c r="C298" s="2" t="n"/>
+      <c r="B298" s="3" t="n"/>
+      <c r="C298" s="3" t="n"/>
     </row>
     <row r="299">
-      <c r="B299" s="2" t="n"/>
-      <c r="C299" s="2" t="n"/>
+      <c r="B299" s="3" t="n"/>
+      <c r="C299" s="3" t="n"/>
     </row>
     <row r="300">
-      <c r="B300" s="2" t="n"/>
-      <c r="C300" s="2" t="n"/>
+      <c r="B300" s="3" t="n"/>
+      <c r="C300" s="3" t="n"/>
     </row>
     <row r="301">
-      <c r="B301" s="2" t="n"/>
-      <c r="C301" s="2" t="n"/>
+      <c r="B301" s="3" t="n"/>
+      <c r="C301" s="3" t="n"/>
     </row>
     <row r="302">
-      <c r="B302" s="2" t="n"/>
-      <c r="C302" s="2" t="n"/>
+      <c r="B302" s="3" t="n"/>
+      <c r="C302" s="3" t="n"/>
     </row>
     <row r="303">
-      <c r="B303" s="2" t="n"/>
-      <c r="C303" s="2" t="n"/>
+      <c r="B303" s="3" t="n"/>
+      <c r="C303" s="3" t="n"/>
     </row>
     <row r="304">
-      <c r="B304" s="2" t="n"/>
-      <c r="C304" s="2" t="n"/>
+      <c r="B304" s="3" t="n"/>
+      <c r="C304" s="3" t="n"/>
     </row>
     <row r="305">
-      <c r="B305" s="2" t="n"/>
-      <c r="C305" s="2" t="n"/>
+      <c r="B305" s="3" t="n"/>
+      <c r="C305" s="3" t="n"/>
     </row>
     <row r="306">
-      <c r="B306" s="2" t="n"/>
-      <c r="C306" s="2" t="n"/>
+      <c r="B306" s="3" t="n"/>
+      <c r="C306" s="3" t="n"/>
     </row>
     <row r="307">
-      <c r="B307" s="2" t="n"/>
-      <c r="C307" s="2" t="n"/>
+      <c r="B307" s="3" t="n"/>
+      <c r="C307" s="3" t="n"/>
     </row>
     <row r="308">
-      <c r="B308" s="2" t="n"/>
-      <c r="C308" s="2" t="n"/>
+      <c r="B308" s="3" t="n"/>
+      <c r="C308" s="3" t="n"/>
     </row>
     <row r="309">
-      <c r="B309" s="2" t="n"/>
-      <c r="C309" s="2" t="n"/>
+      <c r="B309" s="3" t="n"/>
+      <c r="C309" s="3" t="n"/>
     </row>
     <row r="310">
-      <c r="B310" s="2" t="n"/>
-      <c r="C310" s="2" t="n"/>
+      <c r="B310" s="3" t="n"/>
+      <c r="C310" s="3" t="n"/>
     </row>
     <row r="311">
-      <c r="B311" s="2" t="n"/>
-      <c r="C311" s="2" t="n"/>
+      <c r="B311" s="3" t="n"/>
+      <c r="C311" s="3" t="n"/>
     </row>
     <row r="312">
-      <c r="B312" s="2" t="n"/>
-      <c r="C312" s="2" t="n"/>
+      <c r="B312" s="3" t="n"/>
+      <c r="C312" s="3" t="n"/>
     </row>
     <row r="313">
-      <c r="B313" s="2" t="n"/>
-      <c r="C313" s="2" t="n"/>
+      <c r="B313" s="3" t="n"/>
+      <c r="C313" s="3" t="n"/>
     </row>
     <row r="314">
-      <c r="B314" s="2" t="n"/>
-      <c r="C314" s="2" t="n"/>
+      <c r="B314" s="3" t="n"/>
+      <c r="C314" s="3" t="n"/>
     </row>
     <row r="315">
-      <c r="B315" s="2" t="n"/>
-      <c r="C315" s="2" t="n"/>
+      <c r="B315" s="3" t="n"/>
+      <c r="C315" s="3" t="n"/>
     </row>
     <row r="316">
-      <c r="B316" s="2" t="n"/>
-      <c r="C316" s="2" t="n"/>
+      <c r="B316" s="3" t="n"/>
+      <c r="C316" s="3" t="n"/>
     </row>
     <row r="317">
-      <c r="B317" s="2" t="n"/>
-      <c r="C317" s="2" t="n"/>
+      <c r="B317" s="3" t="n"/>
+      <c r="C317" s="3" t="n"/>
     </row>
     <row r="318">
-      <c r="B318" s="2" t="n"/>
-      <c r="C318" s="2" t="n"/>
+      <c r="B318" s="3" t="n"/>
+      <c r="C318" s="3" t="n"/>
     </row>
     <row r="319">
-      <c r="B319" s="2" t="n"/>
-      <c r="C319" s="2" t="n"/>
+      <c r="B319" s="3" t="n"/>
+      <c r="C319" s="3" t="n"/>
     </row>
     <row r="320">
-      <c r="B320" s="2" t="n"/>
-      <c r="C320" s="2" t="n"/>
+      <c r="B320" s="3" t="n"/>
+      <c r="C320" s="3" t="n"/>
     </row>
     <row r="321">
-      <c r="B321" s="2" t="n"/>
-      <c r="C321" s="2" t="n"/>
+      <c r="B321" s="3" t="n"/>
+      <c r="C321" s="3" t="n"/>
     </row>
     <row r="322">
-      <c r="B322" s="2" t="n"/>
-      <c r="C322" s="2" t="n"/>
+      <c r="B322" s="3" t="n"/>
+      <c r="C322" s="3" t="n"/>
     </row>
     <row r="323">
-      <c r="B323" s="2" t="n"/>
-      <c r="C323" s="2" t="n"/>
+      <c r="B323" s="3" t="n"/>
+      <c r="C323" s="3" t="n"/>
     </row>
     <row r="324">
-      <c r="B324" s="2" t="n"/>
-      <c r="C324" s="2" t="n"/>
+      <c r="B324" s="3" t="n"/>
+      <c r="C324" s="3" t="n"/>
     </row>
     <row r="325">
-      <c r="B325" s="2" t="n"/>
-      <c r="C325" s="2" t="n"/>
+      <c r="B325" s="3" t="n"/>
+      <c r="C325" s="3" t="n"/>
     </row>
     <row r="326">
-      <c r="B326" s="2" t="n"/>
-      <c r="C326" s="2" t="n"/>
+      <c r="B326" s="3" t="n"/>
+      <c r="C326" s="3" t="n"/>
     </row>
     <row r="327">
-      <c r="B327" s="2" t="n"/>
-      <c r="C327" s="2" t="n"/>
+      <c r="B327" s="3" t="n"/>
+      <c r="C327" s="3" t="n"/>
     </row>
     <row r="328">
-      <c r="B328" s="2" t="n"/>
-      <c r="C328" s="2" t="n"/>
+      <c r="B328" s="3" t="n"/>
+      <c r="C328" s="3" t="n"/>
     </row>
     <row r="329">
-      <c r="B329" s="2" t="n"/>
-      <c r="C329" s="2" t="n"/>
+      <c r="B329" s="3" t="n"/>
+      <c r="C329" s="3" t="n"/>
     </row>
     <row r="330">
-      <c r="B330" s="2" t="n"/>
-      <c r="C330" s="2" t="n"/>
+      <c r="B330" s="3" t="n"/>
+      <c r="C330" s="3" t="n"/>
     </row>
     <row r="331">
-      <c r="B331" s="2" t="n"/>
-      <c r="C331" s="2" t="n"/>
+      <c r="B331" s="3" t="n"/>
+      <c r="C331" s="3" t="n"/>
     </row>
     <row r="332">
-      <c r="B332" s="2" t="n"/>
-      <c r="C332" s="2" t="n"/>
+      <c r="B332" s="3" t="n"/>
+      <c r="C332" s="3" t="n"/>
     </row>
     <row r="333">
-      <c r="B333" s="2" t="n"/>
-      <c r="C333" s="2" t="n"/>
+      <c r="B333" s="3" t="n"/>
+      <c r="C333" s="3" t="n"/>
     </row>
     <row r="334">
-      <c r="B334" s="2" t="n"/>
-      <c r="C334" s="2" t="n"/>
+      <c r="B334" s="3" t="n"/>
+      <c r="C334" s="3" t="n"/>
     </row>
     <row r="335">
-      <c r="B335" s="2" t="n"/>
-      <c r="C335" s="2" t="n"/>
+      <c r="B335" s="3" t="n"/>
+      <c r="C335" s="3" t="n"/>
     </row>
     <row r="336">
-      <c r="B336" s="2" t="n"/>
-      <c r="C336" s="2" t="n"/>
+      <c r="B336" s="3" t="n"/>
+      <c r="C336" s="3" t="n"/>
     </row>
     <row r="337">
-      <c r="B337" s="2" t="n"/>
-      <c r="C337" s="2" t="n"/>
+      <c r="B337" s="3" t="n"/>
+      <c r="C337" s="3" t="n"/>
     </row>
     <row r="338">
-      <c r="B338" s="2" t="n"/>
-      <c r="C338" s="2" t="n"/>
+      <c r="B338" s="3" t="n"/>
+      <c r="C338" s="3" t="n"/>
     </row>
     <row r="339">
-      <c r="B339" s="2" t="n"/>
-      <c r="C339" s="2" t="n"/>
+      <c r="B339" s="3" t="n"/>
+      <c r="C339" s="3" t="n"/>
     </row>
     <row r="340">
-      <c r="B340" s="2" t="n"/>
-      <c r="C340" s="2" t="n"/>
+      <c r="B340" s="3" t="n"/>
+      <c r="C340" s="3" t="n"/>
     </row>
     <row r="341">
-      <c r="B341" s="2" t="n"/>
-      <c r="C341" s="2" t="n"/>
+      <c r="B341" s="3" t="n"/>
+      <c r="C341" s="3" t="n"/>
     </row>
     <row r="342">
-      <c r="B342" s="2" t="n"/>
-      <c r="C342" s="2" t="n"/>
+      <c r="B342" s="3" t="n"/>
+      <c r="C342" s="3" t="n"/>
     </row>
     <row r="343">
-      <c r="B343" s="2" t="n"/>
-      <c r="C343" s="2" t="n"/>
+      <c r="B343" s="3" t="n"/>
+      <c r="C343" s="3" t="n"/>
     </row>
     <row r="344">
-      <c r="B344" s="2" t="n"/>
-      <c r="C344" s="2" t="n"/>
+      <c r="B344" s="3" t="n"/>
+      <c r="C344" s="3" t="n"/>
     </row>
     <row r="345">
-      <c r="B345" s="2" t="n"/>
-      <c r="C345" s="2" t="n"/>
+      <c r="B345" s="3" t="n"/>
+      <c r="C345" s="3" t="n"/>
     </row>
     <row r="346">
-      <c r="B346" s="2" t="n"/>
-      <c r="C346" s="2" t="n"/>
+      <c r="B346" s="3" t="n"/>
+      <c r="C346" s="3" t="n"/>
     </row>
     <row r="347">
-      <c r="B347" s="2" t="n"/>
-      <c r="C347" s="2" t="n"/>
+      <c r="B347" s="3" t="n"/>
+      <c r="C347" s="3" t="n"/>
     </row>
     <row r="348">
-      <c r="B348" s="2" t="n"/>
-      <c r="C348" s="2" t="n"/>
+      <c r="B348" s="3" t="n"/>
+      <c r="C348" s="3" t="n"/>
     </row>
     <row r="349">
-      <c r="B349" s="2" t="n"/>
-      <c r="C349" s="2" t="n"/>
+      <c r="B349" s="3" t="n"/>
+      <c r="C349" s="3" t="n"/>
     </row>
     <row r="350">
-      <c r="B350" s="2" t="n"/>
-      <c r="C350" s="2" t="n"/>
+      <c r="B350" s="3" t="n"/>
+      <c r="C350" s="3" t="n"/>
     </row>
     <row r="351">
-      <c r="B351" s="2" t="n"/>
-      <c r="C351" s="2" t="n"/>
+      <c r="B351" s="3" t="n"/>
+      <c r="C351" s="3" t="n"/>
     </row>
     <row r="352">
-      <c r="B352" s="2" t="n"/>
-      <c r="C352" s="2" t="n"/>
+      <c r="B352" s="3" t="n"/>
+      <c r="C352" s="3" t="n"/>
     </row>
     <row r="353">
-      <c r="B353" s="2" t="n"/>
-      <c r="C353" s="2" t="n"/>
+      <c r="B353" s="3" t="n"/>
+      <c r="C353" s="3" t="n"/>
     </row>
     <row r="354">
-      <c r="B354" s="2" t="n"/>
-      <c r="C354" s="2" t="n"/>
+      <c r="B354" s="3" t="n"/>
+      <c r="C354" s="3" t="n"/>
     </row>
     <row r="355">
-      <c r="B355" s="2" t="n"/>
-      <c r="C355" s="2" t="n"/>
+      <c r="B355" s="3" t="n"/>
+      <c r="C355" s="3" t="n"/>
     </row>
     <row r="356">
-      <c r="B356" s="2" t="n"/>
-      <c r="C356" s="2" t="n"/>
+      <c r="B356" s="3" t="n"/>
+      <c r="C356" s="3" t="n"/>
     </row>
     <row r="357">
-      <c r="B357" s="2" t="n"/>
-      <c r="C357" s="2" t="n"/>
+      <c r="B357" s="3" t="n"/>
+      <c r="C357" s="3" t="n"/>
     </row>
     <row r="358">
-      <c r="B358" s="2" t="n"/>
-      <c r="C358" s="2" t="n"/>
+      <c r="B358" s="3" t="n"/>
+      <c r="C358" s="3" t="n"/>
     </row>
     <row r="359">
-      <c r="B359" s="2" t="n"/>
-      <c r="C359" s="2" t="n"/>
+      <c r="B359" s="3" t="n"/>
+      <c r="C359" s="3" t="n"/>
     </row>
     <row r="360">
-      <c r="B360" s="2" t="n"/>
-      <c r="C360" s="2" t="n"/>
+      <c r="B360" s="3" t="n"/>
+      <c r="C360" s="3" t="n"/>
     </row>
     <row r="361">
-      <c r="B361" s="2" t="n"/>
-      <c r="C361" s="2" t="n"/>
+      <c r="B361" s="3" t="n"/>
+      <c r="C361" s="3" t="n"/>
     </row>
     <row r="362">
-      <c r="B362" s="2" t="n"/>
-      <c r="C362" s="2" t="n"/>
+      <c r="B362" s="3" t="n"/>
+      <c r="C362" s="3" t="n"/>
     </row>
     <row r="363">
-      <c r="B363" s="2" t="n"/>
-      <c r="C363" s="2" t="n"/>
+      <c r="B363" s="3" t="n"/>
+      <c r="C363" s="3" t="n"/>
     </row>
     <row r="364">
-      <c r="B364" s="2" t="n"/>
-      <c r="C364" s="2" t="n"/>
+      <c r="B364" s="3" t="n"/>
+      <c r="C364" s="3" t="n"/>
     </row>
     <row r="365">
-      <c r="B365" s="2" t="n"/>
-      <c r="C365" s="2" t="n"/>
+      <c r="B365" s="3" t="n"/>
+      <c r="C365" s="3" t="n"/>
     </row>
     <row r="366">
-      <c r="B366" s="2" t="n"/>
-      <c r="C366" s="2" t="n"/>
+      <c r="B366" s="3" t="n"/>
+      <c r="C366" s="3" t="n"/>
     </row>
     <row r="367">
-      <c r="B367" s="2" t="n"/>
-      <c r="C367" s="2" t="n"/>
+      <c r="B367" s="3" t="n"/>
+      <c r="C367" s="3" t="n"/>
     </row>
     <row r="368">
-      <c r="B368" s="2" t="n"/>
-      <c r="C368" s="2" t="n"/>
+      <c r="B368" s="3" t="n"/>
+      <c r="C368" s="3" t="n"/>
     </row>
     <row r="369">
-      <c r="B369" s="2" t="n"/>
-      <c r="C369" s="2" t="n"/>
+      <c r="B369" s="3" t="n"/>
+      <c r="C369" s="3" t="n"/>
     </row>
     <row r="370">
-      <c r="B370" s="2" t="n"/>
-      <c r="C370" s="2" t="n"/>
+      <c r="B370" s="3" t="n"/>
+      <c r="C370" s="3" t="n"/>
     </row>
     <row r="371">
-      <c r="B371" s="2" t="n"/>
-      <c r="C371" s="2" t="n"/>
+      <c r="B371" s="3" t="n"/>
+      <c r="C371" s="3" t="n"/>
     </row>
     <row r="372">
-      <c r="B372" s="2" t="n"/>
-      <c r="C372" s="2" t="n"/>
+      <c r="B372" s="3" t="n"/>
+      <c r="C372" s="3" t="n"/>
     </row>
     <row r="373">
-      <c r="B373" s="2" t="n"/>
-      <c r="C373" s="2" t="n"/>
+      <c r="B373" s="3" t="n"/>
+      <c r="C373" s="3" t="n"/>
     </row>
     <row r="374">
-      <c r="B374" s="2" t="n"/>
-      <c r="C374" s="2" t="n"/>
+      <c r="B374" s="3" t="n"/>
+      <c r="C374" s="3" t="n"/>
     </row>
     <row r="375">
-      <c r="B375" s="2" t="n"/>
-      <c r="C375" s="2" t="n"/>
+      <c r="B375" s="3" t="n"/>
+      <c r="C375" s="3" t="n"/>
     </row>
     <row r="376">
-      <c r="B376" s="2" t="n"/>
-      <c r="C376" s="2" t="n"/>
+      <c r="B376" s="3" t="n"/>
+      <c r="C376" s="3" t="n"/>
     </row>
     <row r="377">
-      <c r="B377" s="2" t="n"/>
-      <c r="C377" s="2" t="n"/>
+      <c r="B377" s="3" t="n"/>
+      <c r="C377" s="3" t="n"/>
     </row>
     <row r="378">
-      <c r="B378" s="2" t="n"/>
-      <c r="C378" s="2" t="n"/>
+      <c r="B378" s="3" t="n"/>
+      <c r="C378" s="3" t="n"/>
     </row>
     <row r="379">
-      <c r="B379" s="2" t="n"/>
-      <c r="C379" s="2" t="n"/>
+      <c r="B379" s="3" t="n"/>
+      <c r="C379" s="3" t="n"/>
     </row>
     <row r="380">
-      <c r="B380" s="2" t="n"/>
-      <c r="C380" s="2" t="n"/>
+      <c r="B380" s="3" t="n"/>
+      <c r="C380" s="3" t="n"/>
     </row>
     <row r="381">
-      <c r="B381" s="2" t="n"/>
-      <c r="C381" s="2" t="n"/>
+      <c r="B381" s="3" t="n"/>
+      <c r="C381" s="3" t="n"/>
     </row>
     <row r="382">
-      <c r="B382" s="2" t="n"/>
-      <c r="C382" s="2" t="n"/>
+      <c r="B382" s="3" t="n"/>
+      <c r="C382" s="3" t="n"/>
     </row>
     <row r="383">
-      <c r="B383" s="2" t="n"/>
-      <c r="C383" s="2" t="n"/>
+      <c r="B383" s="3" t="n"/>
+      <c r="C383" s="3" t="n"/>
     </row>
     <row r="384">
-      <c r="B384" s="2" t="n"/>
-      <c r="C384" s="2" t="n"/>
+      <c r="B384" s="3" t="n"/>
+      <c r="C384" s="3" t="n"/>
     </row>
     <row r="385">
-      <c r="B385" s="2" t="n"/>
-      <c r="C385" s="2" t="n"/>
+      <c r="B385" s="3" t="n"/>
+      <c r="C385" s="3" t="n"/>
     </row>
     <row r="386">
-      <c r="B386" s="2" t="n"/>
-      <c r="C386" s="2" t="n"/>
+      <c r="B386" s="3" t="n"/>
+      <c r="C386" s="3" t="n"/>
     </row>
     <row r="387">
-      <c r="B387" s="2" t="n"/>
-      <c r="C387" s="2" t="n"/>
+      <c r="B387" s="3" t="n"/>
+      <c r="C387" s="3" t="n"/>
     </row>
     <row r="388">
-      <c r="B388" s="2" t="n"/>
-      <c r="C388" s="2" t="n"/>
+      <c r="B388" s="3" t="n"/>
+      <c r="C388" s="3" t="n"/>
     </row>
     <row r="389">
-      <c r="B389" s="2" t="n"/>
-      <c r="C389" s="2" t="n"/>
+      <c r="B389" s="3" t="n"/>
+      <c r="C389" s="3" t="n"/>
     </row>
     <row r="390">
-      <c r="B390" s="2" t="n"/>
-      <c r="C390" s="2" t="n"/>
+      <c r="B390" s="3" t="n"/>
+      <c r="C390" s="3" t="n"/>
     </row>
     <row r="391">
-      <c r="B391" s="2" t="n"/>
-      <c r="C391" s="2" t="n"/>
+      <c r="B391" s="3" t="n"/>
+      <c r="C391" s="3" t="n"/>
     </row>
     <row r="392">
-      <c r="B392" s="2" t="n"/>
-      <c r="C392" s="2" t="n"/>
+      <c r="B392" s="3" t="n"/>
+      <c r="C392" s="3" t="n"/>
     </row>
     <row r="393">
-      <c r="B393" s="2" t="n"/>
-      <c r="C393" s="2" t="n"/>
+      <c r="B393" s="3" t="n"/>
+      <c r="C393" s="3" t="n"/>
     </row>
     <row r="394">
-      <c r="B394" s="2" t="n"/>
-      <c r="C394" s="2" t="n"/>
+      <c r="B394" s="3" t="n"/>
+      <c r="C394" s="3" t="n"/>
     </row>
     <row r="395">
-      <c r="B395" s="2" t="n"/>
-      <c r="C395" s="2" t="n"/>
+      <c r="B395" s="3" t="n"/>
+      <c r="C395" s="3" t="n"/>
     </row>
     <row r="396">
-      <c r="B396" s="2" t="n"/>
-      <c r="C396" s="2" t="n"/>
+      <c r="B396" s="3" t="n"/>
+      <c r="C396" s="3" t="n"/>
     </row>
     <row r="397">
-      <c r="B397" s="2" t="n"/>
-      <c r="C397" s="2" t="n"/>
+      <c r="B397" s="3" t="n"/>
+      <c r="C397" s="3" t="n"/>
     </row>
     <row r="398">
-      <c r="B398" s="2" t="n"/>
-      <c r="C398" s="2" t="n"/>
+      <c r="B398" s="3" t="n"/>
+      <c r="C398" s="3" t="n"/>
     </row>
     <row r="399">
-      <c r="B399" s="2" t="n"/>
-      <c r="C399" s="2" t="n"/>
+      <c r="B399" s="3" t="n"/>
+      <c r="C399" s="3" t="n"/>
     </row>
     <row r="400">
-      <c r="B400" s="2" t="n"/>
-      <c r="C400" s="2" t="n"/>
+      <c r="B400" s="3" t="n"/>
+      <c r="C400" s="3" t="n"/>
     </row>
     <row r="401">
-      <c r="B401" s="2" t="n"/>
-      <c r="C401" s="2" t="n"/>
+      <c r="B401" s="3" t="n"/>
+      <c r="C401" s="3" t="n"/>
     </row>
     <row r="402">
-      <c r="B402" s="2" t="n"/>
-      <c r="C402" s="2" t="n"/>
+      <c r="B402" s="3" t="n"/>
+      <c r="C402" s="3" t="n"/>
     </row>
     <row r="403">
-      <c r="B403" s="2" t="n"/>
-      <c r="C403" s="2" t="n"/>
+      <c r="B403" s="3" t="n"/>
+      <c r="C403" s="3" t="n"/>
     </row>
     <row r="404">
-      <c r="B404" s="2" t="n"/>
-      <c r="C404" s="2" t="n"/>
+      <c r="B404" s="3" t="n"/>
+      <c r="C404" s="3" t="n"/>
     </row>
     <row r="405">
-      <c r="B405" s="2" t="n"/>
-      <c r="C405" s="2" t="n"/>
+      <c r="B405" s="3" t="n"/>
+      <c r="C405" s="3" t="n"/>
     </row>
     <row r="406">
-      <c r="B406" s="2" t="n"/>
-      <c r="C406" s="2" t="n"/>
+      <c r="B406" s="3" t="n"/>
+      <c r="C406" s="3" t="n"/>
     </row>
     <row r="407">
-      <c r="B407" s="2" t="n"/>
-      <c r="C407" s="2" t="n"/>
+      <c r="B407" s="3" t="n"/>
+      <c r="C407" s="3" t="n"/>
     </row>
     <row r="408">
-      <c r="B408" s="2" t="n"/>
-      <c r="C408" s="2" t="n"/>
+      <c r="B408" s="3" t="n"/>
+      <c r="C408" s="3" t="n"/>
     </row>
     <row r="409">
-      <c r="B409" s="2" t="n"/>
-      <c r="C409" s="2" t="n"/>
+      <c r="B409" s="3" t="n"/>
+      <c r="C409" s="3" t="n"/>
     </row>
     <row r="410">
-      <c r="B410" s="2" t="n"/>
-      <c r="C410" s="2" t="n"/>
+      <c r="B410" s="3" t="n"/>
+      <c r="C410" s="3" t="n"/>
     </row>
     <row r="411">
-      <c r="B411" s="2" t="n"/>
-      <c r="C411" s="2" t="n"/>
+      <c r="B411" s="3" t="n"/>
+      <c r="C411" s="3" t="n"/>
     </row>
     <row r="412">
-      <c r="B412" s="2" t="n"/>
-      <c r="C412" s="2" t="n"/>
+      <c r="B412" s="3" t="n"/>
+      <c r="C412" s="3" t="n"/>
     </row>
     <row r="413">
-      <c r="B413" s="2" t="n"/>
-      <c r="C413" s="2" t="n"/>
+      <c r="B413" s="3" t="n"/>
+      <c r="C413" s="3" t="n"/>
     </row>
     <row r="414">
-      <c r="B414" s="2" t="n"/>
-      <c r="C414" s="2" t="n"/>
+      <c r="B414" s="3" t="n"/>
+      <c r="C414" s="3" t="n"/>
     </row>
     <row r="415">
-      <c r="B415" s="2" t="n"/>
-      <c r="C415" s="2" t="n"/>
+      <c r="B415" s="3" t="n"/>
+      <c r="C415" s="3" t="n"/>
     </row>
     <row r="416">
-      <c r="B416" s="2" t="n"/>
-      <c r="C416" s="2" t="n"/>
+      <c r="B416" s="3" t="n"/>
+      <c r="C416" s="3" t="n"/>
     </row>
     <row r="417">
-      <c r="B417" s="2" t="n"/>
-      <c r="C417" s="2" t="n"/>
+      <c r="B417" s="3" t="n"/>
+      <c r="C417" s="3" t="n"/>
     </row>
     <row r="418">
-      <c r="B418" s="2" t="n"/>
-      <c r="C418" s="2" t="n"/>
+      <c r="B418" s="3" t="n"/>
+      <c r="C418" s="3" t="n"/>
     </row>
     <row r="419">
-      <c r="B419" s="2" t="n"/>
-      <c r="C419" s="2" t="n"/>
+      <c r="B419" s="3" t="n"/>
+      <c r="C419" s="3" t="n"/>
     </row>
     <row r="420">
-      <c r="B420" s="2" t="n"/>
-      <c r="C420" s="2" t="n"/>
+      <c r="B420" s="3" t="n"/>
+      <c r="C420" s="3" t="n"/>
     </row>
     <row r="421">
-      <c r="B421" s="2" t="n"/>
-      <c r="C421" s="2" t="n"/>
+      <c r="B421" s="3" t="n"/>
+      <c r="C421" s="3" t="n"/>
     </row>
     <row r="422">
-      <c r="B422" s="2" t="n"/>
-      <c r="C422" s="2" t="n"/>
+      <c r="B422" s="3" t="n"/>
+      <c r="C422" s="3" t="n"/>
     </row>
     <row r="423">
-      <c r="B423" s="2" t="n"/>
-      <c r="C423" s="2" t="n"/>
+      <c r="B423" s="3" t="n"/>
+      <c r="C423" s="3" t="n"/>
     </row>
     <row r="424">
-      <c r="B424" s="2" t="n"/>
-      <c r="C424" s="2" t="n"/>
+      <c r="B424" s="3" t="n"/>
+      <c r="C424" s="3" t="n"/>
     </row>
     <row r="425">
-      <c r="B425" s="2" t="n"/>
-      <c r="C425" s="2" t="n"/>
+      <c r="B425" s="3" t="n"/>
+      <c r="C425" s="3" t="n"/>
     </row>
     <row r="426">
-      <c r="B426" s="2" t="n"/>
-      <c r="C426" s="2" t="n"/>
+      <c r="B426" s="3" t="n"/>
+      <c r="C426" s="3" t="n"/>
     </row>
     <row r="427">
-      <c r="B427" s="2" t="n"/>
-      <c r="C427" s="2" t="n"/>
+      <c r="B427" s="3" t="n"/>
+      <c r="C427" s="3" t="n"/>
     </row>
     <row r="428">
-      <c r="B428" s="2" t="n"/>
-      <c r="C428" s="2" t="n"/>
+      <c r="B428" s="3" t="n"/>
+      <c r="C428" s="3" t="n"/>
     </row>
     <row r="429">
-      <c r="B429" s="2" t="n"/>
-      <c r="C429" s="2" t="n"/>
+      <c r="B429" s="3" t="n"/>
+      <c r="C429" s="3" t="n"/>
     </row>
     <row r="430">
-      <c r="B430" s="2" t="n"/>
-      <c r="C430" s="2" t="n"/>
+      <c r="B430" s="3" t="n"/>
+      <c r="C430" s="3" t="n"/>
     </row>
     <row r="431">
-      <c r="B431" s="2" t="n"/>
-      <c r="C431" s="2" t="n"/>
+      <c r="B431" s="3" t="n"/>
+      <c r="C431" s="3" t="n"/>
     </row>
     <row r="432">
-      <c r="B432" s="2" t="n"/>
-      <c r="C432" s="2" t="n"/>
+      <c r="B432" s="3" t="n"/>
+      <c r="C432" s="3" t="n"/>
     </row>
     <row r="433">
-      <c r="B433" s="2" t="n"/>
-      <c r="C433" s="2" t="n"/>
+      <c r="B433" s="3" t="n"/>
+      <c r="C433" s="3" t="n"/>
     </row>
     <row r="434">
-      <c r="B434" s="2" t="n"/>
-      <c r="C434" s="2" t="n"/>
+      <c r="B434" s="3" t="n"/>
+      <c r="C434" s="3" t="n"/>
     </row>
     <row r="435">
-      <c r="B435" s="2" t="n"/>
-      <c r="C435" s="2" t="n"/>
+      <c r="B435" s="3" t="n"/>
+      <c r="C435" s="3" t="n"/>
     </row>
     <row r="436">
-      <c r="B436" s="2" t="n"/>
-      <c r="C436" s="2" t="n"/>
+      <c r="B436" s="3" t="n"/>
+      <c r="C436" s="3" t="n"/>
     </row>
     <row r="437">
-      <c r="B437" s="2" t="n"/>
-      <c r="C437" s="2" t="n"/>
+      <c r="B437" s="3" t="n"/>
+      <c r="C437" s="3" t="n"/>
     </row>
     <row r="438">
-      <c r="B438" s="2" t="n"/>
-      <c r="C438" s="2" t="n"/>
+      <c r="B438" s="3" t="n"/>
+      <c r="C438" s="3" t="n"/>
     </row>
     <row r="439">
-      <c r="B439" s="2" t="n"/>
-      <c r="C439" s="2" t="n"/>
+      <c r="B439" s="3" t="n"/>
+      <c r="C439" s="3" t="n"/>
     </row>
     <row r="440">
-      <c r="B440" s="2" t="n"/>
-      <c r="C440" s="2" t="n"/>
+      <c r="B440" s="3" t="n"/>
+      <c r="C440" s="3" t="n"/>
     </row>
     <row r="441">
-      <c r="B441" s="2" t="n"/>
-      <c r="C441" s="2" t="n"/>
+      <c r="B441" s="3" t="n"/>
+      <c r="C441" s="3" t="n"/>
     </row>
     <row r="442">
-      <c r="B442" s="2" t="n"/>
-      <c r="C442" s="2" t="n"/>
+      <c r="B442" s="3" t="n"/>
+      <c r="C442" s="3" t="n"/>
     </row>
     <row r="443">
-      <c r="B443" s="2" t="n"/>
-      <c r="C443" s="2" t="n"/>
+      <c r="B443" s="3" t="n"/>
+      <c r="C443" s="3" t="n"/>
     </row>
     <row r="444">
-      <c r="B444" s="2" t="n"/>
-      <c r="C444" s="2" t="n"/>
+      <c r="B444" s="3" t="n"/>
+      <c r="C444" s="3" t="n"/>
     </row>
     <row r="445">
-      <c r="B445" s="2" t="n"/>
-      <c r="C445" s="2" t="n"/>
+      <c r="B445" s="3" t="n"/>
+      <c r="C445" s="3" t="n"/>
     </row>
     <row r="446">
-      <c r="B446" s="2" t="n"/>
-      <c r="C446" s="2" t="n"/>
+      <c r="B446" s="3" t="n"/>
+      <c r="C446" s="3" t="n"/>
     </row>
     <row r="447">
-      <c r="B447" s="2" t="n"/>
-      <c r="C447" s="2" t="n"/>
+      <c r="B447" s="3" t="n"/>
+      <c r="C447" s="3" t="n"/>
     </row>
     <row r="448">
-      <c r="B448" s="2" t="n"/>
-      <c r="C448" s="2" t="n"/>
+      <c r="B448" s="3" t="n"/>
+      <c r="C448" s="3" t="n"/>
     </row>
     <row r="449">
-      <c r="B449" s="2" t="n"/>
-      <c r="C449" s="2" t="n"/>
+      <c r="B449" s="3" t="n"/>
+      <c r="C449" s="3" t="n"/>
     </row>
     <row r="450">
-      <c r="B450" s="2" t="n"/>
-      <c r="C450" s="2" t="n"/>
+      <c r="B450" s="3" t="n"/>
+      <c r="C450" s="3" t="n"/>
     </row>
     <row r="451">
-      <c r="B451" s="2" t="n"/>
-      <c r="C451" s="2" t="n"/>
+      <c r="B451" s="3" t="n"/>
+      <c r="C451" s="3" t="n"/>
     </row>
     <row r="452">
-      <c r="B452" s="2" t="n"/>
-      <c r="C452" s="2" t="n"/>
+      <c r="B452" s="3" t="n"/>
+      <c r="C452" s="3" t="n"/>
     </row>
     <row r="453">
-      <c r="B453" s="2" t="n"/>
-      <c r="C453" s="2" t="n"/>
+      <c r="B453" s="3" t="n"/>
+      <c r="C453" s="3" t="n"/>
     </row>
     <row r="454">
-      <c r="B454" s="2" t="n"/>
-      <c r="C454" s="2" t="n"/>
+      <c r="B454" s="3" t="n"/>
+      <c r="C454" s="3" t="n"/>
     </row>
     <row r="455">
-      <c r="B455" s="2" t="n"/>
-      <c r="C455" s="2" t="n"/>
+      <c r="B455" s="3" t="n"/>
+      <c r="C455" s="3" t="n"/>
     </row>
     <row r="456">
-      <c r="B456" s="2" t="n"/>
-      <c r="C456" s="2" t="n"/>
+      <c r="B456" s="3" t="n"/>
+      <c r="C456" s="3" t="n"/>
     </row>
     <row r="457">
-      <c r="B457" s="2" t="n"/>
-      <c r="C457" s="2" t="n"/>
+      <c r="B457" s="3" t="n"/>
+      <c r="C457" s="3" t="n"/>
     </row>
     <row r="458">
-      <c r="B458" s="2" t="n"/>
-      <c r="C458" s="2" t="n"/>
+      <c r="B458" s="3" t="n"/>
+      <c r="C458" s="3" t="n"/>
     </row>
     <row r="459">
-      <c r="B459" s="2" t="n"/>
-      <c r="C459" s="2" t="n"/>
+      <c r="B459" s="3" t="n"/>
+      <c r="C459" s="3" t="n"/>
     </row>
     <row r="460">
-      <c r="B460" s="2" t="n"/>
-      <c r="C460" s="2" t="n"/>
+      <c r="B460" s="3" t="n"/>
+      <c r="C460" s="3" t="n"/>
     </row>
     <row r="461">
-      <c r="B461" s="2" t="n"/>
-      <c r="C461" s="2" t="n"/>
+      <c r="B461" s="3" t="n"/>
+      <c r="C461" s="3" t="n"/>
     </row>
     <row r="462">
-      <c r="B462" s="2" t="n"/>
-      <c r="C462" s="2" t="n"/>
+      <c r="B462" s="3" t="n"/>
+      <c r="C462" s="3" t="n"/>
     </row>
     <row r="463">
-      <c r="B463" s="2" t="n"/>
-      <c r="C463" s="2" t="n"/>
+      <c r="B463" s="3" t="n"/>
+      <c r="C463" s="3" t="n"/>
     </row>
     <row r="464">
-      <c r="B464" s="2" t="n"/>
-      <c r="C464" s="2" t="n"/>
+      <c r="B464" s="3" t="n"/>
+      <c r="C464" s="3" t="n"/>
     </row>
     <row r="465">
-      <c r="B465" s="2" t="n"/>
-      <c r="C465" s="2" t="n"/>
+      <c r="B465" s="3" t="n"/>
+      <c r="C465" s="3" t="n"/>
     </row>
     <row r="466">
-      <c r="B466" s="2" t="n"/>
-      <c r="C466" s="2" t="n"/>
+      <c r="B466" s="3" t="n"/>
+      <c r="C466" s="3" t="n"/>
     </row>
     <row r="467">
-      <c r="B467" s="2" t="n"/>
-      <c r="C467" s="2" t="n"/>
+      <c r="B467" s="3" t="n"/>
+      <c r="C467" s="3" t="n"/>
     </row>
     <row r="468">
-      <c r="B468" s="2" t="n"/>
-      <c r="C468" s="2" t="n"/>
+      <c r="B468" s="3" t="n"/>
+      <c r="C468" s="3" t="n"/>
     </row>
     <row r="469">
-      <c r="B469" s="2" t="n"/>
-      <c r="C469" s="2" t="n"/>
+      <c r="B469" s="3" t="n"/>
+      <c r="C469" s="3" t="n"/>
     </row>
     <row r="470">
-      <c r="B470" s="2" t="n"/>
-      <c r="C470" s="2" t="n"/>
+      <c r="B470" s="3" t="n"/>
+      <c r="C470" s="3" t="n"/>
     </row>
     <row r="471">
-      <c r="B471" s="2" t="n"/>
-      <c r="C471" s="2" t="n"/>
+      <c r="B471" s="3" t="n"/>
+      <c r="C471" s="3" t="n"/>
     </row>
     <row r="472">
-      <c r="B472" s="2" t="n"/>
-      <c r="C472" s="2" t="n"/>
+      <c r="B472" s="3" t="n"/>
+      <c r="C472" s="3" t="n"/>
     </row>
     <row r="473">
-      <c r="B473" s="2" t="n"/>
-      <c r="C473" s="2" t="n"/>
+      <c r="B473" s="3" t="n"/>
+      <c r="C473" s="3" t="n"/>
     </row>
     <row r="474">
-      <c r="B474" s="2" t="n"/>
-      <c r="C474" s="2" t="n"/>
+      <c r="B474" s="3" t="n"/>
+      <c r="C474" s="3" t="n"/>
     </row>
     <row r="475">
-      <c r="B475" s="2" t="n"/>
-      <c r="C475" s="2" t="n"/>
+      <c r="B475" s="3" t="n"/>
+      <c r="C475" s="3" t="n"/>
     </row>
     <row r="476">
-      <c r="B476" s="2" t="n"/>
-      <c r="C476" s="2" t="n"/>
+      <c r="B476" s="3" t="n"/>
+      <c r="C476" s="3" t="n"/>
     </row>
     <row r="477">
-      <c r="B477" s="2" t="n"/>
-      <c r="C477" s="2" t="n"/>
+      <c r="B477" s="3" t="n"/>
+      <c r="C477" s="3" t="n"/>
     </row>
     <row r="478">
-      <c r="B478" s="2" t="n"/>
-      <c r="C478" s="2" t="n"/>
+      <c r="B478" s="3" t="n"/>
+      <c r="C478" s="3" t="n"/>
     </row>
     <row r="479">
-      <c r="B479" s="2" t="n"/>
-      <c r="C479" s="2" t="n"/>
+      <c r="B479" s="3" t="n"/>
+      <c r="C479" s="3" t="n"/>
     </row>
     <row r="480">
-      <c r="B480" s="2" t="n"/>
-      <c r="C480" s="2" t="n"/>
+      <c r="B480" s="3" t="n"/>
+      <c r="C480" s="3" t="n"/>
     </row>
     <row r="481">
-      <c r="B481" s="2" t="n"/>
-      <c r="C481" s="2" t="n"/>
+      <c r="B481" s="3" t="n"/>
+      <c r="C481" s="3" t="n"/>
     </row>
     <row r="482">
-      <c r="B482" s="2" t="n"/>
-      <c r="C482" s="2" t="n"/>
+      <c r="B482" s="3" t="n"/>
+      <c r="C482" s="3" t="n"/>
     </row>
     <row r="483">
-      <c r="B483" s="2" t="n"/>
-      <c r="C483" s="2" t="n"/>
+      <c r="B483" s="3" t="n"/>
+      <c r="C483" s="3" t="n"/>
     </row>
     <row r="484">
-      <c r="B484" s="2" t="n"/>
-      <c r="C484" s="2" t="n"/>
+      <c r="B484" s="3" t="n"/>
+      <c r="C484" s="3" t="n"/>
     </row>
     <row r="485">
-      <c r="B485" s="2" t="n"/>
-      <c r="C485" s="2" t="n"/>
+      <c r="B485" s="3" t="n"/>
+      <c r="C485" s="3" t="n"/>
     </row>
     <row r="486">
-      <c r="B486" s="2" t="n"/>
-      <c r="C486" s="2" t="n"/>
+      <c r="B486" s="3" t="n"/>
+      <c r="C486" s="3" t="n"/>
     </row>
     <row r="487">
-      <c r="B487" s="2" t="n"/>
-      <c r="C487" s="2" t="n"/>
+      <c r="B487" s="3" t="n"/>
+      <c r="C487" s="3" t="n"/>
     </row>
     <row r="488">
-      <c r="B488" s="2" t="n"/>
-      <c r="C488" s="2" t="n"/>
+      <c r="B488" s="3" t="n"/>
+      <c r="C488" s="3" t="n"/>
     </row>
     <row r="489">
-      <c r="B489" s="2" t="n"/>
-      <c r="C489" s="2" t="n"/>
+      <c r="B489" s="3" t="n"/>
+      <c r="C489" s="3" t="n"/>
     </row>
     <row r="490">
-      <c r="B490" s="2" t="n"/>
-      <c r="C490" s="2" t="n"/>
+      <c r="B490" s="3" t="n"/>
+      <c r="C490" s="3" t="n"/>
     </row>
     <row r="491">
-      <c r="B491" s="2" t="n"/>
-      <c r="C491" s="2" t="n"/>
+      <c r="B491" s="3" t="n"/>
+      <c r="C491" s="3" t="n"/>
     </row>
     <row r="492">
-      <c r="B492" s="2" t="n"/>
-      <c r="C492" s="2" t="n"/>
+      <c r="B492" s="3" t="n"/>
+      <c r="C492" s="3" t="n"/>
     </row>
     <row r="493">
-      <c r="B493" s="2" t="n"/>
-      <c r="C493" s="2" t="n"/>
+      <c r="B493" s="3" t="n"/>
+      <c r="C493" s="3" t="n"/>
     </row>
     <row r="494">
-      <c r="B494" s="2" t="n"/>
-      <c r="C494" s="2" t="n"/>
+      <c r="B494" s="3" t="n"/>
+      <c r="C494" s="3" t="n"/>
     </row>
     <row r="495">
-      <c r="B495" s="2" t="n"/>
-      <c r="C495" s="2" t="n"/>
+      <c r="B495" s="3" t="n"/>
+      <c r="C495" s="3" t="n"/>
     </row>
     <row r="496">
-      <c r="B496" s="2" t="n"/>
-      <c r="C496" s="2" t="n"/>
+      <c r="B496" s="3" t="n"/>
+      <c r="C496" s="3" t="n"/>
     </row>
     <row r="497">
-      <c r="B497" s="2" t="n"/>
-      <c r="C497" s="2" t="n"/>
+      <c r="B497" s="3" t="n"/>
+      <c r="C497" s="3" t="n"/>
     </row>
     <row r="498">
-      <c r="B498" s="2" t="n"/>
-      <c r="C498" s="2" t="n"/>
+      <c r="B498" s="3" t="n"/>
+      <c r="C498" s="3" t="n"/>
     </row>
     <row r="499">
-      <c r="B499" s="2" t="n"/>
-      <c r="C499" s="2" t="n"/>
+      <c r="B499" s="3" t="n"/>
+      <c r="C499" s="3" t="n"/>
     </row>
     <row r="500">
-      <c r="B500" s="2" t="n"/>
-      <c r="C500" s="2" t="n"/>
+      <c r="B500" s="3" t="n"/>
+      <c r="C500" s="3" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -5116,10 +5131,10 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>46300.25</v>
+        <v>46300</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>46302.91666666666</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -5147,10 +5162,10 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>46307.29166666666</v>
+        <v>46307</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>46307.66666666666</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -7173,14 +7188,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Terminübersicht – so wird sie ausgefüllt</t>
         </is>
@@ -7188,7 +7203,7 @@
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Blatt „Termine“ – hier wird alles eingetragen</t>
         </is>
@@ -7218,202 +7233,245 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>D  Von       – Datum und Uhrzeit, z. B. 16.11.2026 08:00</t>
+          <t>D  Von       – nur Datum, z. B. 16.11.2026</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>E  Bis       – Datum und Uhrzeit, bei „Info“ darf das Feld leer bleiben</t>
+          <t>E  Bis       – nur Datum, bei „Info“ darf das Feld leer bleiben</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>F  Info      – kurze Beschreibung</t>
+          <t xml:space="preserve">              Uhrzeiten gehören NICHT hierher, sondern ins Blatt „Zeiten“.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
+          <t>F  Info      – kurze Beschreibung</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
           <t>G  Status    – offen / abgeschlossen / storniert</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="B12" s="5" t="inlineStr">
+    <row r="12"/>
+    <row r="13">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Die Spalten Art, Prüfstand, Status und Termin-Nr haben ein Drop-Down:</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="5" t="inlineStr">
+    <row r="14">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>in die Zelle klicken, dann rechts am Zellrand auf den Pfeil klicken.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="5" t="inlineStr">
+    <row r="15">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>So kann kein Tippfehler und kein unbekannter Prüfstand entstehen.</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Wann ist das Blatt „Zeiten“ nötig?</t>
-        </is>
-      </c>
-    </row>
+    <row r="16"/>
     <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Nur wenn der Prüfstand NICHT durchgehend außer Betrieb ist.</t>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Blatt „Zeiten“ – hier stehen die Uhrzeiten</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>Beispiel: Kalibrierung von Montag bis Samstag, aber täglich nur 4–8 Stunden,</t>
+          <t>Das Blatt „Termine“ kennt nur ganze Tage. Sobald eine Uhrzeit eine Rolle</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>und zwischendurch zwei Tage gar nicht.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
+          <t>spielt, wird sie hier eingetragen – als Zeitraum mit Von und Bis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ein Termin kann mehrere Zeilen haben (z. B. eine Kalibrierung, die über</t>
+        </is>
+      </c>
+    </row>
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>Dann für jeden Zeitraum, in dem wirklich gearbeitet wurde, eine Zeile:</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Termin-Nr | Von | Bis | Notiz</t>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
+          <t>mehrere Tage läuft, aber täglich nur vormittags).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Wann ist das Blatt „Zeiten“ nötig?</t>
+        </is>
+      </c>
+    </row>
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
-          <t>Kein Eintrag im Blatt „Zeiten“ = Prüfstand war durchgehend außer Betrieb.</t>
+          <t>Nur wenn der Prüfstand NICHT durchgehend außer Betrieb ist.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bei Wartung und Ausfall ist das der Normalfall – das Blatt bleibt dann leer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
+          <t>Beispiel: Kalibrierung von Montag bis Samstag, aber täglich nur 4–8 Stunden,</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>und zwischendurch zwei Tage gar nicht.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>offen         – Termin läuft bzw. steht noch aus, wird am Kiosk angezeigt</t>
+          <t>Dann für jeden Zeitraum, in dem wirklich gearbeitet wurde, eine Zeile:</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="inlineStr">
         <is>
+          <t xml:space="preserve">   Termin-Nr | Von | Bis | Notiz</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Kein Eintrag im Blatt „Zeiten“ = Prüfstand war durchgehend außer Betrieb.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Bei Wartung und Ausfall ist das der Normalfall – das Blatt bleibt dann leer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>offen         – Termin läuft bzw. steht noch aus, wird am Kiosk angezeigt</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
           <t>abgeschlossen – erledigt, geht in die Historie und in die Ausfallstatistik</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>storniert     – versehentlich eingetragen, zählt NICHT als Ausfall</t>
-        </is>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Nach dem Abschluss</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Abgeschlossene Zeilen aus „Termine“ in das Blatt „Archiv“ verschieben.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Die Historie bleibt im Gerät erhalten, auch wenn die Zeile hier verschwindet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>Neue Prüfstände</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="inlineStr">
         <is>
-          <t>Im Blatt „Prüfstände“ unten eine Zeile ergänzen (Kennung, Bezeichnung, Auswahl).</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Das Dropdown im Blatt „Termine“ zieht automatisch nach.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39"/>
+          <t>storniert     – versehentlich eingetragen, zählt NICHT als Ausfall</t>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Nach dem Abschluss</t>
+        </is>
+      </c>
+    </row>
     <row r="40">
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>Beispiele</t>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Abgeschlossene Zeilen aus „Termine“ in das Blatt „Archiv“ verschieben.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="inlineStr">
         <is>
+          <t>Die Historie bleibt im Gerät erhalten, auch wenn die Zeile hier verschwindet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
+    <row r="43">
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Neue Prüfstände</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Im Blatt „Prüfstände“ unten eine Zeile ergänzen (Kennung, Bezeichnung, Auswahl).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Das Dropdown im Blatt „Termine“ zieht automatisch nach.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46"/>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Beispiele</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
           <t>Die Zeilen in dieser Vorlage sind Muster zum Ansehen. Vor dem ersten</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" t="inlineStr">
+    <row r="49">
+      <c r="B49" t="inlineStr">
         <is>
           <t>echten Eintrag löschen – sonst werden sie als echte Termine importiert.</t>
         </is>

--- a/terminboard/vorlagen/termine_modell2.xlsx
+++ b/terminboard/vorlagen/termine_modell2.xlsx
@@ -28,7 +28,7 @@
     <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="167" formatCode="DD.MM.YYYY HH:MM"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,6 +38,18 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="00808080"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
+    </font>
+    <font>
+      <color rgb="00808080"/>
     </font>
     <font>
       <b val="1"/>
@@ -71,16 +83,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G500"/>
+  <dimension ref="A1:I500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -455,7 +472,9 @@
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="46" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="3" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,6 +513,11 @@
           <t>Status</t>
         </is>
       </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Beispiel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -509,10 +533,10 @@
           <t>P03 NRA</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="3" t="n">
         <v>46328</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="3" t="n">
         <v>46328</v>
       </c>
       <c r="F2" t="inlineStr">
@@ -523,6 +547,16 @@
       <c r="G2" t="inlineStr">
         <is>
           <t>abgeschlossen</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Wartung, erledigt</t>
         </is>
       </c>
     </row>
@@ -540,10 +574,10 @@
           <t>P10 PTU TESTFUCHS</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="3" t="n">
         <v>46342</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="3" t="n">
         <v>46347</v>
       </c>
       <c r="F3" t="inlineStr">
@@ -554,6 +588,16 @@
       <c r="G3" t="inlineStr">
         <is>
           <t>abgeschlossen</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Kalibrierung über mehrere Tage –</t>
         </is>
       </c>
     </row>
@@ -571,10 +615,10 @@
           <t>P21 NRC HYCOM</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="3" t="n">
         <v>46344</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="3" t="n">
         <v>46345</v>
       </c>
       <c r="F4" t="inlineStr">
@@ -585,6 +629,12 @@
       <c r="G4" t="inlineStr">
         <is>
           <t>offen</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Zeitblöcke im Blatt „Zeiten“</t>
         </is>
       </c>
     </row>
@@ -602,10 +652,10 @@
           <t>P31 THSA</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="3" t="n">
         <v>46350</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="3" t="n">
         <v>46350</v>
       </c>
       <c r="F5" t="inlineStr">
@@ -616,6 +666,16 @@
       <c r="G5" t="inlineStr">
         <is>
           <t>offen</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Info – „Bis“ darf leer bleiben</t>
         </is>
       </c>
     </row>
@@ -633,10 +693,10 @@
           <t>P40 AKKU/HOCHDRUCK-RAUM</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="3" t="n">
         <v>46353</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="3" t="n">
         <v>46353</v>
       </c>
       <c r="F6" t="inlineStr">
@@ -649,6 +709,8 @@
           <t>offen</t>
         </is>
       </c>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -664,10 +726,10 @@
           <t>P07 EHSV NRA</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="3" t="n">
         <v>46357</v>
       </c>
-      <c r="E7" s="2" t="n"/>
+      <c r="E7" s="3" t="n"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>Hinweis Software-Update</t>
@@ -678,1978 +740,2028 @@
           <t>offen</t>
         </is>
       </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Von / Bis</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>nur Datum, keine Uhrzeit</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="n"/>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="n"/>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Kalibrierung / Wartung /</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Ausfall / Audit / Info</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Prüfstand</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Reihenfolge: erst mit</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="H12" s="4" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Dropdown wählen – falsche</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Namen zählen nicht</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="n"/>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
     </row>
     <row r="15">
-      <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
     </row>
     <row r="16">
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
     </row>
     <row r="17">
-      <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
     </row>
     <row r="18">
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="n"/>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
     </row>
     <row r="19">
-      <c r="D19" s="2" t="n"/>
-      <c r="E19" s="2" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
     </row>
     <row r="20">
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="n"/>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="n"/>
     </row>
     <row r="21">
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="n"/>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
     </row>
     <row r="22">
-      <c r="D22" s="2" t="n"/>
-      <c r="E22" s="2" t="n"/>
+      <c r="D22" s="3" t="n"/>
+      <c r="E22" s="3" t="n"/>
     </row>
     <row r="23">
-      <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="n"/>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
     </row>
     <row r="24">
-      <c r="D24" s="2" t="n"/>
-      <c r="E24" s="2" t="n"/>
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="n"/>
     </row>
     <row r="25">
-      <c r="D25" s="2" t="n"/>
-      <c r="E25" s="2" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
     </row>
     <row r="26">
-      <c r="D26" s="2" t="n"/>
-      <c r="E26" s="2" t="n"/>
+      <c r="D26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
     </row>
     <row r="27">
-      <c r="D27" s="2" t="n"/>
-      <c r="E27" s="2" t="n"/>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
     </row>
     <row r="28">
-      <c r="D28" s="2" t="n"/>
-      <c r="E28" s="2" t="n"/>
+      <c r="D28" s="3" t="n"/>
+      <c r="E28" s="3" t="n"/>
     </row>
     <row r="29">
-      <c r="D29" s="2" t="n"/>
-      <c r="E29" s="2" t="n"/>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
     </row>
     <row r="30">
-      <c r="D30" s="2" t="n"/>
-      <c r="E30" s="2" t="n"/>
+      <c r="D30" s="3" t="n"/>
+      <c r="E30" s="3" t="n"/>
     </row>
     <row r="31">
-      <c r="D31" s="2" t="n"/>
-      <c r="E31" s="2" t="n"/>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n"/>
     </row>
     <row r="32">
-      <c r="D32" s="2" t="n"/>
-      <c r="E32" s="2" t="n"/>
+      <c r="D32" s="3" t="n"/>
+      <c r="E32" s="3" t="n"/>
     </row>
     <row r="33">
-      <c r="D33" s="2" t="n"/>
-      <c r="E33" s="2" t="n"/>
+      <c r="D33" s="3" t="n"/>
+      <c r="E33" s="3" t="n"/>
     </row>
     <row r="34">
-      <c r="D34" s="2" t="n"/>
-      <c r="E34" s="2" t="n"/>
+      <c r="D34" s="3" t="n"/>
+      <c r="E34" s="3" t="n"/>
     </row>
     <row r="35">
-      <c r="D35" s="2" t="n"/>
-      <c r="E35" s="2" t="n"/>
+      <c r="D35" s="3" t="n"/>
+      <c r="E35" s="3" t="n"/>
     </row>
     <row r="36">
-      <c r="D36" s="2" t="n"/>
-      <c r="E36" s="2" t="n"/>
+      <c r="D36" s="3" t="n"/>
+      <c r="E36" s="3" t="n"/>
     </row>
     <row r="37">
-      <c r="D37" s="2" t="n"/>
-      <c r="E37" s="2" t="n"/>
+      <c r="D37" s="3" t="n"/>
+      <c r="E37" s="3" t="n"/>
     </row>
     <row r="38">
-      <c r="D38" s="2" t="n"/>
-      <c r="E38" s="2" t="n"/>
+      <c r="D38" s="3" t="n"/>
+      <c r="E38" s="3" t="n"/>
     </row>
     <row r="39">
-      <c r="D39" s="2" t="n"/>
-      <c r="E39" s="2" t="n"/>
+      <c r="D39" s="3" t="n"/>
+      <c r="E39" s="3" t="n"/>
     </row>
     <row r="40">
-      <c r="D40" s="2" t="n"/>
-      <c r="E40" s="2" t="n"/>
+      <c r="D40" s="3" t="n"/>
+      <c r="E40" s="3" t="n"/>
     </row>
     <row r="41">
-      <c r="D41" s="2" t="n"/>
-      <c r="E41" s="2" t="n"/>
+      <c r="D41" s="3" t="n"/>
+      <c r="E41" s="3" t="n"/>
     </row>
     <row r="42">
-      <c r="D42" s="2" t="n"/>
-      <c r="E42" s="2" t="n"/>
+      <c r="D42" s="3" t="n"/>
+      <c r="E42" s="3" t="n"/>
     </row>
     <row r="43">
-      <c r="D43" s="2" t="n"/>
-      <c r="E43" s="2" t="n"/>
+      <c r="D43" s="3" t="n"/>
+      <c r="E43" s="3" t="n"/>
     </row>
     <row r="44">
-      <c r="D44" s="2" t="n"/>
-      <c r="E44" s="2" t="n"/>
+      <c r="D44" s="3" t="n"/>
+      <c r="E44" s="3" t="n"/>
     </row>
     <row r="45">
-      <c r="D45" s="2" t="n"/>
-      <c r="E45" s="2" t="n"/>
+      <c r="D45" s="3" t="n"/>
+      <c r="E45" s="3" t="n"/>
     </row>
     <row r="46">
-      <c r="D46" s="2" t="n"/>
-      <c r="E46" s="2" t="n"/>
+      <c r="D46" s="3" t="n"/>
+      <c r="E46" s="3" t="n"/>
     </row>
     <row r="47">
-      <c r="D47" s="2" t="n"/>
-      <c r="E47" s="2" t="n"/>
+      <c r="D47" s="3" t="n"/>
+      <c r="E47" s="3" t="n"/>
     </row>
     <row r="48">
-      <c r="D48" s="2" t="n"/>
-      <c r="E48" s="2" t="n"/>
+      <c r="D48" s="3" t="n"/>
+      <c r="E48" s="3" t="n"/>
     </row>
     <row r="49">
-      <c r="D49" s="2" t="n"/>
-      <c r="E49" s="2" t="n"/>
+      <c r="D49" s="3" t="n"/>
+      <c r="E49" s="3" t="n"/>
     </row>
     <row r="50">
-      <c r="D50" s="2" t="n"/>
-      <c r="E50" s="2" t="n"/>
+      <c r="D50" s="3" t="n"/>
+      <c r="E50" s="3" t="n"/>
     </row>
     <row r="51">
-      <c r="D51" s="2" t="n"/>
-      <c r="E51" s="2" t="n"/>
+      <c r="D51" s="3" t="n"/>
+      <c r="E51" s="3" t="n"/>
     </row>
     <row r="52">
-      <c r="D52" s="2" t="n"/>
-      <c r="E52" s="2" t="n"/>
+      <c r="D52" s="3" t="n"/>
+      <c r="E52" s="3" t="n"/>
     </row>
     <row r="53">
-      <c r="D53" s="2" t="n"/>
-      <c r="E53" s="2" t="n"/>
+      <c r="D53" s="3" t="n"/>
+      <c r="E53" s="3" t="n"/>
     </row>
     <row r="54">
-      <c r="D54" s="2" t="n"/>
-      <c r="E54" s="2" t="n"/>
+      <c r="D54" s="3" t="n"/>
+      <c r="E54" s="3" t="n"/>
     </row>
     <row r="55">
-      <c r="D55" s="2" t="n"/>
-      <c r="E55" s="2" t="n"/>
+      <c r="D55" s="3" t="n"/>
+      <c r="E55" s="3" t="n"/>
     </row>
     <row r="56">
-      <c r="D56" s="2" t="n"/>
-      <c r="E56" s="2" t="n"/>
+      <c r="D56" s="3" t="n"/>
+      <c r="E56" s="3" t="n"/>
     </row>
     <row r="57">
-      <c r="D57" s="2" t="n"/>
-      <c r="E57" s="2" t="n"/>
+      <c r="D57" s="3" t="n"/>
+      <c r="E57" s="3" t="n"/>
     </row>
     <row r="58">
-      <c r="D58" s="2" t="n"/>
-      <c r="E58" s="2" t="n"/>
+      <c r="D58" s="3" t="n"/>
+      <c r="E58" s="3" t="n"/>
     </row>
     <row r="59">
-      <c r="D59" s="2" t="n"/>
-      <c r="E59" s="2" t="n"/>
+      <c r="D59" s="3" t="n"/>
+      <c r="E59" s="3" t="n"/>
     </row>
     <row r="60">
-      <c r="D60" s="2" t="n"/>
-      <c r="E60" s="2" t="n"/>
+      <c r="D60" s="3" t="n"/>
+      <c r="E60" s="3" t="n"/>
     </row>
     <row r="61">
-      <c r="D61" s="2" t="n"/>
-      <c r="E61" s="2" t="n"/>
+      <c r="D61" s="3" t="n"/>
+      <c r="E61" s="3" t="n"/>
     </row>
     <row r="62">
-      <c r="D62" s="2" t="n"/>
-      <c r="E62" s="2" t="n"/>
+      <c r="D62" s="3" t="n"/>
+      <c r="E62" s="3" t="n"/>
     </row>
     <row r="63">
-      <c r="D63" s="2" t="n"/>
-      <c r="E63" s="2" t="n"/>
+      <c r="D63" s="3" t="n"/>
+      <c r="E63" s="3" t="n"/>
     </row>
     <row r="64">
-      <c r="D64" s="2" t="n"/>
-      <c r="E64" s="2" t="n"/>
+      <c r="D64" s="3" t="n"/>
+      <c r="E64" s="3" t="n"/>
     </row>
     <row r="65">
-      <c r="D65" s="2" t="n"/>
-      <c r="E65" s="2" t="n"/>
+      <c r="D65" s="3" t="n"/>
+      <c r="E65" s="3" t="n"/>
     </row>
     <row r="66">
-      <c r="D66" s="2" t="n"/>
-      <c r="E66" s="2" t="n"/>
+      <c r="D66" s="3" t="n"/>
+      <c r="E66" s="3" t="n"/>
     </row>
     <row r="67">
-      <c r="D67" s="2" t="n"/>
-      <c r="E67" s="2" t="n"/>
+      <c r="D67" s="3" t="n"/>
+      <c r="E67" s="3" t="n"/>
     </row>
     <row r="68">
-      <c r="D68" s="2" t="n"/>
-      <c r="E68" s="2" t="n"/>
+      <c r="D68" s="3" t="n"/>
+      <c r="E68" s="3" t="n"/>
     </row>
     <row r="69">
-      <c r="D69" s="2" t="n"/>
-      <c r="E69" s="2" t="n"/>
+      <c r="D69" s="3" t="n"/>
+      <c r="E69" s="3" t="n"/>
     </row>
     <row r="70">
-      <c r="D70" s="2" t="n"/>
-      <c r="E70" s="2" t="n"/>
+      <c r="D70" s="3" t="n"/>
+      <c r="E70" s="3" t="n"/>
     </row>
     <row r="71">
-      <c r="D71" s="2" t="n"/>
-      <c r="E71" s="2" t="n"/>
+      <c r="D71" s="3" t="n"/>
+      <c r="E71" s="3" t="n"/>
     </row>
     <row r="72">
-      <c r="D72" s="2" t="n"/>
-      <c r="E72" s="2" t="n"/>
+      <c r="D72" s="3" t="n"/>
+      <c r="E72" s="3" t="n"/>
     </row>
     <row r="73">
-      <c r="D73" s="2" t="n"/>
-      <c r="E73" s="2" t="n"/>
+      <c r="D73" s="3" t="n"/>
+      <c r="E73" s="3" t="n"/>
     </row>
     <row r="74">
-      <c r="D74" s="2" t="n"/>
-      <c r="E74" s="2" t="n"/>
+      <c r="D74" s="3" t="n"/>
+      <c r="E74" s="3" t="n"/>
     </row>
     <row r="75">
-      <c r="D75" s="2" t="n"/>
-      <c r="E75" s="2" t="n"/>
+      <c r="D75" s="3" t="n"/>
+      <c r="E75" s="3" t="n"/>
     </row>
     <row r="76">
-      <c r="D76" s="2" t="n"/>
-      <c r="E76" s="2" t="n"/>
+      <c r="D76" s="3" t="n"/>
+      <c r="E76" s="3" t="n"/>
     </row>
     <row r="77">
-      <c r="D77" s="2" t="n"/>
-      <c r="E77" s="2" t="n"/>
+      <c r="D77" s="3" t="n"/>
+      <c r="E77" s="3" t="n"/>
     </row>
     <row r="78">
-      <c r="D78" s="2" t="n"/>
-      <c r="E78" s="2" t="n"/>
+      <c r="D78" s="3" t="n"/>
+      <c r="E78" s="3" t="n"/>
     </row>
     <row r="79">
-      <c r="D79" s="2" t="n"/>
-      <c r="E79" s="2" t="n"/>
+      <c r="D79" s="3" t="n"/>
+      <c r="E79" s="3" t="n"/>
     </row>
     <row r="80">
-      <c r="D80" s="2" t="n"/>
-      <c r="E80" s="2" t="n"/>
+      <c r="D80" s="3" t="n"/>
+      <c r="E80" s="3" t="n"/>
     </row>
     <row r="81">
-      <c r="D81" s="2" t="n"/>
-      <c r="E81" s="2" t="n"/>
+      <c r="D81" s="3" t="n"/>
+      <c r="E81" s="3" t="n"/>
     </row>
     <row r="82">
-      <c r="D82" s="2" t="n"/>
-      <c r="E82" s="2" t="n"/>
+      <c r="D82" s="3" t="n"/>
+      <c r="E82" s="3" t="n"/>
     </row>
     <row r="83">
-      <c r="D83" s="2" t="n"/>
-      <c r="E83" s="2" t="n"/>
+      <c r="D83" s="3" t="n"/>
+      <c r="E83" s="3" t="n"/>
     </row>
     <row r="84">
-      <c r="D84" s="2" t="n"/>
-      <c r="E84" s="2" t="n"/>
+      <c r="D84" s="3" t="n"/>
+      <c r="E84" s="3" t="n"/>
     </row>
     <row r="85">
-      <c r="D85" s="2" t="n"/>
-      <c r="E85" s="2" t="n"/>
+      <c r="D85" s="3" t="n"/>
+      <c r="E85" s="3" t="n"/>
     </row>
     <row r="86">
-      <c r="D86" s="2" t="n"/>
-      <c r="E86" s="2" t="n"/>
+      <c r="D86" s="3" t="n"/>
+      <c r="E86" s="3" t="n"/>
     </row>
     <row r="87">
-      <c r="D87" s="2" t="n"/>
-      <c r="E87" s="2" t="n"/>
+      <c r="D87" s="3" t="n"/>
+      <c r="E87" s="3" t="n"/>
     </row>
     <row r="88">
-      <c r="D88" s="2" t="n"/>
-      <c r="E88" s="2" t="n"/>
+      <c r="D88" s="3" t="n"/>
+      <c r="E88" s="3" t="n"/>
     </row>
     <row r="89">
-      <c r="D89" s="2" t="n"/>
-      <c r="E89" s="2" t="n"/>
+      <c r="D89" s="3" t="n"/>
+      <c r="E89" s="3" t="n"/>
     </row>
     <row r="90">
-      <c r="D90" s="2" t="n"/>
-      <c r="E90" s="2" t="n"/>
+      <c r="D90" s="3" t="n"/>
+      <c r="E90" s="3" t="n"/>
     </row>
     <row r="91">
-      <c r="D91" s="2" t="n"/>
-      <c r="E91" s="2" t="n"/>
+      <c r="D91" s="3" t="n"/>
+      <c r="E91" s="3" t="n"/>
     </row>
     <row r="92">
-      <c r="D92" s="2" t="n"/>
-      <c r="E92" s="2" t="n"/>
+      <c r="D92" s="3" t="n"/>
+      <c r="E92" s="3" t="n"/>
     </row>
     <row r="93">
-      <c r="D93" s="2" t="n"/>
-      <c r="E93" s="2" t="n"/>
+      <c r="D93" s="3" t="n"/>
+      <c r="E93" s="3" t="n"/>
     </row>
     <row r="94">
-      <c r="D94" s="2" t="n"/>
-      <c r="E94" s="2" t="n"/>
+      <c r="D94" s="3" t="n"/>
+      <c r="E94" s="3" t="n"/>
     </row>
     <row r="95">
-      <c r="D95" s="2" t="n"/>
-      <c r="E95" s="2" t="n"/>
+      <c r="D95" s="3" t="n"/>
+      <c r="E95" s="3" t="n"/>
     </row>
     <row r="96">
-      <c r="D96" s="2" t="n"/>
-      <c r="E96" s="2" t="n"/>
+      <c r="D96" s="3" t="n"/>
+      <c r="E96" s="3" t="n"/>
     </row>
     <row r="97">
-      <c r="D97" s="2" t="n"/>
-      <c r="E97" s="2" t="n"/>
+      <c r="D97" s="3" t="n"/>
+      <c r="E97" s="3" t="n"/>
     </row>
     <row r="98">
-      <c r="D98" s="2" t="n"/>
-      <c r="E98" s="2" t="n"/>
+      <c r="D98" s="3" t="n"/>
+      <c r="E98" s="3" t="n"/>
     </row>
     <row r="99">
-      <c r="D99" s="2" t="n"/>
-      <c r="E99" s="2" t="n"/>
+      <c r="D99" s="3" t="n"/>
+      <c r="E99" s="3" t="n"/>
     </row>
     <row r="100">
-      <c r="D100" s="2" t="n"/>
-      <c r="E100" s="2" t="n"/>
+      <c r="D100" s="3" t="n"/>
+      <c r="E100" s="3" t="n"/>
     </row>
     <row r="101">
-      <c r="D101" s="2" t="n"/>
-      <c r="E101" s="2" t="n"/>
+      <c r="D101" s="3" t="n"/>
+      <c r="E101" s="3" t="n"/>
     </row>
     <row r="102">
-      <c r="D102" s="2" t="n"/>
-      <c r="E102" s="2" t="n"/>
+      <c r="D102" s="3" t="n"/>
+      <c r="E102" s="3" t="n"/>
     </row>
     <row r="103">
-      <c r="D103" s="2" t="n"/>
-      <c r="E103" s="2" t="n"/>
+      <c r="D103" s="3" t="n"/>
+      <c r="E103" s="3" t="n"/>
     </row>
     <row r="104">
-      <c r="D104" s="2" t="n"/>
-      <c r="E104" s="2" t="n"/>
+      <c r="D104" s="3" t="n"/>
+      <c r="E104" s="3" t="n"/>
     </row>
     <row r="105">
-      <c r="D105" s="2" t="n"/>
-      <c r="E105" s="2" t="n"/>
+      <c r="D105" s="3" t="n"/>
+      <c r="E105" s="3" t="n"/>
     </row>
     <row r="106">
-      <c r="D106" s="2" t="n"/>
-      <c r="E106" s="2" t="n"/>
+      <c r="D106" s="3" t="n"/>
+      <c r="E106" s="3" t="n"/>
     </row>
     <row r="107">
-      <c r="D107" s="2" t="n"/>
-      <c r="E107" s="2" t="n"/>
+      <c r="D107" s="3" t="n"/>
+      <c r="E107" s="3" t="n"/>
     </row>
     <row r="108">
-      <c r="D108" s="2" t="n"/>
-      <c r="E108" s="2" t="n"/>
+      <c r="D108" s="3" t="n"/>
+      <c r="E108" s="3" t="n"/>
     </row>
     <row r="109">
-      <c r="D109" s="2" t="n"/>
-      <c r="E109" s="2" t="n"/>
+      <c r="D109" s="3" t="n"/>
+      <c r="E109" s="3" t="n"/>
     </row>
     <row r="110">
-      <c r="D110" s="2" t="n"/>
-      <c r="E110" s="2" t="n"/>
+      <c r="D110" s="3" t="n"/>
+      <c r="E110" s="3" t="n"/>
     </row>
     <row r="111">
-      <c r="D111" s="2" t="n"/>
-      <c r="E111" s="2" t="n"/>
+      <c r="D111" s="3" t="n"/>
+      <c r="E111" s="3" t="n"/>
     </row>
     <row r="112">
-      <c r="D112" s="2" t="n"/>
-      <c r="E112" s="2" t="n"/>
+      <c r="D112" s="3" t="n"/>
+      <c r="E112" s="3" t="n"/>
     </row>
     <row r="113">
-      <c r="D113" s="2" t="n"/>
-      <c r="E113" s="2" t="n"/>
+      <c r="D113" s="3" t="n"/>
+      <c r="E113" s="3" t="n"/>
     </row>
     <row r="114">
-      <c r="D114" s="2" t="n"/>
-      <c r="E114" s="2" t="n"/>
+      <c r="D114" s="3" t="n"/>
+      <c r="E114" s="3" t="n"/>
     </row>
     <row r="115">
-      <c r="D115" s="2" t="n"/>
-      <c r="E115" s="2" t="n"/>
+      <c r="D115" s="3" t="n"/>
+      <c r="E115" s="3" t="n"/>
     </row>
     <row r="116">
-      <c r="D116" s="2" t="n"/>
-      <c r="E116" s="2" t="n"/>
+      <c r="D116" s="3" t="n"/>
+      <c r="E116" s="3" t="n"/>
     </row>
     <row r="117">
-      <c r="D117" s="2" t="n"/>
-      <c r="E117" s="2" t="n"/>
+      <c r="D117" s="3" t="n"/>
+      <c r="E117" s="3" t="n"/>
     </row>
     <row r="118">
-      <c r="D118" s="2" t="n"/>
-      <c r="E118" s="2" t="n"/>
+      <c r="D118" s="3" t="n"/>
+      <c r="E118" s="3" t="n"/>
     </row>
     <row r="119">
-      <c r="D119" s="2" t="n"/>
-      <c r="E119" s="2" t="n"/>
+      <c r="D119" s="3" t="n"/>
+      <c r="E119" s="3" t="n"/>
     </row>
     <row r="120">
-      <c r="D120" s="2" t="n"/>
-      <c r="E120" s="2" t="n"/>
+      <c r="D120" s="3" t="n"/>
+      <c r="E120" s="3" t="n"/>
     </row>
     <row r="121">
-      <c r="D121" s="2" t="n"/>
-      <c r="E121" s="2" t="n"/>
+      <c r="D121" s="3" t="n"/>
+      <c r="E121" s="3" t="n"/>
     </row>
     <row r="122">
-      <c r="D122" s="2" t="n"/>
-      <c r="E122" s="2" t="n"/>
+      <c r="D122" s="3" t="n"/>
+      <c r="E122" s="3" t="n"/>
     </row>
     <row r="123">
-      <c r="D123" s="2" t="n"/>
-      <c r="E123" s="2" t="n"/>
+      <c r="D123" s="3" t="n"/>
+      <c r="E123" s="3" t="n"/>
     </row>
     <row r="124">
-      <c r="D124" s="2" t="n"/>
-      <c r="E124" s="2" t="n"/>
+      <c r="D124" s="3" t="n"/>
+      <c r="E124" s="3" t="n"/>
     </row>
     <row r="125">
-      <c r="D125" s="2" t="n"/>
-      <c r="E125" s="2" t="n"/>
+      <c r="D125" s="3" t="n"/>
+      <c r="E125" s="3" t="n"/>
     </row>
     <row r="126">
-      <c r="D126" s="2" t="n"/>
-      <c r="E126" s="2" t="n"/>
+      <c r="D126" s="3" t="n"/>
+      <c r="E126" s="3" t="n"/>
     </row>
     <row r="127">
-      <c r="D127" s="2" t="n"/>
-      <c r="E127" s="2" t="n"/>
+      <c r="D127" s="3" t="n"/>
+      <c r="E127" s="3" t="n"/>
     </row>
     <row r="128">
-      <c r="D128" s="2" t="n"/>
-      <c r="E128" s="2" t="n"/>
+      <c r="D128" s="3" t="n"/>
+      <c r="E128" s="3" t="n"/>
     </row>
     <row r="129">
-      <c r="D129" s="2" t="n"/>
-      <c r="E129" s="2" t="n"/>
+      <c r="D129" s="3" t="n"/>
+      <c r="E129" s="3" t="n"/>
     </row>
     <row r="130">
-      <c r="D130" s="2" t="n"/>
-      <c r="E130" s="2" t="n"/>
+      <c r="D130" s="3" t="n"/>
+      <c r="E130" s="3" t="n"/>
     </row>
     <row r="131">
-      <c r="D131" s="2" t="n"/>
-      <c r="E131" s="2" t="n"/>
+      <c r="D131" s="3" t="n"/>
+      <c r="E131" s="3" t="n"/>
     </row>
     <row r="132">
-      <c r="D132" s="2" t="n"/>
-      <c r="E132" s="2" t="n"/>
+      <c r="D132" s="3" t="n"/>
+      <c r="E132" s="3" t="n"/>
     </row>
     <row r="133">
-      <c r="D133" s="2" t="n"/>
-      <c r="E133" s="2" t="n"/>
+      <c r="D133" s="3" t="n"/>
+      <c r="E133" s="3" t="n"/>
     </row>
     <row r="134">
-      <c r="D134" s="2" t="n"/>
-      <c r="E134" s="2" t="n"/>
+      <c r="D134" s="3" t="n"/>
+      <c r="E134" s="3" t="n"/>
     </row>
     <row r="135">
-      <c r="D135" s="2" t="n"/>
-      <c r="E135" s="2" t="n"/>
+      <c r="D135" s="3" t="n"/>
+      <c r="E135" s="3" t="n"/>
     </row>
     <row r="136">
-      <c r="D136" s="2" t="n"/>
-      <c r="E136" s="2" t="n"/>
+      <c r="D136" s="3" t="n"/>
+      <c r="E136" s="3" t="n"/>
     </row>
     <row r="137">
-      <c r="D137" s="2" t="n"/>
-      <c r="E137" s="2" t="n"/>
+      <c r="D137" s="3" t="n"/>
+      <c r="E137" s="3" t="n"/>
     </row>
     <row r="138">
-      <c r="D138" s="2" t="n"/>
-      <c r="E138" s="2" t="n"/>
+      <c r="D138" s="3" t="n"/>
+      <c r="E138" s="3" t="n"/>
     </row>
     <row r="139">
-      <c r="D139" s="2" t="n"/>
-      <c r="E139" s="2" t="n"/>
+      <c r="D139" s="3" t="n"/>
+      <c r="E139" s="3" t="n"/>
     </row>
     <row r="140">
-      <c r="D140" s="2" t="n"/>
-      <c r="E140" s="2" t="n"/>
+      <c r="D140" s="3" t="n"/>
+      <c r="E140" s="3" t="n"/>
     </row>
     <row r="141">
-      <c r="D141" s="2" t="n"/>
-      <c r="E141" s="2" t="n"/>
+      <c r="D141" s="3" t="n"/>
+      <c r="E141" s="3" t="n"/>
     </row>
     <row r="142">
-      <c r="D142" s="2" t="n"/>
-      <c r="E142" s="2" t="n"/>
+      <c r="D142" s="3" t="n"/>
+      <c r="E142" s="3" t="n"/>
     </row>
     <row r="143">
-      <c r="D143" s="2" t="n"/>
-      <c r="E143" s="2" t="n"/>
+      <c r="D143" s="3" t="n"/>
+      <c r="E143" s="3" t="n"/>
     </row>
     <row r="144">
-      <c r="D144" s="2" t="n"/>
-      <c r="E144" s="2" t="n"/>
+      <c r="D144" s="3" t="n"/>
+      <c r="E144" s="3" t="n"/>
     </row>
     <row r="145">
-      <c r="D145" s="2" t="n"/>
-      <c r="E145" s="2" t="n"/>
+      <c r="D145" s="3" t="n"/>
+      <c r="E145" s="3" t="n"/>
     </row>
     <row r="146">
-      <c r="D146" s="2" t="n"/>
-      <c r="E146" s="2" t="n"/>
+      <c r="D146" s="3" t="n"/>
+      <c r="E146" s="3" t="n"/>
     </row>
     <row r="147">
-      <c r="D147" s="2" t="n"/>
-      <c r="E147" s="2" t="n"/>
+      <c r="D147" s="3" t="n"/>
+      <c r="E147" s="3" t="n"/>
     </row>
     <row r="148">
-      <c r="D148" s="2" t="n"/>
-      <c r="E148" s="2" t="n"/>
+      <c r="D148" s="3" t="n"/>
+      <c r="E148" s="3" t="n"/>
     </row>
     <row r="149">
-      <c r="D149" s="2" t="n"/>
-      <c r="E149" s="2" t="n"/>
+      <c r="D149" s="3" t="n"/>
+      <c r="E149" s="3" t="n"/>
     </row>
     <row r="150">
-      <c r="D150" s="2" t="n"/>
-      <c r="E150" s="2" t="n"/>
+      <c r="D150" s="3" t="n"/>
+      <c r="E150" s="3" t="n"/>
     </row>
     <row r="151">
-      <c r="D151" s="2" t="n"/>
-      <c r="E151" s="2" t="n"/>
+      <c r="D151" s="3" t="n"/>
+      <c r="E151" s="3" t="n"/>
     </row>
     <row r="152">
-      <c r="D152" s="2" t="n"/>
-      <c r="E152" s="2" t="n"/>
+      <c r="D152" s="3" t="n"/>
+      <c r="E152" s="3" t="n"/>
     </row>
     <row r="153">
-      <c r="D153" s="2" t="n"/>
-      <c r="E153" s="2" t="n"/>
+      <c r="D153" s="3" t="n"/>
+      <c r="E153" s="3" t="n"/>
     </row>
     <row r="154">
-      <c r="D154" s="2" t="n"/>
-      <c r="E154" s="2" t="n"/>
+      <c r="D154" s="3" t="n"/>
+      <c r="E154" s="3" t="n"/>
     </row>
     <row r="155">
-      <c r="D155" s="2" t="n"/>
-      <c r="E155" s="2" t="n"/>
+      <c r="D155" s="3" t="n"/>
+      <c r="E155" s="3" t="n"/>
     </row>
     <row r="156">
-      <c r="D156" s="2" t="n"/>
-      <c r="E156" s="2" t="n"/>
+      <c r="D156" s="3" t="n"/>
+      <c r="E156" s="3" t="n"/>
     </row>
     <row r="157">
-      <c r="D157" s="2" t="n"/>
-      <c r="E157" s="2" t="n"/>
+      <c r="D157" s="3" t="n"/>
+      <c r="E157" s="3" t="n"/>
     </row>
     <row r="158">
-      <c r="D158" s="2" t="n"/>
-      <c r="E158" s="2" t="n"/>
+      <c r="D158" s="3" t="n"/>
+      <c r="E158" s="3" t="n"/>
     </row>
     <row r="159">
-      <c r="D159" s="2" t="n"/>
-      <c r="E159" s="2" t="n"/>
+      <c r="D159" s="3" t="n"/>
+      <c r="E159" s="3" t="n"/>
     </row>
     <row r="160">
-      <c r="D160" s="2" t="n"/>
-      <c r="E160" s="2" t="n"/>
+      <c r="D160" s="3" t="n"/>
+      <c r="E160" s="3" t="n"/>
     </row>
     <row r="161">
-      <c r="D161" s="2" t="n"/>
-      <c r="E161" s="2" t="n"/>
+      <c r="D161" s="3" t="n"/>
+      <c r="E161" s="3" t="n"/>
     </row>
     <row r="162">
-      <c r="D162" s="2" t="n"/>
-      <c r="E162" s="2" t="n"/>
+      <c r="D162" s="3" t="n"/>
+      <c r="E162" s="3" t="n"/>
     </row>
     <row r="163">
-      <c r="D163" s="2" t="n"/>
-      <c r="E163" s="2" t="n"/>
+      <c r="D163" s="3" t="n"/>
+      <c r="E163" s="3" t="n"/>
     </row>
     <row r="164">
-      <c r="D164" s="2" t="n"/>
-      <c r="E164" s="2" t="n"/>
+      <c r="D164" s="3" t="n"/>
+      <c r="E164" s="3" t="n"/>
     </row>
     <row r="165">
-      <c r="D165" s="2" t="n"/>
-      <c r="E165" s="2" t="n"/>
+      <c r="D165" s="3" t="n"/>
+      <c r="E165" s="3" t="n"/>
     </row>
     <row r="166">
-      <c r="D166" s="2" t="n"/>
-      <c r="E166" s="2" t="n"/>
+      <c r="D166" s="3" t="n"/>
+      <c r="E166" s="3" t="n"/>
     </row>
     <row r="167">
-      <c r="D167" s="2" t="n"/>
-      <c r="E167" s="2" t="n"/>
+      <c r="D167" s="3" t="n"/>
+      <c r="E167" s="3" t="n"/>
     </row>
     <row r="168">
-      <c r="D168" s="2" t="n"/>
-      <c r="E168" s="2" t="n"/>
+      <c r="D168" s="3" t="n"/>
+      <c r="E168" s="3" t="n"/>
     </row>
     <row r="169">
-      <c r="D169" s="2" t="n"/>
-      <c r="E169" s="2" t="n"/>
+      <c r="D169" s="3" t="n"/>
+      <c r="E169" s="3" t="n"/>
     </row>
     <row r="170">
-      <c r="D170" s="2" t="n"/>
-      <c r="E170" s="2" t="n"/>
+      <c r="D170" s="3" t="n"/>
+      <c r="E170" s="3" t="n"/>
     </row>
     <row r="171">
-      <c r="D171" s="2" t="n"/>
-      <c r="E171" s="2" t="n"/>
+      <c r="D171" s="3" t="n"/>
+      <c r="E171" s="3" t="n"/>
     </row>
     <row r="172">
-      <c r="D172" s="2" t="n"/>
-      <c r="E172" s="2" t="n"/>
+      <c r="D172" s="3" t="n"/>
+      <c r="E172" s="3" t="n"/>
     </row>
     <row r="173">
-      <c r="D173" s="2" t="n"/>
-      <c r="E173" s="2" t="n"/>
+      <c r="D173" s="3" t="n"/>
+      <c r="E173" s="3" t="n"/>
     </row>
     <row r="174">
-      <c r="D174" s="2" t="n"/>
-      <c r="E174" s="2" t="n"/>
+      <c r="D174" s="3" t="n"/>
+      <c r="E174" s="3" t="n"/>
     </row>
     <row r="175">
-      <c r="D175" s="2" t="n"/>
-      <c r="E175" s="2" t="n"/>
+      <c r="D175" s="3" t="n"/>
+      <c r="E175" s="3" t="n"/>
     </row>
     <row r="176">
-      <c r="D176" s="2" t="n"/>
-      <c r="E176" s="2" t="n"/>
+      <c r="D176" s="3" t="n"/>
+      <c r="E176" s="3" t="n"/>
     </row>
     <row r="177">
-      <c r="D177" s="2" t="n"/>
-      <c r="E177" s="2" t="n"/>
+      <c r="D177" s="3" t="n"/>
+      <c r="E177" s="3" t="n"/>
     </row>
     <row r="178">
-      <c r="D178" s="2" t="n"/>
-      <c r="E178" s="2" t="n"/>
+      <c r="D178" s="3" t="n"/>
+      <c r="E178" s="3" t="n"/>
     </row>
     <row r="179">
-      <c r="D179" s="2" t="n"/>
-      <c r="E179" s="2" t="n"/>
+      <c r="D179" s="3" t="n"/>
+      <c r="E179" s="3" t="n"/>
     </row>
     <row r="180">
-      <c r="D180" s="2" t="n"/>
-      <c r="E180" s="2" t="n"/>
+      <c r="D180" s="3" t="n"/>
+      <c r="E180" s="3" t="n"/>
     </row>
     <row r="181">
-      <c r="D181" s="2" t="n"/>
-      <c r="E181" s="2" t="n"/>
+      <c r="D181" s="3" t="n"/>
+      <c r="E181" s="3" t="n"/>
     </row>
     <row r="182">
-      <c r="D182" s="2" t="n"/>
-      <c r="E182" s="2" t="n"/>
+      <c r="D182" s="3" t="n"/>
+      <c r="E182" s="3" t="n"/>
     </row>
     <row r="183">
-      <c r="D183" s="2" t="n"/>
-      <c r="E183" s="2" t="n"/>
+      <c r="D183" s="3" t="n"/>
+      <c r="E183" s="3" t="n"/>
     </row>
     <row r="184">
-      <c r="D184" s="2" t="n"/>
-      <c r="E184" s="2" t="n"/>
+      <c r="D184" s="3" t="n"/>
+      <c r="E184" s="3" t="n"/>
     </row>
     <row r="185">
-      <c r="D185" s="2" t="n"/>
-      <c r="E185" s="2" t="n"/>
+      <c r="D185" s="3" t="n"/>
+      <c r="E185" s="3" t="n"/>
     </row>
     <row r="186">
-      <c r="D186" s="2" t="n"/>
-      <c r="E186" s="2" t="n"/>
+      <c r="D186" s="3" t="n"/>
+      <c r="E186" s="3" t="n"/>
     </row>
     <row r="187">
-      <c r="D187" s="2" t="n"/>
-      <c r="E187" s="2" t="n"/>
+      <c r="D187" s="3" t="n"/>
+      <c r="E187" s="3" t="n"/>
     </row>
     <row r="188">
-      <c r="D188" s="2" t="n"/>
-      <c r="E188" s="2" t="n"/>
+      <c r="D188" s="3" t="n"/>
+      <c r="E188" s="3" t="n"/>
     </row>
     <row r="189">
-      <c r="D189" s="2" t="n"/>
-      <c r="E189" s="2" t="n"/>
+      <c r="D189" s="3" t="n"/>
+      <c r="E189" s="3" t="n"/>
     </row>
     <row r="190">
-      <c r="D190" s="2" t="n"/>
-      <c r="E190" s="2" t="n"/>
+      <c r="D190" s="3" t="n"/>
+      <c r="E190" s="3" t="n"/>
     </row>
     <row r="191">
-      <c r="D191" s="2" t="n"/>
-      <c r="E191" s="2" t="n"/>
+      <c r="D191" s="3" t="n"/>
+      <c r="E191" s="3" t="n"/>
     </row>
     <row r="192">
-      <c r="D192" s="2" t="n"/>
-      <c r="E192" s="2" t="n"/>
+      <c r="D192" s="3" t="n"/>
+      <c r="E192" s="3" t="n"/>
     </row>
     <row r="193">
-      <c r="D193" s="2" t="n"/>
-      <c r="E193" s="2" t="n"/>
+      <c r="D193" s="3" t="n"/>
+      <c r="E193" s="3" t="n"/>
     </row>
     <row r="194">
-      <c r="D194" s="2" t="n"/>
-      <c r="E194" s="2" t="n"/>
+      <c r="D194" s="3" t="n"/>
+      <c r="E194" s="3" t="n"/>
     </row>
     <row r="195">
-      <c r="D195" s="2" t="n"/>
-      <c r="E195" s="2" t="n"/>
+      <c r="D195" s="3" t="n"/>
+      <c r="E195" s="3" t="n"/>
     </row>
     <row r="196">
-      <c r="D196" s="2" t="n"/>
-      <c r="E196" s="2" t="n"/>
+      <c r="D196" s="3" t="n"/>
+      <c r="E196" s="3" t="n"/>
     </row>
     <row r="197">
-      <c r="D197" s="2" t="n"/>
-      <c r="E197" s="2" t="n"/>
+      <c r="D197" s="3" t="n"/>
+      <c r="E197" s="3" t="n"/>
     </row>
     <row r="198">
-      <c r="D198" s="2" t="n"/>
-      <c r="E198" s="2" t="n"/>
+      <c r="D198" s="3" t="n"/>
+      <c r="E198" s="3" t="n"/>
     </row>
     <row r="199">
-      <c r="D199" s="2" t="n"/>
-      <c r="E199" s="2" t="n"/>
+      <c r="D199" s="3" t="n"/>
+      <c r="E199" s="3" t="n"/>
     </row>
     <row r="200">
-      <c r="D200" s="2" t="n"/>
-      <c r="E200" s="2" t="n"/>
+      <c r="D200" s="3" t="n"/>
+      <c r="E200" s="3" t="n"/>
     </row>
     <row r="201">
-      <c r="D201" s="2" t="n"/>
-      <c r="E201" s="2" t="n"/>
+      <c r="D201" s="3" t="n"/>
+      <c r="E201" s="3" t="n"/>
     </row>
     <row r="202">
-      <c r="D202" s="2" t="n"/>
-      <c r="E202" s="2" t="n"/>
+      <c r="D202" s="3" t="n"/>
+      <c r="E202" s="3" t="n"/>
     </row>
     <row r="203">
-      <c r="D203" s="2" t="n"/>
-      <c r="E203" s="2" t="n"/>
+      <c r="D203" s="3" t="n"/>
+      <c r="E203" s="3" t="n"/>
     </row>
     <row r="204">
-      <c r="D204" s="2" t="n"/>
-      <c r="E204" s="2" t="n"/>
+      <c r="D204" s="3" t="n"/>
+      <c r="E204" s="3" t="n"/>
     </row>
     <row r="205">
-      <c r="D205" s="2" t="n"/>
-      <c r="E205" s="2" t="n"/>
+      <c r="D205" s="3" t="n"/>
+      <c r="E205" s="3" t="n"/>
     </row>
     <row r="206">
-      <c r="D206" s="2" t="n"/>
-      <c r="E206" s="2" t="n"/>
+      <c r="D206" s="3" t="n"/>
+      <c r="E206" s="3" t="n"/>
     </row>
     <row r="207">
-      <c r="D207" s="2" t="n"/>
-      <c r="E207" s="2" t="n"/>
+      <c r="D207" s="3" t="n"/>
+      <c r="E207" s="3" t="n"/>
     </row>
     <row r="208">
-      <c r="D208" s="2" t="n"/>
-      <c r="E208" s="2" t="n"/>
+      <c r="D208" s="3" t="n"/>
+      <c r="E208" s="3" t="n"/>
     </row>
     <row r="209">
-      <c r="D209" s="2" t="n"/>
-      <c r="E209" s="2" t="n"/>
+      <c r="D209" s="3" t="n"/>
+      <c r="E209" s="3" t="n"/>
     </row>
     <row r="210">
-      <c r="D210" s="2" t="n"/>
-      <c r="E210" s="2" t="n"/>
+      <c r="D210" s="3" t="n"/>
+      <c r="E210" s="3" t="n"/>
     </row>
     <row r="211">
-      <c r="D211" s="2" t="n"/>
-      <c r="E211" s="2" t="n"/>
+      <c r="D211" s="3" t="n"/>
+      <c r="E211" s="3" t="n"/>
     </row>
     <row r="212">
-      <c r="D212" s="2" t="n"/>
-      <c r="E212" s="2" t="n"/>
+      <c r="D212" s="3" t="n"/>
+      <c r="E212" s="3" t="n"/>
     </row>
     <row r="213">
-      <c r="D213" s="2" t="n"/>
-      <c r="E213" s="2" t="n"/>
+      <c r="D213" s="3" t="n"/>
+      <c r="E213" s="3" t="n"/>
     </row>
     <row r="214">
-      <c r="D214" s="2" t="n"/>
-      <c r="E214" s="2" t="n"/>
+      <c r="D214" s="3" t="n"/>
+      <c r="E214" s="3" t="n"/>
     </row>
     <row r="215">
-      <c r="D215" s="2" t="n"/>
-      <c r="E215" s="2" t="n"/>
+      <c r="D215" s="3" t="n"/>
+      <c r="E215" s="3" t="n"/>
     </row>
     <row r="216">
-      <c r="D216" s="2" t="n"/>
-      <c r="E216" s="2" t="n"/>
+      <c r="D216" s="3" t="n"/>
+      <c r="E216" s="3" t="n"/>
     </row>
     <row r="217">
-      <c r="D217" s="2" t="n"/>
-      <c r="E217" s="2" t="n"/>
+      <c r="D217" s="3" t="n"/>
+      <c r="E217" s="3" t="n"/>
     </row>
     <row r="218">
-      <c r="D218" s="2" t="n"/>
-      <c r="E218" s="2" t="n"/>
+      <c r="D218" s="3" t="n"/>
+      <c r="E218" s="3" t="n"/>
     </row>
     <row r="219">
-      <c r="D219" s="2" t="n"/>
-      <c r="E219" s="2" t="n"/>
+      <c r="D219" s="3" t="n"/>
+      <c r="E219" s="3" t="n"/>
     </row>
     <row r="220">
-      <c r="D220" s="2" t="n"/>
-      <c r="E220" s="2" t="n"/>
+      <c r="D220" s="3" t="n"/>
+      <c r="E220" s="3" t="n"/>
     </row>
     <row r="221">
-      <c r="D221" s="2" t="n"/>
-      <c r="E221" s="2" t="n"/>
+      <c r="D221" s="3" t="n"/>
+      <c r="E221" s="3" t="n"/>
     </row>
     <row r="222">
-      <c r="D222" s="2" t="n"/>
-      <c r="E222" s="2" t="n"/>
+      <c r="D222" s="3" t="n"/>
+      <c r="E222" s="3" t="n"/>
     </row>
     <row r="223">
-      <c r="D223" s="2" t="n"/>
-      <c r="E223" s="2" t="n"/>
+      <c r="D223" s="3" t="n"/>
+      <c r="E223" s="3" t="n"/>
     </row>
     <row r="224">
-      <c r="D224" s="2" t="n"/>
-      <c r="E224" s="2" t="n"/>
+      <c r="D224" s="3" t="n"/>
+      <c r="E224" s="3" t="n"/>
     </row>
     <row r="225">
-      <c r="D225" s="2" t="n"/>
-      <c r="E225" s="2" t="n"/>
+      <c r="D225" s="3" t="n"/>
+      <c r="E225" s="3" t="n"/>
     </row>
     <row r="226">
-      <c r="D226" s="2" t="n"/>
-      <c r="E226" s="2" t="n"/>
+      <c r="D226" s="3" t="n"/>
+      <c r="E226" s="3" t="n"/>
     </row>
     <row r="227">
-      <c r="D227" s="2" t="n"/>
-      <c r="E227" s="2" t="n"/>
+      <c r="D227" s="3" t="n"/>
+      <c r="E227" s="3" t="n"/>
     </row>
     <row r="228">
-      <c r="D228" s="2" t="n"/>
-      <c r="E228" s="2" t="n"/>
+      <c r="D228" s="3" t="n"/>
+      <c r="E228" s="3" t="n"/>
     </row>
     <row r="229">
-      <c r="D229" s="2" t="n"/>
-      <c r="E229" s="2" t="n"/>
+      <c r="D229" s="3" t="n"/>
+      <c r="E229" s="3" t="n"/>
     </row>
     <row r="230">
-      <c r="D230" s="2" t="n"/>
-      <c r="E230" s="2" t="n"/>
+      <c r="D230" s="3" t="n"/>
+      <c r="E230" s="3" t="n"/>
     </row>
     <row r="231">
-      <c r="D231" s="2" t="n"/>
-      <c r="E231" s="2" t="n"/>
+      <c r="D231" s="3" t="n"/>
+      <c r="E231" s="3" t="n"/>
     </row>
     <row r="232">
-      <c r="D232" s="2" t="n"/>
-      <c r="E232" s="2" t="n"/>
+      <c r="D232" s="3" t="n"/>
+      <c r="E232" s="3" t="n"/>
     </row>
     <row r="233">
-      <c r="D233" s="2" t="n"/>
-      <c r="E233" s="2" t="n"/>
+      <c r="D233" s="3" t="n"/>
+      <c r="E233" s="3" t="n"/>
     </row>
     <row r="234">
-      <c r="D234" s="2" t="n"/>
-      <c r="E234" s="2" t="n"/>
+      <c r="D234" s="3" t="n"/>
+      <c r="E234" s="3" t="n"/>
     </row>
     <row r="235">
-      <c r="D235" s="2" t="n"/>
-      <c r="E235" s="2" t="n"/>
+      <c r="D235" s="3" t="n"/>
+      <c r="E235" s="3" t="n"/>
     </row>
     <row r="236">
-      <c r="D236" s="2" t="n"/>
-      <c r="E236" s="2" t="n"/>
+      <c r="D236" s="3" t="n"/>
+      <c r="E236" s="3" t="n"/>
     </row>
     <row r="237">
-      <c r="D237" s="2" t="n"/>
-      <c r="E237" s="2" t="n"/>
+      <c r="D237" s="3" t="n"/>
+      <c r="E237" s="3" t="n"/>
     </row>
     <row r="238">
-      <c r="D238" s="2" t="n"/>
-      <c r="E238" s="2" t="n"/>
+      <c r="D238" s="3" t="n"/>
+      <c r="E238" s="3" t="n"/>
     </row>
     <row r="239">
-      <c r="D239" s="2" t="n"/>
-      <c r="E239" s="2" t="n"/>
+      <c r="D239" s="3" t="n"/>
+      <c r="E239" s="3" t="n"/>
     </row>
     <row r="240">
-      <c r="D240" s="2" t="n"/>
-      <c r="E240" s="2" t="n"/>
+      <c r="D240" s="3" t="n"/>
+      <c r="E240" s="3" t="n"/>
     </row>
     <row r="241">
-      <c r="D241" s="2" t="n"/>
-      <c r="E241" s="2" t="n"/>
+      <c r="D241" s="3" t="n"/>
+      <c r="E241" s="3" t="n"/>
     </row>
     <row r="242">
-      <c r="D242" s="2" t="n"/>
-      <c r="E242" s="2" t="n"/>
+      <c r="D242" s="3" t="n"/>
+      <c r="E242" s="3" t="n"/>
     </row>
     <row r="243">
-      <c r="D243" s="2" t="n"/>
-      <c r="E243" s="2" t="n"/>
+      <c r="D243" s="3" t="n"/>
+      <c r="E243" s="3" t="n"/>
     </row>
     <row r="244">
-      <c r="D244" s="2" t="n"/>
-      <c r="E244" s="2" t="n"/>
+      <c r="D244" s="3" t="n"/>
+      <c r="E244" s="3" t="n"/>
     </row>
     <row r="245">
-      <c r="D245" s="2" t="n"/>
-      <c r="E245" s="2" t="n"/>
+      <c r="D245" s="3" t="n"/>
+      <c r="E245" s="3" t="n"/>
     </row>
     <row r="246">
-      <c r="D246" s="2" t="n"/>
-      <c r="E246" s="2" t="n"/>
+      <c r="D246" s="3" t="n"/>
+      <c r="E246" s="3" t="n"/>
     </row>
     <row r="247">
-      <c r="D247" s="2" t="n"/>
-      <c r="E247" s="2" t="n"/>
+      <c r="D247" s="3" t="n"/>
+      <c r="E247" s="3" t="n"/>
     </row>
     <row r="248">
-      <c r="D248" s="2" t="n"/>
-      <c r="E248" s="2" t="n"/>
+      <c r="D248" s="3" t="n"/>
+      <c r="E248" s="3" t="n"/>
     </row>
     <row r="249">
-      <c r="D249" s="2" t="n"/>
-      <c r="E249" s="2" t="n"/>
+      <c r="D249" s="3" t="n"/>
+      <c r="E249" s="3" t="n"/>
     </row>
     <row r="250">
-      <c r="D250" s="2" t="n"/>
-      <c r="E250" s="2" t="n"/>
+      <c r="D250" s="3" t="n"/>
+      <c r="E250" s="3" t="n"/>
     </row>
     <row r="251">
-      <c r="D251" s="2" t="n"/>
-      <c r="E251" s="2" t="n"/>
+      <c r="D251" s="3" t="n"/>
+      <c r="E251" s="3" t="n"/>
     </row>
     <row r="252">
-      <c r="D252" s="2" t="n"/>
-      <c r="E252" s="2" t="n"/>
+      <c r="D252" s="3" t="n"/>
+      <c r="E252" s="3" t="n"/>
     </row>
     <row r="253">
-      <c r="D253" s="2" t="n"/>
-      <c r="E253" s="2" t="n"/>
+      <c r="D253" s="3" t="n"/>
+      <c r="E253" s="3" t="n"/>
     </row>
     <row r="254">
-      <c r="D254" s="2" t="n"/>
-      <c r="E254" s="2" t="n"/>
+      <c r="D254" s="3" t="n"/>
+      <c r="E254" s="3" t="n"/>
     </row>
     <row r="255">
-      <c r="D255" s="2" t="n"/>
-      <c r="E255" s="2" t="n"/>
+      <c r="D255" s="3" t="n"/>
+      <c r="E255" s="3" t="n"/>
     </row>
     <row r="256">
-      <c r="D256" s="2" t="n"/>
-      <c r="E256" s="2" t="n"/>
+      <c r="D256" s="3" t="n"/>
+      <c r="E256" s="3" t="n"/>
     </row>
     <row r="257">
-      <c r="D257" s="2" t="n"/>
-      <c r="E257" s="2" t="n"/>
+      <c r="D257" s="3" t="n"/>
+      <c r="E257" s="3" t="n"/>
     </row>
     <row r="258">
-      <c r="D258" s="2" t="n"/>
-      <c r="E258" s="2" t="n"/>
+      <c r="D258" s="3" t="n"/>
+      <c r="E258" s="3" t="n"/>
     </row>
     <row r="259">
-      <c r="D259" s="2" t="n"/>
-      <c r="E259" s="2" t="n"/>
+      <c r="D259" s="3" t="n"/>
+      <c r="E259" s="3" t="n"/>
     </row>
     <row r="260">
-      <c r="D260" s="2" t="n"/>
-      <c r="E260" s="2" t="n"/>
+      <c r="D260" s="3" t="n"/>
+      <c r="E260" s="3" t="n"/>
     </row>
     <row r="261">
-      <c r="D261" s="2" t="n"/>
-      <c r="E261" s="2" t="n"/>
+      <c r="D261" s="3" t="n"/>
+      <c r="E261" s="3" t="n"/>
     </row>
     <row r="262">
-      <c r="D262" s="2" t="n"/>
-      <c r="E262" s="2" t="n"/>
+      <c r="D262" s="3" t="n"/>
+      <c r="E262" s="3" t="n"/>
     </row>
     <row r="263">
-      <c r="D263" s="2" t="n"/>
-      <c r="E263" s="2" t="n"/>
+      <c r="D263" s="3" t="n"/>
+      <c r="E263" s="3" t="n"/>
     </row>
     <row r="264">
-      <c r="D264" s="2" t="n"/>
-      <c r="E264" s="2" t="n"/>
+      <c r="D264" s="3" t="n"/>
+      <c r="E264" s="3" t="n"/>
     </row>
     <row r="265">
-      <c r="D265" s="2" t="n"/>
-      <c r="E265" s="2" t="n"/>
+      <c r="D265" s="3" t="n"/>
+      <c r="E265" s="3" t="n"/>
     </row>
     <row r="266">
-      <c r="D266" s="2" t="n"/>
-      <c r="E266" s="2" t="n"/>
+      <c r="D266" s="3" t="n"/>
+      <c r="E266" s="3" t="n"/>
     </row>
     <row r="267">
-      <c r="D267" s="2" t="n"/>
-      <c r="E267" s="2" t="n"/>
+      <c r="D267" s="3" t="n"/>
+      <c r="E267" s="3" t="n"/>
     </row>
     <row r="268">
-      <c r="D268" s="2" t="n"/>
-      <c r="E268" s="2" t="n"/>
+      <c r="D268" s="3" t="n"/>
+      <c r="E268" s="3" t="n"/>
     </row>
     <row r="269">
-      <c r="D269" s="2" t="n"/>
-      <c r="E269" s="2" t="n"/>
+      <c r="D269" s="3" t="n"/>
+      <c r="E269" s="3" t="n"/>
     </row>
     <row r="270">
-      <c r="D270" s="2" t="n"/>
-      <c r="E270" s="2" t="n"/>
+      <c r="D270" s="3" t="n"/>
+      <c r="E270" s="3" t="n"/>
     </row>
     <row r="271">
-      <c r="D271" s="2" t="n"/>
-      <c r="E271" s="2" t="n"/>
+      <c r="D271" s="3" t="n"/>
+      <c r="E271" s="3" t="n"/>
     </row>
     <row r="272">
-      <c r="D272" s="2" t="n"/>
-      <c r="E272" s="2" t="n"/>
+      <c r="D272" s="3" t="n"/>
+      <c r="E272" s="3" t="n"/>
     </row>
     <row r="273">
-      <c r="D273" s="2" t="n"/>
-      <c r="E273" s="2" t="n"/>
+      <c r="D273" s="3" t="n"/>
+      <c r="E273" s="3" t="n"/>
     </row>
     <row r="274">
-      <c r="D274" s="2" t="n"/>
-      <c r="E274" s="2" t="n"/>
+      <c r="D274" s="3" t="n"/>
+      <c r="E274" s="3" t="n"/>
     </row>
     <row r="275">
-      <c r="D275" s="2" t="n"/>
-      <c r="E275" s="2" t="n"/>
+      <c r="D275" s="3" t="n"/>
+      <c r="E275" s="3" t="n"/>
     </row>
     <row r="276">
-      <c r="D276" s="2" t="n"/>
-      <c r="E276" s="2" t="n"/>
+      <c r="D276" s="3" t="n"/>
+      <c r="E276" s="3" t="n"/>
     </row>
     <row r="277">
-      <c r="D277" s="2" t="n"/>
-      <c r="E277" s="2" t="n"/>
+      <c r="D277" s="3" t="n"/>
+      <c r="E277" s="3" t="n"/>
     </row>
     <row r="278">
-      <c r="D278" s="2" t="n"/>
-      <c r="E278" s="2" t="n"/>
+      <c r="D278" s="3" t="n"/>
+      <c r="E278" s="3" t="n"/>
     </row>
     <row r="279">
-      <c r="D279" s="2" t="n"/>
-      <c r="E279" s="2" t="n"/>
+      <c r="D279" s="3" t="n"/>
+      <c r="E279" s="3" t="n"/>
     </row>
     <row r="280">
-      <c r="D280" s="2" t="n"/>
-      <c r="E280" s="2" t="n"/>
+      <c r="D280" s="3" t="n"/>
+      <c r="E280" s="3" t="n"/>
     </row>
     <row r="281">
-      <c r="D281" s="2" t="n"/>
-      <c r="E281" s="2" t="n"/>
+      <c r="D281" s="3" t="n"/>
+      <c r="E281" s="3" t="n"/>
     </row>
     <row r="282">
-      <c r="D282" s="2" t="n"/>
-      <c r="E282" s="2" t="n"/>
+      <c r="D282" s="3" t="n"/>
+      <c r="E282" s="3" t="n"/>
     </row>
     <row r="283">
-      <c r="D283" s="2" t="n"/>
-      <c r="E283" s="2" t="n"/>
+      <c r="D283" s="3" t="n"/>
+      <c r="E283" s="3" t="n"/>
     </row>
     <row r="284">
-      <c r="D284" s="2" t="n"/>
-      <c r="E284" s="2" t="n"/>
+      <c r="D284" s="3" t="n"/>
+      <c r="E284" s="3" t="n"/>
     </row>
     <row r="285">
-      <c r="D285" s="2" t="n"/>
-      <c r="E285" s="2" t="n"/>
+      <c r="D285" s="3" t="n"/>
+      <c r="E285" s="3" t="n"/>
     </row>
     <row r="286">
-      <c r="D286" s="2" t="n"/>
-      <c r="E286" s="2" t="n"/>
+      <c r="D286" s="3" t="n"/>
+      <c r="E286" s="3" t="n"/>
     </row>
     <row r="287">
-      <c r="D287" s="2" t="n"/>
-      <c r="E287" s="2" t="n"/>
+      <c r="D287" s="3" t="n"/>
+      <c r="E287" s="3" t="n"/>
     </row>
     <row r="288">
-      <c r="D288" s="2" t="n"/>
-      <c r="E288" s="2" t="n"/>
+      <c r="D288" s="3" t="n"/>
+      <c r="E288" s="3" t="n"/>
     </row>
     <row r="289">
-      <c r="D289" s="2" t="n"/>
-      <c r="E289" s="2" t="n"/>
+      <c r="D289" s="3" t="n"/>
+      <c r="E289" s="3" t="n"/>
     </row>
     <row r="290">
-      <c r="D290" s="2" t="n"/>
-      <c r="E290" s="2" t="n"/>
+      <c r="D290" s="3" t="n"/>
+      <c r="E290" s="3" t="n"/>
     </row>
     <row r="291">
-      <c r="D291" s="2" t="n"/>
-      <c r="E291" s="2" t="n"/>
+      <c r="D291" s="3" t="n"/>
+      <c r="E291" s="3" t="n"/>
     </row>
     <row r="292">
-      <c r="D292" s="2" t="n"/>
-      <c r="E292" s="2" t="n"/>
+      <c r="D292" s="3" t="n"/>
+      <c r="E292" s="3" t="n"/>
     </row>
     <row r="293">
-      <c r="D293" s="2" t="n"/>
-      <c r="E293" s="2" t="n"/>
+      <c r="D293" s="3" t="n"/>
+      <c r="E293" s="3" t="n"/>
     </row>
     <row r="294">
-      <c r="D294" s="2" t="n"/>
-      <c r="E294" s="2" t="n"/>
+      <c r="D294" s="3" t="n"/>
+      <c r="E294" s="3" t="n"/>
     </row>
     <row r="295">
-      <c r="D295" s="2" t="n"/>
-      <c r="E295" s="2" t="n"/>
+      <c r="D295" s="3" t="n"/>
+      <c r="E295" s="3" t="n"/>
     </row>
     <row r="296">
-      <c r="D296" s="2" t="n"/>
-      <c r="E296" s="2" t="n"/>
+      <c r="D296" s="3" t="n"/>
+      <c r="E296" s="3" t="n"/>
     </row>
     <row r="297">
-      <c r="D297" s="2" t="n"/>
-      <c r="E297" s="2" t="n"/>
+      <c r="D297" s="3" t="n"/>
+      <c r="E297" s="3" t="n"/>
     </row>
     <row r="298">
-      <c r="D298" s="2" t="n"/>
-      <c r="E298" s="2" t="n"/>
+      <c r="D298" s="3" t="n"/>
+      <c r="E298" s="3" t="n"/>
     </row>
     <row r="299">
-      <c r="D299" s="2" t="n"/>
-      <c r="E299" s="2" t="n"/>
+      <c r="D299" s="3" t="n"/>
+      <c r="E299" s="3" t="n"/>
     </row>
     <row r="300">
-      <c r="D300" s="2" t="n"/>
-      <c r="E300" s="2" t="n"/>
+      <c r="D300" s="3" t="n"/>
+      <c r="E300" s="3" t="n"/>
     </row>
     <row r="301">
-      <c r="D301" s="2" t="n"/>
-      <c r="E301" s="2" t="n"/>
+      <c r="D301" s="3" t="n"/>
+      <c r="E301" s="3" t="n"/>
     </row>
     <row r="302">
-      <c r="D302" s="2" t="n"/>
-      <c r="E302" s="2" t="n"/>
+      <c r="D302" s="3" t="n"/>
+      <c r="E302" s="3" t="n"/>
     </row>
     <row r="303">
-      <c r="D303" s="2" t="n"/>
-      <c r="E303" s="2" t="n"/>
+      <c r="D303" s="3" t="n"/>
+      <c r="E303" s="3" t="n"/>
     </row>
     <row r="304">
-      <c r="D304" s="2" t="n"/>
-      <c r="E304" s="2" t="n"/>
+      <c r="D304" s="3" t="n"/>
+      <c r="E304" s="3" t="n"/>
     </row>
     <row r="305">
-      <c r="D305" s="2" t="n"/>
-      <c r="E305" s="2" t="n"/>
+      <c r="D305" s="3" t="n"/>
+      <c r="E305" s="3" t="n"/>
     </row>
     <row r="306">
-      <c r="D306" s="2" t="n"/>
-      <c r="E306" s="2" t="n"/>
+      <c r="D306" s="3" t="n"/>
+      <c r="E306" s="3" t="n"/>
     </row>
     <row r="307">
-      <c r="D307" s="2" t="n"/>
-      <c r="E307" s="2" t="n"/>
+      <c r="D307" s="3" t="n"/>
+      <c r="E307" s="3" t="n"/>
     </row>
     <row r="308">
-      <c r="D308" s="2" t="n"/>
-      <c r="E308" s="2" t="n"/>
+      <c r="D308" s="3" t="n"/>
+      <c r="E308" s="3" t="n"/>
     </row>
     <row r="309">
-      <c r="D309" s="2" t="n"/>
-      <c r="E309" s="2" t="n"/>
+      <c r="D309" s="3" t="n"/>
+      <c r="E309" s="3" t="n"/>
     </row>
     <row r="310">
-      <c r="D310" s="2" t="n"/>
-      <c r="E310" s="2" t="n"/>
+      <c r="D310" s="3" t="n"/>
+      <c r="E310" s="3" t="n"/>
     </row>
     <row r="311">
-      <c r="D311" s="2" t="n"/>
-      <c r="E311" s="2" t="n"/>
+      <c r="D311" s="3" t="n"/>
+      <c r="E311" s="3" t="n"/>
     </row>
     <row r="312">
-      <c r="D312" s="2" t="n"/>
-      <c r="E312" s="2" t="n"/>
+      <c r="D312" s="3" t="n"/>
+      <c r="E312" s="3" t="n"/>
     </row>
     <row r="313">
-      <c r="D313" s="2" t="n"/>
-      <c r="E313" s="2" t="n"/>
+      <c r="D313" s="3" t="n"/>
+      <c r="E313" s="3" t="n"/>
     </row>
     <row r="314">
-      <c r="D314" s="2" t="n"/>
-      <c r="E314" s="2" t="n"/>
+      <c r="D314" s="3" t="n"/>
+      <c r="E314" s="3" t="n"/>
     </row>
     <row r="315">
-      <c r="D315" s="2" t="n"/>
-      <c r="E315" s="2" t="n"/>
+      <c r="D315" s="3" t="n"/>
+      <c r="E315" s="3" t="n"/>
     </row>
     <row r="316">
-      <c r="D316" s="2" t="n"/>
-      <c r="E316" s="2" t="n"/>
+      <c r="D316" s="3" t="n"/>
+      <c r="E316" s="3" t="n"/>
     </row>
     <row r="317">
-      <c r="D317" s="2" t="n"/>
-      <c r="E317" s="2" t="n"/>
+      <c r="D317" s="3" t="n"/>
+      <c r="E317" s="3" t="n"/>
     </row>
     <row r="318">
-      <c r="D318" s="2" t="n"/>
-      <c r="E318" s="2" t="n"/>
+      <c r="D318" s="3" t="n"/>
+      <c r="E318" s="3" t="n"/>
     </row>
     <row r="319">
-      <c r="D319" s="2" t="n"/>
-      <c r="E319" s="2" t="n"/>
+      <c r="D319" s="3" t="n"/>
+      <c r="E319" s="3" t="n"/>
     </row>
     <row r="320">
-      <c r="D320" s="2" t="n"/>
-      <c r="E320" s="2" t="n"/>
+      <c r="D320" s="3" t="n"/>
+      <c r="E320" s="3" t="n"/>
     </row>
     <row r="321">
-      <c r="D321" s="2" t="n"/>
-      <c r="E321" s="2" t="n"/>
+      <c r="D321" s="3" t="n"/>
+      <c r="E321" s="3" t="n"/>
     </row>
     <row r="322">
-      <c r="D322" s="2" t="n"/>
-      <c r="E322" s="2" t="n"/>
+      <c r="D322" s="3" t="n"/>
+      <c r="E322" s="3" t="n"/>
     </row>
     <row r="323">
-      <c r="D323" s="2" t="n"/>
-      <c r="E323" s="2" t="n"/>
+      <c r="D323" s="3" t="n"/>
+      <c r="E323" s="3" t="n"/>
     </row>
     <row r="324">
-      <c r="D324" s="2" t="n"/>
-      <c r="E324" s="2" t="n"/>
+      <c r="D324" s="3" t="n"/>
+      <c r="E324" s="3" t="n"/>
     </row>
     <row r="325">
-      <c r="D325" s="2" t="n"/>
-      <c r="E325" s="2" t="n"/>
+      <c r="D325" s="3" t="n"/>
+      <c r="E325" s="3" t="n"/>
     </row>
     <row r="326">
-      <c r="D326" s="2" t="n"/>
-      <c r="E326" s="2" t="n"/>
+      <c r="D326" s="3" t="n"/>
+      <c r="E326" s="3" t="n"/>
     </row>
     <row r="327">
-      <c r="D327" s="2" t="n"/>
-      <c r="E327" s="2" t="n"/>
+      <c r="D327" s="3" t="n"/>
+      <c r="E327" s="3" t="n"/>
     </row>
     <row r="328">
-      <c r="D328" s="2" t="n"/>
-      <c r="E328" s="2" t="n"/>
+      <c r="D328" s="3" t="n"/>
+      <c r="E328" s="3" t="n"/>
     </row>
     <row r="329">
-      <c r="D329" s="2" t="n"/>
-      <c r="E329" s="2" t="n"/>
+      <c r="D329" s="3" t="n"/>
+      <c r="E329" s="3" t="n"/>
     </row>
     <row r="330">
-      <c r="D330" s="2" t="n"/>
-      <c r="E330" s="2" t="n"/>
+      <c r="D330" s="3" t="n"/>
+      <c r="E330" s="3" t="n"/>
     </row>
     <row r="331">
-      <c r="D331" s="2" t="n"/>
-      <c r="E331" s="2" t="n"/>
+      <c r="D331" s="3" t="n"/>
+      <c r="E331" s="3" t="n"/>
     </row>
     <row r="332">
-      <c r="D332" s="2" t="n"/>
-      <c r="E332" s="2" t="n"/>
+      <c r="D332" s="3" t="n"/>
+      <c r="E332" s="3" t="n"/>
     </row>
     <row r="333">
-      <c r="D333" s="2" t="n"/>
-      <c r="E333" s="2" t="n"/>
+      <c r="D333" s="3" t="n"/>
+      <c r="E333" s="3" t="n"/>
     </row>
     <row r="334">
-      <c r="D334" s="2" t="n"/>
-      <c r="E334" s="2" t="n"/>
+      <c r="D334" s="3" t="n"/>
+      <c r="E334" s="3" t="n"/>
     </row>
     <row r="335">
-      <c r="D335" s="2" t="n"/>
-      <c r="E335" s="2" t="n"/>
+      <c r="D335" s="3" t="n"/>
+      <c r="E335" s="3" t="n"/>
     </row>
     <row r="336">
-      <c r="D336" s="2" t="n"/>
-      <c r="E336" s="2" t="n"/>
+      <c r="D336" s="3" t="n"/>
+      <c r="E336" s="3" t="n"/>
     </row>
     <row r="337">
-      <c r="D337" s="2" t="n"/>
-      <c r="E337" s="2" t="n"/>
+      <c r="D337" s="3" t="n"/>
+      <c r="E337" s="3" t="n"/>
     </row>
     <row r="338">
-      <c r="D338" s="2" t="n"/>
-      <c r="E338" s="2" t="n"/>
+      <c r="D338" s="3" t="n"/>
+      <c r="E338" s="3" t="n"/>
     </row>
     <row r="339">
-      <c r="D339" s="2" t="n"/>
-      <c r="E339" s="2" t="n"/>
+      <c r="D339" s="3" t="n"/>
+      <c r="E339" s="3" t="n"/>
     </row>
     <row r="340">
-      <c r="D340" s="2" t="n"/>
-      <c r="E340" s="2" t="n"/>
+      <c r="D340" s="3" t="n"/>
+      <c r="E340" s="3" t="n"/>
     </row>
     <row r="341">
-      <c r="D341" s="2" t="n"/>
-      <c r="E341" s="2" t="n"/>
+      <c r="D341" s="3" t="n"/>
+      <c r="E341" s="3" t="n"/>
     </row>
     <row r="342">
-      <c r="D342" s="2" t="n"/>
-      <c r="E342" s="2" t="n"/>
+      <c r="D342" s="3" t="n"/>
+      <c r="E342" s="3" t="n"/>
     </row>
     <row r="343">
-      <c r="D343" s="2" t="n"/>
-      <c r="E343" s="2" t="n"/>
+      <c r="D343" s="3" t="n"/>
+      <c r="E343" s="3" t="n"/>
     </row>
     <row r="344">
-      <c r="D344" s="2" t="n"/>
-      <c r="E344" s="2" t="n"/>
+      <c r="D344" s="3" t="n"/>
+      <c r="E344" s="3" t="n"/>
     </row>
     <row r="345">
-      <c r="D345" s="2" t="n"/>
-      <c r="E345" s="2" t="n"/>
+      <c r="D345" s="3" t="n"/>
+      <c r="E345" s="3" t="n"/>
     </row>
     <row r="346">
-      <c r="D346" s="2" t="n"/>
-      <c r="E346" s="2" t="n"/>
+      <c r="D346" s="3" t="n"/>
+      <c r="E346" s="3" t="n"/>
     </row>
     <row r="347">
-      <c r="D347" s="2" t="n"/>
-      <c r="E347" s="2" t="n"/>
+      <c r="D347" s="3" t="n"/>
+      <c r="E347" s="3" t="n"/>
     </row>
     <row r="348">
-      <c r="D348" s="2" t="n"/>
-      <c r="E348" s="2" t="n"/>
+      <c r="D348" s="3" t="n"/>
+      <c r="E348" s="3" t="n"/>
     </row>
     <row r="349">
-      <c r="D349" s="2" t="n"/>
-      <c r="E349" s="2" t="n"/>
+      <c r="D349" s="3" t="n"/>
+      <c r="E349" s="3" t="n"/>
     </row>
     <row r="350">
-      <c r="D350" s="2" t="n"/>
-      <c r="E350" s="2" t="n"/>
+      <c r="D350" s="3" t="n"/>
+      <c r="E350" s="3" t="n"/>
     </row>
     <row r="351">
-      <c r="D351" s="2" t="n"/>
-      <c r="E351" s="2" t="n"/>
+      <c r="D351" s="3" t="n"/>
+      <c r="E351" s="3" t="n"/>
     </row>
     <row r="352">
-      <c r="D352" s="2" t="n"/>
-      <c r="E352" s="2" t="n"/>
+      <c r="D352" s="3" t="n"/>
+      <c r="E352" s="3" t="n"/>
     </row>
     <row r="353">
-      <c r="D353" s="2" t="n"/>
-      <c r="E353" s="2" t="n"/>
+      <c r="D353" s="3" t="n"/>
+      <c r="E353" s="3" t="n"/>
     </row>
     <row r="354">
-      <c r="D354" s="2" t="n"/>
-      <c r="E354" s="2" t="n"/>
+      <c r="D354" s="3" t="n"/>
+      <c r="E354" s="3" t="n"/>
     </row>
     <row r="355">
-      <c r="D355" s="2" t="n"/>
-      <c r="E355" s="2" t="n"/>
+      <c r="D355" s="3" t="n"/>
+      <c r="E355" s="3" t="n"/>
     </row>
     <row r="356">
-      <c r="D356" s="2" t="n"/>
-      <c r="E356" s="2" t="n"/>
+      <c r="D356" s="3" t="n"/>
+      <c r="E356" s="3" t="n"/>
     </row>
     <row r="357">
-      <c r="D357" s="2" t="n"/>
-      <c r="E357" s="2" t="n"/>
+      <c r="D357" s="3" t="n"/>
+      <c r="E357" s="3" t="n"/>
     </row>
     <row r="358">
-      <c r="D358" s="2" t="n"/>
-      <c r="E358" s="2" t="n"/>
+      <c r="D358" s="3" t="n"/>
+      <c r="E358" s="3" t="n"/>
     </row>
     <row r="359">
-      <c r="D359" s="2" t="n"/>
-      <c r="E359" s="2" t="n"/>
+      <c r="D359" s="3" t="n"/>
+      <c r="E359" s="3" t="n"/>
     </row>
     <row r="360">
-      <c r="D360" s="2" t="n"/>
-      <c r="E360" s="2" t="n"/>
+      <c r="D360" s="3" t="n"/>
+      <c r="E360" s="3" t="n"/>
     </row>
     <row r="361">
-      <c r="D361" s="2" t="n"/>
-      <c r="E361" s="2" t="n"/>
+      <c r="D361" s="3" t="n"/>
+      <c r="E361" s="3" t="n"/>
     </row>
     <row r="362">
-      <c r="D362" s="2" t="n"/>
-      <c r="E362" s="2" t="n"/>
+      <c r="D362" s="3" t="n"/>
+      <c r="E362" s="3" t="n"/>
     </row>
     <row r="363">
-      <c r="D363" s="2" t="n"/>
-      <c r="E363" s="2" t="n"/>
+      <c r="D363" s="3" t="n"/>
+      <c r="E363" s="3" t="n"/>
     </row>
     <row r="364">
-      <c r="D364" s="2" t="n"/>
-      <c r="E364" s="2" t="n"/>
+      <c r="D364" s="3" t="n"/>
+      <c r="E364" s="3" t="n"/>
     </row>
     <row r="365">
-      <c r="D365" s="2" t="n"/>
-      <c r="E365" s="2" t="n"/>
+      <c r="D365" s="3" t="n"/>
+      <c r="E365" s="3" t="n"/>
     </row>
     <row r="366">
-      <c r="D366" s="2" t="n"/>
-      <c r="E366" s="2" t="n"/>
+      <c r="D366" s="3" t="n"/>
+      <c r="E366" s="3" t="n"/>
     </row>
     <row r="367">
-      <c r="D367" s="2" t="n"/>
-      <c r="E367" s="2" t="n"/>
+      <c r="D367" s="3" t="n"/>
+      <c r="E367" s="3" t="n"/>
     </row>
     <row r="368">
-      <c r="D368" s="2" t="n"/>
-      <c r="E368" s="2" t="n"/>
+      <c r="D368" s="3" t="n"/>
+      <c r="E368" s="3" t="n"/>
     </row>
     <row r="369">
-      <c r="D369" s="2" t="n"/>
-      <c r="E369" s="2" t="n"/>
+      <c r="D369" s="3" t="n"/>
+      <c r="E369" s="3" t="n"/>
     </row>
     <row r="370">
-      <c r="D370" s="2" t="n"/>
-      <c r="E370" s="2" t="n"/>
+      <c r="D370" s="3" t="n"/>
+      <c r="E370" s="3" t="n"/>
     </row>
     <row r="371">
-      <c r="D371" s="2" t="n"/>
-      <c r="E371" s="2" t="n"/>
+      <c r="D371" s="3" t="n"/>
+      <c r="E371" s="3" t="n"/>
     </row>
     <row r="372">
-      <c r="D372" s="2" t="n"/>
-      <c r="E372" s="2" t="n"/>
+      <c r="D372" s="3" t="n"/>
+      <c r="E372" s="3" t="n"/>
     </row>
     <row r="373">
-      <c r="D373" s="2" t="n"/>
-      <c r="E373" s="2" t="n"/>
+      <c r="D373" s="3" t="n"/>
+      <c r="E373" s="3" t="n"/>
     </row>
     <row r="374">
-      <c r="D374" s="2" t="n"/>
-      <c r="E374" s="2" t="n"/>
+      <c r="D374" s="3" t="n"/>
+      <c r="E374" s="3" t="n"/>
     </row>
     <row r="375">
-      <c r="D375" s="2" t="n"/>
-      <c r="E375" s="2" t="n"/>
+      <c r="D375" s="3" t="n"/>
+      <c r="E375" s="3" t="n"/>
     </row>
     <row r="376">
-      <c r="D376" s="2" t="n"/>
-      <c r="E376" s="2" t="n"/>
+      <c r="D376" s="3" t="n"/>
+      <c r="E376" s="3" t="n"/>
     </row>
     <row r="377">
-      <c r="D377" s="2" t="n"/>
-      <c r="E377" s="2" t="n"/>
+      <c r="D377" s="3" t="n"/>
+      <c r="E377" s="3" t="n"/>
     </row>
     <row r="378">
-      <c r="D378" s="2" t="n"/>
-      <c r="E378" s="2" t="n"/>
+      <c r="D378" s="3" t="n"/>
+      <c r="E378" s="3" t="n"/>
     </row>
     <row r="379">
-      <c r="D379" s="2" t="n"/>
-      <c r="E379" s="2" t="n"/>
+      <c r="D379" s="3" t="n"/>
+      <c r="E379" s="3" t="n"/>
     </row>
     <row r="380">
-      <c r="D380" s="2" t="n"/>
-      <c r="E380" s="2" t="n"/>
+      <c r="D380" s="3" t="n"/>
+      <c r="E380" s="3" t="n"/>
     </row>
     <row r="381">
-      <c r="D381" s="2" t="n"/>
-      <c r="E381" s="2" t="n"/>
+      <c r="D381" s="3" t="n"/>
+      <c r="E381" s="3" t="n"/>
     </row>
     <row r="382">
-      <c r="D382" s="2" t="n"/>
-      <c r="E382" s="2" t="n"/>
+      <c r="D382" s="3" t="n"/>
+      <c r="E382" s="3" t="n"/>
     </row>
     <row r="383">
-      <c r="D383" s="2" t="n"/>
-      <c r="E383" s="2" t="n"/>
+      <c r="D383" s="3" t="n"/>
+      <c r="E383" s="3" t="n"/>
     </row>
     <row r="384">
-      <c r="D384" s="2" t="n"/>
-      <c r="E384" s="2" t="n"/>
+      <c r="D384" s="3" t="n"/>
+      <c r="E384" s="3" t="n"/>
     </row>
     <row r="385">
-      <c r="D385" s="2" t="n"/>
-      <c r="E385" s="2" t="n"/>
+      <c r="D385" s="3" t="n"/>
+      <c r="E385" s="3" t="n"/>
     </row>
     <row r="386">
-      <c r="D386" s="2" t="n"/>
-      <c r="E386" s="2" t="n"/>
+      <c r="D386" s="3" t="n"/>
+      <c r="E386" s="3" t="n"/>
     </row>
     <row r="387">
-      <c r="D387" s="2" t="n"/>
-      <c r="E387" s="2" t="n"/>
+      <c r="D387" s="3" t="n"/>
+      <c r="E387" s="3" t="n"/>
     </row>
     <row r="388">
-      <c r="D388" s="2" t="n"/>
-      <c r="E388" s="2" t="n"/>
+      <c r="D388" s="3" t="n"/>
+      <c r="E388" s="3" t="n"/>
     </row>
     <row r="389">
-      <c r="D389" s="2" t="n"/>
-      <c r="E389" s="2" t="n"/>
+      <c r="D389" s="3" t="n"/>
+      <c r="E389" s="3" t="n"/>
     </row>
     <row r="390">
-      <c r="D390" s="2" t="n"/>
-      <c r="E390" s="2" t="n"/>
+      <c r="D390" s="3" t="n"/>
+      <c r="E390" s="3" t="n"/>
     </row>
     <row r="391">
-      <c r="D391" s="2" t="n"/>
-      <c r="E391" s="2" t="n"/>
+      <c r="D391" s="3" t="n"/>
+      <c r="E391" s="3" t="n"/>
     </row>
     <row r="392">
-      <c r="D392" s="2" t="n"/>
-      <c r="E392" s="2" t="n"/>
+      <c r="D392" s="3" t="n"/>
+      <c r="E392" s="3" t="n"/>
     </row>
     <row r="393">
-      <c r="D393" s="2" t="n"/>
-      <c r="E393" s="2" t="n"/>
+      <c r="D393" s="3" t="n"/>
+      <c r="E393" s="3" t="n"/>
     </row>
     <row r="394">
-      <c r="D394" s="2" t="n"/>
-      <c r="E394" s="2" t="n"/>
+      <c r="D394" s="3" t="n"/>
+      <c r="E394" s="3" t="n"/>
     </row>
     <row r="395">
-      <c r="D395" s="2" t="n"/>
-      <c r="E395" s="2" t="n"/>
+      <c r="D395" s="3" t="n"/>
+      <c r="E395" s="3" t="n"/>
     </row>
     <row r="396">
-      <c r="D396" s="2" t="n"/>
-      <c r="E396" s="2" t="n"/>
+      <c r="D396" s="3" t="n"/>
+      <c r="E396" s="3" t="n"/>
     </row>
     <row r="397">
-      <c r="D397" s="2" t="n"/>
-      <c r="E397" s="2" t="n"/>
+      <c r="D397" s="3" t="n"/>
+      <c r="E397" s="3" t="n"/>
     </row>
     <row r="398">
-      <c r="D398" s="2" t="n"/>
-      <c r="E398" s="2" t="n"/>
+      <c r="D398" s="3" t="n"/>
+      <c r="E398" s="3" t="n"/>
     </row>
     <row r="399">
-      <c r="D399" s="2" t="n"/>
-      <c r="E399" s="2" t="n"/>
+      <c r="D399" s="3" t="n"/>
+      <c r="E399" s="3" t="n"/>
     </row>
     <row r="400">
-      <c r="D400" s="2" t="n"/>
-      <c r="E400" s="2" t="n"/>
+      <c r="D400" s="3" t="n"/>
+      <c r="E400" s="3" t="n"/>
     </row>
     <row r="401">
-      <c r="D401" s="2" t="n"/>
-      <c r="E401" s="2" t="n"/>
+      <c r="D401" s="3" t="n"/>
+      <c r="E401" s="3" t="n"/>
     </row>
     <row r="402">
-      <c r="D402" s="2" t="n"/>
-      <c r="E402" s="2" t="n"/>
+      <c r="D402" s="3" t="n"/>
+      <c r="E402" s="3" t="n"/>
     </row>
     <row r="403">
-      <c r="D403" s="2" t="n"/>
-      <c r="E403" s="2" t="n"/>
+      <c r="D403" s="3" t="n"/>
+      <c r="E403" s="3" t="n"/>
     </row>
     <row r="404">
-      <c r="D404" s="2" t="n"/>
-      <c r="E404" s="2" t="n"/>
+      <c r="D404" s="3" t="n"/>
+      <c r="E404" s="3" t="n"/>
     </row>
     <row r="405">
-      <c r="D405" s="2" t="n"/>
-      <c r="E405" s="2" t="n"/>
+      <c r="D405" s="3" t="n"/>
+      <c r="E405" s="3" t="n"/>
     </row>
     <row r="406">
-      <c r="D406" s="2" t="n"/>
-      <c r="E406" s="2" t="n"/>
+      <c r="D406" s="3" t="n"/>
+      <c r="E406" s="3" t="n"/>
     </row>
     <row r="407">
-      <c r="D407" s="2" t="n"/>
-      <c r="E407" s="2" t="n"/>
+      <c r="D407" s="3" t="n"/>
+      <c r="E407" s="3" t="n"/>
     </row>
     <row r="408">
-      <c r="D408" s="2" t="n"/>
-      <c r="E408" s="2" t="n"/>
+      <c r="D408" s="3" t="n"/>
+      <c r="E408" s="3" t="n"/>
     </row>
     <row r="409">
-      <c r="D409" s="2" t="n"/>
-      <c r="E409" s="2" t="n"/>
+      <c r="D409" s="3" t="n"/>
+      <c r="E409" s="3" t="n"/>
     </row>
     <row r="410">
-      <c r="D410" s="2" t="n"/>
-      <c r="E410" s="2" t="n"/>
+      <c r="D410" s="3" t="n"/>
+      <c r="E410" s="3" t="n"/>
     </row>
     <row r="411">
-      <c r="D411" s="2" t="n"/>
-      <c r="E411" s="2" t="n"/>
+      <c r="D411" s="3" t="n"/>
+      <c r="E411" s="3" t="n"/>
     </row>
     <row r="412">
-      <c r="D412" s="2" t="n"/>
-      <c r="E412" s="2" t="n"/>
+      <c r="D412" s="3" t="n"/>
+      <c r="E412" s="3" t="n"/>
     </row>
     <row r="413">
-      <c r="D413" s="2" t="n"/>
-      <c r="E413" s="2" t="n"/>
+      <c r="D413" s="3" t="n"/>
+      <c r="E413" s="3" t="n"/>
     </row>
     <row r="414">
-      <c r="D414" s="2" t="n"/>
-      <c r="E414" s="2" t="n"/>
+      <c r="D414" s="3" t="n"/>
+      <c r="E414" s="3" t="n"/>
     </row>
     <row r="415">
-      <c r="D415" s="2" t="n"/>
-      <c r="E415" s="2" t="n"/>
+      <c r="D415" s="3" t="n"/>
+      <c r="E415" s="3" t="n"/>
     </row>
     <row r="416">
-      <c r="D416" s="2" t="n"/>
-      <c r="E416" s="2" t="n"/>
+      <c r="D416" s="3" t="n"/>
+      <c r="E416" s="3" t="n"/>
     </row>
     <row r="417">
-      <c r="D417" s="2" t="n"/>
-      <c r="E417" s="2" t="n"/>
+      <c r="D417" s="3" t="n"/>
+      <c r="E417" s="3" t="n"/>
     </row>
     <row r="418">
-      <c r="D418" s="2" t="n"/>
-      <c r="E418" s="2" t="n"/>
+      <c r="D418" s="3" t="n"/>
+      <c r="E418" s="3" t="n"/>
     </row>
     <row r="419">
-      <c r="D419" s="2" t="n"/>
-      <c r="E419" s="2" t="n"/>
+      <c r="D419" s="3" t="n"/>
+      <c r="E419" s="3" t="n"/>
     </row>
     <row r="420">
-      <c r="D420" s="2" t="n"/>
-      <c r="E420" s="2" t="n"/>
+      <c r="D420" s="3" t="n"/>
+      <c r="E420" s="3" t="n"/>
     </row>
     <row r="421">
-      <c r="D421" s="2" t="n"/>
-      <c r="E421" s="2" t="n"/>
+      <c r="D421" s="3" t="n"/>
+      <c r="E421" s="3" t="n"/>
     </row>
     <row r="422">
-      <c r="D422" s="2" t="n"/>
-      <c r="E422" s="2" t="n"/>
+      <c r="D422" s="3" t="n"/>
+      <c r="E422" s="3" t="n"/>
     </row>
     <row r="423">
-      <c r="D423" s="2" t="n"/>
-      <c r="E423" s="2" t="n"/>
+      <c r="D423" s="3" t="n"/>
+      <c r="E423" s="3" t="n"/>
     </row>
     <row r="424">
-      <c r="D424" s="2" t="n"/>
-      <c r="E424" s="2" t="n"/>
+      <c r="D424" s="3" t="n"/>
+      <c r="E424" s="3" t="n"/>
     </row>
     <row r="425">
-      <c r="D425" s="2" t="n"/>
-      <c r="E425" s="2" t="n"/>
+      <c r="D425" s="3" t="n"/>
+      <c r="E425" s="3" t="n"/>
     </row>
     <row r="426">
-      <c r="D426" s="2" t="n"/>
-      <c r="E426" s="2" t="n"/>
+      <c r="D426" s="3" t="n"/>
+      <c r="E426" s="3" t="n"/>
     </row>
     <row r="427">
-      <c r="D427" s="2" t="n"/>
-      <c r="E427" s="2" t="n"/>
+      <c r="D427" s="3" t="n"/>
+      <c r="E427" s="3" t="n"/>
     </row>
     <row r="428">
-      <c r="D428" s="2" t="n"/>
-      <c r="E428" s="2" t="n"/>
+      <c r="D428" s="3" t="n"/>
+      <c r="E428" s="3" t="n"/>
     </row>
     <row r="429">
-      <c r="D429" s="2" t="n"/>
-      <c r="E429" s="2" t="n"/>
+      <c r="D429" s="3" t="n"/>
+      <c r="E429" s="3" t="n"/>
     </row>
     <row r="430">
-      <c r="D430" s="2" t="n"/>
-      <c r="E430" s="2" t="n"/>
+      <c r="D430" s="3" t="n"/>
+      <c r="E430" s="3" t="n"/>
     </row>
     <row r="431">
-      <c r="D431" s="2" t="n"/>
-      <c r="E431" s="2" t="n"/>
+      <c r="D431" s="3" t="n"/>
+      <c r="E431" s="3" t="n"/>
     </row>
     <row r="432">
-      <c r="D432" s="2" t="n"/>
-      <c r="E432" s="2" t="n"/>
+      <c r="D432" s="3" t="n"/>
+      <c r="E432" s="3" t="n"/>
     </row>
     <row r="433">
-      <c r="D433" s="2" t="n"/>
-      <c r="E433" s="2" t="n"/>
+      <c r="D433" s="3" t="n"/>
+      <c r="E433" s="3" t="n"/>
     </row>
     <row r="434">
-      <c r="D434" s="2" t="n"/>
-      <c r="E434" s="2" t="n"/>
+      <c r="D434" s="3" t="n"/>
+      <c r="E434" s="3" t="n"/>
     </row>
     <row r="435">
-      <c r="D435" s="2" t="n"/>
-      <c r="E435" s="2" t="n"/>
+      <c r="D435" s="3" t="n"/>
+      <c r="E435" s="3" t="n"/>
     </row>
     <row r="436">
-      <c r="D436" s="2" t="n"/>
-      <c r="E436" s="2" t="n"/>
+      <c r="D436" s="3" t="n"/>
+      <c r="E436" s="3" t="n"/>
     </row>
     <row r="437">
-      <c r="D437" s="2" t="n"/>
-      <c r="E437" s="2" t="n"/>
+      <c r="D437" s="3" t="n"/>
+      <c r="E437" s="3" t="n"/>
     </row>
     <row r="438">
-      <c r="D438" s="2" t="n"/>
-      <c r="E438" s="2" t="n"/>
+      <c r="D438" s="3" t="n"/>
+      <c r="E438" s="3" t="n"/>
     </row>
     <row r="439">
-      <c r="D439" s="2" t="n"/>
-      <c r="E439" s="2" t="n"/>
+      <c r="D439" s="3" t="n"/>
+      <c r="E439" s="3" t="n"/>
     </row>
     <row r="440">
-      <c r="D440" s="2" t="n"/>
-      <c r="E440" s="2" t="n"/>
+      <c r="D440" s="3" t="n"/>
+      <c r="E440" s="3" t="n"/>
     </row>
     <row r="441">
-      <c r="D441" s="2" t="n"/>
-      <c r="E441" s="2" t="n"/>
+      <c r="D441" s="3" t="n"/>
+      <c r="E441" s="3" t="n"/>
     </row>
     <row r="442">
-      <c r="D442" s="2" t="n"/>
-      <c r="E442" s="2" t="n"/>
+      <c r="D442" s="3" t="n"/>
+      <c r="E442" s="3" t="n"/>
     </row>
     <row r="443">
-      <c r="D443" s="2" t="n"/>
-      <c r="E443" s="2" t="n"/>
+      <c r="D443" s="3" t="n"/>
+      <c r="E443" s="3" t="n"/>
     </row>
     <row r="444">
-      <c r="D444" s="2" t="n"/>
-      <c r="E444" s="2" t="n"/>
+      <c r="D444" s="3" t="n"/>
+      <c r="E444" s="3" t="n"/>
     </row>
     <row r="445">
-      <c r="D445" s="2" t="n"/>
-      <c r="E445" s="2" t="n"/>
+      <c r="D445" s="3" t="n"/>
+      <c r="E445" s="3" t="n"/>
     </row>
     <row r="446">
-      <c r="D446" s="2" t="n"/>
-      <c r="E446" s="2" t="n"/>
+      <c r="D446" s="3" t="n"/>
+      <c r="E446" s="3" t="n"/>
     </row>
     <row r="447">
-      <c r="D447" s="2" t="n"/>
-      <c r="E447" s="2" t="n"/>
+      <c r="D447" s="3" t="n"/>
+      <c r="E447" s="3" t="n"/>
     </row>
     <row r="448">
-      <c r="D448" s="2" t="n"/>
-      <c r="E448" s="2" t="n"/>
+      <c r="D448" s="3" t="n"/>
+      <c r="E448" s="3" t="n"/>
     </row>
     <row r="449">
-      <c r="D449" s="2" t="n"/>
-      <c r="E449" s="2" t="n"/>
+      <c r="D449" s="3" t="n"/>
+      <c r="E449" s="3" t="n"/>
     </row>
     <row r="450">
-      <c r="D450" s="2" t="n"/>
-      <c r="E450" s="2" t="n"/>
+      <c r="D450" s="3" t="n"/>
+      <c r="E450" s="3" t="n"/>
     </row>
     <row r="451">
-      <c r="D451" s="2" t="n"/>
-      <c r="E451" s="2" t="n"/>
+      <c r="D451" s="3" t="n"/>
+      <c r="E451" s="3" t="n"/>
     </row>
     <row r="452">
-      <c r="D452" s="2" t="n"/>
-      <c r="E452" s="2" t="n"/>
+      <c r="D452" s="3" t="n"/>
+      <c r="E452" s="3" t="n"/>
     </row>
     <row r="453">
-      <c r="D453" s="2" t="n"/>
-      <c r="E453" s="2" t="n"/>
+      <c r="D453" s="3" t="n"/>
+      <c r="E453" s="3" t="n"/>
     </row>
     <row r="454">
-      <c r="D454" s="2" t="n"/>
-      <c r="E454" s="2" t="n"/>
+      <c r="D454" s="3" t="n"/>
+      <c r="E454" s="3" t="n"/>
     </row>
     <row r="455">
-      <c r="D455" s="2" t="n"/>
-      <c r="E455" s="2" t="n"/>
+      <c r="D455" s="3" t="n"/>
+      <c r="E455" s="3" t="n"/>
     </row>
     <row r="456">
-      <c r="D456" s="2" t="n"/>
-      <c r="E456" s="2" t="n"/>
+      <c r="D456" s="3" t="n"/>
+      <c r="E456" s="3" t="n"/>
     </row>
     <row r="457">
-      <c r="D457" s="2" t="n"/>
-      <c r="E457" s="2" t="n"/>
+      <c r="D457" s="3" t="n"/>
+      <c r="E457" s="3" t="n"/>
     </row>
     <row r="458">
-      <c r="D458" s="2" t="n"/>
-      <c r="E458" s="2" t="n"/>
+      <c r="D458" s="3" t="n"/>
+      <c r="E458" s="3" t="n"/>
     </row>
     <row r="459">
-      <c r="D459" s="2" t="n"/>
-      <c r="E459" s="2" t="n"/>
+      <c r="D459" s="3" t="n"/>
+      <c r="E459" s="3" t="n"/>
     </row>
     <row r="460">
-      <c r="D460" s="2" t="n"/>
-      <c r="E460" s="2" t="n"/>
+      <c r="D460" s="3" t="n"/>
+      <c r="E460" s="3" t="n"/>
     </row>
     <row r="461">
-      <c r="D461" s="2" t="n"/>
-      <c r="E461" s="2" t="n"/>
+      <c r="D461" s="3" t="n"/>
+      <c r="E461" s="3" t="n"/>
     </row>
     <row r="462">
-      <c r="D462" s="2" t="n"/>
-      <c r="E462" s="2" t="n"/>
+      <c r="D462" s="3" t="n"/>
+      <c r="E462" s="3" t="n"/>
     </row>
     <row r="463">
-      <c r="D463" s="2" t="n"/>
-      <c r="E463" s="2" t="n"/>
+      <c r="D463" s="3" t="n"/>
+      <c r="E463" s="3" t="n"/>
     </row>
     <row r="464">
-      <c r="D464" s="2" t="n"/>
-      <c r="E464" s="2" t="n"/>
+      <c r="D464" s="3" t="n"/>
+      <c r="E464" s="3" t="n"/>
     </row>
     <row r="465">
-      <c r="D465" s="2" t="n"/>
-      <c r="E465" s="2" t="n"/>
+      <c r="D465" s="3" t="n"/>
+      <c r="E465" s="3" t="n"/>
     </row>
     <row r="466">
-      <c r="D466" s="2" t="n"/>
-      <c r="E466" s="2" t="n"/>
+      <c r="D466" s="3" t="n"/>
+      <c r="E466" s="3" t="n"/>
     </row>
     <row r="467">
-      <c r="D467" s="2" t="n"/>
-      <c r="E467" s="2" t="n"/>
+      <c r="D467" s="3" t="n"/>
+      <c r="E467" s="3" t="n"/>
     </row>
     <row r="468">
-      <c r="D468" s="2" t="n"/>
-      <c r="E468" s="2" t="n"/>
+      <c r="D468" s="3" t="n"/>
+      <c r="E468" s="3" t="n"/>
     </row>
     <row r="469">
-      <c r="D469" s="2" t="n"/>
-      <c r="E469" s="2" t="n"/>
+      <c r="D469" s="3" t="n"/>
+      <c r="E469" s="3" t="n"/>
     </row>
     <row r="470">
-      <c r="D470" s="2" t="n"/>
-      <c r="E470" s="2" t="n"/>
+      <c r="D470" s="3" t="n"/>
+      <c r="E470" s="3" t="n"/>
     </row>
     <row r="471">
-      <c r="D471" s="2" t="n"/>
-      <c r="E471" s="2" t="n"/>
+      <c r="D471" s="3" t="n"/>
+      <c r="E471" s="3" t="n"/>
     </row>
     <row r="472">
-      <c r="D472" s="2" t="n"/>
-      <c r="E472" s="2" t="n"/>
+      <c r="D472" s="3" t="n"/>
+      <c r="E472" s="3" t="n"/>
     </row>
     <row r="473">
-      <c r="D473" s="2" t="n"/>
-      <c r="E473" s="2" t="n"/>
+      <c r="D473" s="3" t="n"/>
+      <c r="E473" s="3" t="n"/>
     </row>
     <row r="474">
-      <c r="D474" s="2" t="n"/>
-      <c r="E474" s="2" t="n"/>
+      <c r="D474" s="3" t="n"/>
+      <c r="E474" s="3" t="n"/>
     </row>
     <row r="475">
-      <c r="D475" s="2" t="n"/>
-      <c r="E475" s="2" t="n"/>
+      <c r="D475" s="3" t="n"/>
+      <c r="E475" s="3" t="n"/>
     </row>
     <row r="476">
-      <c r="D476" s="2" t="n"/>
-      <c r="E476" s="2" t="n"/>
+      <c r="D476" s="3" t="n"/>
+      <c r="E476" s="3" t="n"/>
     </row>
     <row r="477">
-      <c r="D477" s="2" t="n"/>
-      <c r="E477" s="2" t="n"/>
+      <c r="D477" s="3" t="n"/>
+      <c r="E477" s="3" t="n"/>
     </row>
     <row r="478">
-      <c r="D478" s="2" t="n"/>
-      <c r="E478" s="2" t="n"/>
+      <c r="D478" s="3" t="n"/>
+      <c r="E478" s="3" t="n"/>
     </row>
     <row r="479">
-      <c r="D479" s="2" t="n"/>
-      <c r="E479" s="2" t="n"/>
+      <c r="D479" s="3" t="n"/>
+      <c r="E479" s="3" t="n"/>
     </row>
     <row r="480">
-      <c r="D480" s="2" t="n"/>
-      <c r="E480" s="2" t="n"/>
+      <c r="D480" s="3" t="n"/>
+      <c r="E480" s="3" t="n"/>
     </row>
     <row r="481">
-      <c r="D481" s="2" t="n"/>
-      <c r="E481" s="2" t="n"/>
+      <c r="D481" s="3" t="n"/>
+      <c r="E481" s="3" t="n"/>
     </row>
     <row r="482">
-      <c r="D482" s="2" t="n"/>
-      <c r="E482" s="2" t="n"/>
+      <c r="D482" s="3" t="n"/>
+      <c r="E482" s="3" t="n"/>
     </row>
     <row r="483">
-      <c r="D483" s="2" t="n"/>
-      <c r="E483" s="2" t="n"/>
+      <c r="D483" s="3" t="n"/>
+      <c r="E483" s="3" t="n"/>
     </row>
     <row r="484">
-      <c r="D484" s="2" t="n"/>
-      <c r="E484" s="2" t="n"/>
+      <c r="D484" s="3" t="n"/>
+      <c r="E484" s="3" t="n"/>
     </row>
     <row r="485">
-      <c r="D485" s="2" t="n"/>
-      <c r="E485" s="2" t="n"/>
+      <c r="D485" s="3" t="n"/>
+      <c r="E485" s="3" t="n"/>
     </row>
     <row r="486">
-      <c r="D486" s="2" t="n"/>
-      <c r="E486" s="2" t="n"/>
+      <c r="D486" s="3" t="n"/>
+      <c r="E486" s="3" t="n"/>
     </row>
     <row r="487">
-      <c r="D487" s="2" t="n"/>
-      <c r="E487" s="2" t="n"/>
+      <c r="D487" s="3" t="n"/>
+      <c r="E487" s="3" t="n"/>
     </row>
     <row r="488">
-      <c r="D488" s="2" t="n"/>
-      <c r="E488" s="2" t="n"/>
+      <c r="D488" s="3" t="n"/>
+      <c r="E488" s="3" t="n"/>
     </row>
     <row r="489">
-      <c r="D489" s="2" t="n"/>
-      <c r="E489" s="2" t="n"/>
+      <c r="D489" s="3" t="n"/>
+      <c r="E489" s="3" t="n"/>
     </row>
     <row r="490">
-      <c r="D490" s="2" t="n"/>
-      <c r="E490" s="2" t="n"/>
+      <c r="D490" s="3" t="n"/>
+      <c r="E490" s="3" t="n"/>
     </row>
     <row r="491">
-      <c r="D491" s="2" t="n"/>
-      <c r="E491" s="2" t="n"/>
+      <c r="D491" s="3" t="n"/>
+      <c r="E491" s="3" t="n"/>
     </row>
     <row r="492">
-      <c r="D492" s="2" t="n"/>
-      <c r="E492" s="2" t="n"/>
+      <c r="D492" s="3" t="n"/>
+      <c r="E492" s="3" t="n"/>
     </row>
     <row r="493">
-      <c r="D493" s="2" t="n"/>
-      <c r="E493" s="2" t="n"/>
+      <c r="D493" s="3" t="n"/>
+      <c r="E493" s="3" t="n"/>
     </row>
     <row r="494">
-      <c r="D494" s="2" t="n"/>
-      <c r="E494" s="2" t="n"/>
+      <c r="D494" s="3" t="n"/>
+      <c r="E494" s="3" t="n"/>
     </row>
     <row r="495">
-      <c r="D495" s="2" t="n"/>
-      <c r="E495" s="2" t="n"/>
+      <c r="D495" s="3" t="n"/>
+      <c r="E495" s="3" t="n"/>
     </row>
     <row r="496">
-      <c r="D496" s="2" t="n"/>
-      <c r="E496" s="2" t="n"/>
+      <c r="D496" s="3" t="n"/>
+      <c r="E496" s="3" t="n"/>
     </row>
     <row r="497">
-      <c r="D497" s="2" t="n"/>
-      <c r="E497" s="2" t="n"/>
+      <c r="D497" s="3" t="n"/>
+      <c r="E497" s="3" t="n"/>
     </row>
     <row r="498">
-      <c r="D498" s="2" t="n"/>
-      <c r="E498" s="2" t="n"/>
+      <c r="D498" s="3" t="n"/>
+      <c r="E498" s="3" t="n"/>
     </row>
     <row r="499">
-      <c r="D499" s="2" t="n"/>
-      <c r="E499" s="2" t="n"/>
+      <c r="D499" s="3" t="n"/>
+      <c r="E499" s="3" t="n"/>
     </row>
     <row r="500">
-      <c r="D500" s="2" t="n"/>
-      <c r="E500" s="2" t="n"/>
+      <c r="D500" s="3" t="n"/>
+      <c r="E500" s="3" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -2673,13 +2785,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D500"/>
+  <dimension ref="A1:I500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="3" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2703,20 +2818,35 @@
           <t>Notiz</t>
         </is>
       </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Beispiel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="6" t="n">
         <v>46350.375</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="6" t="n">
         <v>46350.54166666666</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Halbtag, Rest des Tages freigegeben</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Halbtag: 09:00–13:00</t>
         </is>
       </c>
     </row>
@@ -2724,15 +2854,25 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" s="6" t="n">
         <v>46342.33333333334</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="6" t="n">
         <v>46342.5</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>Tag 1, vormittags</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>erster Block einer mehrtägigen</t>
         </is>
       </c>
     </row>
@@ -2740,15 +2880,21 @@
       <c r="A4" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="6" t="n">
         <v>46343.33333333334</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="6" t="n">
         <v>46343.66666666666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>Tag 2, ganztags</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Kalibrierung</t>
         </is>
       </c>
     </row>
@@ -2756,10 +2902,10 @@
       <c r="A5" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="6" t="n">
         <v>46345.29166666666</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="6" t="n">
         <v>46345.45833333334</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -2767,15 +2913,17 @@
           <t>Tag 4, vormittags</t>
         </is>
       </c>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="6" t="n">
         <v>46346.33333333334</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="6" t="n">
         <v>46346.58333333334</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -2783,1982 +2931,2016 @@
           <t>Tag 5, 6 Stunden</t>
         </is>
       </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Uhrzeiten</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>gehören ausschließlich</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>in dieses Blatt</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Kein Eintrag</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Prüfstand war durchgehend</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>außer Betrieb</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n"/>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n"/>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n"/>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n"/>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="3" t="n"/>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="3" t="n"/>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="3" t="n"/>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
     </row>
     <row r="25">
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="3" t="n"/>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
     </row>
     <row r="26">
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n"/>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="3" t="n"/>
-      <c r="C27" s="3" t="n"/>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
     </row>
     <row r="28">
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="3" t="n"/>
-      <c r="C29" s="3" t="n"/>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="3" t="n"/>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
     </row>
     <row r="31">
-      <c r="B31" s="3" t="n"/>
-      <c r="C31" s="3" t="n"/>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="n"/>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="3" t="n"/>
-      <c r="C33" s="3" t="n"/>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
     </row>
     <row r="34">
-      <c r="B34" s="3" t="n"/>
-      <c r="C34" s="3" t="n"/>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="3" t="n"/>
-      <c r="C35" s="3" t="n"/>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n"/>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
     </row>
     <row r="37">
-      <c r="B37" s="3" t="n"/>
-      <c r="C37" s="3" t="n"/>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
     </row>
     <row r="38">
-      <c r="B38" s="3" t="n"/>
-      <c r="C38" s="3" t="n"/>
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" s="3" t="n"/>
-      <c r="C39" s="3" t="n"/>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" s="3" t="n"/>
-      <c r="C40" s="3" t="n"/>
+      <c r="B40" s="6" t="n"/>
+      <c r="C40" s="6" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="3" t="n"/>
-      <c r="C41" s="3" t="n"/>
+      <c r="B41" s="6" t="n"/>
+      <c r="C41" s="6" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" s="3" t="n"/>
-      <c r="C42" s="3" t="n"/>
+      <c r="B42" s="6" t="n"/>
+      <c r="C42" s="6" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" s="3" t="n"/>
-      <c r="C43" s="3" t="n"/>
+      <c r="B43" s="6" t="n"/>
+      <c r="C43" s="6" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" s="3" t="n"/>
-      <c r="C44" s="3" t="n"/>
+      <c r="B44" s="6" t="n"/>
+      <c r="C44" s="6" t="n"/>
     </row>
     <row r="45">
-      <c r="B45" s="3" t="n"/>
-      <c r="C45" s="3" t="n"/>
+      <c r="B45" s="6" t="n"/>
+      <c r="C45" s="6" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="3" t="n"/>
-      <c r="C46" s="3" t="n"/>
+      <c r="B46" s="6" t="n"/>
+      <c r="C46" s="6" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="3" t="n"/>
-      <c r="C47" s="3" t="n"/>
+      <c r="B47" s="6" t="n"/>
+      <c r="C47" s="6" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="3" t="n"/>
-      <c r="C48" s="3" t="n"/>
+      <c r="B48" s="6" t="n"/>
+      <c r="C48" s="6" t="n"/>
     </row>
     <row r="49">
-      <c r="B49" s="3" t="n"/>
-      <c r="C49" s="3" t="n"/>
+      <c r="B49" s="6" t="n"/>
+      <c r="C49" s="6" t="n"/>
     </row>
     <row r="50">
-      <c r="B50" s="3" t="n"/>
-      <c r="C50" s="3" t="n"/>
+      <c r="B50" s="6" t="n"/>
+      <c r="C50" s="6" t="n"/>
     </row>
     <row r="51">
-      <c r="B51" s="3" t="n"/>
-      <c r="C51" s="3" t="n"/>
+      <c r="B51" s="6" t="n"/>
+      <c r="C51" s="6" t="n"/>
     </row>
     <row r="52">
-      <c r="B52" s="3" t="n"/>
-      <c r="C52" s="3" t="n"/>
+      <c r="B52" s="6" t="n"/>
+      <c r="C52" s="6" t="n"/>
     </row>
     <row r="53">
-      <c r="B53" s="3" t="n"/>
-      <c r="C53" s="3" t="n"/>
+      <c r="B53" s="6" t="n"/>
+      <c r="C53" s="6" t="n"/>
     </row>
     <row r="54">
-      <c r="B54" s="3" t="n"/>
-      <c r="C54" s="3" t="n"/>
+      <c r="B54" s="6" t="n"/>
+      <c r="C54" s="6" t="n"/>
     </row>
     <row r="55">
-      <c r="B55" s="3" t="n"/>
-      <c r="C55" s="3" t="n"/>
+      <c r="B55" s="6" t="n"/>
+      <c r="C55" s="6" t="n"/>
     </row>
     <row r="56">
-      <c r="B56" s="3" t="n"/>
-      <c r="C56" s="3" t="n"/>
+      <c r="B56" s="6" t="n"/>
+      <c r="C56" s="6" t="n"/>
     </row>
     <row r="57">
-      <c r="B57" s="3" t="n"/>
-      <c r="C57" s="3" t="n"/>
+      <c r="B57" s="6" t="n"/>
+      <c r="C57" s="6" t="n"/>
     </row>
     <row r="58">
-      <c r="B58" s="3" t="n"/>
-      <c r="C58" s="3" t="n"/>
+      <c r="B58" s="6" t="n"/>
+      <c r="C58" s="6" t="n"/>
     </row>
     <row r="59">
-      <c r="B59" s="3" t="n"/>
-      <c r="C59" s="3" t="n"/>
+      <c r="B59" s="6" t="n"/>
+      <c r="C59" s="6" t="n"/>
     </row>
     <row r="60">
-      <c r="B60" s="3" t="n"/>
-      <c r="C60" s="3" t="n"/>
+      <c r="B60" s="6" t="n"/>
+      <c r="C60" s="6" t="n"/>
     </row>
     <row r="61">
-      <c r="B61" s="3" t="n"/>
-      <c r="C61" s="3" t="n"/>
+      <c r="B61" s="6" t="n"/>
+      <c r="C61" s="6" t="n"/>
     </row>
     <row r="62">
-      <c r="B62" s="3" t="n"/>
-      <c r="C62" s="3" t="n"/>
+      <c r="B62" s="6" t="n"/>
+      <c r="C62" s="6" t="n"/>
     </row>
     <row r="63">
-      <c r="B63" s="3" t="n"/>
-      <c r="C63" s="3" t="n"/>
+      <c r="B63" s="6" t="n"/>
+      <c r="C63" s="6" t="n"/>
     </row>
     <row r="64">
-      <c r="B64" s="3" t="n"/>
-      <c r="C64" s="3" t="n"/>
+      <c r="B64" s="6" t="n"/>
+      <c r="C64" s="6" t="n"/>
     </row>
     <row r="65">
-      <c r="B65" s="3" t="n"/>
-      <c r="C65" s="3" t="n"/>
+      <c r="B65" s="6" t="n"/>
+      <c r="C65" s="6" t="n"/>
     </row>
     <row r="66">
-      <c r="B66" s="3" t="n"/>
-      <c r="C66" s="3" t="n"/>
+      <c r="B66" s="6" t="n"/>
+      <c r="C66" s="6" t="n"/>
     </row>
     <row r="67">
-      <c r="B67" s="3" t="n"/>
-      <c r="C67" s="3" t="n"/>
+      <c r="B67" s="6" t="n"/>
+      <c r="C67" s="6" t="n"/>
     </row>
     <row r="68">
-      <c r="B68" s="3" t="n"/>
-      <c r="C68" s="3" t="n"/>
+      <c r="B68" s="6" t="n"/>
+      <c r="C68" s="6" t="n"/>
     </row>
     <row r="69">
-      <c r="B69" s="3" t="n"/>
-      <c r="C69" s="3" t="n"/>
+      <c r="B69" s="6" t="n"/>
+      <c r="C69" s="6" t="n"/>
     </row>
     <row r="70">
-      <c r="B70" s="3" t="n"/>
-      <c r="C70" s="3" t="n"/>
+      <c r="B70" s="6" t="n"/>
+      <c r="C70" s="6" t="n"/>
     </row>
     <row r="71">
-      <c r="B71" s="3" t="n"/>
-      <c r="C71" s="3" t="n"/>
+      <c r="B71" s="6" t="n"/>
+      <c r="C71" s="6" t="n"/>
     </row>
     <row r="72">
-      <c r="B72" s="3" t="n"/>
-      <c r="C72" s="3" t="n"/>
+      <c r="B72" s="6" t="n"/>
+      <c r="C72" s="6" t="n"/>
     </row>
     <row r="73">
-      <c r="B73" s="3" t="n"/>
-      <c r="C73" s="3" t="n"/>
+      <c r="B73" s="6" t="n"/>
+      <c r="C73" s="6" t="n"/>
     </row>
     <row r="74">
-      <c r="B74" s="3" t="n"/>
-      <c r="C74" s="3" t="n"/>
+      <c r="B74" s="6" t="n"/>
+      <c r="C74" s="6" t="n"/>
     </row>
     <row r="75">
-      <c r="B75" s="3" t="n"/>
-      <c r="C75" s="3" t="n"/>
+      <c r="B75" s="6" t="n"/>
+      <c r="C75" s="6" t="n"/>
     </row>
     <row r="76">
-      <c r="B76" s="3" t="n"/>
-      <c r="C76" s="3" t="n"/>
+      <c r="B76" s="6" t="n"/>
+      <c r="C76" s="6" t="n"/>
     </row>
     <row r="77">
-      <c r="B77" s="3" t="n"/>
-      <c r="C77" s="3" t="n"/>
+      <c r="B77" s="6" t="n"/>
+      <c r="C77" s="6" t="n"/>
     </row>
     <row r="78">
-      <c r="B78" s="3" t="n"/>
-      <c r="C78" s="3" t="n"/>
+      <c r="B78" s="6" t="n"/>
+      <c r="C78" s="6" t="n"/>
     </row>
     <row r="79">
-      <c r="B79" s="3" t="n"/>
-      <c r="C79" s="3" t="n"/>
+      <c r="B79" s="6" t="n"/>
+      <c r="C79" s="6" t="n"/>
     </row>
     <row r="80">
-      <c r="B80" s="3" t="n"/>
-      <c r="C80" s="3" t="n"/>
+      <c r="B80" s="6" t="n"/>
+      <c r="C80" s="6" t="n"/>
     </row>
     <row r="81">
-      <c r="B81" s="3" t="n"/>
-      <c r="C81" s="3" t="n"/>
+      <c r="B81" s="6" t="n"/>
+      <c r="C81" s="6" t="n"/>
     </row>
     <row r="82">
-      <c r="B82" s="3" t="n"/>
-      <c r="C82" s="3" t="n"/>
+      <c r="B82" s="6" t="n"/>
+      <c r="C82" s="6" t="n"/>
     </row>
     <row r="83">
-      <c r="B83" s="3" t="n"/>
-      <c r="C83" s="3" t="n"/>
+      <c r="B83" s="6" t="n"/>
+      <c r="C83" s="6" t="n"/>
     </row>
     <row r="84">
-      <c r="B84" s="3" t="n"/>
-      <c r="C84" s="3" t="n"/>
+      <c r="B84" s="6" t="n"/>
+      <c r="C84" s="6" t="n"/>
     </row>
     <row r="85">
-      <c r="B85" s="3" t="n"/>
-      <c r="C85" s="3" t="n"/>
+      <c r="B85" s="6" t="n"/>
+      <c r="C85" s="6" t="n"/>
     </row>
     <row r="86">
-      <c r="B86" s="3" t="n"/>
-      <c r="C86" s="3" t="n"/>
+      <c r="B86" s="6" t="n"/>
+      <c r="C86" s="6" t="n"/>
     </row>
     <row r="87">
-      <c r="B87" s="3" t="n"/>
-      <c r="C87" s="3" t="n"/>
+      <c r="B87" s="6" t="n"/>
+      <c r="C87" s="6" t="n"/>
     </row>
     <row r="88">
-      <c r="B88" s="3" t="n"/>
-      <c r="C88" s="3" t="n"/>
+      <c r="B88" s="6" t="n"/>
+      <c r="C88" s="6" t="n"/>
     </row>
     <row r="89">
-      <c r="B89" s="3" t="n"/>
-      <c r="C89" s="3" t="n"/>
+      <c r="B89" s="6" t="n"/>
+      <c r="C89" s="6" t="n"/>
     </row>
     <row r="90">
-      <c r="B90" s="3" t="n"/>
-      <c r="C90" s="3" t="n"/>
+      <c r="B90" s="6" t="n"/>
+      <c r="C90" s="6" t="n"/>
     </row>
     <row r="91">
-      <c r="B91" s="3" t="n"/>
-      <c r="C91" s="3" t="n"/>
+      <c r="B91" s="6" t="n"/>
+      <c r="C91" s="6" t="n"/>
     </row>
     <row r="92">
-      <c r="B92" s="3" t="n"/>
-      <c r="C92" s="3" t="n"/>
+      <c r="B92" s="6" t="n"/>
+      <c r="C92" s="6" t="n"/>
     </row>
     <row r="93">
-      <c r="B93" s="3" t="n"/>
-      <c r="C93" s="3" t="n"/>
+      <c r="B93" s="6" t="n"/>
+      <c r="C93" s="6" t="n"/>
     </row>
     <row r="94">
-      <c r="B94" s="3" t="n"/>
-      <c r="C94" s="3" t="n"/>
+      <c r="B94" s="6" t="n"/>
+      <c r="C94" s="6" t="n"/>
     </row>
     <row r="95">
-      <c r="B95" s="3" t="n"/>
-      <c r="C95" s="3" t="n"/>
+      <c r="B95" s="6" t="n"/>
+      <c r="C95" s="6" t="n"/>
     </row>
     <row r="96">
-      <c r="B96" s="3" t="n"/>
-      <c r="C96" s="3" t="n"/>
+      <c r="B96" s="6" t="n"/>
+      <c r="C96" s="6" t="n"/>
     </row>
     <row r="97">
-      <c r="B97" s="3" t="n"/>
-      <c r="C97" s="3" t="n"/>
+      <c r="B97" s="6" t="n"/>
+      <c r="C97" s="6" t="n"/>
     </row>
     <row r="98">
-      <c r="B98" s="3" t="n"/>
-      <c r="C98" s="3" t="n"/>
+      <c r="B98" s="6" t="n"/>
+      <c r="C98" s="6" t="n"/>
     </row>
     <row r="99">
-      <c r="B99" s="3" t="n"/>
-      <c r="C99" s="3" t="n"/>
+      <c r="B99" s="6" t="n"/>
+      <c r="C99" s="6" t="n"/>
     </row>
     <row r="100">
-      <c r="B100" s="3" t="n"/>
-      <c r="C100" s="3" t="n"/>
+      <c r="B100" s="6" t="n"/>
+      <c r="C100" s="6" t="n"/>
     </row>
     <row r="101">
-      <c r="B101" s="3" t="n"/>
-      <c r="C101" s="3" t="n"/>
+      <c r="B101" s="6" t="n"/>
+      <c r="C101" s="6" t="n"/>
     </row>
     <row r="102">
-      <c r="B102" s="3" t="n"/>
-      <c r="C102" s="3" t="n"/>
+      <c r="B102" s="6" t="n"/>
+      <c r="C102" s="6" t="n"/>
     </row>
     <row r="103">
-      <c r="B103" s="3" t="n"/>
-      <c r="C103" s="3" t="n"/>
+      <c r="B103" s="6" t="n"/>
+      <c r="C103" s="6" t="n"/>
     </row>
     <row r="104">
-      <c r="B104" s="3" t="n"/>
-      <c r="C104" s="3" t="n"/>
+      <c r="B104" s="6" t="n"/>
+      <c r="C104" s="6" t="n"/>
     </row>
     <row r="105">
-      <c r="B105" s="3" t="n"/>
-      <c r="C105" s="3" t="n"/>
+      <c r="B105" s="6" t="n"/>
+      <c r="C105" s="6" t="n"/>
     </row>
     <row r="106">
-      <c r="B106" s="3" t="n"/>
-      <c r="C106" s="3" t="n"/>
+      <c r="B106" s="6" t="n"/>
+      <c r="C106" s="6" t="n"/>
     </row>
     <row r="107">
-      <c r="B107" s="3" t="n"/>
-      <c r="C107" s="3" t="n"/>
+      <c r="B107" s="6" t="n"/>
+      <c r="C107" s="6" t="n"/>
     </row>
     <row r="108">
-      <c r="B108" s="3" t="n"/>
-      <c r="C108" s="3" t="n"/>
+      <c r="B108" s="6" t="n"/>
+      <c r="C108" s="6" t="n"/>
     </row>
     <row r="109">
-      <c r="B109" s="3" t="n"/>
-      <c r="C109" s="3" t="n"/>
+      <c r="B109" s="6" t="n"/>
+      <c r="C109" s="6" t="n"/>
     </row>
     <row r="110">
-      <c r="B110" s="3" t="n"/>
-      <c r="C110" s="3" t="n"/>
+      <c r="B110" s="6" t="n"/>
+      <c r="C110" s="6" t="n"/>
     </row>
     <row r="111">
-      <c r="B111" s="3" t="n"/>
-      <c r="C111" s="3" t="n"/>
+      <c r="B111" s="6" t="n"/>
+      <c r="C111" s="6" t="n"/>
     </row>
     <row r="112">
-      <c r="B112" s="3" t="n"/>
-      <c r="C112" s="3" t="n"/>
+      <c r="B112" s="6" t="n"/>
+      <c r="C112" s="6" t="n"/>
     </row>
     <row r="113">
-      <c r="B113" s="3" t="n"/>
-      <c r="C113" s="3" t="n"/>
+      <c r="B113" s="6" t="n"/>
+      <c r="C113" s="6" t="n"/>
     </row>
     <row r="114">
-      <c r="B114" s="3" t="n"/>
-      <c r="C114" s="3" t="n"/>
+      <c r="B114" s="6" t="n"/>
+      <c r="C114" s="6" t="n"/>
     </row>
     <row r="115">
-      <c r="B115" s="3" t="n"/>
-      <c r="C115" s="3" t="n"/>
+      <c r="B115" s="6" t="n"/>
+      <c r="C115" s="6" t="n"/>
     </row>
     <row r="116">
-      <c r="B116" s="3" t="n"/>
-      <c r="C116" s="3" t="n"/>
+      <c r="B116" s="6" t="n"/>
+      <c r="C116" s="6" t="n"/>
     </row>
     <row r="117">
-      <c r="B117" s="3" t="n"/>
-      <c r="C117" s="3" t="n"/>
+      <c r="B117" s="6" t="n"/>
+      <c r="C117" s="6" t="n"/>
     </row>
     <row r="118">
-      <c r="B118" s="3" t="n"/>
-      <c r="C118" s="3" t="n"/>
+      <c r="B118" s="6" t="n"/>
+      <c r="C118" s="6" t="n"/>
     </row>
     <row r="119">
-      <c r="B119" s="3" t="n"/>
-      <c r="C119" s="3" t="n"/>
+      <c r="B119" s="6" t="n"/>
+      <c r="C119" s="6" t="n"/>
     </row>
     <row r="120">
-      <c r="B120" s="3" t="n"/>
-      <c r="C120" s="3" t="n"/>
+      <c r="B120" s="6" t="n"/>
+      <c r="C120" s="6" t="n"/>
     </row>
     <row r="121">
-      <c r="B121" s="3" t="n"/>
-      <c r="C121" s="3" t="n"/>
+      <c r="B121" s="6" t="n"/>
+      <c r="C121" s="6" t="n"/>
     </row>
     <row r="122">
-      <c r="B122" s="3" t="n"/>
-      <c r="C122" s="3" t="n"/>
+      <c r="B122" s="6" t="n"/>
+      <c r="C122" s="6" t="n"/>
     </row>
     <row r="123">
-      <c r="B123" s="3" t="n"/>
-      <c r="C123" s="3" t="n"/>
+      <c r="B123" s="6" t="n"/>
+      <c r="C123" s="6" t="n"/>
     </row>
     <row r="124">
-      <c r="B124" s="3" t="n"/>
-      <c r="C124" s="3" t="n"/>
+      <c r="B124" s="6" t="n"/>
+      <c r="C124" s="6" t="n"/>
     </row>
     <row r="125">
-      <c r="B125" s="3" t="n"/>
-      <c r="C125" s="3" t="n"/>
+      <c r="B125" s="6" t="n"/>
+      <c r="C125" s="6" t="n"/>
     </row>
     <row r="126">
-      <c r="B126" s="3" t="n"/>
-      <c r="C126" s="3" t="n"/>
+      <c r="B126" s="6" t="n"/>
+      <c r="C126" s="6" t="n"/>
     </row>
     <row r="127">
-      <c r="B127" s="3" t="n"/>
-      <c r="C127" s="3" t="n"/>
+      <c r="B127" s="6" t="n"/>
+      <c r="C127" s="6" t="n"/>
     </row>
     <row r="128">
-      <c r="B128" s="3" t="n"/>
-      <c r="C128" s="3" t="n"/>
+      <c r="B128" s="6" t="n"/>
+      <c r="C128" s="6" t="n"/>
     </row>
     <row r="129">
-      <c r="B129" s="3" t="n"/>
-      <c r="C129" s="3" t="n"/>
+      <c r="B129" s="6" t="n"/>
+      <c r="C129" s="6" t="n"/>
     </row>
     <row r="130">
-      <c r="B130" s="3" t="n"/>
-      <c r="C130" s="3" t="n"/>
+      <c r="B130" s="6" t="n"/>
+      <c r="C130" s="6" t="n"/>
     </row>
     <row r="131">
-      <c r="B131" s="3" t="n"/>
-      <c r="C131" s="3" t="n"/>
+      <c r="B131" s="6" t="n"/>
+      <c r="C131" s="6" t="n"/>
     </row>
     <row r="132">
-      <c r="B132" s="3" t="n"/>
-      <c r="C132" s="3" t="n"/>
+      <c r="B132" s="6" t="n"/>
+      <c r="C132" s="6" t="n"/>
     </row>
     <row r="133">
-      <c r="B133" s="3" t="n"/>
-      <c r="C133" s="3" t="n"/>
+      <c r="B133" s="6" t="n"/>
+      <c r="C133" s="6" t="n"/>
     </row>
     <row r="134">
-      <c r="B134" s="3" t="n"/>
-      <c r="C134" s="3" t="n"/>
+      <c r="B134" s="6" t="n"/>
+      <c r="C134" s="6" t="n"/>
     </row>
     <row r="135">
-      <c r="B135" s="3" t="n"/>
-      <c r="C135" s="3" t="n"/>
+      <c r="B135" s="6" t="n"/>
+      <c r="C135" s="6" t="n"/>
     </row>
     <row r="136">
-      <c r="B136" s="3" t="n"/>
-      <c r="C136" s="3" t="n"/>
+      <c r="B136" s="6" t="n"/>
+      <c r="C136" s="6" t="n"/>
     </row>
     <row r="137">
-      <c r="B137" s="3" t="n"/>
-      <c r="C137" s="3" t="n"/>
+      <c r="B137" s="6" t="n"/>
+      <c r="C137" s="6" t="n"/>
     </row>
     <row r="138">
-      <c r="B138" s="3" t="n"/>
-      <c r="C138" s="3" t="n"/>
+      <c r="B138" s="6" t="n"/>
+      <c r="C138" s="6" t="n"/>
     </row>
     <row r="139">
-      <c r="B139" s="3" t="n"/>
-      <c r="C139" s="3" t="n"/>
+      <c r="B139" s="6" t="n"/>
+      <c r="C139" s="6" t="n"/>
     </row>
     <row r="140">
-      <c r="B140" s="3" t="n"/>
-      <c r="C140" s="3" t="n"/>
+      <c r="B140" s="6" t="n"/>
+      <c r="C140" s="6" t="n"/>
     </row>
     <row r="141">
-      <c r="B141" s="3" t="n"/>
-      <c r="C141" s="3" t="n"/>
+      <c r="B141" s="6" t="n"/>
+      <c r="C141" s="6" t="n"/>
     </row>
     <row r="142">
-      <c r="B142" s="3" t="n"/>
-      <c r="C142" s="3" t="n"/>
+      <c r="B142" s="6" t="n"/>
+      <c r="C142" s="6" t="n"/>
     </row>
     <row r="143">
-      <c r="B143" s="3" t="n"/>
-      <c r="C143" s="3" t="n"/>
+      <c r="B143" s="6" t="n"/>
+      <c r="C143" s="6" t="n"/>
     </row>
     <row r="144">
-      <c r="B144" s="3" t="n"/>
-      <c r="C144" s="3" t="n"/>
+      <c r="B144" s="6" t="n"/>
+      <c r="C144" s="6" t="n"/>
     </row>
     <row r="145">
-      <c r="B145" s="3" t="n"/>
-      <c r="C145" s="3" t="n"/>
+      <c r="B145" s="6" t="n"/>
+      <c r="C145" s="6" t="n"/>
     </row>
     <row r="146">
-      <c r="B146" s="3" t="n"/>
-      <c r="C146" s="3" t="n"/>
+      <c r="B146" s="6" t="n"/>
+      <c r="C146" s="6" t="n"/>
     </row>
     <row r="147">
-      <c r="B147" s="3" t="n"/>
-      <c r="C147" s="3" t="n"/>
+      <c r="B147" s="6" t="n"/>
+      <c r="C147" s="6" t="n"/>
     </row>
     <row r="148">
-      <c r="B148" s="3" t="n"/>
-      <c r="C148" s="3" t="n"/>
+      <c r="B148" s="6" t="n"/>
+      <c r="C148" s="6" t="n"/>
     </row>
     <row r="149">
-      <c r="B149" s="3" t="n"/>
-      <c r="C149" s="3" t="n"/>
+      <c r="B149" s="6" t="n"/>
+      <c r="C149" s="6" t="n"/>
     </row>
     <row r="150">
-      <c r="B150" s="3" t="n"/>
-      <c r="C150" s="3" t="n"/>
+      <c r="B150" s="6" t="n"/>
+      <c r="C150" s="6" t="n"/>
     </row>
     <row r="151">
-      <c r="B151" s="3" t="n"/>
-      <c r="C151" s="3" t="n"/>
+      <c r="B151" s="6" t="n"/>
+      <c r="C151" s="6" t="n"/>
     </row>
     <row r="152">
-      <c r="B152" s="3" t="n"/>
-      <c r="C152" s="3" t="n"/>
+      <c r="B152" s="6" t="n"/>
+      <c r="C152" s="6" t="n"/>
     </row>
     <row r="153">
-      <c r="B153" s="3" t="n"/>
-      <c r="C153" s="3" t="n"/>
+      <c r="B153" s="6" t="n"/>
+      <c r="C153" s="6" t="n"/>
     </row>
     <row r="154">
-      <c r="B154" s="3" t="n"/>
-      <c r="C154" s="3" t="n"/>
+      <c r="B154" s="6" t="n"/>
+      <c r="C154" s="6" t="n"/>
     </row>
     <row r="155">
-      <c r="B155" s="3" t="n"/>
-      <c r="C155" s="3" t="n"/>
+      <c r="B155" s="6" t="n"/>
+      <c r="C155" s="6" t="n"/>
     </row>
     <row r="156">
-      <c r="B156" s="3" t="n"/>
-      <c r="C156" s="3" t="n"/>
+      <c r="B156" s="6" t="n"/>
+      <c r="C156" s="6" t="n"/>
     </row>
     <row r="157">
-      <c r="B157" s="3" t="n"/>
-      <c r="C157" s="3" t="n"/>
+      <c r="B157" s="6" t="n"/>
+      <c r="C157" s="6" t="n"/>
     </row>
     <row r="158">
-      <c r="B158" s="3" t="n"/>
-      <c r="C158" s="3" t="n"/>
+      <c r="B158" s="6" t="n"/>
+      <c r="C158" s="6" t="n"/>
     </row>
     <row r="159">
-      <c r="B159" s="3" t="n"/>
-      <c r="C159" s="3" t="n"/>
+      <c r="B159" s="6" t="n"/>
+      <c r="C159" s="6" t="n"/>
     </row>
     <row r="160">
-      <c r="B160" s="3" t="n"/>
-      <c r="C160" s="3" t="n"/>
+      <c r="B160" s="6" t="n"/>
+      <c r="C160" s="6" t="n"/>
     </row>
     <row r="161">
-      <c r="B161" s="3" t="n"/>
-      <c r="C161" s="3" t="n"/>
+      <c r="B161" s="6" t="n"/>
+      <c r="C161" s="6" t="n"/>
     </row>
     <row r="162">
-      <c r="B162" s="3" t="n"/>
-      <c r="C162" s="3" t="n"/>
+      <c r="B162" s="6" t="n"/>
+      <c r="C162" s="6" t="n"/>
     </row>
     <row r="163">
-      <c r="B163" s="3" t="n"/>
-      <c r="C163" s="3" t="n"/>
+      <c r="B163" s="6" t="n"/>
+      <c r="C163" s="6" t="n"/>
     </row>
     <row r="164">
-      <c r="B164" s="3" t="n"/>
-      <c r="C164" s="3" t="n"/>
+      <c r="B164" s="6" t="n"/>
+      <c r="C164" s="6" t="n"/>
     </row>
     <row r="165">
-      <c r="B165" s="3" t="n"/>
-      <c r="C165" s="3" t="n"/>
+      <c r="B165" s="6" t="n"/>
+      <c r="C165" s="6" t="n"/>
     </row>
     <row r="166">
-      <c r="B166" s="3" t="n"/>
-      <c r="C166" s="3" t="n"/>
+      <c r="B166" s="6" t="n"/>
+      <c r="C166" s="6" t="n"/>
     </row>
     <row r="167">
-      <c r="B167" s="3" t="n"/>
-      <c r="C167" s="3" t="n"/>
+      <c r="B167" s="6" t="n"/>
+      <c r="C167" s="6" t="n"/>
     </row>
     <row r="168">
-      <c r="B168" s="3" t="n"/>
-      <c r="C168" s="3" t="n"/>
+      <c r="B168" s="6" t="n"/>
+      <c r="C168" s="6" t="n"/>
     </row>
     <row r="169">
-      <c r="B169" s="3" t="n"/>
-      <c r="C169" s="3" t="n"/>
+      <c r="B169" s="6" t="n"/>
+      <c r="C169" s="6" t="n"/>
     </row>
     <row r="170">
-      <c r="B170" s="3" t="n"/>
-      <c r="C170" s="3" t="n"/>
+      <c r="B170" s="6" t="n"/>
+      <c r="C170" s="6" t="n"/>
     </row>
     <row r="171">
-      <c r="B171" s="3" t="n"/>
-      <c r="C171" s="3" t="n"/>
+      <c r="B171" s="6" t="n"/>
+      <c r="C171" s="6" t="n"/>
     </row>
     <row r="172">
-      <c r="B172" s="3" t="n"/>
-      <c r="C172" s="3" t="n"/>
+      <c r="B172" s="6" t="n"/>
+      <c r="C172" s="6" t="n"/>
     </row>
     <row r="173">
-      <c r="B173" s="3" t="n"/>
-      <c r="C173" s="3" t="n"/>
+      <c r="B173" s="6" t="n"/>
+      <c r="C173" s="6" t="n"/>
     </row>
     <row r="174">
-      <c r="B174" s="3" t="n"/>
-      <c r="C174" s="3" t="n"/>
+      <c r="B174" s="6" t="n"/>
+      <c r="C174" s="6" t="n"/>
     </row>
     <row r="175">
-      <c r="B175" s="3" t="n"/>
-      <c r="C175" s="3" t="n"/>
+      <c r="B175" s="6" t="n"/>
+      <c r="C175" s="6" t="n"/>
     </row>
     <row r="176">
-      <c r="B176" s="3" t="n"/>
-      <c r="C176" s="3" t="n"/>
+      <c r="B176" s="6" t="n"/>
+      <c r="C176" s="6" t="n"/>
     </row>
     <row r="177">
-      <c r="B177" s="3" t="n"/>
-      <c r="C177" s="3" t="n"/>
+      <c r="B177" s="6" t="n"/>
+      <c r="C177" s="6" t="n"/>
     </row>
     <row r="178">
-      <c r="B178" s="3" t="n"/>
-      <c r="C178" s="3" t="n"/>
+      <c r="B178" s="6" t="n"/>
+      <c r="C178" s="6" t="n"/>
     </row>
     <row r="179">
-      <c r="B179" s="3" t="n"/>
-      <c r="C179" s="3" t="n"/>
+      <c r="B179" s="6" t="n"/>
+      <c r="C179" s="6" t="n"/>
     </row>
     <row r="180">
-      <c r="B180" s="3" t="n"/>
-      <c r="C180" s="3" t="n"/>
+      <c r="B180" s="6" t="n"/>
+      <c r="C180" s="6" t="n"/>
     </row>
     <row r="181">
-      <c r="B181" s="3" t="n"/>
-      <c r="C181" s="3" t="n"/>
+      <c r="B181" s="6" t="n"/>
+      <c r="C181" s="6" t="n"/>
     </row>
     <row r="182">
-      <c r="B182" s="3" t="n"/>
-      <c r="C182" s="3" t="n"/>
+      <c r="B182" s="6" t="n"/>
+      <c r="C182" s="6" t="n"/>
     </row>
     <row r="183">
-      <c r="B183" s="3" t="n"/>
-      <c r="C183" s="3" t="n"/>
+      <c r="B183" s="6" t="n"/>
+      <c r="C183" s="6" t="n"/>
     </row>
     <row r="184">
-      <c r="B184" s="3" t="n"/>
-      <c r="C184" s="3" t="n"/>
+      <c r="B184" s="6" t="n"/>
+      <c r="C184" s="6" t="n"/>
     </row>
     <row r="185">
-      <c r="B185" s="3" t="n"/>
-      <c r="C185" s="3" t="n"/>
+      <c r="B185" s="6" t="n"/>
+      <c r="C185" s="6" t="n"/>
     </row>
     <row r="186">
-      <c r="B186" s="3" t="n"/>
-      <c r="C186" s="3" t="n"/>
+      <c r="B186" s="6" t="n"/>
+      <c r="C186" s="6" t="n"/>
     </row>
     <row r="187">
-      <c r="B187" s="3" t="n"/>
-      <c r="C187" s="3" t="n"/>
+      <c r="B187" s="6" t="n"/>
+      <c r="C187" s="6" t="n"/>
     </row>
     <row r="188">
-      <c r="B188" s="3" t="n"/>
-      <c r="C188" s="3" t="n"/>
+      <c r="B188" s="6" t="n"/>
+      <c r="C188" s="6" t="n"/>
     </row>
     <row r="189">
-      <c r="B189" s="3" t="n"/>
-      <c r="C189" s="3" t="n"/>
+      <c r="B189" s="6" t="n"/>
+      <c r="C189" s="6" t="n"/>
     </row>
     <row r="190">
-      <c r="B190" s="3" t="n"/>
-      <c r="C190" s="3" t="n"/>
+      <c r="B190" s="6" t="n"/>
+      <c r="C190" s="6" t="n"/>
     </row>
     <row r="191">
-      <c r="B191" s="3" t="n"/>
-      <c r="C191" s="3" t="n"/>
+      <c r="B191" s="6" t="n"/>
+      <c r="C191" s="6" t="n"/>
     </row>
     <row r="192">
-      <c r="B192" s="3" t="n"/>
-      <c r="C192" s="3" t="n"/>
+      <c r="B192" s="6" t="n"/>
+      <c r="C192" s="6" t="n"/>
     </row>
     <row r="193">
-      <c r="B193" s="3" t="n"/>
-      <c r="C193" s="3" t="n"/>
+      <c r="B193" s="6" t="n"/>
+      <c r="C193" s="6" t="n"/>
     </row>
     <row r="194">
-      <c r="B194" s="3" t="n"/>
-      <c r="C194" s="3" t="n"/>
+      <c r="B194" s="6" t="n"/>
+      <c r="C194" s="6" t="n"/>
     </row>
     <row r="195">
-      <c r="B195" s="3" t="n"/>
-      <c r="C195" s="3" t="n"/>
+      <c r="B195" s="6" t="n"/>
+      <c r="C195" s="6" t="n"/>
     </row>
     <row r="196">
-      <c r="B196" s="3" t="n"/>
-      <c r="C196" s="3" t="n"/>
+      <c r="B196" s="6" t="n"/>
+      <c r="C196" s="6" t="n"/>
     </row>
     <row r="197">
-      <c r="B197" s="3" t="n"/>
-      <c r="C197" s="3" t="n"/>
+      <c r="B197" s="6" t="n"/>
+      <c r="C197" s="6" t="n"/>
     </row>
     <row r="198">
-      <c r="B198" s="3" t="n"/>
-      <c r="C198" s="3" t="n"/>
+      <c r="B198" s="6" t="n"/>
+      <c r="C198" s="6" t="n"/>
     </row>
     <row r="199">
-      <c r="B199" s="3" t="n"/>
-      <c r="C199" s="3" t="n"/>
+      <c r="B199" s="6" t="n"/>
+      <c r="C199" s="6" t="n"/>
     </row>
     <row r="200">
-      <c r="B200" s="3" t="n"/>
-      <c r="C200" s="3" t="n"/>
+      <c r="B200" s="6" t="n"/>
+      <c r="C200" s="6" t="n"/>
     </row>
     <row r="201">
-      <c r="B201" s="3" t="n"/>
-      <c r="C201" s="3" t="n"/>
+      <c r="B201" s="6" t="n"/>
+      <c r="C201" s="6" t="n"/>
     </row>
     <row r="202">
-      <c r="B202" s="3" t="n"/>
-      <c r="C202" s="3" t="n"/>
+      <c r="B202" s="6" t="n"/>
+      <c r="C202" s="6" t="n"/>
     </row>
     <row r="203">
-      <c r="B203" s="3" t="n"/>
-      <c r="C203" s="3" t="n"/>
+      <c r="B203" s="6" t="n"/>
+      <c r="C203" s="6" t="n"/>
     </row>
     <row r="204">
-      <c r="B204" s="3" t="n"/>
-      <c r="C204" s="3" t="n"/>
+      <c r="B204" s="6" t="n"/>
+      <c r="C204" s="6" t="n"/>
     </row>
     <row r="205">
-      <c r="B205" s="3" t="n"/>
-      <c r="C205" s="3" t="n"/>
+      <c r="B205" s="6" t="n"/>
+      <c r="C205" s="6" t="n"/>
     </row>
     <row r="206">
-      <c r="B206" s="3" t="n"/>
-      <c r="C206" s="3" t="n"/>
+      <c r="B206" s="6" t="n"/>
+      <c r="C206" s="6" t="n"/>
     </row>
     <row r="207">
-      <c r="B207" s="3" t="n"/>
-      <c r="C207" s="3" t="n"/>
+      <c r="B207" s="6" t="n"/>
+      <c r="C207" s="6" t="n"/>
     </row>
     <row r="208">
-      <c r="B208" s="3" t="n"/>
-      <c r="C208" s="3" t="n"/>
+      <c r="B208" s="6" t="n"/>
+      <c r="C208" s="6" t="n"/>
     </row>
     <row r="209">
-      <c r="B209" s="3" t="n"/>
-      <c r="C209" s="3" t="n"/>
+      <c r="B209" s="6" t="n"/>
+      <c r="C209" s="6" t="n"/>
     </row>
     <row r="210">
-      <c r="B210" s="3" t="n"/>
-      <c r="C210" s="3" t="n"/>
+      <c r="B210" s="6" t="n"/>
+      <c r="C210" s="6" t="n"/>
     </row>
     <row r="211">
-      <c r="B211" s="3" t="n"/>
-      <c r="C211" s="3" t="n"/>
+      <c r="B211" s="6" t="n"/>
+      <c r="C211" s="6" t="n"/>
     </row>
     <row r="212">
-      <c r="B212" s="3" t="n"/>
-      <c r="C212" s="3" t="n"/>
+      <c r="B212" s="6" t="n"/>
+      <c r="C212" s="6" t="n"/>
     </row>
     <row r="213">
-      <c r="B213" s="3" t="n"/>
-      <c r="C213" s="3" t="n"/>
+      <c r="B213" s="6" t="n"/>
+      <c r="C213" s="6" t="n"/>
     </row>
     <row r="214">
-      <c r="B214" s="3" t="n"/>
-      <c r="C214" s="3" t="n"/>
+      <c r="B214" s="6" t="n"/>
+      <c r="C214" s="6" t="n"/>
     </row>
     <row r="215">
-      <c r="B215" s="3" t="n"/>
-      <c r="C215" s="3" t="n"/>
+      <c r="B215" s="6" t="n"/>
+      <c r="C215" s="6" t="n"/>
     </row>
     <row r="216">
-      <c r="B216" s="3" t="n"/>
-      <c r="C216" s="3" t="n"/>
+      <c r="B216" s="6" t="n"/>
+      <c r="C216" s="6" t="n"/>
     </row>
     <row r="217">
-      <c r="B217" s="3" t="n"/>
-      <c r="C217" s="3" t="n"/>
+      <c r="B217" s="6" t="n"/>
+      <c r="C217" s="6" t="n"/>
     </row>
     <row r="218">
-      <c r="B218" s="3" t="n"/>
-      <c r="C218" s="3" t="n"/>
+      <c r="B218" s="6" t="n"/>
+      <c r="C218" s="6" t="n"/>
     </row>
     <row r="219">
-      <c r="B219" s="3" t="n"/>
-      <c r="C219" s="3" t="n"/>
+      <c r="B219" s="6" t="n"/>
+      <c r="C219" s="6" t="n"/>
     </row>
     <row r="220">
-      <c r="B220" s="3" t="n"/>
-      <c r="C220" s="3" t="n"/>
+      <c r="B220" s="6" t="n"/>
+      <c r="C220" s="6" t="n"/>
     </row>
     <row r="221">
-      <c r="B221" s="3" t="n"/>
-      <c r="C221" s="3" t="n"/>
+      <c r="B221" s="6" t="n"/>
+      <c r="C221" s="6" t="n"/>
     </row>
     <row r="222">
-      <c r="B222" s="3" t="n"/>
-      <c r="C222" s="3" t="n"/>
+      <c r="B222" s="6" t="n"/>
+      <c r="C222" s="6" t="n"/>
     </row>
     <row r="223">
-      <c r="B223" s="3" t="n"/>
-      <c r="C223" s="3" t="n"/>
+      <c r="B223" s="6" t="n"/>
+      <c r="C223" s="6" t="n"/>
     </row>
     <row r="224">
-      <c r="B224" s="3" t="n"/>
-      <c r="C224" s="3" t="n"/>
+      <c r="B224" s="6" t="n"/>
+      <c r="C224" s="6" t="n"/>
     </row>
     <row r="225">
-      <c r="B225" s="3" t="n"/>
-      <c r="C225" s="3" t="n"/>
+      <c r="B225" s="6" t="n"/>
+      <c r="C225" s="6" t="n"/>
     </row>
     <row r="226">
-      <c r="B226" s="3" t="n"/>
-      <c r="C226" s="3" t="n"/>
+      <c r="B226" s="6" t="n"/>
+      <c r="C226" s="6" t="n"/>
     </row>
     <row r="227">
-      <c r="B227" s="3" t="n"/>
-      <c r="C227" s="3" t="n"/>
+      <c r="B227" s="6" t="n"/>
+      <c r="C227" s="6" t="n"/>
     </row>
     <row r="228">
-      <c r="B228" s="3" t="n"/>
-      <c r="C228" s="3" t="n"/>
+      <c r="B228" s="6" t="n"/>
+      <c r="C228" s="6" t="n"/>
     </row>
     <row r="229">
-      <c r="B229" s="3" t="n"/>
-      <c r="C229" s="3" t="n"/>
+      <c r="B229" s="6" t="n"/>
+      <c r="C229" s="6" t="n"/>
     </row>
     <row r="230">
-      <c r="B230" s="3" t="n"/>
-      <c r="C230" s="3" t="n"/>
+      <c r="B230" s="6" t="n"/>
+      <c r="C230" s="6" t="n"/>
     </row>
     <row r="231">
-      <c r="B231" s="3" t="n"/>
-      <c r="C231" s="3" t="n"/>
+      <c r="B231" s="6" t="n"/>
+      <c r="C231" s="6" t="n"/>
     </row>
     <row r="232">
-      <c r="B232" s="3" t="n"/>
-      <c r="C232" s="3" t="n"/>
+      <c r="B232" s="6" t="n"/>
+      <c r="C232" s="6" t="n"/>
     </row>
     <row r="233">
-      <c r="B233" s="3" t="n"/>
-      <c r="C233" s="3" t="n"/>
+      <c r="B233" s="6" t="n"/>
+      <c r="C233" s="6" t="n"/>
     </row>
     <row r="234">
-      <c r="B234" s="3" t="n"/>
-      <c r="C234" s="3" t="n"/>
+      <c r="B234" s="6" t="n"/>
+      <c r="C234" s="6" t="n"/>
     </row>
     <row r="235">
-      <c r="B235" s="3" t="n"/>
-      <c r="C235" s="3" t="n"/>
+      <c r="B235" s="6" t="n"/>
+      <c r="C235" s="6" t="n"/>
     </row>
     <row r="236">
-      <c r="B236" s="3" t="n"/>
-      <c r="C236" s="3" t="n"/>
+      <c r="B236" s="6" t="n"/>
+      <c r="C236" s="6" t="n"/>
     </row>
     <row r="237">
-      <c r="B237" s="3" t="n"/>
-      <c r="C237" s="3" t="n"/>
+      <c r="B237" s="6" t="n"/>
+      <c r="C237" s="6" t="n"/>
     </row>
     <row r="238">
-      <c r="B238" s="3" t="n"/>
-      <c r="C238" s="3" t="n"/>
+      <c r="B238" s="6" t="n"/>
+      <c r="C238" s="6" t="n"/>
     </row>
     <row r="239">
-      <c r="B239" s="3" t="n"/>
-      <c r="C239" s="3" t="n"/>
+      <c r="B239" s="6" t="n"/>
+      <c r="C239" s="6" t="n"/>
     </row>
     <row r="240">
-      <c r="B240" s="3" t="n"/>
-      <c r="C240" s="3" t="n"/>
+      <c r="B240" s="6" t="n"/>
+      <c r="C240" s="6" t="n"/>
     </row>
     <row r="241">
-      <c r="B241" s="3" t="n"/>
-      <c r="C241" s="3" t="n"/>
+      <c r="B241" s="6" t="n"/>
+      <c r="C241" s="6" t="n"/>
     </row>
     <row r="242">
-      <c r="B242" s="3" t="n"/>
-      <c r="C242" s="3" t="n"/>
+      <c r="B242" s="6" t="n"/>
+      <c r="C242" s="6" t="n"/>
     </row>
     <row r="243">
-      <c r="B243" s="3" t="n"/>
-      <c r="C243" s="3" t="n"/>
+      <c r="B243" s="6" t="n"/>
+      <c r="C243" s="6" t="n"/>
     </row>
     <row r="244">
-      <c r="B244" s="3" t="n"/>
-      <c r="C244" s="3" t="n"/>
+      <c r="B244" s="6" t="n"/>
+      <c r="C244" s="6" t="n"/>
     </row>
     <row r="245">
-      <c r="B245" s="3" t="n"/>
-      <c r="C245" s="3" t="n"/>
+      <c r="B245" s="6" t="n"/>
+      <c r="C245" s="6" t="n"/>
     </row>
     <row r="246">
-      <c r="B246" s="3" t="n"/>
-      <c r="C246" s="3" t="n"/>
+      <c r="B246" s="6" t="n"/>
+      <c r="C246" s="6" t="n"/>
     </row>
     <row r="247">
-      <c r="B247" s="3" t="n"/>
-      <c r="C247" s="3" t="n"/>
+      <c r="B247" s="6" t="n"/>
+      <c r="C247" s="6" t="n"/>
     </row>
     <row r="248">
-      <c r="B248" s="3" t="n"/>
-      <c r="C248" s="3" t="n"/>
+      <c r="B248" s="6" t="n"/>
+      <c r="C248" s="6" t="n"/>
     </row>
     <row r="249">
-      <c r="B249" s="3" t="n"/>
-      <c r="C249" s="3" t="n"/>
+      <c r="B249" s="6" t="n"/>
+      <c r="C249" s="6" t="n"/>
     </row>
     <row r="250">
-      <c r="B250" s="3" t="n"/>
-      <c r="C250" s="3" t="n"/>
+      <c r="B250" s="6" t="n"/>
+      <c r="C250" s="6" t="n"/>
     </row>
     <row r="251">
-      <c r="B251" s="3" t="n"/>
-      <c r="C251" s="3" t="n"/>
+      <c r="B251" s="6" t="n"/>
+      <c r="C251" s="6" t="n"/>
     </row>
     <row r="252">
-      <c r="B252" s="3" t="n"/>
-      <c r="C252" s="3" t="n"/>
+      <c r="B252" s="6" t="n"/>
+      <c r="C252" s="6" t="n"/>
     </row>
     <row r="253">
-      <c r="B253" s="3" t="n"/>
-      <c r="C253" s="3" t="n"/>
+      <c r="B253" s="6" t="n"/>
+      <c r="C253" s="6" t="n"/>
     </row>
     <row r="254">
-      <c r="B254" s="3" t="n"/>
-      <c r="C254" s="3" t="n"/>
+      <c r="B254" s="6" t="n"/>
+      <c r="C254" s="6" t="n"/>
     </row>
     <row r="255">
-      <c r="B255" s="3" t="n"/>
-      <c r="C255" s="3" t="n"/>
+      <c r="B255" s="6" t="n"/>
+      <c r="C255" s="6" t="n"/>
     </row>
     <row r="256">
-      <c r="B256" s="3" t="n"/>
-      <c r="C256" s="3" t="n"/>
+      <c r="B256" s="6" t="n"/>
+      <c r="C256" s="6" t="n"/>
     </row>
     <row r="257">
-      <c r="B257" s="3" t="n"/>
-      <c r="C257" s="3" t="n"/>
+      <c r="B257" s="6" t="n"/>
+      <c r="C257" s="6" t="n"/>
     </row>
     <row r="258">
-      <c r="B258" s="3" t="n"/>
-      <c r="C258" s="3" t="n"/>
+      <c r="B258" s="6" t="n"/>
+      <c r="C258" s="6" t="n"/>
     </row>
     <row r="259">
-      <c r="B259" s="3" t="n"/>
-      <c r="C259" s="3" t="n"/>
+      <c r="B259" s="6" t="n"/>
+      <c r="C259" s="6" t="n"/>
     </row>
     <row r="260">
-      <c r="B260" s="3" t="n"/>
-      <c r="C260" s="3" t="n"/>
+      <c r="B260" s="6" t="n"/>
+      <c r="C260" s="6" t="n"/>
     </row>
     <row r="261">
-      <c r="B261" s="3" t="n"/>
-      <c r="C261" s="3" t="n"/>
+      <c r="B261" s="6" t="n"/>
+      <c r="C261" s="6" t="n"/>
     </row>
     <row r="262">
-      <c r="B262" s="3" t="n"/>
-      <c r="C262" s="3" t="n"/>
+      <c r="B262" s="6" t="n"/>
+      <c r="C262" s="6" t="n"/>
     </row>
     <row r="263">
-      <c r="B263" s="3" t="n"/>
-      <c r="C263" s="3" t="n"/>
+      <c r="B263" s="6" t="n"/>
+      <c r="C263" s="6" t="n"/>
     </row>
     <row r="264">
-      <c r="B264" s="3" t="n"/>
-      <c r="C264" s="3" t="n"/>
+      <c r="B264" s="6" t="n"/>
+      <c r="C264" s="6" t="n"/>
     </row>
     <row r="265">
-      <c r="B265" s="3" t="n"/>
-      <c r="C265" s="3" t="n"/>
+      <c r="B265" s="6" t="n"/>
+      <c r="C265" s="6" t="n"/>
     </row>
     <row r="266">
-      <c r="B266" s="3" t="n"/>
-      <c r="C266" s="3" t="n"/>
+      <c r="B266" s="6" t="n"/>
+      <c r="C266" s="6" t="n"/>
     </row>
     <row r="267">
-      <c r="B267" s="3" t="n"/>
-      <c r="C267" s="3" t="n"/>
+      <c r="B267" s="6" t="n"/>
+      <c r="C267" s="6" t="n"/>
     </row>
     <row r="268">
-      <c r="B268" s="3" t="n"/>
-      <c r="C268" s="3" t="n"/>
+      <c r="B268" s="6" t="n"/>
+      <c r="C268" s="6" t="n"/>
     </row>
     <row r="269">
-      <c r="B269" s="3" t="n"/>
-      <c r="C269" s="3" t="n"/>
+      <c r="B269" s="6" t="n"/>
+      <c r="C269" s="6" t="n"/>
     </row>
     <row r="270">
-      <c r="B270" s="3" t="n"/>
-      <c r="C270" s="3" t="n"/>
+      <c r="B270" s="6" t="n"/>
+      <c r="C270" s="6" t="n"/>
     </row>
     <row r="271">
-      <c r="B271" s="3" t="n"/>
-      <c r="C271" s="3" t="n"/>
+      <c r="B271" s="6" t="n"/>
+      <c r="C271" s="6" t="n"/>
     </row>
     <row r="272">
-      <c r="B272" s="3" t="n"/>
-      <c r="C272" s="3" t="n"/>
+      <c r="B272" s="6" t="n"/>
+      <c r="C272" s="6" t="n"/>
     </row>
     <row r="273">
-      <c r="B273" s="3" t="n"/>
-      <c r="C273" s="3" t="n"/>
+      <c r="B273" s="6" t="n"/>
+      <c r="C273" s="6" t="n"/>
     </row>
     <row r="274">
-      <c r="B274" s="3" t="n"/>
-      <c r="C274" s="3" t="n"/>
+      <c r="B274" s="6" t="n"/>
+      <c r="C274" s="6" t="n"/>
     </row>
     <row r="275">
-      <c r="B275" s="3" t="n"/>
-      <c r="C275" s="3" t="n"/>
+      <c r="B275" s="6" t="n"/>
+      <c r="C275" s="6" t="n"/>
     </row>
     <row r="276">
-      <c r="B276" s="3" t="n"/>
-      <c r="C276" s="3" t="n"/>
+      <c r="B276" s="6" t="n"/>
+      <c r="C276" s="6" t="n"/>
     </row>
     <row r="277">
-      <c r="B277" s="3" t="n"/>
-      <c r="C277" s="3" t="n"/>
+      <c r="B277" s="6" t="n"/>
+      <c r="C277" s="6" t="n"/>
     </row>
     <row r="278">
-      <c r="B278" s="3" t="n"/>
-      <c r="C278" s="3" t="n"/>
+      <c r="B278" s="6" t="n"/>
+      <c r="C278" s="6" t="n"/>
     </row>
     <row r="279">
-      <c r="B279" s="3" t="n"/>
-      <c r="C279" s="3" t="n"/>
+      <c r="B279" s="6" t="n"/>
+      <c r="C279" s="6" t="n"/>
     </row>
     <row r="280">
-      <c r="B280" s="3" t="n"/>
-      <c r="C280" s="3" t="n"/>
+      <c r="B280" s="6" t="n"/>
+      <c r="C280" s="6" t="n"/>
     </row>
     <row r="281">
-      <c r="B281" s="3" t="n"/>
-      <c r="C281" s="3" t="n"/>
+      <c r="B281" s="6" t="n"/>
+      <c r="C281" s="6" t="n"/>
     </row>
     <row r="282">
-      <c r="B282" s="3" t="n"/>
-      <c r="C282" s="3" t="n"/>
+      <c r="B282" s="6" t="n"/>
+      <c r="C282" s="6" t="n"/>
     </row>
     <row r="283">
-      <c r="B283" s="3" t="n"/>
-      <c r="C283" s="3" t="n"/>
+      <c r="B283" s="6" t="n"/>
+      <c r="C283" s="6" t="n"/>
     </row>
     <row r="284">
-      <c r="B284" s="3" t="n"/>
-      <c r="C284" s="3" t="n"/>
+      <c r="B284" s="6" t="n"/>
+      <c r="C284" s="6" t="n"/>
     </row>
     <row r="285">
-      <c r="B285" s="3" t="n"/>
-      <c r="C285" s="3" t="n"/>
+      <c r="B285" s="6" t="n"/>
+      <c r="C285" s="6" t="n"/>
     </row>
     <row r="286">
-      <c r="B286" s="3" t="n"/>
-      <c r="C286" s="3" t="n"/>
+      <c r="B286" s="6" t="n"/>
+      <c r="C286" s="6" t="n"/>
     </row>
     <row r="287">
-      <c r="B287" s="3" t="n"/>
-      <c r="C287" s="3" t="n"/>
+      <c r="B287" s="6" t="n"/>
+      <c r="C287" s="6" t="n"/>
     </row>
     <row r="288">
-      <c r="B288" s="3" t="n"/>
-      <c r="C288" s="3" t="n"/>
+      <c r="B288" s="6" t="n"/>
+      <c r="C288" s="6" t="n"/>
     </row>
     <row r="289">
-      <c r="B289" s="3" t="n"/>
-      <c r="C289" s="3" t="n"/>
+      <c r="B289" s="6" t="n"/>
+      <c r="C289" s="6" t="n"/>
     </row>
     <row r="290">
-      <c r="B290" s="3" t="n"/>
-      <c r="C290" s="3" t="n"/>
+      <c r="B290" s="6" t="n"/>
+      <c r="C290" s="6" t="n"/>
     </row>
     <row r="291">
-      <c r="B291" s="3" t="n"/>
-      <c r="C291" s="3" t="n"/>
+      <c r="B291" s="6" t="n"/>
+      <c r="C291" s="6" t="n"/>
     </row>
     <row r="292">
-      <c r="B292" s="3" t="n"/>
-      <c r="C292" s="3" t="n"/>
+      <c r="B292" s="6" t="n"/>
+      <c r="C292" s="6" t="n"/>
     </row>
     <row r="293">
-      <c r="B293" s="3" t="n"/>
-      <c r="C293" s="3" t="n"/>
+      <c r="B293" s="6" t="n"/>
+      <c r="C293" s="6" t="n"/>
     </row>
     <row r="294">
-      <c r="B294" s="3" t="n"/>
-      <c r="C294" s="3" t="n"/>
+      <c r="B294" s="6" t="n"/>
+      <c r="C294" s="6" t="n"/>
     </row>
     <row r="295">
-      <c r="B295" s="3" t="n"/>
-      <c r="C295" s="3" t="n"/>
+      <c r="B295" s="6" t="n"/>
+      <c r="C295" s="6" t="n"/>
     </row>
     <row r="296">
-      <c r="B296" s="3" t="n"/>
-      <c r="C296" s="3" t="n"/>
+      <c r="B296" s="6" t="n"/>
+      <c r="C296" s="6" t="n"/>
     </row>
     <row r="297">
-      <c r="B297" s="3" t="n"/>
-      <c r="C297" s="3" t="n"/>
+      <c r="B297" s="6" t="n"/>
+      <c r="C297" s="6" t="n"/>
     </row>
     <row r="298">
-      <c r="B298" s="3" t="n"/>
-      <c r="C298" s="3" t="n"/>
+      <c r="B298" s="6" t="n"/>
+      <c r="C298" s="6" t="n"/>
     </row>
     <row r="299">
-      <c r="B299" s="3" t="n"/>
-      <c r="C299" s="3" t="n"/>
+      <c r="B299" s="6" t="n"/>
+      <c r="C299" s="6" t="n"/>
     </row>
     <row r="300">
-      <c r="B300" s="3" t="n"/>
-      <c r="C300" s="3" t="n"/>
+      <c r="B300" s="6" t="n"/>
+      <c r="C300" s="6" t="n"/>
     </row>
     <row r="301">
-      <c r="B301" s="3" t="n"/>
-      <c r="C301" s="3" t="n"/>
+      <c r="B301" s="6" t="n"/>
+      <c r="C301" s="6" t="n"/>
     </row>
     <row r="302">
-      <c r="B302" s="3" t="n"/>
-      <c r="C302" s="3" t="n"/>
+      <c r="B302" s="6" t="n"/>
+      <c r="C302" s="6" t="n"/>
     </row>
     <row r="303">
-      <c r="B303" s="3" t="n"/>
-      <c r="C303" s="3" t="n"/>
+      <c r="B303" s="6" t="n"/>
+      <c r="C303" s="6" t="n"/>
     </row>
     <row r="304">
-      <c r="B304" s="3" t="n"/>
-      <c r="C304" s="3" t="n"/>
+      <c r="B304" s="6" t="n"/>
+      <c r="C304" s="6" t="n"/>
     </row>
     <row r="305">
-      <c r="B305" s="3" t="n"/>
-      <c r="C305" s="3" t="n"/>
+      <c r="B305" s="6" t="n"/>
+      <c r="C305" s="6" t="n"/>
     </row>
     <row r="306">
-      <c r="B306" s="3" t="n"/>
-      <c r="C306" s="3" t="n"/>
+      <c r="B306" s="6" t="n"/>
+      <c r="C306" s="6" t="n"/>
     </row>
     <row r="307">
-      <c r="B307" s="3" t="n"/>
-      <c r="C307" s="3" t="n"/>
+      <c r="B307" s="6" t="n"/>
+      <c r="C307" s="6" t="n"/>
     </row>
     <row r="308">
-      <c r="B308" s="3" t="n"/>
-      <c r="C308" s="3" t="n"/>
+      <c r="B308" s="6" t="n"/>
+      <c r="C308" s="6" t="n"/>
     </row>
     <row r="309">
-      <c r="B309" s="3" t="n"/>
-      <c r="C309" s="3" t="n"/>
+      <c r="B309" s="6" t="n"/>
+      <c r="C309" s="6" t="n"/>
     </row>
     <row r="310">
-      <c r="B310" s="3" t="n"/>
-      <c r="C310" s="3" t="n"/>
+      <c r="B310" s="6" t="n"/>
+      <c r="C310" s="6" t="n"/>
     </row>
     <row r="311">
-      <c r="B311" s="3" t="n"/>
-      <c r="C311" s="3" t="n"/>
+      <c r="B311" s="6" t="n"/>
+      <c r="C311" s="6" t="n"/>
     </row>
     <row r="312">
-      <c r="B312" s="3" t="n"/>
-      <c r="C312" s="3" t="n"/>
+      <c r="B312" s="6" t="n"/>
+      <c r="C312" s="6" t="n"/>
     </row>
     <row r="313">
-      <c r="B313" s="3" t="n"/>
-      <c r="C313" s="3" t="n"/>
+      <c r="B313" s="6" t="n"/>
+      <c r="C313" s="6" t="n"/>
     </row>
     <row r="314">
-      <c r="B314" s="3" t="n"/>
-      <c r="C314" s="3" t="n"/>
+      <c r="B314" s="6" t="n"/>
+      <c r="C314" s="6" t="n"/>
     </row>
     <row r="315">
-      <c r="B315" s="3" t="n"/>
-      <c r="C315" s="3" t="n"/>
+      <c r="B315" s="6" t="n"/>
+      <c r="C315" s="6" t="n"/>
     </row>
     <row r="316">
-      <c r="B316" s="3" t="n"/>
-      <c r="C316" s="3" t="n"/>
+      <c r="B316" s="6" t="n"/>
+      <c r="C316" s="6" t="n"/>
     </row>
     <row r="317">
-      <c r="B317" s="3" t="n"/>
-      <c r="C317" s="3" t="n"/>
+      <c r="B317" s="6" t="n"/>
+      <c r="C317" s="6" t="n"/>
     </row>
     <row r="318">
-      <c r="B318" s="3" t="n"/>
-      <c r="C318" s="3" t="n"/>
+      <c r="B318" s="6" t="n"/>
+      <c r="C318" s="6" t="n"/>
     </row>
     <row r="319">
-      <c r="B319" s="3" t="n"/>
-      <c r="C319" s="3" t="n"/>
+      <c r="B319" s="6" t="n"/>
+      <c r="C319" s="6" t="n"/>
     </row>
     <row r="320">
-      <c r="B320" s="3" t="n"/>
-      <c r="C320" s="3" t="n"/>
+      <c r="B320" s="6" t="n"/>
+      <c r="C320" s="6" t="n"/>
     </row>
     <row r="321">
-      <c r="B321" s="3" t="n"/>
-      <c r="C321" s="3" t="n"/>
+      <c r="B321" s="6" t="n"/>
+      <c r="C321" s="6" t="n"/>
     </row>
     <row r="322">
-      <c r="B322" s="3" t="n"/>
-      <c r="C322" s="3" t="n"/>
+      <c r="B322" s="6" t="n"/>
+      <c r="C322" s="6" t="n"/>
     </row>
     <row r="323">
-      <c r="B323" s="3" t="n"/>
-      <c r="C323" s="3" t="n"/>
+      <c r="B323" s="6" t="n"/>
+      <c r="C323" s="6" t="n"/>
     </row>
     <row r="324">
-      <c r="B324" s="3" t="n"/>
-      <c r="C324" s="3" t="n"/>
+      <c r="B324" s="6" t="n"/>
+      <c r="C324" s="6" t="n"/>
     </row>
     <row r="325">
-      <c r="B325" s="3" t="n"/>
-      <c r="C325" s="3" t="n"/>
+      <c r="B325" s="6" t="n"/>
+      <c r="C325" s="6" t="n"/>
     </row>
     <row r="326">
-      <c r="B326" s="3" t="n"/>
-      <c r="C326" s="3" t="n"/>
+      <c r="B326" s="6" t="n"/>
+      <c r="C326" s="6" t="n"/>
     </row>
     <row r="327">
-      <c r="B327" s="3" t="n"/>
-      <c r="C327" s="3" t="n"/>
+      <c r="B327" s="6" t="n"/>
+      <c r="C327" s="6" t="n"/>
     </row>
     <row r="328">
-      <c r="B328" s="3" t="n"/>
-      <c r="C328" s="3" t="n"/>
+      <c r="B328" s="6" t="n"/>
+      <c r="C328" s="6" t="n"/>
     </row>
     <row r="329">
-      <c r="B329" s="3" t="n"/>
-      <c r="C329" s="3" t="n"/>
+      <c r="B329" s="6" t="n"/>
+      <c r="C329" s="6" t="n"/>
     </row>
     <row r="330">
-      <c r="B330" s="3" t="n"/>
-      <c r="C330" s="3" t="n"/>
+      <c r="B330" s="6" t="n"/>
+      <c r="C330" s="6" t="n"/>
     </row>
     <row r="331">
-      <c r="B331" s="3" t="n"/>
-      <c r="C331" s="3" t="n"/>
+      <c r="B331" s="6" t="n"/>
+      <c r="C331" s="6" t="n"/>
     </row>
     <row r="332">
-      <c r="B332" s="3" t="n"/>
-      <c r="C332" s="3" t="n"/>
+      <c r="B332" s="6" t="n"/>
+      <c r="C332" s="6" t="n"/>
     </row>
     <row r="333">
-      <c r="B333" s="3" t="n"/>
-      <c r="C333" s="3" t="n"/>
+      <c r="B333" s="6" t="n"/>
+      <c r="C333" s="6" t="n"/>
     </row>
     <row r="334">
-      <c r="B334" s="3" t="n"/>
-      <c r="C334" s="3" t="n"/>
+      <c r="B334" s="6" t="n"/>
+      <c r="C334" s="6" t="n"/>
     </row>
     <row r="335">
-      <c r="B335" s="3" t="n"/>
-      <c r="C335" s="3" t="n"/>
+      <c r="B335" s="6" t="n"/>
+      <c r="C335" s="6" t="n"/>
     </row>
     <row r="336">
-      <c r="B336" s="3" t="n"/>
-      <c r="C336" s="3" t="n"/>
+      <c r="B336" s="6" t="n"/>
+      <c r="C336" s="6" t="n"/>
     </row>
     <row r="337">
-      <c r="B337" s="3" t="n"/>
-      <c r="C337" s="3" t="n"/>
+      <c r="B337" s="6" t="n"/>
+      <c r="C337" s="6" t="n"/>
     </row>
     <row r="338">
-      <c r="B338" s="3" t="n"/>
-      <c r="C338" s="3" t="n"/>
+      <c r="B338" s="6" t="n"/>
+      <c r="C338" s="6" t="n"/>
     </row>
     <row r="339">
-      <c r="B339" s="3" t="n"/>
-      <c r="C339" s="3" t="n"/>
+      <c r="B339" s="6" t="n"/>
+      <c r="C339" s="6" t="n"/>
     </row>
     <row r="340">
-      <c r="B340" s="3" t="n"/>
-      <c r="C340" s="3" t="n"/>
+      <c r="B340" s="6" t="n"/>
+      <c r="C340" s="6" t="n"/>
     </row>
     <row r="341">
-      <c r="B341" s="3" t="n"/>
-      <c r="C341" s="3" t="n"/>
+      <c r="B341" s="6" t="n"/>
+      <c r="C341" s="6" t="n"/>
     </row>
     <row r="342">
-      <c r="B342" s="3" t="n"/>
-      <c r="C342" s="3" t="n"/>
+      <c r="B342" s="6" t="n"/>
+      <c r="C342" s="6" t="n"/>
     </row>
     <row r="343">
-      <c r="B343" s="3" t="n"/>
-      <c r="C343" s="3" t="n"/>
+      <c r="B343" s="6" t="n"/>
+      <c r="C343" s="6" t="n"/>
     </row>
     <row r="344">
-      <c r="B344" s="3" t="n"/>
-      <c r="C344" s="3" t="n"/>
+      <c r="B344" s="6" t="n"/>
+      <c r="C344" s="6" t="n"/>
     </row>
     <row r="345">
-      <c r="B345" s="3" t="n"/>
-      <c r="C345" s="3" t="n"/>
+      <c r="B345" s="6" t="n"/>
+      <c r="C345" s="6" t="n"/>
     </row>
     <row r="346">
-      <c r="B346" s="3" t="n"/>
-      <c r="C346" s="3" t="n"/>
+      <c r="B346" s="6" t="n"/>
+      <c r="C346" s="6" t="n"/>
     </row>
     <row r="347">
-      <c r="B347" s="3" t="n"/>
-      <c r="C347" s="3" t="n"/>
+      <c r="B347" s="6" t="n"/>
+      <c r="C347" s="6" t="n"/>
     </row>
     <row r="348">
-      <c r="B348" s="3" t="n"/>
-      <c r="C348" s="3" t="n"/>
+      <c r="B348" s="6" t="n"/>
+      <c r="C348" s="6" t="n"/>
     </row>
     <row r="349">
-      <c r="B349" s="3" t="n"/>
-      <c r="C349" s="3" t="n"/>
+      <c r="B349" s="6" t="n"/>
+      <c r="C349" s="6" t="n"/>
     </row>
     <row r="350">
-      <c r="B350" s="3" t="n"/>
-      <c r="C350" s="3" t="n"/>
+      <c r="B350" s="6" t="n"/>
+      <c r="C350" s="6" t="n"/>
     </row>
     <row r="351">
-      <c r="B351" s="3" t="n"/>
-      <c r="C351" s="3" t="n"/>
+      <c r="B351" s="6" t="n"/>
+      <c r="C351" s="6" t="n"/>
     </row>
     <row r="352">
-      <c r="B352" s="3" t="n"/>
-      <c r="C352" s="3" t="n"/>
+      <c r="B352" s="6" t="n"/>
+      <c r="C352" s="6" t="n"/>
     </row>
     <row r="353">
-      <c r="B353" s="3" t="n"/>
-      <c r="C353" s="3" t="n"/>
+      <c r="B353" s="6" t="n"/>
+      <c r="C353" s="6" t="n"/>
     </row>
     <row r="354">
-      <c r="B354" s="3" t="n"/>
-      <c r="C354" s="3" t="n"/>
+      <c r="B354" s="6" t="n"/>
+      <c r="C354" s="6" t="n"/>
     </row>
     <row r="355">
-      <c r="B355" s="3" t="n"/>
-      <c r="C355" s="3" t="n"/>
+      <c r="B355" s="6" t="n"/>
+      <c r="C355" s="6" t="n"/>
     </row>
     <row r="356">
-      <c r="B356" s="3" t="n"/>
-      <c r="C356" s="3" t="n"/>
+      <c r="B356" s="6" t="n"/>
+      <c r="C356" s="6" t="n"/>
     </row>
     <row r="357">
-      <c r="B357" s="3" t="n"/>
-      <c r="C357" s="3" t="n"/>
+      <c r="B357" s="6" t="n"/>
+      <c r="C357" s="6" t="n"/>
     </row>
     <row r="358">
-      <c r="B358" s="3" t="n"/>
-      <c r="C358" s="3" t="n"/>
+      <c r="B358" s="6" t="n"/>
+      <c r="C358" s="6" t="n"/>
     </row>
     <row r="359">
-      <c r="B359" s="3" t="n"/>
-      <c r="C359" s="3" t="n"/>
+      <c r="B359" s="6" t="n"/>
+      <c r="C359" s="6" t="n"/>
     </row>
     <row r="360">
-      <c r="B360" s="3" t="n"/>
-      <c r="C360" s="3" t="n"/>
+      <c r="B360" s="6" t="n"/>
+      <c r="C360" s="6" t="n"/>
     </row>
     <row r="361">
-      <c r="B361" s="3" t="n"/>
-      <c r="C361" s="3" t="n"/>
+      <c r="B361" s="6" t="n"/>
+      <c r="C361" s="6" t="n"/>
     </row>
     <row r="362">
-      <c r="B362" s="3" t="n"/>
-      <c r="C362" s="3" t="n"/>
+      <c r="B362" s="6" t="n"/>
+      <c r="C362" s="6" t="n"/>
     </row>
     <row r="363">
-      <c r="B363" s="3" t="n"/>
-      <c r="C363" s="3" t="n"/>
+      <c r="B363" s="6" t="n"/>
+      <c r="C363" s="6" t="n"/>
     </row>
     <row r="364">
-      <c r="B364" s="3" t="n"/>
-      <c r="C364" s="3" t="n"/>
+      <c r="B364" s="6" t="n"/>
+      <c r="C364" s="6" t="n"/>
     </row>
     <row r="365">
-      <c r="B365" s="3" t="n"/>
-      <c r="C365" s="3" t="n"/>
+      <c r="B365" s="6" t="n"/>
+      <c r="C365" s="6" t="n"/>
     </row>
     <row r="366">
-      <c r="B366" s="3" t="n"/>
-      <c r="C366" s="3" t="n"/>
+      <c r="B366" s="6" t="n"/>
+      <c r="C366" s="6" t="n"/>
     </row>
     <row r="367">
-      <c r="B367" s="3" t="n"/>
-      <c r="C367" s="3" t="n"/>
+      <c r="B367" s="6" t="n"/>
+      <c r="C367" s="6" t="n"/>
     </row>
     <row r="368">
-      <c r="B368" s="3" t="n"/>
-      <c r="C368" s="3" t="n"/>
+      <c r="B368" s="6" t="n"/>
+      <c r="C368" s="6" t="n"/>
     </row>
     <row r="369">
-      <c r="B369" s="3" t="n"/>
-      <c r="C369" s="3" t="n"/>
+      <c r="B369" s="6" t="n"/>
+      <c r="C369" s="6" t="n"/>
     </row>
     <row r="370">
-      <c r="B370" s="3" t="n"/>
-      <c r="C370" s="3" t="n"/>
+      <c r="B370" s="6" t="n"/>
+      <c r="C370" s="6" t="n"/>
     </row>
     <row r="371">
-      <c r="B371" s="3" t="n"/>
-      <c r="C371" s="3" t="n"/>
+      <c r="B371" s="6" t="n"/>
+      <c r="C371" s="6" t="n"/>
     </row>
     <row r="372">
-      <c r="B372" s="3" t="n"/>
-      <c r="C372" s="3" t="n"/>
+      <c r="B372" s="6" t="n"/>
+      <c r="C372" s="6" t="n"/>
     </row>
     <row r="373">
-      <c r="B373" s="3" t="n"/>
-      <c r="C373" s="3" t="n"/>
+      <c r="B373" s="6" t="n"/>
+      <c r="C373" s="6" t="n"/>
     </row>
     <row r="374">
-      <c r="B374" s="3" t="n"/>
-      <c r="C374" s="3" t="n"/>
+      <c r="B374" s="6" t="n"/>
+      <c r="C374" s="6" t="n"/>
     </row>
     <row r="375">
-      <c r="B375" s="3" t="n"/>
-      <c r="C375" s="3" t="n"/>
+      <c r="B375" s="6" t="n"/>
+      <c r="C375" s="6" t="n"/>
     </row>
     <row r="376">
-      <c r="B376" s="3" t="n"/>
-      <c r="C376" s="3" t="n"/>
+      <c r="B376" s="6" t="n"/>
+      <c r="C376" s="6" t="n"/>
     </row>
     <row r="377">
-      <c r="B377" s="3" t="n"/>
-      <c r="C377" s="3" t="n"/>
+      <c r="B377" s="6" t="n"/>
+      <c r="C377" s="6" t="n"/>
     </row>
     <row r="378">
-      <c r="B378" s="3" t="n"/>
-      <c r="C378" s="3" t="n"/>
+      <c r="B378" s="6" t="n"/>
+      <c r="C378" s="6" t="n"/>
     </row>
     <row r="379">
-      <c r="B379" s="3" t="n"/>
-      <c r="C379" s="3" t="n"/>
+      <c r="B379" s="6" t="n"/>
+      <c r="C379" s="6" t="n"/>
     </row>
     <row r="380">
-      <c r="B380" s="3" t="n"/>
-      <c r="C380" s="3" t="n"/>
+      <c r="B380" s="6" t="n"/>
+      <c r="C380" s="6" t="n"/>
     </row>
     <row r="381">
-      <c r="B381" s="3" t="n"/>
-      <c r="C381" s="3" t="n"/>
+      <c r="B381" s="6" t="n"/>
+      <c r="C381" s="6" t="n"/>
     </row>
     <row r="382">
-      <c r="B382" s="3" t="n"/>
-      <c r="C382" s="3" t="n"/>
+      <c r="B382" s="6" t="n"/>
+      <c r="C382" s="6" t="n"/>
     </row>
     <row r="383">
-      <c r="B383" s="3" t="n"/>
-      <c r="C383" s="3" t="n"/>
+      <c r="B383" s="6" t="n"/>
+      <c r="C383" s="6" t="n"/>
     </row>
     <row r="384">
-      <c r="B384" s="3" t="n"/>
-      <c r="C384" s="3" t="n"/>
+      <c r="B384" s="6" t="n"/>
+      <c r="C384" s="6" t="n"/>
     </row>
     <row r="385">
-      <c r="B385" s="3" t="n"/>
-      <c r="C385" s="3" t="n"/>
+      <c r="B385" s="6" t="n"/>
+      <c r="C385" s="6" t="n"/>
     </row>
     <row r="386">
-      <c r="B386" s="3" t="n"/>
-      <c r="C386" s="3" t="n"/>
+      <c r="B386" s="6" t="n"/>
+      <c r="C386" s="6" t="n"/>
     </row>
     <row r="387">
-      <c r="B387" s="3" t="n"/>
-      <c r="C387" s="3" t="n"/>
+      <c r="B387" s="6" t="n"/>
+      <c r="C387" s="6" t="n"/>
     </row>
     <row r="388">
-      <c r="B388" s="3" t="n"/>
-      <c r="C388" s="3" t="n"/>
+      <c r="B388" s="6" t="n"/>
+      <c r="C388" s="6" t="n"/>
     </row>
     <row r="389">
-      <c r="B389" s="3" t="n"/>
-      <c r="C389" s="3" t="n"/>
+      <c r="B389" s="6" t="n"/>
+      <c r="C389" s="6" t="n"/>
     </row>
     <row r="390">
-      <c r="B390" s="3" t="n"/>
-      <c r="C390" s="3" t="n"/>
+      <c r="B390" s="6" t="n"/>
+      <c r="C390" s="6" t="n"/>
     </row>
     <row r="391">
-      <c r="B391" s="3" t="n"/>
-      <c r="C391" s="3" t="n"/>
+      <c r="B391" s="6" t="n"/>
+      <c r="C391" s="6" t="n"/>
     </row>
     <row r="392">
-      <c r="B392" s="3" t="n"/>
-      <c r="C392" s="3" t="n"/>
+      <c r="B392" s="6" t="n"/>
+      <c r="C392" s="6" t="n"/>
     </row>
     <row r="393">
-      <c r="B393" s="3" t="n"/>
-      <c r="C393" s="3" t="n"/>
+      <c r="B393" s="6" t="n"/>
+      <c r="C393" s="6" t="n"/>
     </row>
     <row r="394">
-      <c r="B394" s="3" t="n"/>
-      <c r="C394" s="3" t="n"/>
+      <c r="B394" s="6" t="n"/>
+      <c r="C394" s="6" t="n"/>
     </row>
     <row r="395">
-      <c r="B395" s="3" t="n"/>
-      <c r="C395" s="3" t="n"/>
+      <c r="B395" s="6" t="n"/>
+      <c r="C395" s="6" t="n"/>
     </row>
     <row r="396">
-      <c r="B396" s="3" t="n"/>
-      <c r="C396" s="3" t="n"/>
+      <c r="B396" s="6" t="n"/>
+      <c r="C396" s="6" t="n"/>
     </row>
     <row r="397">
-      <c r="B397" s="3" t="n"/>
-      <c r="C397" s="3" t="n"/>
+      <c r="B397" s="6" t="n"/>
+      <c r="C397" s="6" t="n"/>
     </row>
     <row r="398">
-      <c r="B398" s="3" t="n"/>
-      <c r="C398" s="3" t="n"/>
+      <c r="B398" s="6" t="n"/>
+      <c r="C398" s="6" t="n"/>
     </row>
     <row r="399">
-      <c r="B399" s="3" t="n"/>
-      <c r="C399" s="3" t="n"/>
+      <c r="B399" s="6" t="n"/>
+      <c r="C399" s="6" t="n"/>
     </row>
     <row r="400">
-      <c r="B400" s="3" t="n"/>
-      <c r="C400" s="3" t="n"/>
+      <c r="B400" s="6" t="n"/>
+      <c r="C400" s="6" t="n"/>
     </row>
     <row r="401">
-      <c r="B401" s="3" t="n"/>
-      <c r="C401" s="3" t="n"/>
+      <c r="B401" s="6" t="n"/>
+      <c r="C401" s="6" t="n"/>
     </row>
     <row r="402">
-      <c r="B402" s="3" t="n"/>
-      <c r="C402" s="3" t="n"/>
+      <c r="B402" s="6" t="n"/>
+      <c r="C402" s="6" t="n"/>
     </row>
     <row r="403">
-      <c r="B403" s="3" t="n"/>
-      <c r="C403" s="3" t="n"/>
+      <c r="B403" s="6" t="n"/>
+      <c r="C403" s="6" t="n"/>
     </row>
     <row r="404">
-      <c r="B404" s="3" t="n"/>
-      <c r="C404" s="3" t="n"/>
+      <c r="B404" s="6" t="n"/>
+      <c r="C404" s="6" t="n"/>
     </row>
     <row r="405">
-      <c r="B405" s="3" t="n"/>
-      <c r="C405" s="3" t="n"/>
+      <c r="B405" s="6" t="n"/>
+      <c r="C405" s="6" t="n"/>
     </row>
     <row r="406">
-      <c r="B406" s="3" t="n"/>
-      <c r="C406" s="3" t="n"/>
+      <c r="B406" s="6" t="n"/>
+      <c r="C406" s="6" t="n"/>
     </row>
     <row r="407">
-      <c r="B407" s="3" t="n"/>
-      <c r="C407" s="3" t="n"/>
+      <c r="B407" s="6" t="n"/>
+      <c r="C407" s="6" t="n"/>
     </row>
     <row r="408">
-      <c r="B408" s="3" t="n"/>
-      <c r="C408" s="3" t="n"/>
+      <c r="B408" s="6" t="n"/>
+      <c r="C408" s="6" t="n"/>
     </row>
     <row r="409">
-      <c r="B409" s="3" t="n"/>
-      <c r="C409" s="3" t="n"/>
+      <c r="B409" s="6" t="n"/>
+      <c r="C409" s="6" t="n"/>
     </row>
     <row r="410">
-      <c r="B410" s="3" t="n"/>
-      <c r="C410" s="3" t="n"/>
+      <c r="B410" s="6" t="n"/>
+      <c r="C410" s="6" t="n"/>
     </row>
     <row r="411">
-      <c r="B411" s="3" t="n"/>
-      <c r="C411" s="3" t="n"/>
+      <c r="B411" s="6" t="n"/>
+      <c r="C411" s="6" t="n"/>
     </row>
     <row r="412">
-      <c r="B412" s="3" t="n"/>
-      <c r="C412" s="3" t="n"/>
+      <c r="B412" s="6" t="n"/>
+      <c r="C412" s="6" t="n"/>
     </row>
     <row r="413">
-      <c r="B413" s="3" t="n"/>
-      <c r="C413" s="3" t="n"/>
+      <c r="B413" s="6" t="n"/>
+      <c r="C413" s="6" t="n"/>
     </row>
     <row r="414">
-      <c r="B414" s="3" t="n"/>
-      <c r="C414" s="3" t="n"/>
+      <c r="B414" s="6" t="n"/>
+      <c r="C414" s="6" t="n"/>
     </row>
     <row r="415">
-      <c r="B415" s="3" t="n"/>
-      <c r="C415" s="3" t="n"/>
+      <c r="B415" s="6" t="n"/>
+      <c r="C415" s="6" t="n"/>
     </row>
     <row r="416">
-      <c r="B416" s="3" t="n"/>
-      <c r="C416" s="3" t="n"/>
+      <c r="B416" s="6" t="n"/>
+      <c r="C416" s="6" t="n"/>
     </row>
     <row r="417">
-      <c r="B417" s="3" t="n"/>
-      <c r="C417" s="3" t="n"/>
+      <c r="B417" s="6" t="n"/>
+      <c r="C417" s="6" t="n"/>
     </row>
     <row r="418">
-      <c r="B418" s="3" t="n"/>
-      <c r="C418" s="3" t="n"/>
+      <c r="B418" s="6" t="n"/>
+      <c r="C418" s="6" t="n"/>
     </row>
     <row r="419">
-      <c r="B419" s="3" t="n"/>
-      <c r="C419" s="3" t="n"/>
+      <c r="B419" s="6" t="n"/>
+      <c r="C419" s="6" t="n"/>
     </row>
     <row r="420">
-      <c r="B420" s="3" t="n"/>
-      <c r="C420" s="3" t="n"/>
+      <c r="B420" s="6" t="n"/>
+      <c r="C420" s="6" t="n"/>
     </row>
     <row r="421">
-      <c r="B421" s="3" t="n"/>
-      <c r="C421" s="3" t="n"/>
+      <c r="B421" s="6" t="n"/>
+      <c r="C421" s="6" t="n"/>
     </row>
     <row r="422">
-      <c r="B422" s="3" t="n"/>
-      <c r="C422" s="3" t="n"/>
+      <c r="B422" s="6" t="n"/>
+      <c r="C422" s="6" t="n"/>
     </row>
     <row r="423">
-      <c r="B423" s="3" t="n"/>
-      <c r="C423" s="3" t="n"/>
+      <c r="B423" s="6" t="n"/>
+      <c r="C423" s="6" t="n"/>
     </row>
     <row r="424">
-      <c r="B424" s="3" t="n"/>
-      <c r="C424" s="3" t="n"/>
+      <c r="B424" s="6" t="n"/>
+      <c r="C424" s="6" t="n"/>
     </row>
     <row r="425">
-      <c r="B425" s="3" t="n"/>
-      <c r="C425" s="3" t="n"/>
+      <c r="B425" s="6" t="n"/>
+      <c r="C425" s="6" t="n"/>
     </row>
     <row r="426">
-      <c r="B426" s="3" t="n"/>
-      <c r="C426" s="3" t="n"/>
+      <c r="B426" s="6" t="n"/>
+      <c r="C426" s="6" t="n"/>
     </row>
     <row r="427">
-      <c r="B427" s="3" t="n"/>
-      <c r="C427" s="3" t="n"/>
+      <c r="B427" s="6" t="n"/>
+      <c r="C427" s="6" t="n"/>
     </row>
     <row r="428">
-      <c r="B428" s="3" t="n"/>
-      <c r="C428" s="3" t="n"/>
+      <c r="B428" s="6" t="n"/>
+      <c r="C428" s="6" t="n"/>
     </row>
     <row r="429">
-      <c r="B429" s="3" t="n"/>
-      <c r="C429" s="3" t="n"/>
+      <c r="B429" s="6" t="n"/>
+      <c r="C429" s="6" t="n"/>
     </row>
     <row r="430">
-      <c r="B430" s="3" t="n"/>
-      <c r="C430" s="3" t="n"/>
+      <c r="B430" s="6" t="n"/>
+      <c r="C430" s="6" t="n"/>
     </row>
     <row r="431">
-      <c r="B431" s="3" t="n"/>
-      <c r="C431" s="3" t="n"/>
+      <c r="B431" s="6" t="n"/>
+      <c r="C431" s="6" t="n"/>
     </row>
     <row r="432">
-      <c r="B432" s="3" t="n"/>
-      <c r="C432" s="3" t="n"/>
+      <c r="B432" s="6" t="n"/>
+      <c r="C432" s="6" t="n"/>
     </row>
     <row r="433">
-      <c r="B433" s="3" t="n"/>
-      <c r="C433" s="3" t="n"/>
+      <c r="B433" s="6" t="n"/>
+      <c r="C433" s="6" t="n"/>
     </row>
     <row r="434">
-      <c r="B434" s="3" t="n"/>
-      <c r="C434" s="3" t="n"/>
+      <c r="B434" s="6" t="n"/>
+      <c r="C434" s="6" t="n"/>
     </row>
     <row r="435">
-      <c r="B435" s="3" t="n"/>
-      <c r="C435" s="3" t="n"/>
+      <c r="B435" s="6" t="n"/>
+      <c r="C435" s="6" t="n"/>
     </row>
     <row r="436">
-      <c r="B436" s="3" t="n"/>
-      <c r="C436" s="3" t="n"/>
+      <c r="B436" s="6" t="n"/>
+      <c r="C436" s="6" t="n"/>
     </row>
     <row r="437">
-      <c r="B437" s="3" t="n"/>
-      <c r="C437" s="3" t="n"/>
+      <c r="B437" s="6" t="n"/>
+      <c r="C437" s="6" t="n"/>
     </row>
     <row r="438">
-      <c r="B438" s="3" t="n"/>
-      <c r="C438" s="3" t="n"/>
+      <c r="B438" s="6" t="n"/>
+      <c r="C438" s="6" t="n"/>
     </row>
     <row r="439">
-      <c r="B439" s="3" t="n"/>
-      <c r="C439" s="3" t="n"/>
+      <c r="B439" s="6" t="n"/>
+      <c r="C439" s="6" t="n"/>
     </row>
     <row r="440">
-      <c r="B440" s="3" t="n"/>
-      <c r="C440" s="3" t="n"/>
+      <c r="B440" s="6" t="n"/>
+      <c r="C440" s="6" t="n"/>
     </row>
     <row r="441">
-      <c r="B441" s="3" t="n"/>
-      <c r="C441" s="3" t="n"/>
+      <c r="B441" s="6" t="n"/>
+      <c r="C441" s="6" t="n"/>
     </row>
     <row r="442">
-      <c r="B442" s="3" t="n"/>
-      <c r="C442" s="3" t="n"/>
+      <c r="B442" s="6" t="n"/>
+      <c r="C442" s="6" t="n"/>
     </row>
     <row r="443">
-      <c r="B443" s="3" t="n"/>
-      <c r="C443" s="3" t="n"/>
+      <c r="B443" s="6" t="n"/>
+      <c r="C443" s="6" t="n"/>
     </row>
     <row r="444">
-      <c r="B444" s="3" t="n"/>
-      <c r="C444" s="3" t="n"/>
+      <c r="B444" s="6" t="n"/>
+      <c r="C444" s="6" t="n"/>
     </row>
     <row r="445">
-      <c r="B445" s="3" t="n"/>
-      <c r="C445" s="3" t="n"/>
+      <c r="B445" s="6" t="n"/>
+      <c r="C445" s="6" t="n"/>
     </row>
     <row r="446">
-      <c r="B446" s="3" t="n"/>
-      <c r="C446" s="3" t="n"/>
+      <c r="B446" s="6" t="n"/>
+      <c r="C446" s="6" t="n"/>
     </row>
     <row r="447">
-      <c r="B447" s="3" t="n"/>
-      <c r="C447" s="3" t="n"/>
+      <c r="B447" s="6" t="n"/>
+      <c r="C447" s="6" t="n"/>
     </row>
     <row r="448">
-      <c r="B448" s="3" t="n"/>
-      <c r="C448" s="3" t="n"/>
+      <c r="B448" s="6" t="n"/>
+      <c r="C448" s="6" t="n"/>
     </row>
     <row r="449">
-      <c r="B449" s="3" t="n"/>
-      <c r="C449" s="3" t="n"/>
+      <c r="B449" s="6" t="n"/>
+      <c r="C449" s="6" t="n"/>
     </row>
     <row r="450">
-      <c r="B450" s="3" t="n"/>
-      <c r="C450" s="3" t="n"/>
+      <c r="B450" s="6" t="n"/>
+      <c r="C450" s="6" t="n"/>
     </row>
     <row r="451">
-      <c r="B451" s="3" t="n"/>
-      <c r="C451" s="3" t="n"/>
+      <c r="B451" s="6" t="n"/>
+      <c r="C451" s="6" t="n"/>
     </row>
     <row r="452">
-      <c r="B452" s="3" t="n"/>
-      <c r="C452" s="3" t="n"/>
+      <c r="B452" s="6" t="n"/>
+      <c r="C452" s="6" t="n"/>
     </row>
     <row r="453">
-      <c r="B453" s="3" t="n"/>
-      <c r="C453" s="3" t="n"/>
+      <c r="B453" s="6" t="n"/>
+      <c r="C453" s="6" t="n"/>
     </row>
     <row r="454">
-      <c r="B454" s="3" t="n"/>
-      <c r="C454" s="3" t="n"/>
+      <c r="B454" s="6" t="n"/>
+      <c r="C454" s="6" t="n"/>
     </row>
     <row r="455">
-      <c r="B455" s="3" t="n"/>
-      <c r="C455" s="3" t="n"/>
+      <c r="B455" s="6" t="n"/>
+      <c r="C455" s="6" t="n"/>
     </row>
     <row r="456">
-      <c r="B456" s="3" t="n"/>
-      <c r="C456" s="3" t="n"/>
+      <c r="B456" s="6" t="n"/>
+      <c r="C456" s="6" t="n"/>
     </row>
     <row r="457">
-      <c r="B457" s="3" t="n"/>
-      <c r="C457" s="3" t="n"/>
+      <c r="B457" s="6" t="n"/>
+      <c r="C457" s="6" t="n"/>
     </row>
     <row r="458">
-      <c r="B458" s="3" t="n"/>
-      <c r="C458" s="3" t="n"/>
+      <c r="B458" s="6" t="n"/>
+      <c r="C458" s="6" t="n"/>
     </row>
     <row r="459">
-      <c r="B459" s="3" t="n"/>
-      <c r="C459" s="3" t="n"/>
+      <c r="B459" s="6" t="n"/>
+      <c r="C459" s="6" t="n"/>
     </row>
     <row r="460">
-      <c r="B460" s="3" t="n"/>
-      <c r="C460" s="3" t="n"/>
+      <c r="B460" s="6" t="n"/>
+      <c r="C460" s="6" t="n"/>
     </row>
     <row r="461">
-      <c r="B461" s="3" t="n"/>
-      <c r="C461" s="3" t="n"/>
+      <c r="B461" s="6" t="n"/>
+      <c r="C461" s="6" t="n"/>
     </row>
     <row r="462">
-      <c r="B462" s="3" t="n"/>
-      <c r="C462" s="3" t="n"/>
+      <c r="B462" s="6" t="n"/>
+      <c r="C462" s="6" t="n"/>
     </row>
     <row r="463">
-      <c r="B463" s="3" t="n"/>
-      <c r="C463" s="3" t="n"/>
+      <c r="B463" s="6" t="n"/>
+      <c r="C463" s="6" t="n"/>
     </row>
     <row r="464">
-      <c r="B464" s="3" t="n"/>
-      <c r="C464" s="3" t="n"/>
+      <c r="B464" s="6" t="n"/>
+      <c r="C464" s="6" t="n"/>
     </row>
     <row r="465">
-      <c r="B465" s="3" t="n"/>
-      <c r="C465" s="3" t="n"/>
+      <c r="B465" s="6" t="n"/>
+      <c r="C465" s="6" t="n"/>
     </row>
     <row r="466">
-      <c r="B466" s="3" t="n"/>
-      <c r="C466" s="3" t="n"/>
+      <c r="B466" s="6" t="n"/>
+      <c r="C466" s="6" t="n"/>
     </row>
     <row r="467">
-      <c r="B467" s="3" t="n"/>
-      <c r="C467" s="3" t="n"/>
+      <c r="B467" s="6" t="n"/>
+      <c r="C467" s="6" t="n"/>
     </row>
     <row r="468">
-      <c r="B468" s="3" t="n"/>
-      <c r="C468" s="3" t="n"/>
+      <c r="B468" s="6" t="n"/>
+      <c r="C468" s="6" t="n"/>
     </row>
     <row r="469">
-      <c r="B469" s="3" t="n"/>
-      <c r="C469" s="3" t="n"/>
+      <c r="B469" s="6" t="n"/>
+      <c r="C469" s="6" t="n"/>
     </row>
     <row r="470">
-      <c r="B470" s="3" t="n"/>
-      <c r="C470" s="3" t="n"/>
+      <c r="B470" s="6" t="n"/>
+      <c r="C470" s="6" t="n"/>
     </row>
     <row r="471">
-      <c r="B471" s="3" t="n"/>
-      <c r="C471" s="3" t="n"/>
+      <c r="B471" s="6" t="n"/>
+      <c r="C471" s="6" t="n"/>
     </row>
     <row r="472">
-      <c r="B472" s="3" t="n"/>
-      <c r="C472" s="3" t="n"/>
+      <c r="B472" s="6" t="n"/>
+      <c r="C472" s="6" t="n"/>
     </row>
     <row r="473">
-      <c r="B473" s="3" t="n"/>
-      <c r="C473" s="3" t="n"/>
+      <c r="B473" s="6" t="n"/>
+      <c r="C473" s="6" t="n"/>
     </row>
     <row r="474">
-      <c r="B474" s="3" t="n"/>
-      <c r="C474" s="3" t="n"/>
+      <c r="B474" s="6" t="n"/>
+      <c r="C474" s="6" t="n"/>
     </row>
     <row r="475">
-      <c r="B475" s="3" t="n"/>
-      <c r="C475" s="3" t="n"/>
+      <c r="B475" s="6" t="n"/>
+      <c r="C475" s="6" t="n"/>
     </row>
     <row r="476">
-      <c r="B476" s="3" t="n"/>
-      <c r="C476" s="3" t="n"/>
+      <c r="B476" s="6" t="n"/>
+      <c r="C476" s="6" t="n"/>
     </row>
     <row r="477">
-      <c r="B477" s="3" t="n"/>
-      <c r="C477" s="3" t="n"/>
+      <c r="B477" s="6" t="n"/>
+      <c r="C477" s="6" t="n"/>
     </row>
     <row r="478">
-      <c r="B478" s="3" t="n"/>
-      <c r="C478" s="3" t="n"/>
+      <c r="B478" s="6" t="n"/>
+      <c r="C478" s="6" t="n"/>
     </row>
     <row r="479">
-      <c r="B479" s="3" t="n"/>
-      <c r="C479" s="3" t="n"/>
+      <c r="B479" s="6" t="n"/>
+      <c r="C479" s="6" t="n"/>
     </row>
     <row r="480">
-      <c r="B480" s="3" t="n"/>
-      <c r="C480" s="3" t="n"/>
+      <c r="B480" s="6" t="n"/>
+      <c r="C480" s="6" t="n"/>
     </row>
     <row r="481">
-      <c r="B481" s="3" t="n"/>
-      <c r="C481" s="3" t="n"/>
+      <c r="B481" s="6" t="n"/>
+      <c r="C481" s="6" t="n"/>
     </row>
     <row r="482">
-      <c r="B482" s="3" t="n"/>
-      <c r="C482" s="3" t="n"/>
+      <c r="B482" s="6" t="n"/>
+      <c r="C482" s="6" t="n"/>
     </row>
     <row r="483">
-      <c r="B483" s="3" t="n"/>
-      <c r="C483" s="3" t="n"/>
+      <c r="B483" s="6" t="n"/>
+      <c r="C483" s="6" t="n"/>
     </row>
     <row r="484">
-      <c r="B484" s="3" t="n"/>
-      <c r="C484" s="3" t="n"/>
+      <c r="B484" s="6" t="n"/>
+      <c r="C484" s="6" t="n"/>
     </row>
     <row r="485">
-      <c r="B485" s="3" t="n"/>
-      <c r="C485" s="3" t="n"/>
+      <c r="B485" s="6" t="n"/>
+      <c r="C485" s="6" t="n"/>
     </row>
     <row r="486">
-      <c r="B486" s="3" t="n"/>
-      <c r="C486" s="3" t="n"/>
+      <c r="B486" s="6" t="n"/>
+      <c r="C486" s="6" t="n"/>
     </row>
     <row r="487">
-      <c r="B487" s="3" t="n"/>
-      <c r="C487" s="3" t="n"/>
+      <c r="B487" s="6" t="n"/>
+      <c r="C487" s="6" t="n"/>
     </row>
     <row r="488">
-      <c r="B488" s="3" t="n"/>
-      <c r="C488" s="3" t="n"/>
+      <c r="B488" s="6" t="n"/>
+      <c r="C488" s="6" t="n"/>
     </row>
     <row r="489">
-      <c r="B489" s="3" t="n"/>
-      <c r="C489" s="3" t="n"/>
+      <c r="B489" s="6" t="n"/>
+      <c r="C489" s="6" t="n"/>
     </row>
     <row r="490">
-      <c r="B490" s="3" t="n"/>
-      <c r="C490" s="3" t="n"/>
+      <c r="B490" s="6" t="n"/>
+      <c r="C490" s="6" t="n"/>
     </row>
     <row r="491">
-      <c r="B491" s="3" t="n"/>
-      <c r="C491" s="3" t="n"/>
+      <c r="B491" s="6" t="n"/>
+      <c r="C491" s="6" t="n"/>
     </row>
     <row r="492">
-      <c r="B492" s="3" t="n"/>
-      <c r="C492" s="3" t="n"/>
+      <c r="B492" s="6" t="n"/>
+      <c r="C492" s="6" t="n"/>
     </row>
     <row r="493">
-      <c r="B493" s="3" t="n"/>
-      <c r="C493" s="3" t="n"/>
+      <c r="B493" s="6" t="n"/>
+      <c r="C493" s="6" t="n"/>
     </row>
     <row r="494">
-      <c r="B494" s="3" t="n"/>
-      <c r="C494" s="3" t="n"/>
+      <c r="B494" s="6" t="n"/>
+      <c r="C494" s="6" t="n"/>
     </row>
     <row r="495">
-      <c r="B495" s="3" t="n"/>
-      <c r="C495" s="3" t="n"/>
+      <c r="B495" s="6" t="n"/>
+      <c r="C495" s="6" t="n"/>
     </row>
     <row r="496">
-      <c r="B496" s="3" t="n"/>
-      <c r="C496" s="3" t="n"/>
+      <c r="B496" s="6" t="n"/>
+      <c r="C496" s="6" t="n"/>
     </row>
     <row r="497">
-      <c r="B497" s="3" t="n"/>
-      <c r="C497" s="3" t="n"/>
+      <c r="B497" s="6" t="n"/>
+      <c r="C497" s="6" t="n"/>
     </row>
     <row r="498">
-      <c r="B498" s="3" t="n"/>
-      <c r="C498" s="3" t="n"/>
+      <c r="B498" s="6" t="n"/>
+      <c r="C498" s="6" t="n"/>
     </row>
     <row r="499">
-      <c r="B499" s="3" t="n"/>
-      <c r="C499" s="3" t="n"/>
+      <c r="B499" s="6" t="n"/>
+      <c r="C499" s="6" t="n"/>
     </row>
     <row r="500">
-      <c r="B500" s="3" t="n"/>
-      <c r="C500" s="3" t="n"/>
+      <c r="B500" s="6" t="n"/>
+      <c r="C500" s="6" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -5130,10 +5312,10 @@
           <t>P02 NRA</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="3" t="n">
         <v>46300</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="3" t="n">
         <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
@@ -5161,10 +5343,10 @@
           <t>P41 MIL</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="3" t="n">
         <v>46307</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="3" t="n">
         <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
@@ -5179,1992 +5361,1992 @@
       </c>
     </row>
     <row r="4">
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
     </row>
     <row r="5">
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
     </row>
     <row r="6">
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
     </row>
     <row r="7">
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
     </row>
     <row r="8">
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="n"/>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
     </row>
     <row r="9">
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="n"/>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
     </row>
     <row r="10">
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
     </row>
     <row r="11">
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
     </row>
     <row r="12">
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
     </row>
     <row r="13">
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
     </row>
     <row r="14">
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="n"/>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
     </row>
     <row r="15">
-      <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
     </row>
     <row r="16">
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
     </row>
     <row r="17">
-      <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
     </row>
     <row r="18">
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="n"/>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
     </row>
     <row r="19">
-      <c r="D19" s="2" t="n"/>
-      <c r="E19" s="2" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
     </row>
     <row r="20">
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="n"/>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="n"/>
     </row>
     <row r="21">
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="n"/>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
     </row>
     <row r="22">
-      <c r="D22" s="2" t="n"/>
-      <c r="E22" s="2" t="n"/>
+      <c r="D22" s="3" t="n"/>
+      <c r="E22" s="3" t="n"/>
     </row>
     <row r="23">
-      <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="n"/>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
     </row>
     <row r="24">
-      <c r="D24" s="2" t="n"/>
-      <c r="E24" s="2" t="n"/>
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="n"/>
     </row>
     <row r="25">
-      <c r="D25" s="2" t="n"/>
-      <c r="E25" s="2" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
     </row>
     <row r="26">
-      <c r="D26" s="2" t="n"/>
-      <c r="E26" s="2" t="n"/>
+      <c r="D26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
     </row>
     <row r="27">
-      <c r="D27" s="2" t="n"/>
-      <c r="E27" s="2" t="n"/>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
     </row>
     <row r="28">
-      <c r="D28" s="2" t="n"/>
-      <c r="E28" s="2" t="n"/>
+      <c r="D28" s="3" t="n"/>
+      <c r="E28" s="3" t="n"/>
     </row>
     <row r="29">
-      <c r="D29" s="2" t="n"/>
-      <c r="E29" s="2" t="n"/>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
     </row>
     <row r="30">
-      <c r="D30" s="2" t="n"/>
-      <c r="E30" s="2" t="n"/>
+      <c r="D30" s="3" t="n"/>
+      <c r="E30" s="3" t="n"/>
     </row>
     <row r="31">
-      <c r="D31" s="2" t="n"/>
-      <c r="E31" s="2" t="n"/>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n"/>
     </row>
     <row r="32">
-      <c r="D32" s="2" t="n"/>
-      <c r="E32" s="2" t="n"/>
+      <c r="D32" s="3" t="n"/>
+      <c r="E32" s="3" t="n"/>
     </row>
     <row r="33">
-      <c r="D33" s="2" t="n"/>
-      <c r="E33" s="2" t="n"/>
+      <c r="D33" s="3" t="n"/>
+      <c r="E33" s="3" t="n"/>
     </row>
     <row r="34">
-      <c r="D34" s="2" t="n"/>
-      <c r="E34" s="2" t="n"/>
+      <c r="D34" s="3" t="n"/>
+      <c r="E34" s="3" t="n"/>
     </row>
     <row r="35">
-      <c r="D35" s="2" t="n"/>
-      <c r="E35" s="2" t="n"/>
+      <c r="D35" s="3" t="n"/>
+      <c r="E35" s="3" t="n"/>
     </row>
     <row r="36">
-      <c r="D36" s="2" t="n"/>
-      <c r="E36" s="2" t="n"/>
+      <c r="D36" s="3" t="n"/>
+      <c r="E36" s="3" t="n"/>
     </row>
     <row r="37">
-      <c r="D37" s="2" t="n"/>
-      <c r="E37" s="2" t="n"/>
+      <c r="D37" s="3" t="n"/>
+      <c r="E37" s="3" t="n"/>
     </row>
     <row r="38">
-      <c r="D38" s="2" t="n"/>
-      <c r="E38" s="2" t="n"/>
+      <c r="D38" s="3" t="n"/>
+      <c r="E38" s="3" t="n"/>
     </row>
     <row r="39">
-      <c r="D39" s="2" t="n"/>
-      <c r="E39" s="2" t="n"/>
+      <c r="D39" s="3" t="n"/>
+      <c r="E39" s="3" t="n"/>
     </row>
     <row r="40">
-      <c r="D40" s="2" t="n"/>
-      <c r="E40" s="2" t="n"/>
+      <c r="D40" s="3" t="n"/>
+      <c r="E40" s="3" t="n"/>
     </row>
     <row r="41">
-      <c r="D41" s="2" t="n"/>
-      <c r="E41" s="2" t="n"/>
+      <c r="D41" s="3" t="n"/>
+      <c r="E41" s="3" t="n"/>
     </row>
     <row r="42">
-      <c r="D42" s="2" t="n"/>
-      <c r="E42" s="2" t="n"/>
+      <c r="D42" s="3" t="n"/>
+      <c r="E42" s="3" t="n"/>
     </row>
     <row r="43">
-      <c r="D43" s="2" t="n"/>
-      <c r="E43" s="2" t="n"/>
+      <c r="D43" s="3" t="n"/>
+      <c r="E43" s="3" t="n"/>
     </row>
     <row r="44">
-      <c r="D44" s="2" t="n"/>
-      <c r="E44" s="2" t="n"/>
+      <c r="D44" s="3" t="n"/>
+      <c r="E44" s="3" t="n"/>
     </row>
     <row r="45">
-      <c r="D45" s="2" t="n"/>
-      <c r="E45" s="2" t="n"/>
+      <c r="D45" s="3" t="n"/>
+      <c r="E45" s="3" t="n"/>
     </row>
     <row r="46">
-      <c r="D46" s="2" t="n"/>
-      <c r="E46" s="2" t="n"/>
+      <c r="D46" s="3" t="n"/>
+      <c r="E46" s="3" t="n"/>
     </row>
     <row r="47">
-      <c r="D47" s="2" t="n"/>
-      <c r="E47" s="2" t="n"/>
+      <c r="D47" s="3" t="n"/>
+      <c r="E47" s="3" t="n"/>
     </row>
     <row r="48">
-      <c r="D48" s="2" t="n"/>
-      <c r="E48" s="2" t="n"/>
+      <c r="D48" s="3" t="n"/>
+      <c r="E48" s="3" t="n"/>
     </row>
     <row r="49">
-      <c r="D49" s="2" t="n"/>
-      <c r="E49" s="2" t="n"/>
+      <c r="D49" s="3" t="n"/>
+      <c r="E49" s="3" t="n"/>
     </row>
     <row r="50">
-      <c r="D50" s="2" t="n"/>
-      <c r="E50" s="2" t="n"/>
+      <c r="D50" s="3" t="n"/>
+      <c r="E50" s="3" t="n"/>
     </row>
     <row r="51">
-      <c r="D51" s="2" t="n"/>
-      <c r="E51" s="2" t="n"/>
+      <c r="D51" s="3" t="n"/>
+      <c r="E51" s="3" t="n"/>
     </row>
     <row r="52">
-      <c r="D52" s="2" t="n"/>
-      <c r="E52" s="2" t="n"/>
+      <c r="D52" s="3" t="n"/>
+      <c r="E52" s="3" t="n"/>
     </row>
     <row r="53">
-      <c r="D53" s="2" t="n"/>
-      <c r="E53" s="2" t="n"/>
+      <c r="D53" s="3" t="n"/>
+      <c r="E53" s="3" t="n"/>
     </row>
     <row r="54">
-      <c r="D54" s="2" t="n"/>
-      <c r="E54" s="2" t="n"/>
+      <c r="D54" s="3" t="n"/>
+      <c r="E54" s="3" t="n"/>
     </row>
     <row r="55">
-      <c r="D55" s="2" t="n"/>
-      <c r="E55" s="2" t="n"/>
+      <c r="D55" s="3" t="n"/>
+      <c r="E55" s="3" t="n"/>
     </row>
     <row r="56">
-      <c r="D56" s="2" t="n"/>
-      <c r="E56" s="2" t="n"/>
+      <c r="D56" s="3" t="n"/>
+      <c r="E56" s="3" t="n"/>
     </row>
     <row r="57">
-      <c r="D57" s="2" t="n"/>
-      <c r="E57" s="2" t="n"/>
+      <c r="D57" s="3" t="n"/>
+      <c r="E57" s="3" t="n"/>
     </row>
     <row r="58">
-      <c r="D58" s="2" t="n"/>
-      <c r="E58" s="2" t="n"/>
+      <c r="D58" s="3" t="n"/>
+      <c r="E58" s="3" t="n"/>
     </row>
     <row r="59">
-      <c r="D59" s="2" t="n"/>
-      <c r="E59" s="2" t="n"/>
+      <c r="D59" s="3" t="n"/>
+      <c r="E59" s="3" t="n"/>
     </row>
     <row r="60">
-      <c r="D60" s="2" t="n"/>
-      <c r="E60" s="2" t="n"/>
+      <c r="D60" s="3" t="n"/>
+      <c r="E60" s="3" t="n"/>
     </row>
     <row r="61">
-      <c r="D61" s="2" t="n"/>
-      <c r="E61" s="2" t="n"/>
+      <c r="D61" s="3" t="n"/>
+      <c r="E61" s="3" t="n"/>
     </row>
     <row r="62">
-      <c r="D62" s="2" t="n"/>
-      <c r="E62" s="2" t="n"/>
+      <c r="D62" s="3" t="n"/>
+      <c r="E62" s="3" t="n"/>
     </row>
     <row r="63">
-      <c r="D63" s="2" t="n"/>
-      <c r="E63" s="2" t="n"/>
+      <c r="D63" s="3" t="n"/>
+      <c r="E63" s="3" t="n"/>
     </row>
     <row r="64">
-      <c r="D64" s="2" t="n"/>
-      <c r="E64" s="2" t="n"/>
+      <c r="D64" s="3" t="n"/>
+      <c r="E64" s="3" t="n"/>
     </row>
     <row r="65">
-      <c r="D65" s="2" t="n"/>
-      <c r="E65" s="2" t="n"/>
+      <c r="D65" s="3" t="n"/>
+      <c r="E65" s="3" t="n"/>
     </row>
     <row r="66">
-      <c r="D66" s="2" t="n"/>
-      <c r="E66" s="2" t="n"/>
+      <c r="D66" s="3" t="n"/>
+      <c r="E66" s="3" t="n"/>
     </row>
     <row r="67">
-      <c r="D67" s="2" t="n"/>
-      <c r="E67" s="2" t="n"/>
+      <c r="D67" s="3" t="n"/>
+      <c r="E67" s="3" t="n"/>
     </row>
     <row r="68">
-      <c r="D68" s="2" t="n"/>
-      <c r="E68" s="2" t="n"/>
+      <c r="D68" s="3" t="n"/>
+      <c r="E68" s="3" t="n"/>
     </row>
     <row r="69">
-      <c r="D69" s="2" t="n"/>
-      <c r="E69" s="2" t="n"/>
+      <c r="D69" s="3" t="n"/>
+      <c r="E69" s="3" t="n"/>
     </row>
     <row r="70">
-      <c r="D70" s="2" t="n"/>
-      <c r="E70" s="2" t="n"/>
+      <c r="D70" s="3" t="n"/>
+      <c r="E70" s="3" t="n"/>
     </row>
     <row r="71">
-      <c r="D71" s="2" t="n"/>
-      <c r="E71" s="2" t="n"/>
+      <c r="D71" s="3" t="n"/>
+      <c r="E71" s="3" t="n"/>
     </row>
     <row r="72">
-      <c r="D72" s="2" t="n"/>
-      <c r="E72" s="2" t="n"/>
+      <c r="D72" s="3" t="n"/>
+      <c r="E72" s="3" t="n"/>
     </row>
     <row r="73">
-      <c r="D73" s="2" t="n"/>
-      <c r="E73" s="2" t="n"/>
+      <c r="D73" s="3" t="n"/>
+      <c r="E73" s="3" t="n"/>
     </row>
     <row r="74">
-      <c r="D74" s="2" t="n"/>
-      <c r="E74" s="2" t="n"/>
+      <c r="D74" s="3" t="n"/>
+      <c r="E74" s="3" t="n"/>
     </row>
     <row r="75">
-      <c r="D75" s="2" t="n"/>
-      <c r="E75" s="2" t="n"/>
+      <c r="D75" s="3" t="n"/>
+      <c r="E75" s="3" t="n"/>
     </row>
     <row r="76">
-      <c r="D76" s="2" t="n"/>
-      <c r="E76" s="2" t="n"/>
+      <c r="D76" s="3" t="n"/>
+      <c r="E76" s="3" t="n"/>
     </row>
     <row r="77">
-      <c r="D77" s="2" t="n"/>
-      <c r="E77" s="2" t="n"/>
+      <c r="D77" s="3" t="n"/>
+      <c r="E77" s="3" t="n"/>
     </row>
     <row r="78">
-      <c r="D78" s="2" t="n"/>
-      <c r="E78" s="2" t="n"/>
+      <c r="D78" s="3" t="n"/>
+      <c r="E78" s="3" t="n"/>
     </row>
     <row r="79">
-      <c r="D79" s="2" t="n"/>
-      <c r="E79" s="2" t="n"/>
+      <c r="D79" s="3" t="n"/>
+      <c r="E79" s="3" t="n"/>
     </row>
     <row r="80">
-      <c r="D80" s="2" t="n"/>
-      <c r="E80" s="2" t="n"/>
+      <c r="D80" s="3" t="n"/>
+      <c r="E80" s="3" t="n"/>
     </row>
     <row r="81">
-      <c r="D81" s="2" t="n"/>
-      <c r="E81" s="2" t="n"/>
+      <c r="D81" s="3" t="n"/>
+      <c r="E81" s="3" t="n"/>
     </row>
     <row r="82">
-      <c r="D82" s="2" t="n"/>
-      <c r="E82" s="2" t="n"/>
+      <c r="D82" s="3" t="n"/>
+      <c r="E82" s="3" t="n"/>
     </row>
     <row r="83">
-      <c r="D83" s="2" t="n"/>
-      <c r="E83" s="2" t="n"/>
+      <c r="D83" s="3" t="n"/>
+      <c r="E83" s="3" t="n"/>
     </row>
     <row r="84">
-      <c r="D84" s="2" t="n"/>
-      <c r="E84" s="2" t="n"/>
+      <c r="D84" s="3" t="n"/>
+      <c r="E84" s="3" t="n"/>
     </row>
     <row r="85">
-      <c r="D85" s="2" t="n"/>
-      <c r="E85" s="2" t="n"/>
+      <c r="D85" s="3" t="n"/>
+      <c r="E85" s="3" t="n"/>
     </row>
     <row r="86">
-      <c r="D86" s="2" t="n"/>
-      <c r="E86" s="2" t="n"/>
+      <c r="D86" s="3" t="n"/>
+      <c r="E86" s="3" t="n"/>
     </row>
     <row r="87">
-      <c r="D87" s="2" t="n"/>
-      <c r="E87" s="2" t="n"/>
+      <c r="D87" s="3" t="n"/>
+      <c r="E87" s="3" t="n"/>
     </row>
     <row r="88">
-      <c r="D88" s="2" t="n"/>
-      <c r="E88" s="2" t="n"/>
+      <c r="D88" s="3" t="n"/>
+      <c r="E88" s="3" t="n"/>
     </row>
     <row r="89">
-      <c r="D89" s="2" t="n"/>
-      <c r="E89" s="2" t="n"/>
+      <c r="D89" s="3" t="n"/>
+      <c r="E89" s="3" t="n"/>
     </row>
     <row r="90">
-      <c r="D90" s="2" t="n"/>
-      <c r="E90" s="2" t="n"/>
+      <c r="D90" s="3" t="n"/>
+      <c r="E90" s="3" t="n"/>
     </row>
     <row r="91">
-      <c r="D91" s="2" t="n"/>
-      <c r="E91" s="2" t="n"/>
+      <c r="D91" s="3" t="n"/>
+      <c r="E91" s="3" t="n"/>
     </row>
     <row r="92">
-      <c r="D92" s="2" t="n"/>
-      <c r="E92" s="2" t="n"/>
+      <c r="D92" s="3" t="n"/>
+      <c r="E92" s="3" t="n"/>
     </row>
     <row r="93">
-      <c r="D93" s="2" t="n"/>
-      <c r="E93" s="2" t="n"/>
+      <c r="D93" s="3" t="n"/>
+      <c r="E93" s="3" t="n"/>
     </row>
     <row r="94">
-      <c r="D94" s="2" t="n"/>
-      <c r="E94" s="2" t="n"/>
+      <c r="D94" s="3" t="n"/>
+      <c r="E94" s="3" t="n"/>
     </row>
     <row r="95">
-      <c r="D95" s="2" t="n"/>
-      <c r="E95" s="2" t="n"/>
+      <c r="D95" s="3" t="n"/>
+      <c r="E95" s="3" t="n"/>
     </row>
     <row r="96">
-      <c r="D96" s="2" t="n"/>
-      <c r="E96" s="2" t="n"/>
+      <c r="D96" s="3" t="n"/>
+      <c r="E96" s="3" t="n"/>
     </row>
     <row r="97">
-      <c r="D97" s="2" t="n"/>
-      <c r="E97" s="2" t="n"/>
+      <c r="D97" s="3" t="n"/>
+      <c r="E97" s="3" t="n"/>
     </row>
     <row r="98">
-      <c r="D98" s="2" t="n"/>
-      <c r="E98" s="2" t="n"/>
+      <c r="D98" s="3" t="n"/>
+      <c r="E98" s="3" t="n"/>
     </row>
     <row r="99">
-      <c r="D99" s="2" t="n"/>
-      <c r="E99" s="2" t="n"/>
+      <c r="D99" s="3" t="n"/>
+      <c r="E99" s="3" t="n"/>
     </row>
     <row r="100">
-      <c r="D100" s="2" t="n"/>
-      <c r="E100" s="2" t="n"/>
+      <c r="D100" s="3" t="n"/>
+      <c r="E100" s="3" t="n"/>
     </row>
     <row r="101">
-      <c r="D101" s="2" t="n"/>
-      <c r="E101" s="2" t="n"/>
+      <c r="D101" s="3" t="n"/>
+      <c r="E101" s="3" t="n"/>
     </row>
     <row r="102">
-      <c r="D102" s="2" t="n"/>
-      <c r="E102" s="2" t="n"/>
+      <c r="D102" s="3" t="n"/>
+      <c r="E102" s="3" t="n"/>
     </row>
     <row r="103">
-      <c r="D103" s="2" t="n"/>
-      <c r="E103" s="2" t="n"/>
+      <c r="D103" s="3" t="n"/>
+      <c r="E103" s="3" t="n"/>
     </row>
     <row r="104">
-      <c r="D104" s="2" t="n"/>
-      <c r="E104" s="2" t="n"/>
+      <c r="D104" s="3" t="n"/>
+      <c r="E104" s="3" t="n"/>
     </row>
     <row r="105">
-      <c r="D105" s="2" t="n"/>
-      <c r="E105" s="2" t="n"/>
+      <c r="D105" s="3" t="n"/>
+      <c r="E105" s="3" t="n"/>
     </row>
     <row r="106">
-      <c r="D106" s="2" t="n"/>
-      <c r="E106" s="2" t="n"/>
+      <c r="D106" s="3" t="n"/>
+      <c r="E106" s="3" t="n"/>
     </row>
     <row r="107">
-      <c r="D107" s="2" t="n"/>
-      <c r="E107" s="2" t="n"/>
+      <c r="D107" s="3" t="n"/>
+      <c r="E107" s="3" t="n"/>
     </row>
     <row r="108">
-      <c r="D108" s="2" t="n"/>
-      <c r="E108" s="2" t="n"/>
+      <c r="D108" s="3" t="n"/>
+      <c r="E108" s="3" t="n"/>
     </row>
     <row r="109">
-      <c r="D109" s="2" t="n"/>
-      <c r="E109" s="2" t="n"/>
+      <c r="D109" s="3" t="n"/>
+      <c r="E109" s="3" t="n"/>
     </row>
     <row r="110">
-      <c r="D110" s="2" t="n"/>
-      <c r="E110" s="2" t="n"/>
+      <c r="D110" s="3" t="n"/>
+      <c r="E110" s="3" t="n"/>
     </row>
     <row r="111">
-      <c r="D111" s="2" t="n"/>
-      <c r="E111" s="2" t="n"/>
+      <c r="D111" s="3" t="n"/>
+      <c r="E111" s="3" t="n"/>
     </row>
     <row r="112">
-      <c r="D112" s="2" t="n"/>
-      <c r="E112" s="2" t="n"/>
+      <c r="D112" s="3" t="n"/>
+      <c r="E112" s="3" t="n"/>
     </row>
     <row r="113">
-      <c r="D113" s="2" t="n"/>
-      <c r="E113" s="2" t="n"/>
+      <c r="D113" s="3" t="n"/>
+      <c r="E113" s="3" t="n"/>
     </row>
     <row r="114">
-      <c r="D114" s="2" t="n"/>
-      <c r="E114" s="2" t="n"/>
+      <c r="D114" s="3" t="n"/>
+      <c r="E114" s="3" t="n"/>
     </row>
     <row r="115">
-      <c r="D115" s="2" t="n"/>
-      <c r="E115" s="2" t="n"/>
+      <c r="D115" s="3" t="n"/>
+      <c r="E115" s="3" t="n"/>
     </row>
     <row r="116">
-      <c r="D116" s="2" t="n"/>
-      <c r="E116" s="2" t="n"/>
+      <c r="D116" s="3" t="n"/>
+      <c r="E116" s="3" t="n"/>
     </row>
     <row r="117">
-      <c r="D117" s="2" t="n"/>
-      <c r="E117" s="2" t="n"/>
+      <c r="D117" s="3" t="n"/>
+      <c r="E117" s="3" t="n"/>
     </row>
     <row r="118">
-      <c r="D118" s="2" t="n"/>
-      <c r="E118" s="2" t="n"/>
+      <c r="D118" s="3" t="n"/>
+      <c r="E118" s="3" t="n"/>
     </row>
     <row r="119">
-      <c r="D119" s="2" t="n"/>
-      <c r="E119" s="2" t="n"/>
+      <c r="D119" s="3" t="n"/>
+      <c r="E119" s="3" t="n"/>
     </row>
     <row r="120">
-      <c r="D120" s="2" t="n"/>
-      <c r="E120" s="2" t="n"/>
+      <c r="D120" s="3" t="n"/>
+      <c r="E120" s="3" t="n"/>
     </row>
     <row r="121">
-      <c r="D121" s="2" t="n"/>
-      <c r="E121" s="2" t="n"/>
+      <c r="D121" s="3" t="n"/>
+      <c r="E121" s="3" t="n"/>
     </row>
     <row r="122">
-      <c r="D122" s="2" t="n"/>
-      <c r="E122" s="2" t="n"/>
+      <c r="D122" s="3" t="n"/>
+      <c r="E122" s="3" t="n"/>
     </row>
     <row r="123">
-      <c r="D123" s="2" t="n"/>
-      <c r="E123" s="2" t="n"/>
+      <c r="D123" s="3" t="n"/>
+      <c r="E123" s="3" t="n"/>
     </row>
     <row r="124">
-      <c r="D124" s="2" t="n"/>
-      <c r="E124" s="2" t="n"/>
+      <c r="D124" s="3" t="n"/>
+      <c r="E124" s="3" t="n"/>
     </row>
     <row r="125">
-      <c r="D125" s="2" t="n"/>
-      <c r="E125" s="2" t="n"/>
+      <c r="D125" s="3" t="n"/>
+      <c r="E125" s="3" t="n"/>
     </row>
     <row r="126">
-      <c r="D126" s="2" t="n"/>
-      <c r="E126" s="2" t="n"/>
+      <c r="D126" s="3" t="n"/>
+      <c r="E126" s="3" t="n"/>
     </row>
     <row r="127">
-      <c r="D127" s="2" t="n"/>
-      <c r="E127" s="2" t="n"/>
+      <c r="D127" s="3" t="n"/>
+      <c r="E127" s="3" t="n"/>
     </row>
     <row r="128">
-      <c r="D128" s="2" t="n"/>
-      <c r="E128" s="2" t="n"/>
+      <c r="D128" s="3" t="n"/>
+      <c r="E128" s="3" t="n"/>
     </row>
     <row r="129">
-      <c r="D129" s="2" t="n"/>
-      <c r="E129" s="2" t="n"/>
+      <c r="D129" s="3" t="n"/>
+      <c r="E129" s="3" t="n"/>
     </row>
     <row r="130">
-      <c r="D130" s="2" t="n"/>
-      <c r="E130" s="2" t="n"/>
+      <c r="D130" s="3" t="n"/>
+      <c r="E130" s="3" t="n"/>
     </row>
     <row r="131">
-      <c r="D131" s="2" t="n"/>
-      <c r="E131" s="2" t="n"/>
+      <c r="D131" s="3" t="n"/>
+      <c r="E131" s="3" t="n"/>
     </row>
     <row r="132">
-      <c r="D132" s="2" t="n"/>
-      <c r="E132" s="2" t="n"/>
+      <c r="D132" s="3" t="n"/>
+      <c r="E132" s="3" t="n"/>
     </row>
     <row r="133">
-      <c r="D133" s="2" t="n"/>
-      <c r="E133" s="2" t="n"/>
+      <c r="D133" s="3" t="n"/>
+      <c r="E133" s="3" t="n"/>
     </row>
     <row r="134">
-      <c r="D134" s="2" t="n"/>
-      <c r="E134" s="2" t="n"/>
+      <c r="D134" s="3" t="n"/>
+      <c r="E134" s="3" t="n"/>
     </row>
     <row r="135">
-      <c r="D135" s="2" t="n"/>
-      <c r="E135" s="2" t="n"/>
+      <c r="D135" s="3" t="n"/>
+      <c r="E135" s="3" t="n"/>
     </row>
     <row r="136">
-      <c r="D136" s="2" t="n"/>
-      <c r="E136" s="2" t="n"/>
+      <c r="D136" s="3" t="n"/>
+      <c r="E136" s="3" t="n"/>
     </row>
     <row r="137">
-      <c r="D137" s="2" t="n"/>
-      <c r="E137" s="2" t="n"/>
+      <c r="D137" s="3" t="n"/>
+      <c r="E137" s="3" t="n"/>
     </row>
     <row r="138">
-      <c r="D138" s="2" t="n"/>
-      <c r="E138" s="2" t="n"/>
+      <c r="D138" s="3" t="n"/>
+      <c r="E138" s="3" t="n"/>
     </row>
     <row r="139">
-      <c r="D139" s="2" t="n"/>
-      <c r="E139" s="2" t="n"/>
+      <c r="D139" s="3" t="n"/>
+      <c r="E139" s="3" t="n"/>
     </row>
     <row r="140">
-      <c r="D140" s="2" t="n"/>
-      <c r="E140" s="2" t="n"/>
+      <c r="D140" s="3" t="n"/>
+      <c r="E140" s="3" t="n"/>
     </row>
     <row r="141">
-      <c r="D141" s="2" t="n"/>
-      <c r="E141" s="2" t="n"/>
+      <c r="D141" s="3" t="n"/>
+      <c r="E141" s="3" t="n"/>
     </row>
     <row r="142">
-      <c r="D142" s="2" t="n"/>
-      <c r="E142" s="2" t="n"/>
+      <c r="D142" s="3" t="n"/>
+      <c r="E142" s="3" t="n"/>
     </row>
     <row r="143">
-      <c r="D143" s="2" t="n"/>
-      <c r="E143" s="2" t="n"/>
+      <c r="D143" s="3" t="n"/>
+      <c r="E143" s="3" t="n"/>
     </row>
     <row r="144">
-      <c r="D144" s="2" t="n"/>
-      <c r="E144" s="2" t="n"/>
+      <c r="D144" s="3" t="n"/>
+      <c r="E144" s="3" t="n"/>
     </row>
     <row r="145">
-      <c r="D145" s="2" t="n"/>
-      <c r="E145" s="2" t="n"/>
+      <c r="D145" s="3" t="n"/>
+      <c r="E145" s="3" t="n"/>
     </row>
     <row r="146">
-      <c r="D146" s="2" t="n"/>
-      <c r="E146" s="2" t="n"/>
+      <c r="D146" s="3" t="n"/>
+      <c r="E146" s="3" t="n"/>
     </row>
     <row r="147">
-      <c r="D147" s="2" t="n"/>
-      <c r="E147" s="2" t="n"/>
+      <c r="D147" s="3" t="n"/>
+      <c r="E147" s="3" t="n"/>
     </row>
     <row r="148">
-      <c r="D148" s="2" t="n"/>
-      <c r="E148" s="2" t="n"/>
+      <c r="D148" s="3" t="n"/>
+      <c r="E148" s="3" t="n"/>
     </row>
     <row r="149">
-      <c r="D149" s="2" t="n"/>
-      <c r="E149" s="2" t="n"/>
+      <c r="D149" s="3" t="n"/>
+      <c r="E149" s="3" t="n"/>
     </row>
     <row r="150">
-      <c r="D150" s="2" t="n"/>
-      <c r="E150" s="2" t="n"/>
+      <c r="D150" s="3" t="n"/>
+      <c r="E150" s="3" t="n"/>
     </row>
     <row r="151">
-      <c r="D151" s="2" t="n"/>
-      <c r="E151" s="2" t="n"/>
+      <c r="D151" s="3" t="n"/>
+      <c r="E151" s="3" t="n"/>
     </row>
     <row r="152">
-      <c r="D152" s="2" t="n"/>
-      <c r="E152" s="2" t="n"/>
+      <c r="D152" s="3" t="n"/>
+      <c r="E152" s="3" t="n"/>
     </row>
     <row r="153">
-      <c r="D153" s="2" t="n"/>
-      <c r="E153" s="2" t="n"/>
+      <c r="D153" s="3" t="n"/>
+      <c r="E153" s="3" t="n"/>
     </row>
     <row r="154">
-      <c r="D154" s="2" t="n"/>
-      <c r="E154" s="2" t="n"/>
+      <c r="D154" s="3" t="n"/>
+      <c r="E154" s="3" t="n"/>
     </row>
     <row r="155">
-      <c r="D155" s="2" t="n"/>
-      <c r="E155" s="2" t="n"/>
+      <c r="D155" s="3" t="n"/>
+      <c r="E155" s="3" t="n"/>
     </row>
     <row r="156">
-      <c r="D156" s="2" t="n"/>
-      <c r="E156" s="2" t="n"/>
+      <c r="D156" s="3" t="n"/>
+      <c r="E156" s="3" t="n"/>
     </row>
     <row r="157">
-      <c r="D157" s="2" t="n"/>
-      <c r="E157" s="2" t="n"/>
+      <c r="D157" s="3" t="n"/>
+      <c r="E157" s="3" t="n"/>
     </row>
     <row r="158">
-      <c r="D158" s="2" t="n"/>
-      <c r="E158" s="2" t="n"/>
+      <c r="D158" s="3" t="n"/>
+      <c r="E158" s="3" t="n"/>
     </row>
     <row r="159">
-      <c r="D159" s="2" t="n"/>
-      <c r="E159" s="2" t="n"/>
+      <c r="D159" s="3" t="n"/>
+      <c r="E159" s="3" t="n"/>
     </row>
     <row r="160">
-      <c r="D160" s="2" t="n"/>
-      <c r="E160" s="2" t="n"/>
+      <c r="D160" s="3" t="n"/>
+      <c r="E160" s="3" t="n"/>
     </row>
     <row r="161">
-      <c r="D161" s="2" t="n"/>
-      <c r="E161" s="2" t="n"/>
+      <c r="D161" s="3" t="n"/>
+      <c r="E161" s="3" t="n"/>
     </row>
     <row r="162">
-      <c r="D162" s="2" t="n"/>
-      <c r="E162" s="2" t="n"/>
+      <c r="D162" s="3" t="n"/>
+      <c r="E162" s="3" t="n"/>
     </row>
     <row r="163">
-      <c r="D163" s="2" t="n"/>
-      <c r="E163" s="2" t="n"/>
+      <c r="D163" s="3" t="n"/>
+      <c r="E163" s="3" t="n"/>
     </row>
     <row r="164">
-      <c r="D164" s="2" t="n"/>
-      <c r="E164" s="2" t="n"/>
+      <c r="D164" s="3" t="n"/>
+      <c r="E164" s="3" t="n"/>
     </row>
     <row r="165">
-      <c r="D165" s="2" t="n"/>
-      <c r="E165" s="2" t="n"/>
+      <c r="D165" s="3" t="n"/>
+      <c r="E165" s="3" t="n"/>
     </row>
     <row r="166">
-      <c r="D166" s="2" t="n"/>
-      <c r="E166" s="2" t="n"/>
+      <c r="D166" s="3" t="n"/>
+      <c r="E166" s="3" t="n"/>
     </row>
     <row r="167">
-      <c r="D167" s="2" t="n"/>
-      <c r="E167" s="2" t="n"/>
+      <c r="D167" s="3" t="n"/>
+      <c r="E167" s="3" t="n"/>
     </row>
     <row r="168">
-      <c r="D168" s="2" t="n"/>
-      <c r="E168" s="2" t="n"/>
+      <c r="D168" s="3" t="n"/>
+      <c r="E168" s="3" t="n"/>
     </row>
     <row r="169">
-      <c r="D169" s="2" t="n"/>
-      <c r="E169" s="2" t="n"/>
+      <c r="D169" s="3" t="n"/>
+      <c r="E169" s="3" t="n"/>
     </row>
     <row r="170">
-      <c r="D170" s="2" t="n"/>
-      <c r="E170" s="2" t="n"/>
+      <c r="D170" s="3" t="n"/>
+      <c r="E170" s="3" t="n"/>
     </row>
     <row r="171">
-      <c r="D171" s="2" t="n"/>
-      <c r="E171" s="2" t="n"/>
+      <c r="D171" s="3" t="n"/>
+      <c r="E171" s="3" t="n"/>
     </row>
     <row r="172">
-      <c r="D172" s="2" t="n"/>
-      <c r="E172" s="2" t="n"/>
+      <c r="D172" s="3" t="n"/>
+      <c r="E172" s="3" t="n"/>
     </row>
     <row r="173">
-      <c r="D173" s="2" t="n"/>
-      <c r="E173" s="2" t="n"/>
+      <c r="D173" s="3" t="n"/>
+      <c r="E173" s="3" t="n"/>
     </row>
     <row r="174">
-      <c r="D174" s="2" t="n"/>
-      <c r="E174" s="2" t="n"/>
+      <c r="D174" s="3" t="n"/>
+      <c r="E174" s="3" t="n"/>
     </row>
     <row r="175">
-      <c r="D175" s="2" t="n"/>
-      <c r="E175" s="2" t="n"/>
+      <c r="D175" s="3" t="n"/>
+      <c r="E175" s="3" t="n"/>
     </row>
     <row r="176">
-      <c r="D176" s="2" t="n"/>
-      <c r="E176" s="2" t="n"/>
+      <c r="D176" s="3" t="n"/>
+      <c r="E176" s="3" t="n"/>
     </row>
     <row r="177">
-      <c r="D177" s="2" t="n"/>
-      <c r="E177" s="2" t="n"/>
+      <c r="D177" s="3" t="n"/>
+      <c r="E177" s="3" t="n"/>
     </row>
     <row r="178">
-      <c r="D178" s="2" t="n"/>
-      <c r="E178" s="2" t="n"/>
+      <c r="D178" s="3" t="n"/>
+      <c r="E178" s="3" t="n"/>
     </row>
     <row r="179">
-      <c r="D179" s="2" t="n"/>
-      <c r="E179" s="2" t="n"/>
+      <c r="D179" s="3" t="n"/>
+      <c r="E179" s="3" t="n"/>
     </row>
     <row r="180">
-      <c r="D180" s="2" t="n"/>
-      <c r="E180" s="2" t="n"/>
+      <c r="D180" s="3" t="n"/>
+      <c r="E180" s="3" t="n"/>
     </row>
     <row r="181">
-      <c r="D181" s="2" t="n"/>
-      <c r="E181" s="2" t="n"/>
+      <c r="D181" s="3" t="n"/>
+      <c r="E181" s="3" t="n"/>
     </row>
     <row r="182">
-      <c r="D182" s="2" t="n"/>
-      <c r="E182" s="2" t="n"/>
+      <c r="D182" s="3" t="n"/>
+      <c r="E182" s="3" t="n"/>
     </row>
     <row r="183">
-      <c r="D183" s="2" t="n"/>
-      <c r="E183" s="2" t="n"/>
+      <c r="D183" s="3" t="n"/>
+      <c r="E183" s="3" t="n"/>
     </row>
     <row r="184">
-      <c r="D184" s="2" t="n"/>
-      <c r="E184" s="2" t="n"/>
+      <c r="D184" s="3" t="n"/>
+      <c r="E184" s="3" t="n"/>
     </row>
     <row r="185">
-      <c r="D185" s="2" t="n"/>
-      <c r="E185" s="2" t="n"/>
+      <c r="D185" s="3" t="n"/>
+      <c r="E185" s="3" t="n"/>
     </row>
     <row r="186">
-      <c r="D186" s="2" t="n"/>
-      <c r="E186" s="2" t="n"/>
+      <c r="D186" s="3" t="n"/>
+      <c r="E186" s="3" t="n"/>
     </row>
     <row r="187">
-      <c r="D187" s="2" t="n"/>
-      <c r="E187" s="2" t="n"/>
+      <c r="D187" s="3" t="n"/>
+      <c r="E187" s="3" t="n"/>
     </row>
     <row r="188">
-      <c r="D188" s="2" t="n"/>
-      <c r="E188" s="2" t="n"/>
+      <c r="D188" s="3" t="n"/>
+      <c r="E188" s="3" t="n"/>
     </row>
     <row r="189">
-      <c r="D189" s="2" t="n"/>
-      <c r="E189" s="2" t="n"/>
+      <c r="D189" s="3" t="n"/>
+      <c r="E189" s="3" t="n"/>
     </row>
     <row r="190">
-      <c r="D190" s="2" t="n"/>
-      <c r="E190" s="2" t="n"/>
+      <c r="D190" s="3" t="n"/>
+      <c r="E190" s="3" t="n"/>
     </row>
     <row r="191">
-      <c r="D191" s="2" t="n"/>
-      <c r="E191" s="2" t="n"/>
+      <c r="D191" s="3" t="n"/>
+      <c r="E191" s="3" t="n"/>
     </row>
     <row r="192">
-      <c r="D192" s="2" t="n"/>
-      <c r="E192" s="2" t="n"/>
+      <c r="D192" s="3" t="n"/>
+      <c r="E192" s="3" t="n"/>
     </row>
     <row r="193">
-      <c r="D193" s="2" t="n"/>
-      <c r="E193" s="2" t="n"/>
+      <c r="D193" s="3" t="n"/>
+      <c r="E193" s="3" t="n"/>
     </row>
     <row r="194">
-      <c r="D194" s="2" t="n"/>
-      <c r="E194" s="2" t="n"/>
+      <c r="D194" s="3" t="n"/>
+      <c r="E194" s="3" t="n"/>
     </row>
     <row r="195">
-      <c r="D195" s="2" t="n"/>
-      <c r="E195" s="2" t="n"/>
+      <c r="D195" s="3" t="n"/>
+      <c r="E195" s="3" t="n"/>
     </row>
     <row r="196">
-      <c r="D196" s="2" t="n"/>
-      <c r="E196" s="2" t="n"/>
+      <c r="D196" s="3" t="n"/>
+      <c r="E196" s="3" t="n"/>
     </row>
     <row r="197">
-      <c r="D197" s="2" t="n"/>
-      <c r="E197" s="2" t="n"/>
+      <c r="D197" s="3" t="n"/>
+      <c r="E197" s="3" t="n"/>
     </row>
     <row r="198">
-      <c r="D198" s="2" t="n"/>
-      <c r="E198" s="2" t="n"/>
+      <c r="D198" s="3" t="n"/>
+      <c r="E198" s="3" t="n"/>
     </row>
     <row r="199">
-      <c r="D199" s="2" t="n"/>
-      <c r="E199" s="2" t="n"/>
+      <c r="D199" s="3" t="n"/>
+      <c r="E199" s="3" t="n"/>
     </row>
     <row r="200">
-      <c r="D200" s="2" t="n"/>
-      <c r="E200" s="2" t="n"/>
+      <c r="D200" s="3" t="n"/>
+      <c r="E200" s="3" t="n"/>
     </row>
     <row r="201">
-      <c r="D201" s="2" t="n"/>
-      <c r="E201" s="2" t="n"/>
+      <c r="D201" s="3" t="n"/>
+      <c r="E201" s="3" t="n"/>
     </row>
     <row r="202">
-      <c r="D202" s="2" t="n"/>
-      <c r="E202" s="2" t="n"/>
+      <c r="D202" s="3" t="n"/>
+      <c r="E202" s="3" t="n"/>
     </row>
     <row r="203">
-      <c r="D203" s="2" t="n"/>
-      <c r="E203" s="2" t="n"/>
+      <c r="D203" s="3" t="n"/>
+      <c r="E203" s="3" t="n"/>
     </row>
     <row r="204">
-      <c r="D204" s="2" t="n"/>
-      <c r="E204" s="2" t="n"/>
+      <c r="D204" s="3" t="n"/>
+      <c r="E204" s="3" t="n"/>
     </row>
     <row r="205">
-      <c r="D205" s="2" t="n"/>
-      <c r="E205" s="2" t="n"/>
+      <c r="D205" s="3" t="n"/>
+      <c r="E205" s="3" t="n"/>
     </row>
     <row r="206">
-      <c r="D206" s="2" t="n"/>
-      <c r="E206" s="2" t="n"/>
+      <c r="D206" s="3" t="n"/>
+      <c r="E206" s="3" t="n"/>
     </row>
     <row r="207">
-      <c r="D207" s="2" t="n"/>
-      <c r="E207" s="2" t="n"/>
+      <c r="D207" s="3" t="n"/>
+      <c r="E207" s="3" t="n"/>
     </row>
     <row r="208">
-      <c r="D208" s="2" t="n"/>
-      <c r="E208" s="2" t="n"/>
+      <c r="D208" s="3" t="n"/>
+      <c r="E208" s="3" t="n"/>
     </row>
     <row r="209">
-      <c r="D209" s="2" t="n"/>
-      <c r="E209" s="2" t="n"/>
+      <c r="D209" s="3" t="n"/>
+      <c r="E209" s="3" t="n"/>
     </row>
     <row r="210">
-      <c r="D210" s="2" t="n"/>
-      <c r="E210" s="2" t="n"/>
+      <c r="D210" s="3" t="n"/>
+      <c r="E210" s="3" t="n"/>
     </row>
     <row r="211">
-      <c r="D211" s="2" t="n"/>
-      <c r="E211" s="2" t="n"/>
+      <c r="D211" s="3" t="n"/>
+      <c r="E211" s="3" t="n"/>
     </row>
     <row r="212">
-      <c r="D212" s="2" t="n"/>
-      <c r="E212" s="2" t="n"/>
+      <c r="D212" s="3" t="n"/>
+      <c r="E212" s="3" t="n"/>
     </row>
     <row r="213">
-      <c r="D213" s="2" t="n"/>
-      <c r="E213" s="2" t="n"/>
+      <c r="D213" s="3" t="n"/>
+      <c r="E213" s="3" t="n"/>
     </row>
     <row r="214">
-      <c r="D214" s="2" t="n"/>
-      <c r="E214" s="2" t="n"/>
+      <c r="D214" s="3" t="n"/>
+      <c r="E214" s="3" t="n"/>
     </row>
     <row r="215">
-      <c r="D215" s="2" t="n"/>
-      <c r="E215" s="2" t="n"/>
+      <c r="D215" s="3" t="n"/>
+      <c r="E215" s="3" t="n"/>
     </row>
     <row r="216">
-      <c r="D216" s="2" t="n"/>
-      <c r="E216" s="2" t="n"/>
+      <c r="D216" s="3" t="n"/>
+      <c r="E216" s="3" t="n"/>
     </row>
     <row r="217">
-      <c r="D217" s="2" t="n"/>
-      <c r="E217" s="2" t="n"/>
+      <c r="D217" s="3" t="n"/>
+      <c r="E217" s="3" t="n"/>
     </row>
     <row r="218">
-      <c r="D218" s="2" t="n"/>
-      <c r="E218" s="2" t="n"/>
+      <c r="D218" s="3" t="n"/>
+      <c r="E218" s="3" t="n"/>
     </row>
     <row r="219">
-      <c r="D219" s="2" t="n"/>
-      <c r="E219" s="2" t="n"/>
+      <c r="D219" s="3" t="n"/>
+      <c r="E219" s="3" t="n"/>
     </row>
     <row r="220">
-      <c r="D220" s="2" t="n"/>
-      <c r="E220" s="2" t="n"/>
+      <c r="D220" s="3" t="n"/>
+      <c r="E220" s="3" t="n"/>
     </row>
     <row r="221">
-      <c r="D221" s="2" t="n"/>
-      <c r="E221" s="2" t="n"/>
+      <c r="D221" s="3" t="n"/>
+      <c r="E221" s="3" t="n"/>
     </row>
     <row r="222">
-      <c r="D222" s="2" t="n"/>
-      <c r="E222" s="2" t="n"/>
+      <c r="D222" s="3" t="n"/>
+      <c r="E222" s="3" t="n"/>
     </row>
     <row r="223">
-      <c r="D223" s="2" t="n"/>
-      <c r="E223" s="2" t="n"/>
+      <c r="D223" s="3" t="n"/>
+      <c r="E223" s="3" t="n"/>
     </row>
     <row r="224">
-      <c r="D224" s="2" t="n"/>
-      <c r="E224" s="2" t="n"/>
+      <c r="D224" s="3" t="n"/>
+      <c r="E224" s="3" t="n"/>
     </row>
     <row r="225">
-      <c r="D225" s="2" t="n"/>
-      <c r="E225" s="2" t="n"/>
+      <c r="D225" s="3" t="n"/>
+      <c r="E225" s="3" t="n"/>
     </row>
     <row r="226">
-      <c r="D226" s="2" t="n"/>
-      <c r="E226" s="2" t="n"/>
+      <c r="D226" s="3" t="n"/>
+      <c r="E226" s="3" t="n"/>
     </row>
     <row r="227">
-      <c r="D227" s="2" t="n"/>
-      <c r="E227" s="2" t="n"/>
+      <c r="D227" s="3" t="n"/>
+      <c r="E227" s="3" t="n"/>
     </row>
     <row r="228">
-      <c r="D228" s="2" t="n"/>
-      <c r="E228" s="2" t="n"/>
+      <c r="D228" s="3" t="n"/>
+      <c r="E228" s="3" t="n"/>
     </row>
     <row r="229">
-      <c r="D229" s="2" t="n"/>
-      <c r="E229" s="2" t="n"/>
+      <c r="D229" s="3" t="n"/>
+      <c r="E229" s="3" t="n"/>
     </row>
     <row r="230">
-      <c r="D230" s="2" t="n"/>
-      <c r="E230" s="2" t="n"/>
+      <c r="D230" s="3" t="n"/>
+      <c r="E230" s="3" t="n"/>
     </row>
     <row r="231">
-      <c r="D231" s="2" t="n"/>
-      <c r="E231" s="2" t="n"/>
+      <c r="D231" s="3" t="n"/>
+      <c r="E231" s="3" t="n"/>
     </row>
     <row r="232">
-      <c r="D232" s="2" t="n"/>
-      <c r="E232" s="2" t="n"/>
+      <c r="D232" s="3" t="n"/>
+      <c r="E232" s="3" t="n"/>
     </row>
     <row r="233">
-      <c r="D233" s="2" t="n"/>
-      <c r="E233" s="2" t="n"/>
+      <c r="D233" s="3" t="n"/>
+      <c r="E233" s="3" t="n"/>
     </row>
     <row r="234">
-      <c r="D234" s="2" t="n"/>
-      <c r="E234" s="2" t="n"/>
+      <c r="D234" s="3" t="n"/>
+      <c r="E234" s="3" t="n"/>
     </row>
     <row r="235">
-      <c r="D235" s="2" t="n"/>
-      <c r="E235" s="2" t="n"/>
+      <c r="D235" s="3" t="n"/>
+      <c r="E235" s="3" t="n"/>
     </row>
     <row r="236">
-      <c r="D236" s="2" t="n"/>
-      <c r="E236" s="2" t="n"/>
+      <c r="D236" s="3" t="n"/>
+      <c r="E236" s="3" t="n"/>
     </row>
     <row r="237">
-      <c r="D237" s="2" t="n"/>
-      <c r="E237" s="2" t="n"/>
+      <c r="D237" s="3" t="n"/>
+      <c r="E237" s="3" t="n"/>
     </row>
     <row r="238">
-      <c r="D238" s="2" t="n"/>
-      <c r="E238" s="2" t="n"/>
+      <c r="D238" s="3" t="n"/>
+      <c r="E238" s="3" t="n"/>
     </row>
     <row r="239">
-      <c r="D239" s="2" t="n"/>
-      <c r="E239" s="2" t="n"/>
+      <c r="D239" s="3" t="n"/>
+      <c r="E239" s="3" t="n"/>
     </row>
     <row r="240">
-      <c r="D240" s="2" t="n"/>
-      <c r="E240" s="2" t="n"/>
+      <c r="D240" s="3" t="n"/>
+      <c r="E240" s="3" t="n"/>
     </row>
     <row r="241">
-      <c r="D241" s="2" t="n"/>
-      <c r="E241" s="2" t="n"/>
+      <c r="D241" s="3" t="n"/>
+      <c r="E241" s="3" t="n"/>
     </row>
     <row r="242">
-      <c r="D242" s="2" t="n"/>
-      <c r="E242" s="2" t="n"/>
+      <c r="D242" s="3" t="n"/>
+      <c r="E242" s="3" t="n"/>
     </row>
     <row r="243">
-      <c r="D243" s="2" t="n"/>
-      <c r="E243" s="2" t="n"/>
+      <c r="D243" s="3" t="n"/>
+      <c r="E243" s="3" t="n"/>
     </row>
     <row r="244">
-      <c r="D244" s="2" t="n"/>
-      <c r="E244" s="2" t="n"/>
+      <c r="D244" s="3" t="n"/>
+      <c r="E244" s="3" t="n"/>
     </row>
     <row r="245">
-      <c r="D245" s="2" t="n"/>
-      <c r="E245" s="2" t="n"/>
+      <c r="D245" s="3" t="n"/>
+      <c r="E245" s="3" t="n"/>
     </row>
     <row r="246">
-      <c r="D246" s="2" t="n"/>
-      <c r="E246" s="2" t="n"/>
+      <c r="D246" s="3" t="n"/>
+      <c r="E246" s="3" t="n"/>
     </row>
     <row r="247">
-      <c r="D247" s="2" t="n"/>
-      <c r="E247" s="2" t="n"/>
+      <c r="D247" s="3" t="n"/>
+      <c r="E247" s="3" t="n"/>
     </row>
     <row r="248">
-      <c r="D248" s="2" t="n"/>
-      <c r="E248" s="2" t="n"/>
+      <c r="D248" s="3" t="n"/>
+      <c r="E248" s="3" t="n"/>
     </row>
     <row r="249">
-      <c r="D249" s="2" t="n"/>
-      <c r="E249" s="2" t="n"/>
+      <c r="D249" s="3" t="n"/>
+      <c r="E249" s="3" t="n"/>
     </row>
     <row r="250">
-      <c r="D250" s="2" t="n"/>
-      <c r="E250" s="2" t="n"/>
+      <c r="D250" s="3" t="n"/>
+      <c r="E250" s="3" t="n"/>
     </row>
     <row r="251">
-      <c r="D251" s="2" t="n"/>
-      <c r="E251" s="2" t="n"/>
+      <c r="D251" s="3" t="n"/>
+      <c r="E251" s="3" t="n"/>
     </row>
     <row r="252">
-      <c r="D252" s="2" t="n"/>
-      <c r="E252" s="2" t="n"/>
+      <c r="D252" s="3" t="n"/>
+      <c r="E252" s="3" t="n"/>
     </row>
     <row r="253">
-      <c r="D253" s="2" t="n"/>
-      <c r="E253" s="2" t="n"/>
+      <c r="D253" s="3" t="n"/>
+      <c r="E253" s="3" t="n"/>
     </row>
     <row r="254">
-      <c r="D254" s="2" t="n"/>
-      <c r="E254" s="2" t="n"/>
+      <c r="D254" s="3" t="n"/>
+      <c r="E254" s="3" t="n"/>
     </row>
     <row r="255">
-      <c r="D255" s="2" t="n"/>
-      <c r="E255" s="2" t="n"/>
+      <c r="D255" s="3" t="n"/>
+      <c r="E255" s="3" t="n"/>
     </row>
     <row r="256">
-      <c r="D256" s="2" t="n"/>
-      <c r="E256" s="2" t="n"/>
+      <c r="D256" s="3" t="n"/>
+      <c r="E256" s="3" t="n"/>
     </row>
     <row r="257">
-      <c r="D257" s="2" t="n"/>
-      <c r="E257" s="2" t="n"/>
+      <c r="D257" s="3" t="n"/>
+      <c r="E257" s="3" t="n"/>
     </row>
     <row r="258">
-      <c r="D258" s="2" t="n"/>
-      <c r="E258" s="2" t="n"/>
+      <c r="D258" s="3" t="n"/>
+      <c r="E258" s="3" t="n"/>
     </row>
     <row r="259">
-      <c r="D259" s="2" t="n"/>
-      <c r="E259" s="2" t="n"/>
+      <c r="D259" s="3" t="n"/>
+      <c r="E259" s="3" t="n"/>
     </row>
     <row r="260">
-      <c r="D260" s="2" t="n"/>
-      <c r="E260" s="2" t="n"/>
+      <c r="D260" s="3" t="n"/>
+      <c r="E260" s="3" t="n"/>
     </row>
     <row r="261">
-      <c r="D261" s="2" t="n"/>
-      <c r="E261" s="2" t="n"/>
+      <c r="D261" s="3" t="n"/>
+      <c r="E261" s="3" t="n"/>
     </row>
     <row r="262">
-      <c r="D262" s="2" t="n"/>
-      <c r="E262" s="2" t="n"/>
+      <c r="D262" s="3" t="n"/>
+      <c r="E262" s="3" t="n"/>
     </row>
     <row r="263">
-      <c r="D263" s="2" t="n"/>
-      <c r="E263" s="2" t="n"/>
+      <c r="D263" s="3" t="n"/>
+      <c r="E263" s="3" t="n"/>
     </row>
     <row r="264">
-      <c r="D264" s="2" t="n"/>
-      <c r="E264" s="2" t="n"/>
+      <c r="D264" s="3" t="n"/>
+      <c r="E264" s="3" t="n"/>
     </row>
     <row r="265">
-      <c r="D265" s="2" t="n"/>
-      <c r="E265" s="2" t="n"/>
+      <c r="D265" s="3" t="n"/>
+      <c r="E265" s="3" t="n"/>
     </row>
     <row r="266">
-      <c r="D266" s="2" t="n"/>
-      <c r="E266" s="2" t="n"/>
+      <c r="D266" s="3" t="n"/>
+      <c r="E266" s="3" t="n"/>
     </row>
     <row r="267">
-      <c r="D267" s="2" t="n"/>
-      <c r="E267" s="2" t="n"/>
+      <c r="D267" s="3" t="n"/>
+      <c r="E267" s="3" t="n"/>
     </row>
     <row r="268">
-      <c r="D268" s="2" t="n"/>
-      <c r="E268" s="2" t="n"/>
+      <c r="D268" s="3" t="n"/>
+      <c r="E268" s="3" t="n"/>
     </row>
     <row r="269">
-      <c r="D269" s="2" t="n"/>
-      <c r="E269" s="2" t="n"/>
+      <c r="D269" s="3" t="n"/>
+      <c r="E269" s="3" t="n"/>
     </row>
     <row r="270">
-      <c r="D270" s="2" t="n"/>
-      <c r="E270" s="2" t="n"/>
+      <c r="D270" s="3" t="n"/>
+      <c r="E270" s="3" t="n"/>
     </row>
     <row r="271">
-      <c r="D271" s="2" t="n"/>
-      <c r="E271" s="2" t="n"/>
+      <c r="D271" s="3" t="n"/>
+      <c r="E271" s="3" t="n"/>
     </row>
     <row r="272">
-      <c r="D272" s="2" t="n"/>
-      <c r="E272" s="2" t="n"/>
+      <c r="D272" s="3" t="n"/>
+      <c r="E272" s="3" t="n"/>
     </row>
     <row r="273">
-      <c r="D273" s="2" t="n"/>
-      <c r="E273" s="2" t="n"/>
+      <c r="D273" s="3" t="n"/>
+      <c r="E273" s="3" t="n"/>
     </row>
     <row r="274">
-      <c r="D274" s="2" t="n"/>
-      <c r="E274" s="2" t="n"/>
+      <c r="D274" s="3" t="n"/>
+      <c r="E274" s="3" t="n"/>
     </row>
     <row r="275">
-      <c r="D275" s="2" t="n"/>
-      <c r="E275" s="2" t="n"/>
+      <c r="D275" s="3" t="n"/>
+      <c r="E275" s="3" t="n"/>
     </row>
     <row r="276">
-      <c r="D276" s="2" t="n"/>
-      <c r="E276" s="2" t="n"/>
+      <c r="D276" s="3" t="n"/>
+      <c r="E276" s="3" t="n"/>
     </row>
     <row r="277">
-      <c r="D277" s="2" t="n"/>
-      <c r="E277" s="2" t="n"/>
+      <c r="D277" s="3" t="n"/>
+      <c r="E277" s="3" t="n"/>
     </row>
     <row r="278">
-      <c r="D278" s="2" t="n"/>
-      <c r="E278" s="2" t="n"/>
+      <c r="D278" s="3" t="n"/>
+      <c r="E278" s="3" t="n"/>
     </row>
     <row r="279">
-      <c r="D279" s="2" t="n"/>
-      <c r="E279" s="2" t="n"/>
+      <c r="D279" s="3" t="n"/>
+      <c r="E279" s="3" t="n"/>
     </row>
     <row r="280">
-      <c r="D280" s="2" t="n"/>
-      <c r="E280" s="2" t="n"/>
+      <c r="D280" s="3" t="n"/>
+      <c r="E280" s="3" t="n"/>
     </row>
     <row r="281">
-      <c r="D281" s="2" t="n"/>
-      <c r="E281" s="2" t="n"/>
+      <c r="D281" s="3" t="n"/>
+      <c r="E281" s="3" t="n"/>
     </row>
     <row r="282">
-      <c r="D282" s="2" t="n"/>
-      <c r="E282" s="2" t="n"/>
+      <c r="D282" s="3" t="n"/>
+      <c r="E282" s="3" t="n"/>
     </row>
     <row r="283">
-      <c r="D283" s="2" t="n"/>
-      <c r="E283" s="2" t="n"/>
+      <c r="D283" s="3" t="n"/>
+      <c r="E283" s="3" t="n"/>
     </row>
     <row r="284">
-      <c r="D284" s="2" t="n"/>
-      <c r="E284" s="2" t="n"/>
+      <c r="D284" s="3" t="n"/>
+      <c r="E284" s="3" t="n"/>
     </row>
     <row r="285">
-      <c r="D285" s="2" t="n"/>
-      <c r="E285" s="2" t="n"/>
+      <c r="D285" s="3" t="n"/>
+      <c r="E285" s="3" t="n"/>
     </row>
     <row r="286">
-      <c r="D286" s="2" t="n"/>
-      <c r="E286" s="2" t="n"/>
+      <c r="D286" s="3" t="n"/>
+      <c r="E286" s="3" t="n"/>
     </row>
     <row r="287">
-      <c r="D287" s="2" t="n"/>
-      <c r="E287" s="2" t="n"/>
+      <c r="D287" s="3" t="n"/>
+      <c r="E287" s="3" t="n"/>
     </row>
     <row r="288">
-      <c r="D288" s="2" t="n"/>
-      <c r="E288" s="2" t="n"/>
+      <c r="D288" s="3" t="n"/>
+      <c r="E288" s="3" t="n"/>
     </row>
     <row r="289">
-      <c r="D289" s="2" t="n"/>
-      <c r="E289" s="2" t="n"/>
+      <c r="D289" s="3" t="n"/>
+      <c r="E289" s="3" t="n"/>
     </row>
     <row r="290">
-      <c r="D290" s="2" t="n"/>
-      <c r="E290" s="2" t="n"/>
+      <c r="D290" s="3" t="n"/>
+      <c r="E290" s="3" t="n"/>
     </row>
     <row r="291">
-      <c r="D291" s="2" t="n"/>
-      <c r="E291" s="2" t="n"/>
+      <c r="D291" s="3" t="n"/>
+      <c r="E291" s="3" t="n"/>
     </row>
     <row r="292">
-      <c r="D292" s="2" t="n"/>
-      <c r="E292" s="2" t="n"/>
+      <c r="D292" s="3" t="n"/>
+      <c r="E292" s="3" t="n"/>
     </row>
     <row r="293">
-      <c r="D293" s="2" t="n"/>
-      <c r="E293" s="2" t="n"/>
+      <c r="D293" s="3" t="n"/>
+      <c r="E293" s="3" t="n"/>
     </row>
     <row r="294">
-      <c r="D294" s="2" t="n"/>
-      <c r="E294" s="2" t="n"/>
+      <c r="D294" s="3" t="n"/>
+      <c r="E294" s="3" t="n"/>
     </row>
     <row r="295">
-      <c r="D295" s="2" t="n"/>
-      <c r="E295" s="2" t="n"/>
+      <c r="D295" s="3" t="n"/>
+      <c r="E295" s="3" t="n"/>
     </row>
     <row r="296">
-      <c r="D296" s="2" t="n"/>
-      <c r="E296" s="2" t="n"/>
+      <c r="D296" s="3" t="n"/>
+      <c r="E296" s="3" t="n"/>
     </row>
     <row r="297">
-      <c r="D297" s="2" t="n"/>
-      <c r="E297" s="2" t="n"/>
+      <c r="D297" s="3" t="n"/>
+      <c r="E297" s="3" t="n"/>
     </row>
     <row r="298">
-      <c r="D298" s="2" t="n"/>
-      <c r="E298" s="2" t="n"/>
+      <c r="D298" s="3" t="n"/>
+      <c r="E298" s="3" t="n"/>
     </row>
     <row r="299">
-      <c r="D299" s="2" t="n"/>
-      <c r="E299" s="2" t="n"/>
+      <c r="D299" s="3" t="n"/>
+      <c r="E299" s="3" t="n"/>
     </row>
     <row r="300">
-      <c r="D300" s="2" t="n"/>
-      <c r="E300" s="2" t="n"/>
+      <c r="D300" s="3" t="n"/>
+      <c r="E300" s="3" t="n"/>
     </row>
     <row r="301">
-      <c r="D301" s="2" t="n"/>
-      <c r="E301" s="2" t="n"/>
+      <c r="D301" s="3" t="n"/>
+      <c r="E301" s="3" t="n"/>
     </row>
     <row r="302">
-      <c r="D302" s="2" t="n"/>
-      <c r="E302" s="2" t="n"/>
+      <c r="D302" s="3" t="n"/>
+      <c r="E302" s="3" t="n"/>
     </row>
     <row r="303">
-      <c r="D303" s="2" t="n"/>
-      <c r="E303" s="2" t="n"/>
+      <c r="D303" s="3" t="n"/>
+      <c r="E303" s="3" t="n"/>
     </row>
     <row r="304">
-      <c r="D304" s="2" t="n"/>
-      <c r="E304" s="2" t="n"/>
+      <c r="D304" s="3" t="n"/>
+      <c r="E304" s="3" t="n"/>
     </row>
     <row r="305">
-      <c r="D305" s="2" t="n"/>
-      <c r="E305" s="2" t="n"/>
+      <c r="D305" s="3" t="n"/>
+      <c r="E305" s="3" t="n"/>
     </row>
     <row r="306">
-      <c r="D306" s="2" t="n"/>
-      <c r="E306" s="2" t="n"/>
+      <c r="D306" s="3" t="n"/>
+      <c r="E306" s="3" t="n"/>
     </row>
     <row r="307">
-      <c r="D307" s="2" t="n"/>
-      <c r="E307" s="2" t="n"/>
+      <c r="D307" s="3" t="n"/>
+      <c r="E307" s="3" t="n"/>
     </row>
     <row r="308">
-      <c r="D308" s="2" t="n"/>
-      <c r="E308" s="2" t="n"/>
+      <c r="D308" s="3" t="n"/>
+      <c r="E308" s="3" t="n"/>
     </row>
     <row r="309">
-      <c r="D309" s="2" t="n"/>
-      <c r="E309" s="2" t="n"/>
+      <c r="D309" s="3" t="n"/>
+      <c r="E309" s="3" t="n"/>
     </row>
     <row r="310">
-      <c r="D310" s="2" t="n"/>
-      <c r="E310" s="2" t="n"/>
+      <c r="D310" s="3" t="n"/>
+      <c r="E310" s="3" t="n"/>
     </row>
     <row r="311">
-      <c r="D311" s="2" t="n"/>
-      <c r="E311" s="2" t="n"/>
+      <c r="D311" s="3" t="n"/>
+      <c r="E311" s="3" t="n"/>
     </row>
     <row r="312">
-      <c r="D312" s="2" t="n"/>
-      <c r="E312" s="2" t="n"/>
+      <c r="D312" s="3" t="n"/>
+      <c r="E312" s="3" t="n"/>
     </row>
     <row r="313">
-      <c r="D313" s="2" t="n"/>
-      <c r="E313" s="2" t="n"/>
+      <c r="D313" s="3" t="n"/>
+      <c r="E313" s="3" t="n"/>
     </row>
     <row r="314">
-      <c r="D314" s="2" t="n"/>
-      <c r="E314" s="2" t="n"/>
+      <c r="D314" s="3" t="n"/>
+      <c r="E314" s="3" t="n"/>
     </row>
     <row r="315">
-      <c r="D315" s="2" t="n"/>
-      <c r="E315" s="2" t="n"/>
+      <c r="D315" s="3" t="n"/>
+      <c r="E315" s="3" t="n"/>
     </row>
     <row r="316">
-      <c r="D316" s="2" t="n"/>
-      <c r="E316" s="2" t="n"/>
+      <c r="D316" s="3" t="n"/>
+      <c r="E316" s="3" t="n"/>
     </row>
     <row r="317">
-      <c r="D317" s="2" t="n"/>
-      <c r="E317" s="2" t="n"/>
+      <c r="D317" s="3" t="n"/>
+      <c r="E317" s="3" t="n"/>
     </row>
     <row r="318">
-      <c r="D318" s="2" t="n"/>
-      <c r="E318" s="2" t="n"/>
+      <c r="D318" s="3" t="n"/>
+      <c r="E318" s="3" t="n"/>
     </row>
     <row r="319">
-      <c r="D319" s="2" t="n"/>
-      <c r="E319" s="2" t="n"/>
+      <c r="D319" s="3" t="n"/>
+      <c r="E319" s="3" t="n"/>
     </row>
     <row r="320">
-      <c r="D320" s="2" t="n"/>
-      <c r="E320" s="2" t="n"/>
+      <c r="D320" s="3" t="n"/>
+      <c r="E320" s="3" t="n"/>
     </row>
     <row r="321">
-      <c r="D321" s="2" t="n"/>
-      <c r="E321" s="2" t="n"/>
+      <c r="D321" s="3" t="n"/>
+      <c r="E321" s="3" t="n"/>
     </row>
     <row r="322">
-      <c r="D322" s="2" t="n"/>
-      <c r="E322" s="2" t="n"/>
+      <c r="D322" s="3" t="n"/>
+      <c r="E322" s="3" t="n"/>
     </row>
     <row r="323">
-      <c r="D323" s="2" t="n"/>
-      <c r="E323" s="2" t="n"/>
+      <c r="D323" s="3" t="n"/>
+      <c r="E323" s="3" t="n"/>
     </row>
     <row r="324">
-      <c r="D324" s="2" t="n"/>
-      <c r="E324" s="2" t="n"/>
+      <c r="D324" s="3" t="n"/>
+      <c r="E324" s="3" t="n"/>
     </row>
     <row r="325">
-      <c r="D325" s="2" t="n"/>
-      <c r="E325" s="2" t="n"/>
+      <c r="D325" s="3" t="n"/>
+      <c r="E325" s="3" t="n"/>
     </row>
     <row r="326">
-      <c r="D326" s="2" t="n"/>
-      <c r="E326" s="2" t="n"/>
+      <c r="D326" s="3" t="n"/>
+      <c r="E326" s="3" t="n"/>
     </row>
     <row r="327">
-      <c r="D327" s="2" t="n"/>
-      <c r="E327" s="2" t="n"/>
+      <c r="D327" s="3" t="n"/>
+      <c r="E327" s="3" t="n"/>
     </row>
     <row r="328">
-      <c r="D328" s="2" t="n"/>
-      <c r="E328" s="2" t="n"/>
+      <c r="D328" s="3" t="n"/>
+      <c r="E328" s="3" t="n"/>
     </row>
     <row r="329">
-      <c r="D329" s="2" t="n"/>
-      <c r="E329" s="2" t="n"/>
+      <c r="D329" s="3" t="n"/>
+      <c r="E329" s="3" t="n"/>
     </row>
     <row r="330">
-      <c r="D330" s="2" t="n"/>
-      <c r="E330" s="2" t="n"/>
+      <c r="D330" s="3" t="n"/>
+      <c r="E330" s="3" t="n"/>
     </row>
     <row r="331">
-      <c r="D331" s="2" t="n"/>
-      <c r="E331" s="2" t="n"/>
+      <c r="D331" s="3" t="n"/>
+      <c r="E331" s="3" t="n"/>
     </row>
     <row r="332">
-      <c r="D332" s="2" t="n"/>
-      <c r="E332" s="2" t="n"/>
+      <c r="D332" s="3" t="n"/>
+      <c r="E332" s="3" t="n"/>
     </row>
     <row r="333">
-      <c r="D333" s="2" t="n"/>
-      <c r="E333" s="2" t="n"/>
+      <c r="D333" s="3" t="n"/>
+      <c r="E333" s="3" t="n"/>
     </row>
     <row r="334">
-      <c r="D334" s="2" t="n"/>
-      <c r="E334" s="2" t="n"/>
+      <c r="D334" s="3" t="n"/>
+      <c r="E334" s="3" t="n"/>
     </row>
     <row r="335">
-      <c r="D335" s="2" t="n"/>
-      <c r="E335" s="2" t="n"/>
+      <c r="D335" s="3" t="n"/>
+      <c r="E335" s="3" t="n"/>
     </row>
     <row r="336">
-      <c r="D336" s="2" t="n"/>
-      <c r="E336" s="2" t="n"/>
+      <c r="D336" s="3" t="n"/>
+      <c r="E336" s="3" t="n"/>
     </row>
     <row r="337">
-      <c r="D337" s="2" t="n"/>
-      <c r="E337" s="2" t="n"/>
+      <c r="D337" s="3" t="n"/>
+      <c r="E337" s="3" t="n"/>
     </row>
     <row r="338">
-      <c r="D338" s="2" t="n"/>
-      <c r="E338" s="2" t="n"/>
+      <c r="D338" s="3" t="n"/>
+      <c r="E338" s="3" t="n"/>
     </row>
     <row r="339">
-      <c r="D339" s="2" t="n"/>
-      <c r="E339" s="2" t="n"/>
+      <c r="D339" s="3" t="n"/>
+      <c r="E339" s="3" t="n"/>
     </row>
     <row r="340">
-      <c r="D340" s="2" t="n"/>
-      <c r="E340" s="2" t="n"/>
+      <c r="D340" s="3" t="n"/>
+      <c r="E340" s="3" t="n"/>
     </row>
     <row r="341">
-      <c r="D341" s="2" t="n"/>
-      <c r="E341" s="2" t="n"/>
+      <c r="D341" s="3" t="n"/>
+      <c r="E341" s="3" t="n"/>
     </row>
     <row r="342">
-      <c r="D342" s="2" t="n"/>
-      <c r="E342" s="2" t="n"/>
+      <c r="D342" s="3" t="n"/>
+      <c r="E342" s="3" t="n"/>
     </row>
     <row r="343">
-      <c r="D343" s="2" t="n"/>
-      <c r="E343" s="2" t="n"/>
+      <c r="D343" s="3" t="n"/>
+      <c r="E343" s="3" t="n"/>
     </row>
     <row r="344">
-      <c r="D344" s="2" t="n"/>
-      <c r="E344" s="2" t="n"/>
+      <c r="D344" s="3" t="n"/>
+      <c r="E344" s="3" t="n"/>
     </row>
     <row r="345">
-      <c r="D345" s="2" t="n"/>
-      <c r="E345" s="2" t="n"/>
+      <c r="D345" s="3" t="n"/>
+      <c r="E345" s="3" t="n"/>
     </row>
     <row r="346">
-      <c r="D346" s="2" t="n"/>
-      <c r="E346" s="2" t="n"/>
+      <c r="D346" s="3" t="n"/>
+      <c r="E346" s="3" t="n"/>
     </row>
     <row r="347">
-      <c r="D347" s="2" t="n"/>
-      <c r="E347" s="2" t="n"/>
+      <c r="D347" s="3" t="n"/>
+      <c r="E347" s="3" t="n"/>
     </row>
     <row r="348">
-      <c r="D348" s="2" t="n"/>
-      <c r="E348" s="2" t="n"/>
+      <c r="D348" s="3" t="n"/>
+      <c r="E348" s="3" t="n"/>
     </row>
     <row r="349">
-      <c r="D349" s="2" t="n"/>
-      <c r="E349" s="2" t="n"/>
+      <c r="D349" s="3" t="n"/>
+      <c r="E349" s="3" t="n"/>
     </row>
     <row r="350">
-      <c r="D350" s="2" t="n"/>
-      <c r="E350" s="2" t="n"/>
+      <c r="D350" s="3" t="n"/>
+      <c r="E350" s="3" t="n"/>
     </row>
     <row r="351">
-      <c r="D351" s="2" t="n"/>
-      <c r="E351" s="2" t="n"/>
+      <c r="D351" s="3" t="n"/>
+      <c r="E351" s="3" t="n"/>
     </row>
     <row r="352">
-      <c r="D352" s="2" t="n"/>
-      <c r="E352" s="2" t="n"/>
+      <c r="D352" s="3" t="n"/>
+      <c r="E352" s="3" t="n"/>
     </row>
     <row r="353">
-      <c r="D353" s="2" t="n"/>
-      <c r="E353" s="2" t="n"/>
+      <c r="D353" s="3" t="n"/>
+      <c r="E353" s="3" t="n"/>
     </row>
     <row r="354">
-      <c r="D354" s="2" t="n"/>
-      <c r="E354" s="2" t="n"/>
+      <c r="D354" s="3" t="n"/>
+      <c r="E354" s="3" t="n"/>
     </row>
     <row r="355">
-      <c r="D355" s="2" t="n"/>
-      <c r="E355" s="2" t="n"/>
+      <c r="D355" s="3" t="n"/>
+      <c r="E355" s="3" t="n"/>
     </row>
     <row r="356">
-      <c r="D356" s="2" t="n"/>
-      <c r="E356" s="2" t="n"/>
+      <c r="D356" s="3" t="n"/>
+      <c r="E356" s="3" t="n"/>
     </row>
     <row r="357">
-      <c r="D357" s="2" t="n"/>
-      <c r="E357" s="2" t="n"/>
+      <c r="D357" s="3" t="n"/>
+      <c r="E357" s="3" t="n"/>
     </row>
     <row r="358">
-      <c r="D358" s="2" t="n"/>
-      <c r="E358" s="2" t="n"/>
+      <c r="D358" s="3" t="n"/>
+      <c r="E358" s="3" t="n"/>
     </row>
     <row r="359">
-      <c r="D359" s="2" t="n"/>
-      <c r="E359" s="2" t="n"/>
+      <c r="D359" s="3" t="n"/>
+      <c r="E359" s="3" t="n"/>
     </row>
     <row r="360">
-      <c r="D360" s="2" t="n"/>
-      <c r="E360" s="2" t="n"/>
+      <c r="D360" s="3" t="n"/>
+      <c r="E360" s="3" t="n"/>
     </row>
     <row r="361">
-      <c r="D361" s="2" t="n"/>
-      <c r="E361" s="2" t="n"/>
+      <c r="D361" s="3" t="n"/>
+      <c r="E361" s="3" t="n"/>
     </row>
     <row r="362">
-      <c r="D362" s="2" t="n"/>
-      <c r="E362" s="2" t="n"/>
+      <c r="D362" s="3" t="n"/>
+      <c r="E362" s="3" t="n"/>
     </row>
     <row r="363">
-      <c r="D363" s="2" t="n"/>
-      <c r="E363" s="2" t="n"/>
+      <c r="D363" s="3" t="n"/>
+      <c r="E363" s="3" t="n"/>
     </row>
     <row r="364">
-      <c r="D364" s="2" t="n"/>
-      <c r="E364" s="2" t="n"/>
+      <c r="D364" s="3" t="n"/>
+      <c r="E364" s="3" t="n"/>
     </row>
     <row r="365">
-      <c r="D365" s="2" t="n"/>
-      <c r="E365" s="2" t="n"/>
+      <c r="D365" s="3" t="n"/>
+      <c r="E365" s="3" t="n"/>
     </row>
     <row r="366">
-      <c r="D366" s="2" t="n"/>
-      <c r="E366" s="2" t="n"/>
+      <c r="D366" s="3" t="n"/>
+      <c r="E366" s="3" t="n"/>
     </row>
     <row r="367">
-      <c r="D367" s="2" t="n"/>
-      <c r="E367" s="2" t="n"/>
+      <c r="D367" s="3" t="n"/>
+      <c r="E367" s="3" t="n"/>
     </row>
     <row r="368">
-      <c r="D368" s="2" t="n"/>
-      <c r="E368" s="2" t="n"/>
+      <c r="D368" s="3" t="n"/>
+      <c r="E368" s="3" t="n"/>
     </row>
     <row r="369">
-      <c r="D369" s="2" t="n"/>
-      <c r="E369" s="2" t="n"/>
+      <c r="D369" s="3" t="n"/>
+      <c r="E369" s="3" t="n"/>
     </row>
     <row r="370">
-      <c r="D370" s="2" t="n"/>
-      <c r="E370" s="2" t="n"/>
+      <c r="D370" s="3" t="n"/>
+      <c r="E370" s="3" t="n"/>
     </row>
     <row r="371">
-      <c r="D371" s="2" t="n"/>
-      <c r="E371" s="2" t="n"/>
+      <c r="D371" s="3" t="n"/>
+      <c r="E371" s="3" t="n"/>
     </row>
     <row r="372">
-      <c r="D372" s="2" t="n"/>
-      <c r="E372" s="2" t="n"/>
+      <c r="D372" s="3" t="n"/>
+      <c r="E372" s="3" t="n"/>
     </row>
     <row r="373">
-      <c r="D373" s="2" t="n"/>
-      <c r="E373" s="2" t="n"/>
+      <c r="D373" s="3" t="n"/>
+      <c r="E373" s="3" t="n"/>
     </row>
     <row r="374">
-      <c r="D374" s="2" t="n"/>
-      <c r="E374" s="2" t="n"/>
+      <c r="D374" s="3" t="n"/>
+      <c r="E374" s="3" t="n"/>
     </row>
     <row r="375">
-      <c r="D375" s="2" t="n"/>
-      <c r="E375" s="2" t="n"/>
+      <c r="D375" s="3" t="n"/>
+      <c r="E375" s="3" t="n"/>
     </row>
     <row r="376">
-      <c r="D376" s="2" t="n"/>
-      <c r="E376" s="2" t="n"/>
+      <c r="D376" s="3" t="n"/>
+      <c r="E376" s="3" t="n"/>
     </row>
     <row r="377">
-      <c r="D377" s="2" t="n"/>
-      <c r="E377" s="2" t="n"/>
+      <c r="D377" s="3" t="n"/>
+      <c r="E377" s="3" t="n"/>
     </row>
     <row r="378">
-      <c r="D378" s="2" t="n"/>
-      <c r="E378" s="2" t="n"/>
+      <c r="D378" s="3" t="n"/>
+      <c r="E378" s="3" t="n"/>
     </row>
     <row r="379">
-      <c r="D379" s="2" t="n"/>
-      <c r="E379" s="2" t="n"/>
+      <c r="D379" s="3" t="n"/>
+      <c r="E379" s="3" t="n"/>
     </row>
     <row r="380">
-      <c r="D380" s="2" t="n"/>
-      <c r="E380" s="2" t="n"/>
+      <c r="D380" s="3" t="n"/>
+      <c r="E380" s="3" t="n"/>
     </row>
     <row r="381">
-      <c r="D381" s="2" t="n"/>
-      <c r="E381" s="2" t="n"/>
+      <c r="D381" s="3" t="n"/>
+      <c r="E381" s="3" t="n"/>
     </row>
     <row r="382">
-      <c r="D382" s="2" t="n"/>
-      <c r="E382" s="2" t="n"/>
+      <c r="D382" s="3" t="n"/>
+      <c r="E382" s="3" t="n"/>
     </row>
     <row r="383">
-      <c r="D383" s="2" t="n"/>
-      <c r="E383" s="2" t="n"/>
+      <c r="D383" s="3" t="n"/>
+      <c r="E383" s="3" t="n"/>
     </row>
     <row r="384">
-      <c r="D384" s="2" t="n"/>
-      <c r="E384" s="2" t="n"/>
+      <c r="D384" s="3" t="n"/>
+      <c r="E384" s="3" t="n"/>
     </row>
     <row r="385">
-      <c r="D385" s="2" t="n"/>
-      <c r="E385" s="2" t="n"/>
+      <c r="D385" s="3" t="n"/>
+      <c r="E385" s="3" t="n"/>
     </row>
     <row r="386">
-      <c r="D386" s="2" t="n"/>
-      <c r="E386" s="2" t="n"/>
+      <c r="D386" s="3" t="n"/>
+      <c r="E386" s="3" t="n"/>
     </row>
     <row r="387">
-      <c r="D387" s="2" t="n"/>
-      <c r="E387" s="2" t="n"/>
+      <c r="D387" s="3" t="n"/>
+      <c r="E387" s="3" t="n"/>
     </row>
     <row r="388">
-      <c r="D388" s="2" t="n"/>
-      <c r="E388" s="2" t="n"/>
+      <c r="D388" s="3" t="n"/>
+      <c r="E388" s="3" t="n"/>
     </row>
     <row r="389">
-      <c r="D389" s="2" t="n"/>
-      <c r="E389" s="2" t="n"/>
+      <c r="D389" s="3" t="n"/>
+      <c r="E389" s="3" t="n"/>
     </row>
     <row r="390">
-      <c r="D390" s="2" t="n"/>
-      <c r="E390" s="2" t="n"/>
+      <c r="D390" s="3" t="n"/>
+      <c r="E390" s="3" t="n"/>
     </row>
     <row r="391">
-      <c r="D391" s="2" t="n"/>
-      <c r="E391" s="2" t="n"/>
+      <c r="D391" s="3" t="n"/>
+      <c r="E391" s="3" t="n"/>
     </row>
     <row r="392">
-      <c r="D392" s="2" t="n"/>
-      <c r="E392" s="2" t="n"/>
+      <c r="D392" s="3" t="n"/>
+      <c r="E392" s="3" t="n"/>
     </row>
     <row r="393">
-      <c r="D393" s="2" t="n"/>
-      <c r="E393" s="2" t="n"/>
+      <c r="D393" s="3" t="n"/>
+      <c r="E393" s="3" t="n"/>
     </row>
     <row r="394">
-      <c r="D394" s="2" t="n"/>
-      <c r="E394" s="2" t="n"/>
+      <c r="D394" s="3" t="n"/>
+      <c r="E394" s="3" t="n"/>
     </row>
     <row r="395">
-      <c r="D395" s="2" t="n"/>
-      <c r="E395" s="2" t="n"/>
+      <c r="D395" s="3" t="n"/>
+      <c r="E395" s="3" t="n"/>
     </row>
     <row r="396">
-      <c r="D396" s="2" t="n"/>
-      <c r="E396" s="2" t="n"/>
+      <c r="D396" s="3" t="n"/>
+      <c r="E396" s="3" t="n"/>
     </row>
     <row r="397">
-      <c r="D397" s="2" t="n"/>
-      <c r="E397" s="2" t="n"/>
+      <c r="D397" s="3" t="n"/>
+      <c r="E397" s="3" t="n"/>
     </row>
     <row r="398">
-      <c r="D398" s="2" t="n"/>
-      <c r="E398" s="2" t="n"/>
+      <c r="D398" s="3" t="n"/>
+      <c r="E398" s="3" t="n"/>
     </row>
     <row r="399">
-      <c r="D399" s="2" t="n"/>
-      <c r="E399" s="2" t="n"/>
+      <c r="D399" s="3" t="n"/>
+      <c r="E399" s="3" t="n"/>
     </row>
     <row r="400">
-      <c r="D400" s="2" t="n"/>
-      <c r="E400" s="2" t="n"/>
+      <c r="D400" s="3" t="n"/>
+      <c r="E400" s="3" t="n"/>
     </row>
     <row r="401">
-      <c r="D401" s="2" t="n"/>
-      <c r="E401" s="2" t="n"/>
+      <c r="D401" s="3" t="n"/>
+      <c r="E401" s="3" t="n"/>
     </row>
     <row r="402">
-      <c r="D402" s="2" t="n"/>
-      <c r="E402" s="2" t="n"/>
+      <c r="D402" s="3" t="n"/>
+      <c r="E402" s="3" t="n"/>
     </row>
     <row r="403">
-      <c r="D403" s="2" t="n"/>
-      <c r="E403" s="2" t="n"/>
+      <c r="D403" s="3" t="n"/>
+      <c r="E403" s="3" t="n"/>
     </row>
     <row r="404">
-      <c r="D404" s="2" t="n"/>
-      <c r="E404" s="2" t="n"/>
+      <c r="D404" s="3" t="n"/>
+      <c r="E404" s="3" t="n"/>
     </row>
     <row r="405">
-      <c r="D405" s="2" t="n"/>
-      <c r="E405" s="2" t="n"/>
+      <c r="D405" s="3" t="n"/>
+      <c r="E405" s="3" t="n"/>
     </row>
     <row r="406">
-      <c r="D406" s="2" t="n"/>
-      <c r="E406" s="2" t="n"/>
+      <c r="D406" s="3" t="n"/>
+      <c r="E406" s="3" t="n"/>
     </row>
     <row r="407">
-      <c r="D407" s="2" t="n"/>
-      <c r="E407" s="2" t="n"/>
+      <c r="D407" s="3" t="n"/>
+      <c r="E407" s="3" t="n"/>
     </row>
     <row r="408">
-      <c r="D408" s="2" t="n"/>
-      <c r="E408" s="2" t="n"/>
+      <c r="D408" s="3" t="n"/>
+      <c r="E408" s="3" t="n"/>
     </row>
     <row r="409">
-      <c r="D409" s="2" t="n"/>
-      <c r="E409" s="2" t="n"/>
+      <c r="D409" s="3" t="n"/>
+      <c r="E409" s="3" t="n"/>
     </row>
     <row r="410">
-      <c r="D410" s="2" t="n"/>
-      <c r="E410" s="2" t="n"/>
+      <c r="D410" s="3" t="n"/>
+      <c r="E410" s="3" t="n"/>
     </row>
     <row r="411">
-      <c r="D411" s="2" t="n"/>
-      <c r="E411" s="2" t="n"/>
+      <c r="D411" s="3" t="n"/>
+      <c r="E411" s="3" t="n"/>
     </row>
     <row r="412">
-      <c r="D412" s="2" t="n"/>
-      <c r="E412" s="2" t="n"/>
+      <c r="D412" s="3" t="n"/>
+      <c r="E412" s="3" t="n"/>
     </row>
     <row r="413">
-      <c r="D413" s="2" t="n"/>
-      <c r="E413" s="2" t="n"/>
+      <c r="D413" s="3" t="n"/>
+      <c r="E413" s="3" t="n"/>
     </row>
     <row r="414">
-      <c r="D414" s="2" t="n"/>
-      <c r="E414" s="2" t="n"/>
+      <c r="D414" s="3" t="n"/>
+      <c r="E414" s="3" t="n"/>
     </row>
     <row r="415">
-      <c r="D415" s="2" t="n"/>
-      <c r="E415" s="2" t="n"/>
+      <c r="D415" s="3" t="n"/>
+      <c r="E415" s="3" t="n"/>
     </row>
     <row r="416">
-      <c r="D416" s="2" t="n"/>
-      <c r="E416" s="2" t="n"/>
+      <c r="D416" s="3" t="n"/>
+      <c r="E416" s="3" t="n"/>
     </row>
     <row r="417">
-      <c r="D417" s="2" t="n"/>
-      <c r="E417" s="2" t="n"/>
+      <c r="D417" s="3" t="n"/>
+      <c r="E417" s="3" t="n"/>
     </row>
     <row r="418">
-      <c r="D418" s="2" t="n"/>
-      <c r="E418" s="2" t="n"/>
+      <c r="D418" s="3" t="n"/>
+      <c r="E418" s="3" t="n"/>
     </row>
     <row r="419">
-      <c r="D419" s="2" t="n"/>
-      <c r="E419" s="2" t="n"/>
+      <c r="D419" s="3" t="n"/>
+      <c r="E419" s="3" t="n"/>
     </row>
     <row r="420">
-      <c r="D420" s="2" t="n"/>
-      <c r="E420" s="2" t="n"/>
+      <c r="D420" s="3" t="n"/>
+      <c r="E420" s="3" t="n"/>
     </row>
     <row r="421">
-      <c r="D421" s="2" t="n"/>
-      <c r="E421" s="2" t="n"/>
+      <c r="D421" s="3" t="n"/>
+      <c r="E421" s="3" t="n"/>
     </row>
     <row r="422">
-      <c r="D422" s="2" t="n"/>
-      <c r="E422" s="2" t="n"/>
+      <c r="D422" s="3" t="n"/>
+      <c r="E422" s="3" t="n"/>
     </row>
     <row r="423">
-      <c r="D423" s="2" t="n"/>
-      <c r="E423" s="2" t="n"/>
+      <c r="D423" s="3" t="n"/>
+      <c r="E423" s="3" t="n"/>
     </row>
     <row r="424">
-      <c r="D424" s="2" t="n"/>
-      <c r="E424" s="2" t="n"/>
+      <c r="D424" s="3" t="n"/>
+      <c r="E424" s="3" t="n"/>
     </row>
     <row r="425">
-      <c r="D425" s="2" t="n"/>
-      <c r="E425" s="2" t="n"/>
+      <c r="D425" s="3" t="n"/>
+      <c r="E425" s="3" t="n"/>
     </row>
     <row r="426">
-      <c r="D426" s="2" t="n"/>
-      <c r="E426" s="2" t="n"/>
+      <c r="D426" s="3" t="n"/>
+      <c r="E426" s="3" t="n"/>
     </row>
     <row r="427">
-      <c r="D427" s="2" t="n"/>
-      <c r="E427" s="2" t="n"/>
+      <c r="D427" s="3" t="n"/>
+      <c r="E427" s="3" t="n"/>
     </row>
     <row r="428">
-      <c r="D428" s="2" t="n"/>
-      <c r="E428" s="2" t="n"/>
+      <c r="D428" s="3" t="n"/>
+      <c r="E428" s="3" t="n"/>
     </row>
     <row r="429">
-      <c r="D429" s="2" t="n"/>
-      <c r="E429" s="2" t="n"/>
+      <c r="D429" s="3" t="n"/>
+      <c r="E429" s="3" t="n"/>
     </row>
     <row r="430">
-      <c r="D430" s="2" t="n"/>
-      <c r="E430" s="2" t="n"/>
+      <c r="D430" s="3" t="n"/>
+      <c r="E430" s="3" t="n"/>
     </row>
     <row r="431">
-      <c r="D431" s="2" t="n"/>
-      <c r="E431" s="2" t="n"/>
+      <c r="D431" s="3" t="n"/>
+      <c r="E431" s="3" t="n"/>
     </row>
     <row r="432">
-      <c r="D432" s="2" t="n"/>
-      <c r="E432" s="2" t="n"/>
+      <c r="D432" s="3" t="n"/>
+      <c r="E432" s="3" t="n"/>
     </row>
     <row r="433">
-      <c r="D433" s="2" t="n"/>
-      <c r="E433" s="2" t="n"/>
+      <c r="D433" s="3" t="n"/>
+      <c r="E433" s="3" t="n"/>
     </row>
     <row r="434">
-      <c r="D434" s="2" t="n"/>
-      <c r="E434" s="2" t="n"/>
+      <c r="D434" s="3" t="n"/>
+      <c r="E434" s="3" t="n"/>
     </row>
     <row r="435">
-      <c r="D435" s="2" t="n"/>
-      <c r="E435" s="2" t="n"/>
+      <c r="D435" s="3" t="n"/>
+      <c r="E435" s="3" t="n"/>
     </row>
     <row r="436">
-      <c r="D436" s="2" t="n"/>
-      <c r="E436" s="2" t="n"/>
+      <c r="D436" s="3" t="n"/>
+      <c r="E436" s="3" t="n"/>
     </row>
     <row r="437">
-      <c r="D437" s="2" t="n"/>
-      <c r="E437" s="2" t="n"/>
+      <c r="D437" s="3" t="n"/>
+      <c r="E437" s="3" t="n"/>
     </row>
     <row r="438">
-      <c r="D438" s="2" t="n"/>
-      <c r="E438" s="2" t="n"/>
+      <c r="D438" s="3" t="n"/>
+      <c r="E438" s="3" t="n"/>
     </row>
     <row r="439">
-      <c r="D439" s="2" t="n"/>
-      <c r="E439" s="2" t="n"/>
+      <c r="D439" s="3" t="n"/>
+      <c r="E439" s="3" t="n"/>
     </row>
     <row r="440">
-      <c r="D440" s="2" t="n"/>
-      <c r="E440" s="2" t="n"/>
+      <c r="D440" s="3" t="n"/>
+      <c r="E440" s="3" t="n"/>
     </row>
     <row r="441">
-      <c r="D441" s="2" t="n"/>
-      <c r="E441" s="2" t="n"/>
+      <c r="D441" s="3" t="n"/>
+      <c r="E441" s="3" t="n"/>
     </row>
     <row r="442">
-      <c r="D442" s="2" t="n"/>
-      <c r="E442" s="2" t="n"/>
+      <c r="D442" s="3" t="n"/>
+      <c r="E442" s="3" t="n"/>
     </row>
     <row r="443">
-      <c r="D443" s="2" t="n"/>
-      <c r="E443" s="2" t="n"/>
+      <c r="D443" s="3" t="n"/>
+      <c r="E443" s="3" t="n"/>
     </row>
     <row r="444">
-      <c r="D444" s="2" t="n"/>
-      <c r="E444" s="2" t="n"/>
+      <c r="D444" s="3" t="n"/>
+      <c r="E444" s="3" t="n"/>
     </row>
     <row r="445">
-      <c r="D445" s="2" t="n"/>
-      <c r="E445" s="2" t="n"/>
+      <c r="D445" s="3" t="n"/>
+      <c r="E445" s="3" t="n"/>
     </row>
     <row r="446">
-      <c r="D446" s="2" t="n"/>
-      <c r="E446" s="2" t="n"/>
+      <c r="D446" s="3" t="n"/>
+      <c r="E446" s="3" t="n"/>
     </row>
     <row r="447">
-      <c r="D447" s="2" t="n"/>
-      <c r="E447" s="2" t="n"/>
+      <c r="D447" s="3" t="n"/>
+      <c r="E447" s="3" t="n"/>
     </row>
     <row r="448">
-      <c r="D448" s="2" t="n"/>
-      <c r="E448" s="2" t="n"/>
+      <c r="D448" s="3" t="n"/>
+      <c r="E448" s="3" t="n"/>
     </row>
     <row r="449">
-      <c r="D449" s="2" t="n"/>
-      <c r="E449" s="2" t="n"/>
+      <c r="D449" s="3" t="n"/>
+      <c r="E449" s="3" t="n"/>
     </row>
     <row r="450">
-      <c r="D450" s="2" t="n"/>
-      <c r="E450" s="2" t="n"/>
+      <c r="D450" s="3" t="n"/>
+      <c r="E450" s="3" t="n"/>
     </row>
     <row r="451">
-      <c r="D451" s="2" t="n"/>
-      <c r="E451" s="2" t="n"/>
+      <c r="D451" s="3" t="n"/>
+      <c r="E451" s="3" t="n"/>
     </row>
     <row r="452">
-      <c r="D452" s="2" t="n"/>
-      <c r="E452" s="2" t="n"/>
+      <c r="D452" s="3" t="n"/>
+      <c r="E452" s="3" t="n"/>
     </row>
     <row r="453">
-      <c r="D453" s="2" t="n"/>
-      <c r="E453" s="2" t="n"/>
+      <c r="D453" s="3" t="n"/>
+      <c r="E453" s="3" t="n"/>
     </row>
     <row r="454">
-      <c r="D454" s="2" t="n"/>
-      <c r="E454" s="2" t="n"/>
+      <c r="D454" s="3" t="n"/>
+      <c r="E454" s="3" t="n"/>
     </row>
     <row r="455">
-      <c r="D455" s="2" t="n"/>
-      <c r="E455" s="2" t="n"/>
+      <c r="D455" s="3" t="n"/>
+      <c r="E455" s="3" t="n"/>
     </row>
     <row r="456">
-      <c r="D456" s="2" t="n"/>
-      <c r="E456" s="2" t="n"/>
+      <c r="D456" s="3" t="n"/>
+      <c r="E456" s="3" t="n"/>
     </row>
     <row r="457">
-      <c r="D457" s="2" t="n"/>
-      <c r="E457" s="2" t="n"/>
+      <c r="D457" s="3" t="n"/>
+      <c r="E457" s="3" t="n"/>
     </row>
     <row r="458">
-      <c r="D458" s="2" t="n"/>
-      <c r="E458" s="2" t="n"/>
+      <c r="D458" s="3" t="n"/>
+      <c r="E458" s="3" t="n"/>
     </row>
     <row r="459">
-      <c r="D459" s="2" t="n"/>
-      <c r="E459" s="2" t="n"/>
+      <c r="D459" s="3" t="n"/>
+      <c r="E459" s="3" t="n"/>
     </row>
     <row r="460">
-      <c r="D460" s="2" t="n"/>
-      <c r="E460" s="2" t="n"/>
+      <c r="D460" s="3" t="n"/>
+      <c r="E460" s="3" t="n"/>
     </row>
     <row r="461">
-      <c r="D461" s="2" t="n"/>
-      <c r="E461" s="2" t="n"/>
+      <c r="D461" s="3" t="n"/>
+      <c r="E461" s="3" t="n"/>
     </row>
     <row r="462">
-      <c r="D462" s="2" t="n"/>
-      <c r="E462" s="2" t="n"/>
+      <c r="D462" s="3" t="n"/>
+      <c r="E462" s="3" t="n"/>
     </row>
     <row r="463">
-      <c r="D463" s="2" t="n"/>
-      <c r="E463" s="2" t="n"/>
+      <c r="D463" s="3" t="n"/>
+      <c r="E463" s="3" t="n"/>
     </row>
     <row r="464">
-      <c r="D464" s="2" t="n"/>
-      <c r="E464" s="2" t="n"/>
+      <c r="D464" s="3" t="n"/>
+      <c r="E464" s="3" t="n"/>
     </row>
     <row r="465">
-      <c r="D465" s="2" t="n"/>
-      <c r="E465" s="2" t="n"/>
+      <c r="D465" s="3" t="n"/>
+      <c r="E465" s="3" t="n"/>
     </row>
     <row r="466">
-      <c r="D466" s="2" t="n"/>
-      <c r="E466" s="2" t="n"/>
+      <c r="D466" s="3" t="n"/>
+      <c r="E466" s="3" t="n"/>
     </row>
     <row r="467">
-      <c r="D467" s="2" t="n"/>
-      <c r="E467" s="2" t="n"/>
+      <c r="D467" s="3" t="n"/>
+      <c r="E467" s="3" t="n"/>
     </row>
     <row r="468">
-      <c r="D468" s="2" t="n"/>
-      <c r="E468" s="2" t="n"/>
+      <c r="D468" s="3" t="n"/>
+      <c r="E468" s="3" t="n"/>
     </row>
     <row r="469">
-      <c r="D469" s="2" t="n"/>
-      <c r="E469" s="2" t="n"/>
+      <c r="D469" s="3" t="n"/>
+      <c r="E469" s="3" t="n"/>
     </row>
     <row r="470">
-      <c r="D470" s="2" t="n"/>
-      <c r="E470" s="2" t="n"/>
+      <c r="D470" s="3" t="n"/>
+      <c r="E470" s="3" t="n"/>
     </row>
     <row r="471">
-      <c r="D471" s="2" t="n"/>
-      <c r="E471" s="2" t="n"/>
+      <c r="D471" s="3" t="n"/>
+      <c r="E471" s="3" t="n"/>
     </row>
     <row r="472">
-      <c r="D472" s="2" t="n"/>
-      <c r="E472" s="2" t="n"/>
+      <c r="D472" s="3" t="n"/>
+      <c r="E472" s="3" t="n"/>
     </row>
     <row r="473">
-      <c r="D473" s="2" t="n"/>
-      <c r="E473" s="2" t="n"/>
+      <c r="D473" s="3" t="n"/>
+      <c r="E473" s="3" t="n"/>
     </row>
     <row r="474">
-      <c r="D474" s="2" t="n"/>
-      <c r="E474" s="2" t="n"/>
+      <c r="D474" s="3" t="n"/>
+      <c r="E474" s="3" t="n"/>
     </row>
     <row r="475">
-      <c r="D475" s="2" t="n"/>
-      <c r="E475" s="2" t="n"/>
+      <c r="D475" s="3" t="n"/>
+      <c r="E475" s="3" t="n"/>
     </row>
     <row r="476">
-      <c r="D476" s="2" t="n"/>
-      <c r="E476" s="2" t="n"/>
+      <c r="D476" s="3" t="n"/>
+      <c r="E476" s="3" t="n"/>
     </row>
     <row r="477">
-      <c r="D477" s="2" t="n"/>
-      <c r="E477" s="2" t="n"/>
+      <c r="D477" s="3" t="n"/>
+      <c r="E477" s="3" t="n"/>
     </row>
     <row r="478">
-      <c r="D478" s="2" t="n"/>
-      <c r="E478" s="2" t="n"/>
+      <c r="D478" s="3" t="n"/>
+      <c r="E478" s="3" t="n"/>
     </row>
     <row r="479">
-      <c r="D479" s="2" t="n"/>
-      <c r="E479" s="2" t="n"/>
+      <c r="D479" s="3" t="n"/>
+      <c r="E479" s="3" t="n"/>
     </row>
     <row r="480">
-      <c r="D480" s="2" t="n"/>
-      <c r="E480" s="2" t="n"/>
+      <c r="D480" s="3" t="n"/>
+      <c r="E480" s="3" t="n"/>
     </row>
     <row r="481">
-      <c r="D481" s="2" t="n"/>
-      <c r="E481" s="2" t="n"/>
+      <c r="D481" s="3" t="n"/>
+      <c r="E481" s="3" t="n"/>
     </row>
     <row r="482">
-      <c r="D482" s="2" t="n"/>
-      <c r="E482" s="2" t="n"/>
+      <c r="D482" s="3" t="n"/>
+      <c r="E482" s="3" t="n"/>
     </row>
     <row r="483">
-      <c r="D483" s="2" t="n"/>
-      <c r="E483" s="2" t="n"/>
+      <c r="D483" s="3" t="n"/>
+      <c r="E483" s="3" t="n"/>
     </row>
     <row r="484">
-      <c r="D484" s="2" t="n"/>
-      <c r="E484" s="2" t="n"/>
+      <c r="D484" s="3" t="n"/>
+      <c r="E484" s="3" t="n"/>
     </row>
     <row r="485">
-      <c r="D485" s="2" t="n"/>
-      <c r="E485" s="2" t="n"/>
+      <c r="D485" s="3" t="n"/>
+      <c r="E485" s="3" t="n"/>
     </row>
     <row r="486">
-      <c r="D486" s="2" t="n"/>
-      <c r="E486" s="2" t="n"/>
+      <c r="D486" s="3" t="n"/>
+      <c r="E486" s="3" t="n"/>
     </row>
     <row r="487">
-      <c r="D487" s="2" t="n"/>
-      <c r="E487" s="2" t="n"/>
+      <c r="D487" s="3" t="n"/>
+      <c r="E487" s="3" t="n"/>
     </row>
     <row r="488">
-      <c r="D488" s="2" t="n"/>
-      <c r="E488" s="2" t="n"/>
+      <c r="D488" s="3" t="n"/>
+      <c r="E488" s="3" t="n"/>
     </row>
     <row r="489">
-      <c r="D489" s="2" t="n"/>
-      <c r="E489" s="2" t="n"/>
+      <c r="D489" s="3" t="n"/>
+      <c r="E489" s="3" t="n"/>
     </row>
     <row r="490">
-      <c r="D490" s="2" t="n"/>
-      <c r="E490" s="2" t="n"/>
+      <c r="D490" s="3" t="n"/>
+      <c r="E490" s="3" t="n"/>
     </row>
     <row r="491">
-      <c r="D491" s="2" t="n"/>
-      <c r="E491" s="2" t="n"/>
+      <c r="D491" s="3" t="n"/>
+      <c r="E491" s="3" t="n"/>
     </row>
     <row r="492">
-      <c r="D492" s="2" t="n"/>
-      <c r="E492" s="2" t="n"/>
+      <c r="D492" s="3" t="n"/>
+      <c r="E492" s="3" t="n"/>
     </row>
     <row r="493">
-      <c r="D493" s="2" t="n"/>
-      <c r="E493" s="2" t="n"/>
+      <c r="D493" s="3" t="n"/>
+      <c r="E493" s="3" t="n"/>
     </row>
     <row r="494">
-      <c r="D494" s="2" t="n"/>
-      <c r="E494" s="2" t="n"/>
+      <c r="D494" s="3" t="n"/>
+      <c r="E494" s="3" t="n"/>
     </row>
     <row r="495">
-      <c r="D495" s="2" t="n"/>
-      <c r="E495" s="2" t="n"/>
+      <c r="D495" s="3" t="n"/>
+      <c r="E495" s="3" t="n"/>
     </row>
     <row r="496">
-      <c r="D496" s="2" t="n"/>
-      <c r="E496" s="2" t="n"/>
+      <c r="D496" s="3" t="n"/>
+      <c r="E496" s="3" t="n"/>
     </row>
     <row r="497">
-      <c r="D497" s="2" t="n"/>
-      <c r="E497" s="2" t="n"/>
+      <c r="D497" s="3" t="n"/>
+      <c r="E497" s="3" t="n"/>
     </row>
     <row r="498">
-      <c r="D498" s="2" t="n"/>
-      <c r="E498" s="2" t="n"/>
+      <c r="D498" s="3" t="n"/>
+      <c r="E498" s="3" t="n"/>
     </row>
     <row r="499">
-      <c r="D499" s="2" t="n"/>
-      <c r="E499" s="2" t="n"/>
+      <c r="D499" s="3" t="n"/>
+      <c r="E499" s="3" t="n"/>
     </row>
     <row r="500">
-      <c r="D500" s="2" t="n"/>
-      <c r="E500" s="2" t="n"/>
+      <c r="D500" s="3" t="n"/>
+      <c r="E500" s="3" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -7195,7 +7377,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Terminübersicht – so wird sie ausgefüllt</t>
         </is>
@@ -7203,7 +7385,7 @@
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Blatt „Termine“ – hier wird alles eingetragen</t>
         </is>
@@ -7267,21 +7449,21 @@
     </row>
     <row r="12"/>
     <row r="13">
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Die Spalten Art, Prüfstand, Status und Termin-Nr haben ein Drop-Down:</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>in die Zelle klicken, dann rechts am Zellrand auf den Pfeil klicken.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>So kann kein Tippfehler und kein unbekannter Prüfstand entstehen.</t>
         </is>
@@ -7289,7 +7471,7 @@
     </row>
     <row r="16"/>
     <row r="17">
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Blatt „Zeiten“ – hier stehen die Uhrzeiten</t>
         </is>
@@ -7325,7 +7507,7 @@
     </row>
     <row r="22"/>
     <row r="23">
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>Wann ist das Blatt „Zeiten“ nötig?</t>
         </is>
@@ -7384,7 +7566,7 @@
     </row>
     <row r="33"/>
     <row r="34">
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -7413,7 +7595,7 @@
     </row>
     <row r="38"/>
     <row r="39">
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>Nach dem Abschluss</t>
         </is>
@@ -7435,7 +7617,7 @@
     </row>
     <row r="42"/>
     <row r="43">
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>Neue Prüfstände</t>
         </is>
@@ -7457,7 +7639,7 @@
     </row>
     <row r="46"/>
     <row r="47">
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t>Beispiele</t>
         </is>

--- a/terminboard/vorlagen/termine_modell2.xlsx
+++ b/terminboard/vorlagen/termine_modell2.xlsx
@@ -22,11 +22,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="DD.MM.YYYY"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="167" formatCode="DD.MM.YYYY HH:MM"/>
+    <numFmt numFmtId="166" formatCode="DD.MM.YYYY HH:MM"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -94,7 +93,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2785,16 +2784,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I500"/>
+  <dimension ref="A1:D500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="3" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2818,169 +2814,42 @@
           <t>Notiz</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Beispiel</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B2" s="6" t="n">
-        <v>46350.375</v>
-      </c>
-      <c r="C2" s="6" t="n">
-        <v>46350.54166666666</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Halbtag, Rest des Tages freigegeben</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I2" s="5" t="inlineStr">
-        <is>
-          <t>Halbtag: 09:00–13:00</t>
-        </is>
-      </c>
+      <c r="B2" s="6" t="n"/>
+      <c r="C2" s="6" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="6" t="n">
-        <v>46342.33333333334</v>
-      </c>
-      <c r="C3" s="6" t="n">
-        <v>46342.5</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Tag 1, vormittags</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>erster Block einer mehrtägigen</t>
-        </is>
-      </c>
+      <c r="B3" s="6" t="n"/>
+      <c r="C3" s="6" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>46343.33333333334</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>46343.66666666666</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Tag 2, ganztags</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>Kalibrierung</t>
-        </is>
-      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>46345.29166666666</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>46345.45833333334</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Tag 4, vormittags</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>46346.33333333334</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>46346.58333333334</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Tag 5, 6 Stunden</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Uhrzeiten</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>gehören ausschließlich</t>
-        </is>
-      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="6" t="n"/>
       <c r="C7" s="6" t="n"/>
-      <c r="H7" s="4" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>in dieses Blatt</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
-      <c r="H8" s="4" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="6" t="n"/>
       <c r="C9" s="6" t="n"/>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>Kein Eintrag</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>Prüfstand war durchgehend</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="n"/>
       <c r="C10" s="6" t="n"/>
-      <c r="H10" s="4" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>außer Betrieb</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="B11" s="6" t="n"/>

--- a/terminboard/vorlagen/termine_modell2.xlsx
+++ b/terminboard/vorlagen/termine_modell2.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Anleitung" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="Pruefstaende">'Prüfstände'!$C$2:$C$16</definedName>
+    <definedName name="Pruefstaende">'Prüfstände'!$C$2:$C$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -101,6 +101,42 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="00595959"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00E7E6E6"/>
+          <bgColor rgb="00E7E6E6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -514,7 +550,7 @@
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>Beispiel</t>
+          <t>Legende</t>
         </is>
       </c>
     </row>
@@ -524,38 +560,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Wartung</t>
+          <t>Kalibrierung</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>P03 NRA</t>
+          <t>P11 PUMO HYCOM</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>46328</v>
+        <v>46314</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>46328</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jahreswartung Hydraulik</t>
+          <t>Kalibrierung Hycom (Kristin + Glen) 07:00 - 14:00</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>abgeschlossen</t>
+          <t>offen</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>offen</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>Wartung, erledigt</t>
+          <t>Prüfstand steht still (rot)</t>
         </is>
       </c>
     </row>
@@ -570,33 +606,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>P10 PTU TESTFUCHS</t>
+          <t>Belastungsbank AHH</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>46342</v>
+        <v>46321</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>46347</v>
+        <v>46322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kalibrierung Druckmessung, unterbrochen</t>
+          <t>Kalibrierung (Sven + Glen) 15:00 - 22:00</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>abgeschlossen</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>Kalibrierung über mehrere Tage –</t>
+          <t>erledigt (grün)</t>
         </is>
       </c>
     </row>
@@ -606,23 +642,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ausfall</t>
+          <t>Kalibrierung</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>P21 NRC HYCOM</t>
+          <t>P43 LOW-PRESSURE</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>46344</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>46345</v>
-      </c>
+        <v>46331</v>
+      </c>
+      <c r="E4" s="3" t="n"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Steuerung ausgefallen, Ersatzteil</t>
+          <t>Kalibrierung (Kristin) 07:00 - 13:00</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -630,10 +664,14 @@
           <t>offen</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>storniert</t>
+        </is>
+      </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>Zeitblöcke im Blatt „Zeiten“</t>
+          <t>zählt nicht (grau)</t>
         </is>
       </c>
     </row>
@@ -652,14 +690,14 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>46350</v>
+        <v>46335</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>46350</v>
+        <v>46346</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Halbtag, Rest des Tages freigegeben</t>
+          <t>Kalibrierung (Bernd + Tommy) 08:00 - 15:00</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -667,152 +705,80 @@
           <t>offen</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>Info – „Bis“ darf leer bleiben</t>
-        </is>
-      </c>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Audit</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>P40 AKKU/HOCHDRUCK-RAUM</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>46353</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>46353</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>interner Audit</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Von / Bis</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>nur Datum, keine Uhrzeit</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Info</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>P07 EHSV NRA</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>46357</v>
-      </c>
+      <c r="D7" s="3" t="n"/>
       <c r="E7" s="3" t="n"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Hinweis Software-Update</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>Von / Bis</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>nur Datum, keine Uhrzeit</t>
-        </is>
-      </c>
+      <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="D8" s="3" t="n"/>
       <c r="E8" s="3" t="n"/>
-      <c r="H8" s="4" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Uhrzeiten</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>gehören ins Blatt „Zeiten“</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="D9" s="3" t="n"/>
       <c r="E9" s="3" t="n"/>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>Art</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>Kalibrierung / Wartung /</t>
-        </is>
-      </c>
+      <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="D10" s="3" t="n"/>
       <c r="E10" s="3" t="n"/>
-      <c r="H10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>Ausfall / Audit / Info</t>
+          <t>Kalibrierung / Wartung /</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="D11" s="3" t="n"/>
       <c r="E11" s="3" t="n"/>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>Prüfstand</t>
-        </is>
-      </c>
+      <c r="H11" s="4" t="inlineStr"/>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Reihenfolge: erst mit</t>
+          <t>Ausfall / Audit / Info</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="D12" s="3" t="n"/>
       <c r="E12" s="3" t="n"/>
-      <c r="H12" s="4" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>Dropdown wählen – falsche</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="D13" s="3" t="n"/>
       <c r="E13" s="3" t="n"/>
-      <c r="H13" s="4" t="inlineStr"/>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>Namen zählen nicht</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="D14" s="3" t="n"/>
@@ -2763,6 +2729,17 @@
       <c r="E500" s="3" t="n"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="G2:G500">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"offen"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"abgeschlossen"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"storniert"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation sqref="B2:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Ungültiger Wert" error="Bitte einen Wert aus der Liste wählen." promptTitle="Art" prompt="Art des Termins wählen." type="list">
       <formula1>"Kalibrierung,Wartung,Ausfall,Audit,Info"</formula1>
@@ -4827,7 +4804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5104,6 +5081,23 @@
       <c r="C16" t="inlineStr">
         <is>
           <t>P43 LOW-PRESSURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AHH</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Belastungsbank</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Belastungsbank AHH</t>
         </is>
       </c>
     </row>
@@ -5168,66 +5162,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Ausfall</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>P02 NRA</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>46300</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Kühlmittelverlust, Reparatur</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>abgeschlossen</t>
-        </is>
-      </c>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>8</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Wartung</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>P41 MIL</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>46307</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Dichtungen getauscht</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>abgeschlossen</t>
-        </is>
-      </c>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="D4" s="3" t="n"/>
@@ -7218,6 +7158,17 @@
       <c r="E500" s="3" t="n"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="G2:G500">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"offen"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"abgeschlossen"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"storniert"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation sqref="B2:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Ungültiger Wert" error="Bitte einen Wert aus der Liste wählen." promptTitle="Art" prompt="Art des Termins wählen." type="list">
       <formula1>"Kalibrierung,Wartung,Ausfall,Audit,Info"</formula1>

--- a/terminboard/vorlagen/termine_modell2.xlsx
+++ b/terminboard/vorlagen/termine_modell2.xlsx
@@ -658,11 +658,6 @@
       </c>
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="n"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -670,11 +665,6 @@
       </c>
       <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="n"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -682,11 +672,6 @@
       </c>
       <c r="D8" s="2" t="n"/>
       <c r="E8" s="2" t="n"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -694,11 +679,6 @@
       </c>
       <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="n"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -706,11 +686,6 @@
       </c>
       <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="n"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -718,11 +693,6 @@
       </c>
       <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="n"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -730,11 +700,6 @@
       </c>
       <c r="D12" s="2" t="n"/>
       <c r="E12" s="2" t="n"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -742,11 +707,6 @@
       </c>
       <c r="D13" s="2" t="n"/>
       <c r="E13" s="2" t="n"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -754,11 +714,6 @@
       </c>
       <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="n"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -766,11 +721,6 @@
       </c>
       <c r="D15" s="2" t="n"/>
       <c r="E15" s="2" t="n"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -778,11 +728,6 @@
       </c>
       <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="n"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -790,11 +735,6 @@
       </c>
       <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="n"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -802,11 +742,6 @@
       </c>
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="n"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -814,11 +749,6 @@
       </c>
       <c r="D19" s="2" t="n"/>
       <c r="E19" s="2" t="n"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -826,11 +756,6 @@
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="n"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -838,11 +763,6 @@
       </c>
       <c r="D21" s="2" t="n"/>
       <c r="E21" s="2" t="n"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -850,11 +770,6 @@
       </c>
       <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="n"/>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -862,11 +777,6 @@
       </c>
       <c r="D23" s="2" t="n"/>
       <c r="E23" s="2" t="n"/>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -874,11 +784,6 @@
       </c>
       <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="n"/>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -886,11 +791,6 @@
       </c>
       <c r="D25" s="2" t="n"/>
       <c r="E25" s="2" t="n"/>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -898,11 +798,6 @@
       </c>
       <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="n"/>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -910,11 +805,6 @@
       </c>
       <c r="D27" s="2" t="n"/>
       <c r="E27" s="2" t="n"/>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -922,11 +812,6 @@
       </c>
       <c r="D28" s="2" t="n"/>
       <c r="E28" s="2" t="n"/>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -934,11 +819,6 @@
       </c>
       <c r="D29" s="2" t="n"/>
       <c r="E29" s="2" t="n"/>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -946,11 +826,6 @@
       </c>
       <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="n"/>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -958,11 +833,6 @@
       </c>
       <c r="D31" s="2" t="n"/>
       <c r="E31" s="2" t="n"/>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -970,11 +840,6 @@
       </c>
       <c r="D32" s="2" t="n"/>
       <c r="E32" s="2" t="n"/>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -982,11 +847,6 @@
       </c>
       <c r="D33" s="2" t="n"/>
       <c r="E33" s="2" t="n"/>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -994,11 +854,6 @@
       </c>
       <c r="D34" s="2" t="n"/>
       <c r="E34" s="2" t="n"/>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1006,11 +861,6 @@
       </c>
       <c r="D35" s="2" t="n"/>
       <c r="E35" s="2" t="n"/>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1018,11 +868,6 @@
       </c>
       <c r="D36" s="2" t="n"/>
       <c r="E36" s="2" t="n"/>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1030,11 +875,6 @@
       </c>
       <c r="D37" s="2" t="n"/>
       <c r="E37" s="2" t="n"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1042,11 +882,6 @@
       </c>
       <c r="D38" s="2" t="n"/>
       <c r="E38" s="2" t="n"/>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1054,11 +889,6 @@
       </c>
       <c r="D39" s="2" t="n"/>
       <c r="E39" s="2" t="n"/>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1066,11 +896,6 @@
       </c>
       <c r="D40" s="2" t="n"/>
       <c r="E40" s="2" t="n"/>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1078,11 +903,6 @@
       </c>
       <c r="D41" s="2" t="n"/>
       <c r="E41" s="2" t="n"/>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1090,11 +910,6 @@
       </c>
       <c r="D42" s="2" t="n"/>
       <c r="E42" s="2" t="n"/>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1102,11 +917,6 @@
       </c>
       <c r="D43" s="2" t="n"/>
       <c r="E43" s="2" t="n"/>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1114,11 +924,6 @@
       </c>
       <c r="D44" s="2" t="n"/>
       <c r="E44" s="2" t="n"/>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1126,11 +931,6 @@
       </c>
       <c r="D45" s="2" t="n"/>
       <c r="E45" s="2" t="n"/>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1138,11 +938,6 @@
       </c>
       <c r="D46" s="2" t="n"/>
       <c r="E46" s="2" t="n"/>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1150,11 +945,6 @@
       </c>
       <c r="D47" s="2" t="n"/>
       <c r="E47" s="2" t="n"/>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1162,11 +952,6 @@
       </c>
       <c r="D48" s="2" t="n"/>
       <c r="E48" s="2" t="n"/>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1174,11 +959,6 @@
       </c>
       <c r="D49" s="2" t="n"/>
       <c r="E49" s="2" t="n"/>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1186,11 +966,6 @@
       </c>
       <c r="D50" s="2" t="n"/>
       <c r="E50" s="2" t="n"/>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1198,11 +973,6 @@
       </c>
       <c r="D51" s="2" t="n"/>
       <c r="E51" s="2" t="n"/>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1210,11 +980,6 @@
       </c>
       <c r="D52" s="2" t="n"/>
       <c r="E52" s="2" t="n"/>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1222,11 +987,6 @@
       </c>
       <c r="D53" s="2" t="n"/>
       <c r="E53" s="2" t="n"/>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1234,11 +994,6 @@
       </c>
       <c r="D54" s="2" t="n"/>
       <c r="E54" s="2" t="n"/>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1246,11 +1001,6 @@
       </c>
       <c r="D55" s="2" t="n"/>
       <c r="E55" s="2" t="n"/>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1258,11 +1008,6 @@
       </c>
       <c r="D56" s="2" t="n"/>
       <c r="E56" s="2" t="n"/>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1270,11 +1015,6 @@
       </c>
       <c r="D57" s="2" t="n"/>
       <c r="E57" s="2" t="n"/>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1282,11 +1022,6 @@
       </c>
       <c r="D58" s="2" t="n"/>
       <c r="E58" s="2" t="n"/>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1294,11 +1029,6 @@
       </c>
       <c r="D59" s="2" t="n"/>
       <c r="E59" s="2" t="n"/>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1306,11 +1036,6 @@
       </c>
       <c r="D60" s="2" t="n"/>
       <c r="E60" s="2" t="n"/>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1318,11 +1043,6 @@
       </c>
       <c r="D61" s="2" t="n"/>
       <c r="E61" s="2" t="n"/>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1330,11 +1050,6 @@
       </c>
       <c r="D62" s="2" t="n"/>
       <c r="E62" s="2" t="n"/>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1342,11 +1057,6 @@
       </c>
       <c r="D63" s="2" t="n"/>
       <c r="E63" s="2" t="n"/>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1354,11 +1064,6 @@
       </c>
       <c r="D64" s="2" t="n"/>
       <c r="E64" s="2" t="n"/>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1366,11 +1071,6 @@
       </c>
       <c r="D65" s="2" t="n"/>
       <c r="E65" s="2" t="n"/>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1378,11 +1078,6 @@
       </c>
       <c r="D66" s="2" t="n"/>
       <c r="E66" s="2" t="n"/>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1390,11 +1085,6 @@
       </c>
       <c r="D67" s="2" t="n"/>
       <c r="E67" s="2" t="n"/>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1402,11 +1092,6 @@
       </c>
       <c r="D68" s="2" t="n"/>
       <c r="E68" s="2" t="n"/>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1414,11 +1099,6 @@
       </c>
       <c r="D69" s="2" t="n"/>
       <c r="E69" s="2" t="n"/>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1426,11 +1106,6 @@
       </c>
       <c r="D70" s="2" t="n"/>
       <c r="E70" s="2" t="n"/>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1438,11 +1113,6 @@
       </c>
       <c r="D71" s="2" t="n"/>
       <c r="E71" s="2" t="n"/>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -1450,11 +1120,6 @@
       </c>
       <c r="D72" s="2" t="n"/>
       <c r="E72" s="2" t="n"/>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -1462,11 +1127,6 @@
       </c>
       <c r="D73" s="2" t="n"/>
       <c r="E73" s="2" t="n"/>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -1474,11 +1134,6 @@
       </c>
       <c r="D74" s="2" t="n"/>
       <c r="E74" s="2" t="n"/>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -1486,11 +1141,6 @@
       </c>
       <c r="D75" s="2" t="n"/>
       <c r="E75" s="2" t="n"/>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -1498,11 +1148,6 @@
       </c>
       <c r="D76" s="2" t="n"/>
       <c r="E76" s="2" t="n"/>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -1510,11 +1155,6 @@
       </c>
       <c r="D77" s="2" t="n"/>
       <c r="E77" s="2" t="n"/>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -1522,11 +1162,6 @@
       </c>
       <c r="D78" s="2" t="n"/>
       <c r="E78" s="2" t="n"/>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -1534,11 +1169,6 @@
       </c>
       <c r="D79" s="2" t="n"/>
       <c r="E79" s="2" t="n"/>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -1546,11 +1176,6 @@
       </c>
       <c r="D80" s="2" t="n"/>
       <c r="E80" s="2" t="n"/>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -1558,11 +1183,6 @@
       </c>
       <c r="D81" s="2" t="n"/>
       <c r="E81" s="2" t="n"/>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -1570,11 +1190,6 @@
       </c>
       <c r="D82" s="2" t="n"/>
       <c r="E82" s="2" t="n"/>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -1582,11 +1197,6 @@
       </c>
       <c r="D83" s="2" t="n"/>
       <c r="E83" s="2" t="n"/>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -1594,11 +1204,6 @@
       </c>
       <c r="D84" s="2" t="n"/>
       <c r="E84" s="2" t="n"/>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -1606,11 +1211,6 @@
       </c>
       <c r="D85" s="2" t="n"/>
       <c r="E85" s="2" t="n"/>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -1618,11 +1218,6 @@
       </c>
       <c r="D86" s="2" t="n"/>
       <c r="E86" s="2" t="n"/>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -1630,11 +1225,6 @@
       </c>
       <c r="D87" s="2" t="n"/>
       <c r="E87" s="2" t="n"/>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -1642,11 +1232,6 @@
       </c>
       <c r="D88" s="2" t="n"/>
       <c r="E88" s="2" t="n"/>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -1654,11 +1239,6 @@
       </c>
       <c r="D89" s="2" t="n"/>
       <c r="E89" s="2" t="n"/>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -1666,11 +1246,6 @@
       </c>
       <c r="D90" s="2" t="n"/>
       <c r="E90" s="2" t="n"/>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -1678,11 +1253,6 @@
       </c>
       <c r="D91" s="2" t="n"/>
       <c r="E91" s="2" t="n"/>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -1690,11 +1260,6 @@
       </c>
       <c r="D92" s="2" t="n"/>
       <c r="E92" s="2" t="n"/>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -1702,11 +1267,6 @@
       </c>
       <c r="D93" s="2" t="n"/>
       <c r="E93" s="2" t="n"/>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -1714,11 +1274,6 @@
       </c>
       <c r="D94" s="2" t="n"/>
       <c r="E94" s="2" t="n"/>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -1726,11 +1281,6 @@
       </c>
       <c r="D95" s="2" t="n"/>
       <c r="E95" s="2" t="n"/>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -1738,11 +1288,6 @@
       </c>
       <c r="D96" s="2" t="n"/>
       <c r="E96" s="2" t="n"/>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -1750,11 +1295,6 @@
       </c>
       <c r="D97" s="2" t="n"/>
       <c r="E97" s="2" t="n"/>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -1762,11 +1302,6 @@
       </c>
       <c r="D98" s="2" t="n"/>
       <c r="E98" s="2" t="n"/>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -1774,11 +1309,6 @@
       </c>
       <c r="D99" s="2" t="n"/>
       <c r="E99" s="2" t="n"/>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -1786,11 +1316,6 @@
       </c>
       <c r="D100" s="2" t="n"/>
       <c r="E100" s="2" t="n"/>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -1798,11 +1323,6 @@
       </c>
       <c r="D101" s="2" t="n"/>
       <c r="E101" s="2" t="n"/>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -1810,11 +1330,6 @@
       </c>
       <c r="D102" s="2" t="n"/>
       <c r="E102" s="2" t="n"/>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -1822,11 +1337,6 @@
       </c>
       <c r="D103" s="2" t="n"/>
       <c r="E103" s="2" t="n"/>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -1834,11 +1344,6 @@
       </c>
       <c r="D104" s="2" t="n"/>
       <c r="E104" s="2" t="n"/>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -1846,11 +1351,6 @@
       </c>
       <c r="D105" s="2" t="n"/>
       <c r="E105" s="2" t="n"/>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -1858,11 +1358,6 @@
       </c>
       <c r="D106" s="2" t="n"/>
       <c r="E106" s="2" t="n"/>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -1870,11 +1365,6 @@
       </c>
       <c r="D107" s="2" t="n"/>
       <c r="E107" s="2" t="n"/>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -1882,11 +1372,6 @@
       </c>
       <c r="D108" s="2" t="n"/>
       <c r="E108" s="2" t="n"/>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -1894,11 +1379,6 @@
       </c>
       <c r="D109" s="2" t="n"/>
       <c r="E109" s="2" t="n"/>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -1906,11 +1386,6 @@
       </c>
       <c r="D110" s="2" t="n"/>
       <c r="E110" s="2" t="n"/>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -1918,11 +1393,6 @@
       </c>
       <c r="D111" s="2" t="n"/>
       <c r="E111" s="2" t="n"/>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -1930,11 +1400,6 @@
       </c>
       <c r="D112" s="2" t="n"/>
       <c r="E112" s="2" t="n"/>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -1942,11 +1407,6 @@
       </c>
       <c r="D113" s="2" t="n"/>
       <c r="E113" s="2" t="n"/>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -1954,11 +1414,6 @@
       </c>
       <c r="D114" s="2" t="n"/>
       <c r="E114" s="2" t="n"/>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -1966,11 +1421,6 @@
       </c>
       <c r="D115" s="2" t="n"/>
       <c r="E115" s="2" t="n"/>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -1978,11 +1428,6 @@
       </c>
       <c r="D116" s="2" t="n"/>
       <c r="E116" s="2" t="n"/>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -1990,11 +1435,6 @@
       </c>
       <c r="D117" s="2" t="n"/>
       <c r="E117" s="2" t="n"/>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -2002,11 +1442,6 @@
       </c>
       <c r="D118" s="2" t="n"/>
       <c r="E118" s="2" t="n"/>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -2014,11 +1449,6 @@
       </c>
       <c r="D119" s="2" t="n"/>
       <c r="E119" s="2" t="n"/>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -2026,11 +1456,6 @@
       </c>
       <c r="D120" s="2" t="n"/>
       <c r="E120" s="2" t="n"/>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -2038,11 +1463,6 @@
       </c>
       <c r="D121" s="2" t="n"/>
       <c r="E121" s="2" t="n"/>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -2050,11 +1470,6 @@
       </c>
       <c r="D122" s="2" t="n"/>
       <c r="E122" s="2" t="n"/>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -2062,11 +1477,6 @@
       </c>
       <c r="D123" s="2" t="n"/>
       <c r="E123" s="2" t="n"/>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -2074,11 +1484,6 @@
       </c>
       <c r="D124" s="2" t="n"/>
       <c r="E124" s="2" t="n"/>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -2086,11 +1491,6 @@
       </c>
       <c r="D125" s="2" t="n"/>
       <c r="E125" s="2" t="n"/>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -2098,11 +1498,6 @@
       </c>
       <c r="D126" s="2" t="n"/>
       <c r="E126" s="2" t="n"/>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -2110,11 +1505,6 @@
       </c>
       <c r="D127" s="2" t="n"/>
       <c r="E127" s="2" t="n"/>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -2122,11 +1512,6 @@
       </c>
       <c r="D128" s="2" t="n"/>
       <c r="E128" s="2" t="n"/>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -2134,11 +1519,6 @@
       </c>
       <c r="D129" s="2" t="n"/>
       <c r="E129" s="2" t="n"/>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -2146,11 +1526,6 @@
       </c>
       <c r="D130" s="2" t="n"/>
       <c r="E130" s="2" t="n"/>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -2158,11 +1533,6 @@
       </c>
       <c r="D131" s="2" t="n"/>
       <c r="E131" s="2" t="n"/>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -2170,11 +1540,6 @@
       </c>
       <c r="D132" s="2" t="n"/>
       <c r="E132" s="2" t="n"/>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -2182,11 +1547,6 @@
       </c>
       <c r="D133" s="2" t="n"/>
       <c r="E133" s="2" t="n"/>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -2194,11 +1554,6 @@
       </c>
       <c r="D134" s="2" t="n"/>
       <c r="E134" s="2" t="n"/>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -2206,11 +1561,6 @@
       </c>
       <c r="D135" s="2" t="n"/>
       <c r="E135" s="2" t="n"/>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -2218,11 +1568,6 @@
       </c>
       <c r="D136" s="2" t="n"/>
       <c r="E136" s="2" t="n"/>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -2230,11 +1575,6 @@
       </c>
       <c r="D137" s="2" t="n"/>
       <c r="E137" s="2" t="n"/>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -2242,11 +1582,6 @@
       </c>
       <c r="D138" s="2" t="n"/>
       <c r="E138" s="2" t="n"/>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -2254,11 +1589,6 @@
       </c>
       <c r="D139" s="2" t="n"/>
       <c r="E139" s="2" t="n"/>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -2266,11 +1596,6 @@
       </c>
       <c r="D140" s="2" t="n"/>
       <c r="E140" s="2" t="n"/>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -2278,11 +1603,6 @@
       </c>
       <c r="D141" s="2" t="n"/>
       <c r="E141" s="2" t="n"/>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -2290,11 +1610,6 @@
       </c>
       <c r="D142" s="2" t="n"/>
       <c r="E142" s="2" t="n"/>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -2302,11 +1617,6 @@
       </c>
       <c r="D143" s="2" t="n"/>
       <c r="E143" s="2" t="n"/>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -2314,11 +1624,6 @@
       </c>
       <c r="D144" s="2" t="n"/>
       <c r="E144" s="2" t="n"/>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -2326,11 +1631,6 @@
       </c>
       <c r="D145" s="2" t="n"/>
       <c r="E145" s="2" t="n"/>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -2338,11 +1638,6 @@
       </c>
       <c r="D146" s="2" t="n"/>
       <c r="E146" s="2" t="n"/>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -2350,11 +1645,6 @@
       </c>
       <c r="D147" s="2" t="n"/>
       <c r="E147" s="2" t="n"/>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -2362,11 +1652,6 @@
       </c>
       <c r="D148" s="2" t="n"/>
       <c r="E148" s="2" t="n"/>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -2374,11 +1659,6 @@
       </c>
       <c r="D149" s="2" t="n"/>
       <c r="E149" s="2" t="n"/>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -2386,11 +1666,6 @@
       </c>
       <c r="D150" s="2" t="n"/>
       <c r="E150" s="2" t="n"/>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -2398,11 +1673,6 @@
       </c>
       <c r="D151" s="2" t="n"/>
       <c r="E151" s="2" t="n"/>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -2410,11 +1680,6 @@
       </c>
       <c r="D152" s="2" t="n"/>
       <c r="E152" s="2" t="n"/>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -2422,11 +1687,6 @@
       </c>
       <c r="D153" s="2" t="n"/>
       <c r="E153" s="2" t="n"/>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -2434,11 +1694,6 @@
       </c>
       <c r="D154" s="2" t="n"/>
       <c r="E154" s="2" t="n"/>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -2446,11 +1701,6 @@
       </c>
       <c r="D155" s="2" t="n"/>
       <c r="E155" s="2" t="n"/>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -2458,11 +1708,6 @@
       </c>
       <c r="D156" s="2" t="n"/>
       <c r="E156" s="2" t="n"/>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -2470,11 +1715,6 @@
       </c>
       <c r="D157" s="2" t="n"/>
       <c r="E157" s="2" t="n"/>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -2482,11 +1722,6 @@
       </c>
       <c r="D158" s="2" t="n"/>
       <c r="E158" s="2" t="n"/>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -2494,11 +1729,6 @@
       </c>
       <c r="D159" s="2" t="n"/>
       <c r="E159" s="2" t="n"/>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -2506,11 +1736,6 @@
       </c>
       <c r="D160" s="2" t="n"/>
       <c r="E160" s="2" t="n"/>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -2518,11 +1743,6 @@
       </c>
       <c r="D161" s="2" t="n"/>
       <c r="E161" s="2" t="n"/>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -2530,11 +1750,6 @@
       </c>
       <c r="D162" s="2" t="n"/>
       <c r="E162" s="2" t="n"/>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -2542,11 +1757,6 @@
       </c>
       <c r="D163" s="2" t="n"/>
       <c r="E163" s="2" t="n"/>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -2554,11 +1764,6 @@
       </c>
       <c r="D164" s="2" t="n"/>
       <c r="E164" s="2" t="n"/>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -2566,11 +1771,6 @@
       </c>
       <c r="D165" s="2" t="n"/>
       <c r="E165" s="2" t="n"/>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -2578,11 +1778,6 @@
       </c>
       <c r="D166" s="2" t="n"/>
       <c r="E166" s="2" t="n"/>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -2590,11 +1785,6 @@
       </c>
       <c r="D167" s="2" t="n"/>
       <c r="E167" s="2" t="n"/>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -2602,11 +1792,6 @@
       </c>
       <c r="D168" s="2" t="n"/>
       <c r="E168" s="2" t="n"/>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -2614,11 +1799,6 @@
       </c>
       <c r="D169" s="2" t="n"/>
       <c r="E169" s="2" t="n"/>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -2626,11 +1806,6 @@
       </c>
       <c r="D170" s="2" t="n"/>
       <c r="E170" s="2" t="n"/>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -2638,11 +1813,6 @@
       </c>
       <c r="D171" s="2" t="n"/>
       <c r="E171" s="2" t="n"/>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -2650,11 +1820,6 @@
       </c>
       <c r="D172" s="2" t="n"/>
       <c r="E172" s="2" t="n"/>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -2662,11 +1827,6 @@
       </c>
       <c r="D173" s="2" t="n"/>
       <c r="E173" s="2" t="n"/>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -2674,11 +1834,6 @@
       </c>
       <c r="D174" s="2" t="n"/>
       <c r="E174" s="2" t="n"/>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -2686,11 +1841,6 @@
       </c>
       <c r="D175" s="2" t="n"/>
       <c r="E175" s="2" t="n"/>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -2698,11 +1848,6 @@
       </c>
       <c r="D176" s="2" t="n"/>
       <c r="E176" s="2" t="n"/>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -2710,11 +1855,6 @@
       </c>
       <c r="D177" s="2" t="n"/>
       <c r="E177" s="2" t="n"/>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -2722,11 +1862,6 @@
       </c>
       <c r="D178" s="2" t="n"/>
       <c r="E178" s="2" t="n"/>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -2734,11 +1869,6 @@
       </c>
       <c r="D179" s="2" t="n"/>
       <c r="E179" s="2" t="n"/>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -2746,11 +1876,6 @@
       </c>
       <c r="D180" s="2" t="n"/>
       <c r="E180" s="2" t="n"/>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -2758,11 +1883,6 @@
       </c>
       <c r="D181" s="2" t="n"/>
       <c r="E181" s="2" t="n"/>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -2770,11 +1890,6 @@
       </c>
       <c r="D182" s="2" t="n"/>
       <c r="E182" s="2" t="n"/>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -2782,11 +1897,6 @@
       </c>
       <c r="D183" s="2" t="n"/>
       <c r="E183" s="2" t="n"/>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -2794,11 +1904,6 @@
       </c>
       <c r="D184" s="2" t="n"/>
       <c r="E184" s="2" t="n"/>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -2806,11 +1911,6 @@
       </c>
       <c r="D185" s="2" t="n"/>
       <c r="E185" s="2" t="n"/>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -2818,11 +1918,6 @@
       </c>
       <c r="D186" s="2" t="n"/>
       <c r="E186" s="2" t="n"/>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -2830,11 +1925,6 @@
       </c>
       <c r="D187" s="2" t="n"/>
       <c r="E187" s="2" t="n"/>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -2842,11 +1932,6 @@
       </c>
       <c r="D188" s="2" t="n"/>
       <c r="E188" s="2" t="n"/>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -2854,11 +1939,6 @@
       </c>
       <c r="D189" s="2" t="n"/>
       <c r="E189" s="2" t="n"/>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -2866,11 +1946,6 @@
       </c>
       <c r="D190" s="2" t="n"/>
       <c r="E190" s="2" t="n"/>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -2878,11 +1953,6 @@
       </c>
       <c r="D191" s="2" t="n"/>
       <c r="E191" s="2" t="n"/>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -2890,11 +1960,6 @@
       </c>
       <c r="D192" s="2" t="n"/>
       <c r="E192" s="2" t="n"/>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -2902,11 +1967,6 @@
       </c>
       <c r="D193" s="2" t="n"/>
       <c r="E193" s="2" t="n"/>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -2914,11 +1974,6 @@
       </c>
       <c r="D194" s="2" t="n"/>
       <c r="E194" s="2" t="n"/>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -2926,11 +1981,6 @@
       </c>
       <c r="D195" s="2" t="n"/>
       <c r="E195" s="2" t="n"/>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -2938,11 +1988,6 @@
       </c>
       <c r="D196" s="2" t="n"/>
       <c r="E196" s="2" t="n"/>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -2950,11 +1995,6 @@
       </c>
       <c r="D197" s="2" t="n"/>
       <c r="E197" s="2" t="n"/>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -2962,11 +2002,6 @@
       </c>
       <c r="D198" s="2" t="n"/>
       <c r="E198" s="2" t="n"/>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -2974,11 +2009,6 @@
       </c>
       <c r="D199" s="2" t="n"/>
       <c r="E199" s="2" t="n"/>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -2986,11 +2016,6 @@
       </c>
       <c r="D200" s="2" t="n"/>
       <c r="E200" s="2" t="n"/>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -2998,11 +2023,6 @@
       </c>
       <c r="D201" s="2" t="n"/>
       <c r="E201" s="2" t="n"/>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -3010,11 +2030,6 @@
       </c>
       <c r="D202" s="2" t="n"/>
       <c r="E202" s="2" t="n"/>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -3022,11 +2037,6 @@
       </c>
       <c r="D203" s="2" t="n"/>
       <c r="E203" s="2" t="n"/>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -3034,11 +2044,6 @@
       </c>
       <c r="D204" s="2" t="n"/>
       <c r="E204" s="2" t="n"/>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -3046,11 +2051,6 @@
       </c>
       <c r="D205" s="2" t="n"/>
       <c r="E205" s="2" t="n"/>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -3058,11 +2058,6 @@
       </c>
       <c r="D206" s="2" t="n"/>
       <c r="E206" s="2" t="n"/>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -3070,11 +2065,6 @@
       </c>
       <c r="D207" s="2" t="n"/>
       <c r="E207" s="2" t="n"/>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -3082,11 +2072,6 @@
       </c>
       <c r="D208" s="2" t="n"/>
       <c r="E208" s="2" t="n"/>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -3094,11 +2079,6 @@
       </c>
       <c r="D209" s="2" t="n"/>
       <c r="E209" s="2" t="n"/>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -3106,11 +2086,6 @@
       </c>
       <c r="D210" s="2" t="n"/>
       <c r="E210" s="2" t="n"/>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -3118,11 +2093,6 @@
       </c>
       <c r="D211" s="2" t="n"/>
       <c r="E211" s="2" t="n"/>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -3130,11 +2100,6 @@
       </c>
       <c r="D212" s="2" t="n"/>
       <c r="E212" s="2" t="n"/>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -3142,11 +2107,6 @@
       </c>
       <c r="D213" s="2" t="n"/>
       <c r="E213" s="2" t="n"/>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -3154,11 +2114,6 @@
       </c>
       <c r="D214" s="2" t="n"/>
       <c r="E214" s="2" t="n"/>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -3166,11 +2121,6 @@
       </c>
       <c r="D215" s="2" t="n"/>
       <c r="E215" s="2" t="n"/>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -3178,11 +2128,6 @@
       </c>
       <c r="D216" s="2" t="n"/>
       <c r="E216" s="2" t="n"/>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -3190,11 +2135,6 @@
       </c>
       <c r="D217" s="2" t="n"/>
       <c r="E217" s="2" t="n"/>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -3202,11 +2142,6 @@
       </c>
       <c r="D218" s="2" t="n"/>
       <c r="E218" s="2" t="n"/>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -3214,11 +2149,6 @@
       </c>
       <c r="D219" s="2" t="n"/>
       <c r="E219" s="2" t="n"/>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -3226,11 +2156,6 @@
       </c>
       <c r="D220" s="2" t="n"/>
       <c r="E220" s="2" t="n"/>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -3238,11 +2163,6 @@
       </c>
       <c r="D221" s="2" t="n"/>
       <c r="E221" s="2" t="n"/>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -3250,11 +2170,6 @@
       </c>
       <c r="D222" s="2" t="n"/>
       <c r="E222" s="2" t="n"/>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -3262,11 +2177,6 @@
       </c>
       <c r="D223" s="2" t="n"/>
       <c r="E223" s="2" t="n"/>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -3274,11 +2184,6 @@
       </c>
       <c r="D224" s="2" t="n"/>
       <c r="E224" s="2" t="n"/>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -3286,11 +2191,6 @@
       </c>
       <c r="D225" s="2" t="n"/>
       <c r="E225" s="2" t="n"/>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -3298,11 +2198,6 @@
       </c>
       <c r="D226" s="2" t="n"/>
       <c r="E226" s="2" t="n"/>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -3310,11 +2205,6 @@
       </c>
       <c r="D227" s="2" t="n"/>
       <c r="E227" s="2" t="n"/>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -3322,11 +2212,6 @@
       </c>
       <c r="D228" s="2" t="n"/>
       <c r="E228" s="2" t="n"/>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -3334,11 +2219,6 @@
       </c>
       <c r="D229" s="2" t="n"/>
       <c r="E229" s="2" t="n"/>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -3346,11 +2226,6 @@
       </c>
       <c r="D230" s="2" t="n"/>
       <c r="E230" s="2" t="n"/>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -3358,11 +2233,6 @@
       </c>
       <c r="D231" s="2" t="n"/>
       <c r="E231" s="2" t="n"/>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -3370,11 +2240,6 @@
       </c>
       <c r="D232" s="2" t="n"/>
       <c r="E232" s="2" t="n"/>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -3382,11 +2247,6 @@
       </c>
       <c r="D233" s="2" t="n"/>
       <c r="E233" s="2" t="n"/>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -3394,11 +2254,6 @@
       </c>
       <c r="D234" s="2" t="n"/>
       <c r="E234" s="2" t="n"/>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -3406,11 +2261,6 @@
       </c>
       <c r="D235" s="2" t="n"/>
       <c r="E235" s="2" t="n"/>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -3418,11 +2268,6 @@
       </c>
       <c r="D236" s="2" t="n"/>
       <c r="E236" s="2" t="n"/>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -3430,11 +2275,6 @@
       </c>
       <c r="D237" s="2" t="n"/>
       <c r="E237" s="2" t="n"/>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -3442,11 +2282,6 @@
       </c>
       <c r="D238" s="2" t="n"/>
       <c r="E238" s="2" t="n"/>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -3454,11 +2289,6 @@
       </c>
       <c r="D239" s="2" t="n"/>
       <c r="E239" s="2" t="n"/>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -3466,11 +2296,6 @@
       </c>
       <c r="D240" s="2" t="n"/>
       <c r="E240" s="2" t="n"/>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -3478,11 +2303,6 @@
       </c>
       <c r="D241" s="2" t="n"/>
       <c r="E241" s="2" t="n"/>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -3490,11 +2310,6 @@
       </c>
       <c r="D242" s="2" t="n"/>
       <c r="E242" s="2" t="n"/>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -3502,11 +2317,6 @@
       </c>
       <c r="D243" s="2" t="n"/>
       <c r="E243" s="2" t="n"/>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -3514,11 +2324,6 @@
       </c>
       <c r="D244" s="2" t="n"/>
       <c r="E244" s="2" t="n"/>
-      <c r="G244" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -3526,11 +2331,6 @@
       </c>
       <c r="D245" s="2" t="n"/>
       <c r="E245" s="2" t="n"/>
-      <c r="G245" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -3538,11 +2338,6 @@
       </c>
       <c r="D246" s="2" t="n"/>
       <c r="E246" s="2" t="n"/>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -3550,11 +2345,6 @@
       </c>
       <c r="D247" s="2" t="n"/>
       <c r="E247" s="2" t="n"/>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -3562,11 +2352,6 @@
       </c>
       <c r="D248" s="2" t="n"/>
       <c r="E248" s="2" t="n"/>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -3574,11 +2359,6 @@
       </c>
       <c r="D249" s="2" t="n"/>
       <c r="E249" s="2" t="n"/>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -3586,11 +2366,6 @@
       </c>
       <c r="D250" s="2" t="n"/>
       <c r="E250" s="2" t="n"/>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -3598,11 +2373,6 @@
       </c>
       <c r="D251" s="2" t="n"/>
       <c r="E251" s="2" t="n"/>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -3610,11 +2380,6 @@
       </c>
       <c r="D252" s="2" t="n"/>
       <c r="E252" s="2" t="n"/>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -3622,11 +2387,6 @@
       </c>
       <c r="D253" s="2" t="n"/>
       <c r="E253" s="2" t="n"/>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -3634,11 +2394,6 @@
       </c>
       <c r="D254" s="2" t="n"/>
       <c r="E254" s="2" t="n"/>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -3646,11 +2401,6 @@
       </c>
       <c r="D255" s="2" t="n"/>
       <c r="E255" s="2" t="n"/>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -3658,11 +2408,6 @@
       </c>
       <c r="D256" s="2" t="n"/>
       <c r="E256" s="2" t="n"/>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -3670,11 +2415,6 @@
       </c>
       <c r="D257" s="2" t="n"/>
       <c r="E257" s="2" t="n"/>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -3682,11 +2422,6 @@
       </c>
       <c r="D258" s="2" t="n"/>
       <c r="E258" s="2" t="n"/>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -3694,11 +2429,6 @@
       </c>
       <c r="D259" s="2" t="n"/>
       <c r="E259" s="2" t="n"/>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -3706,11 +2436,6 @@
       </c>
       <c r="D260" s="2" t="n"/>
       <c r="E260" s="2" t="n"/>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -3718,11 +2443,6 @@
       </c>
       <c r="D261" s="2" t="n"/>
       <c r="E261" s="2" t="n"/>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -3730,11 +2450,6 @@
       </c>
       <c r="D262" s="2" t="n"/>
       <c r="E262" s="2" t="n"/>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -3742,11 +2457,6 @@
       </c>
       <c r="D263" s="2" t="n"/>
       <c r="E263" s="2" t="n"/>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -3754,11 +2464,6 @@
       </c>
       <c r="D264" s="2" t="n"/>
       <c r="E264" s="2" t="n"/>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -3766,11 +2471,6 @@
       </c>
       <c r="D265" s="2" t="n"/>
       <c r="E265" s="2" t="n"/>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -3778,11 +2478,6 @@
       </c>
       <c r="D266" s="2" t="n"/>
       <c r="E266" s="2" t="n"/>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -3790,11 +2485,6 @@
       </c>
       <c r="D267" s="2" t="n"/>
       <c r="E267" s="2" t="n"/>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -3802,11 +2492,6 @@
       </c>
       <c r="D268" s="2" t="n"/>
       <c r="E268" s="2" t="n"/>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -3814,11 +2499,6 @@
       </c>
       <c r="D269" s="2" t="n"/>
       <c r="E269" s="2" t="n"/>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -3826,11 +2506,6 @@
       </c>
       <c r="D270" s="2" t="n"/>
       <c r="E270" s="2" t="n"/>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -3838,11 +2513,6 @@
       </c>
       <c r="D271" s="2" t="n"/>
       <c r="E271" s="2" t="n"/>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -3850,11 +2520,6 @@
       </c>
       <c r="D272" s="2" t="n"/>
       <c r="E272" s="2" t="n"/>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -3862,11 +2527,6 @@
       </c>
       <c r="D273" s="2" t="n"/>
       <c r="E273" s="2" t="n"/>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -3874,11 +2534,6 @@
       </c>
       <c r="D274" s="2" t="n"/>
       <c r="E274" s="2" t="n"/>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -3886,11 +2541,6 @@
       </c>
       <c r="D275" s="2" t="n"/>
       <c r="E275" s="2" t="n"/>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -3898,11 +2548,6 @@
       </c>
       <c r="D276" s="2" t="n"/>
       <c r="E276" s="2" t="n"/>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -3910,11 +2555,6 @@
       </c>
       <c r="D277" s="2" t="n"/>
       <c r="E277" s="2" t="n"/>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -3922,11 +2562,6 @@
       </c>
       <c r="D278" s="2" t="n"/>
       <c r="E278" s="2" t="n"/>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -3934,11 +2569,6 @@
       </c>
       <c r="D279" s="2" t="n"/>
       <c r="E279" s="2" t="n"/>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -3946,11 +2576,6 @@
       </c>
       <c r="D280" s="2" t="n"/>
       <c r="E280" s="2" t="n"/>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -3958,11 +2583,6 @@
       </c>
       <c r="D281" s="2" t="n"/>
       <c r="E281" s="2" t="n"/>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -3970,11 +2590,6 @@
       </c>
       <c r="D282" s="2" t="n"/>
       <c r="E282" s="2" t="n"/>
-      <c r="G282" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -3982,11 +2597,6 @@
       </c>
       <c r="D283" s="2" t="n"/>
       <c r="E283" s="2" t="n"/>
-      <c r="G283" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -3994,11 +2604,6 @@
       </c>
       <c r="D284" s="2" t="n"/>
       <c r="E284" s="2" t="n"/>
-      <c r="G284" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -4006,11 +2611,6 @@
       </c>
       <c r="D285" s="2" t="n"/>
       <c r="E285" s="2" t="n"/>
-      <c r="G285" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -4018,11 +2618,6 @@
       </c>
       <c r="D286" s="2" t="n"/>
       <c r="E286" s="2" t="n"/>
-      <c r="G286" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -4030,11 +2625,6 @@
       </c>
       <c r="D287" s="2" t="n"/>
       <c r="E287" s="2" t="n"/>
-      <c r="G287" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -4042,11 +2632,6 @@
       </c>
       <c r="D288" s="2" t="n"/>
       <c r="E288" s="2" t="n"/>
-      <c r="G288" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -4054,11 +2639,6 @@
       </c>
       <c r="D289" s="2" t="n"/>
       <c r="E289" s="2" t="n"/>
-      <c r="G289" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -4066,11 +2646,6 @@
       </c>
       <c r="D290" s="2" t="n"/>
       <c r="E290" s="2" t="n"/>
-      <c r="G290" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -4078,11 +2653,6 @@
       </c>
       <c r="D291" s="2" t="n"/>
       <c r="E291" s="2" t="n"/>
-      <c r="G291" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -4090,11 +2660,6 @@
       </c>
       <c r="D292" s="2" t="n"/>
       <c r="E292" s="2" t="n"/>
-      <c r="G292" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -4102,11 +2667,6 @@
       </c>
       <c r="D293" s="2" t="n"/>
       <c r="E293" s="2" t="n"/>
-      <c r="G293" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -4114,11 +2674,6 @@
       </c>
       <c r="D294" s="2" t="n"/>
       <c r="E294" s="2" t="n"/>
-      <c r="G294" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -4126,11 +2681,6 @@
       </c>
       <c r="D295" s="2" t="n"/>
       <c r="E295" s="2" t="n"/>
-      <c r="G295" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -4138,11 +2688,6 @@
       </c>
       <c r="D296" s="2" t="n"/>
       <c r="E296" s="2" t="n"/>
-      <c r="G296" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -4150,11 +2695,6 @@
       </c>
       <c r="D297" s="2" t="n"/>
       <c r="E297" s="2" t="n"/>
-      <c r="G297" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -4162,11 +2702,6 @@
       </c>
       <c r="D298" s="2" t="n"/>
       <c r="E298" s="2" t="n"/>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -4174,11 +2709,6 @@
       </c>
       <c r="D299" s="2" t="n"/>
       <c r="E299" s="2" t="n"/>
-      <c r="G299" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -4186,11 +2716,6 @@
       </c>
       <c r="D300" s="2" t="n"/>
       <c r="E300" s="2" t="n"/>
-      <c r="G300" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -4198,11 +2723,6 @@
       </c>
       <c r="D301" s="2" t="n"/>
       <c r="E301" s="2" t="n"/>
-      <c r="G301" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -4210,11 +2730,6 @@
       </c>
       <c r="D302" s="2" t="n"/>
       <c r="E302" s="2" t="n"/>
-      <c r="G302" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -4222,11 +2737,6 @@
       </c>
       <c r="D303" s="2" t="n"/>
       <c r="E303" s="2" t="n"/>
-      <c r="G303" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -4234,11 +2744,6 @@
       </c>
       <c r="D304" s="2" t="n"/>
       <c r="E304" s="2" t="n"/>
-      <c r="G304" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -4246,11 +2751,6 @@
       </c>
       <c r="D305" s="2" t="n"/>
       <c r="E305" s="2" t="n"/>
-      <c r="G305" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -4258,11 +2758,6 @@
       </c>
       <c r="D306" s="2" t="n"/>
       <c r="E306" s="2" t="n"/>
-      <c r="G306" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -4270,11 +2765,6 @@
       </c>
       <c r="D307" s="2" t="n"/>
       <c r="E307" s="2" t="n"/>
-      <c r="G307" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -4282,11 +2772,6 @@
       </c>
       <c r="D308" s="2" t="n"/>
       <c r="E308" s="2" t="n"/>
-      <c r="G308" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -4294,11 +2779,6 @@
       </c>
       <c r="D309" s="2" t="n"/>
       <c r="E309" s="2" t="n"/>
-      <c r="G309" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -4306,11 +2786,6 @@
       </c>
       <c r="D310" s="2" t="n"/>
       <c r="E310" s="2" t="n"/>
-      <c r="G310" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -4318,11 +2793,6 @@
       </c>
       <c r="D311" s="2" t="n"/>
       <c r="E311" s="2" t="n"/>
-      <c r="G311" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -4330,11 +2800,6 @@
       </c>
       <c r="D312" s="2" t="n"/>
       <c r="E312" s="2" t="n"/>
-      <c r="G312" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -4342,11 +2807,6 @@
       </c>
       <c r="D313" s="2" t="n"/>
       <c r="E313" s="2" t="n"/>
-      <c r="G313" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -4354,11 +2814,6 @@
       </c>
       <c r="D314" s="2" t="n"/>
       <c r="E314" s="2" t="n"/>
-      <c r="G314" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -4366,11 +2821,6 @@
       </c>
       <c r="D315" s="2" t="n"/>
       <c r="E315" s="2" t="n"/>
-      <c r="G315" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -4378,11 +2828,6 @@
       </c>
       <c r="D316" s="2" t="n"/>
       <c r="E316" s="2" t="n"/>
-      <c r="G316" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -4390,11 +2835,6 @@
       </c>
       <c r="D317" s="2" t="n"/>
       <c r="E317" s="2" t="n"/>
-      <c r="G317" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -4402,11 +2842,6 @@
       </c>
       <c r="D318" s="2" t="n"/>
       <c r="E318" s="2" t="n"/>
-      <c r="G318" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -4414,11 +2849,6 @@
       </c>
       <c r="D319" s="2" t="n"/>
       <c r="E319" s="2" t="n"/>
-      <c r="G319" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -4426,11 +2856,6 @@
       </c>
       <c r="D320" s="2" t="n"/>
       <c r="E320" s="2" t="n"/>
-      <c r="G320" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -4438,11 +2863,6 @@
       </c>
       <c r="D321" s="2" t="n"/>
       <c r="E321" s="2" t="n"/>
-      <c r="G321" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -4450,11 +2870,6 @@
       </c>
       <c r="D322" s="2" t="n"/>
       <c r="E322" s="2" t="n"/>
-      <c r="G322" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -4462,11 +2877,6 @@
       </c>
       <c r="D323" s="2" t="n"/>
       <c r="E323" s="2" t="n"/>
-      <c r="G323" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -4474,11 +2884,6 @@
       </c>
       <c r="D324" s="2" t="n"/>
       <c r="E324" s="2" t="n"/>
-      <c r="G324" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -4486,11 +2891,6 @@
       </c>
       <c r="D325" s="2" t="n"/>
       <c r="E325" s="2" t="n"/>
-      <c r="G325" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -4498,11 +2898,6 @@
       </c>
       <c r="D326" s="2" t="n"/>
       <c r="E326" s="2" t="n"/>
-      <c r="G326" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -4510,11 +2905,6 @@
       </c>
       <c r="D327" s="2" t="n"/>
       <c r="E327" s="2" t="n"/>
-      <c r="G327" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -4522,11 +2912,6 @@
       </c>
       <c r="D328" s="2" t="n"/>
       <c r="E328" s="2" t="n"/>
-      <c r="G328" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -4534,11 +2919,6 @@
       </c>
       <c r="D329" s="2" t="n"/>
       <c r="E329" s="2" t="n"/>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -4546,11 +2926,6 @@
       </c>
       <c r="D330" s="2" t="n"/>
       <c r="E330" s="2" t="n"/>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -4558,11 +2933,6 @@
       </c>
       <c r="D331" s="2" t="n"/>
       <c r="E331" s="2" t="n"/>
-      <c r="G331" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -4570,11 +2940,6 @@
       </c>
       <c r="D332" s="2" t="n"/>
       <c r="E332" s="2" t="n"/>
-      <c r="G332" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -4582,11 +2947,6 @@
       </c>
       <c r="D333" s="2" t="n"/>
       <c r="E333" s="2" t="n"/>
-      <c r="G333" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -4594,11 +2954,6 @@
       </c>
       <c r="D334" s="2" t="n"/>
       <c r="E334" s="2" t="n"/>
-      <c r="G334" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -4606,11 +2961,6 @@
       </c>
       <c r="D335" s="2" t="n"/>
       <c r="E335" s="2" t="n"/>
-      <c r="G335" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -4618,11 +2968,6 @@
       </c>
       <c r="D336" s="2" t="n"/>
       <c r="E336" s="2" t="n"/>
-      <c r="G336" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -4630,11 +2975,6 @@
       </c>
       <c r="D337" s="2" t="n"/>
       <c r="E337" s="2" t="n"/>
-      <c r="G337" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -4642,11 +2982,6 @@
       </c>
       <c r="D338" s="2" t="n"/>
       <c r="E338" s="2" t="n"/>
-      <c r="G338" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -4654,11 +2989,6 @@
       </c>
       <c r="D339" s="2" t="n"/>
       <c r="E339" s="2" t="n"/>
-      <c r="G339" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -4666,11 +2996,6 @@
       </c>
       <c r="D340" s="2" t="n"/>
       <c r="E340" s="2" t="n"/>
-      <c r="G340" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -4678,11 +3003,6 @@
       </c>
       <c r="D341" s="2" t="n"/>
       <c r="E341" s="2" t="n"/>
-      <c r="G341" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -4690,11 +3010,6 @@
       </c>
       <c r="D342" s="2" t="n"/>
       <c r="E342" s="2" t="n"/>
-      <c r="G342" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -4702,11 +3017,6 @@
       </c>
       <c r="D343" s="2" t="n"/>
       <c r="E343" s="2" t="n"/>
-      <c r="G343" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -4714,11 +3024,6 @@
       </c>
       <c r="D344" s="2" t="n"/>
       <c r="E344" s="2" t="n"/>
-      <c r="G344" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -4726,11 +3031,6 @@
       </c>
       <c r="D345" s="2" t="n"/>
       <c r="E345" s="2" t="n"/>
-      <c r="G345" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -4738,11 +3038,6 @@
       </c>
       <c r="D346" s="2" t="n"/>
       <c r="E346" s="2" t="n"/>
-      <c r="G346" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -4750,11 +3045,6 @@
       </c>
       <c r="D347" s="2" t="n"/>
       <c r="E347" s="2" t="n"/>
-      <c r="G347" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -4762,11 +3052,6 @@
       </c>
       <c r="D348" s="2" t="n"/>
       <c r="E348" s="2" t="n"/>
-      <c r="G348" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -4774,11 +3059,6 @@
       </c>
       <c r="D349" s="2" t="n"/>
       <c r="E349" s="2" t="n"/>
-      <c r="G349" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -4786,11 +3066,6 @@
       </c>
       <c r="D350" s="2" t="n"/>
       <c r="E350" s="2" t="n"/>
-      <c r="G350" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -4798,11 +3073,6 @@
       </c>
       <c r="D351" s="2" t="n"/>
       <c r="E351" s="2" t="n"/>
-      <c r="G351" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -4810,11 +3080,6 @@
       </c>
       <c r="D352" s="2" t="n"/>
       <c r="E352" s="2" t="n"/>
-      <c r="G352" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -4822,11 +3087,6 @@
       </c>
       <c r="D353" s="2" t="n"/>
       <c r="E353" s="2" t="n"/>
-      <c r="G353" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -4834,11 +3094,6 @@
       </c>
       <c r="D354" s="2" t="n"/>
       <c r="E354" s="2" t="n"/>
-      <c r="G354" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -4846,11 +3101,6 @@
       </c>
       <c r="D355" s="2" t="n"/>
       <c r="E355" s="2" t="n"/>
-      <c r="G355" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -4858,11 +3108,6 @@
       </c>
       <c r="D356" s="2" t="n"/>
       <c r="E356" s="2" t="n"/>
-      <c r="G356" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -4870,11 +3115,6 @@
       </c>
       <c r="D357" s="2" t="n"/>
       <c r="E357" s="2" t="n"/>
-      <c r="G357" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -4882,11 +3122,6 @@
       </c>
       <c r="D358" s="2" t="n"/>
       <c r="E358" s="2" t="n"/>
-      <c r="G358" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -4894,11 +3129,6 @@
       </c>
       <c r="D359" s="2" t="n"/>
       <c r="E359" s="2" t="n"/>
-      <c r="G359" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -4906,11 +3136,6 @@
       </c>
       <c r="D360" s="2" t="n"/>
       <c r="E360" s="2" t="n"/>
-      <c r="G360" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -4918,11 +3143,6 @@
       </c>
       <c r="D361" s="2" t="n"/>
       <c r="E361" s="2" t="n"/>
-      <c r="G361" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -4930,11 +3150,6 @@
       </c>
       <c r="D362" s="2" t="n"/>
       <c r="E362" s="2" t="n"/>
-      <c r="G362" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -4942,11 +3157,6 @@
       </c>
       <c r="D363" s="2" t="n"/>
       <c r="E363" s="2" t="n"/>
-      <c r="G363" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -4954,11 +3164,6 @@
       </c>
       <c r="D364" s="2" t="n"/>
       <c r="E364" s="2" t="n"/>
-      <c r="G364" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -4966,11 +3171,6 @@
       </c>
       <c r="D365" s="2" t="n"/>
       <c r="E365" s="2" t="n"/>
-      <c r="G365" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -4978,11 +3178,6 @@
       </c>
       <c r="D366" s="2" t="n"/>
       <c r="E366" s="2" t="n"/>
-      <c r="G366" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -4990,11 +3185,6 @@
       </c>
       <c r="D367" s="2" t="n"/>
       <c r="E367" s="2" t="n"/>
-      <c r="G367" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -5002,11 +3192,6 @@
       </c>
       <c r="D368" s="2" t="n"/>
       <c r="E368" s="2" t="n"/>
-      <c r="G368" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -5014,11 +3199,6 @@
       </c>
       <c r="D369" s="2" t="n"/>
       <c r="E369" s="2" t="n"/>
-      <c r="G369" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -5026,11 +3206,6 @@
       </c>
       <c r="D370" s="2" t="n"/>
       <c r="E370" s="2" t="n"/>
-      <c r="G370" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -5038,11 +3213,6 @@
       </c>
       <c r="D371" s="2" t="n"/>
       <c r="E371" s="2" t="n"/>
-      <c r="G371" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -5050,11 +3220,6 @@
       </c>
       <c r="D372" s="2" t="n"/>
       <c r="E372" s="2" t="n"/>
-      <c r="G372" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -5062,11 +3227,6 @@
       </c>
       <c r="D373" s="2" t="n"/>
       <c r="E373" s="2" t="n"/>
-      <c r="G373" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -5074,11 +3234,6 @@
       </c>
       <c r="D374" s="2" t="n"/>
       <c r="E374" s="2" t="n"/>
-      <c r="G374" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -5086,11 +3241,6 @@
       </c>
       <c r="D375" s="2" t="n"/>
       <c r="E375" s="2" t="n"/>
-      <c r="G375" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -5098,11 +3248,6 @@
       </c>
       <c r="D376" s="2" t="n"/>
       <c r="E376" s="2" t="n"/>
-      <c r="G376" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -5110,11 +3255,6 @@
       </c>
       <c r="D377" s="2" t="n"/>
       <c r="E377" s="2" t="n"/>
-      <c r="G377" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -5122,11 +3262,6 @@
       </c>
       <c r="D378" s="2" t="n"/>
       <c r="E378" s="2" t="n"/>
-      <c r="G378" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -5134,11 +3269,6 @@
       </c>
       <c r="D379" s="2" t="n"/>
       <c r="E379" s="2" t="n"/>
-      <c r="G379" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -5146,11 +3276,6 @@
       </c>
       <c r="D380" s="2" t="n"/>
       <c r="E380" s="2" t="n"/>
-      <c r="G380" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -5158,11 +3283,6 @@
       </c>
       <c r="D381" s="2" t="n"/>
       <c r="E381" s="2" t="n"/>
-      <c r="G381" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -5170,11 +3290,6 @@
       </c>
       <c r="D382" s="2" t="n"/>
       <c r="E382" s="2" t="n"/>
-      <c r="G382" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -5182,11 +3297,6 @@
       </c>
       <c r="D383" s="2" t="n"/>
       <c r="E383" s="2" t="n"/>
-      <c r="G383" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -5194,11 +3304,6 @@
       </c>
       <c r="D384" s="2" t="n"/>
       <c r="E384" s="2" t="n"/>
-      <c r="G384" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -5206,11 +3311,6 @@
       </c>
       <c r="D385" s="2" t="n"/>
       <c r="E385" s="2" t="n"/>
-      <c r="G385" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -5218,11 +3318,6 @@
       </c>
       <c r="D386" s="2" t="n"/>
       <c r="E386" s="2" t="n"/>
-      <c r="G386" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -5230,11 +3325,6 @@
       </c>
       <c r="D387" s="2" t="n"/>
       <c r="E387" s="2" t="n"/>
-      <c r="G387" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -5242,11 +3332,6 @@
       </c>
       <c r="D388" s="2" t="n"/>
       <c r="E388" s="2" t="n"/>
-      <c r="G388" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -5254,11 +3339,6 @@
       </c>
       <c r="D389" s="2" t="n"/>
       <c r="E389" s="2" t="n"/>
-      <c r="G389" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -5266,11 +3346,6 @@
       </c>
       <c r="D390" s="2" t="n"/>
       <c r="E390" s="2" t="n"/>
-      <c r="G390" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -5278,11 +3353,6 @@
       </c>
       <c r="D391" s="2" t="n"/>
       <c r="E391" s="2" t="n"/>
-      <c r="G391" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -5290,11 +3360,6 @@
       </c>
       <c r="D392" s="2" t="n"/>
       <c r="E392" s="2" t="n"/>
-      <c r="G392" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -5302,11 +3367,6 @@
       </c>
       <c r="D393" s="2" t="n"/>
       <c r="E393" s="2" t="n"/>
-      <c r="G393" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -5314,11 +3374,6 @@
       </c>
       <c r="D394" s="2" t="n"/>
       <c r="E394" s="2" t="n"/>
-      <c r="G394" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -5326,11 +3381,6 @@
       </c>
       <c r="D395" s="2" t="n"/>
       <c r="E395" s="2" t="n"/>
-      <c r="G395" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -5338,11 +3388,6 @@
       </c>
       <c r="D396" s="2" t="n"/>
       <c r="E396" s="2" t="n"/>
-      <c r="G396" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -5350,11 +3395,6 @@
       </c>
       <c r="D397" s="2" t="n"/>
       <c r="E397" s="2" t="n"/>
-      <c r="G397" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -5362,11 +3402,6 @@
       </c>
       <c r="D398" s="2" t="n"/>
       <c r="E398" s="2" t="n"/>
-      <c r="G398" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -5374,11 +3409,6 @@
       </c>
       <c r="D399" s="2" t="n"/>
       <c r="E399" s="2" t="n"/>
-      <c r="G399" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -5386,11 +3416,6 @@
       </c>
       <c r="D400" s="2" t="n"/>
       <c r="E400" s="2" t="n"/>
-      <c r="G400" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -5398,11 +3423,6 @@
       </c>
       <c r="D401" s="2" t="n"/>
       <c r="E401" s="2" t="n"/>
-      <c r="G401" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -5410,11 +3430,6 @@
       </c>
       <c r="D402" s="2" t="n"/>
       <c r="E402" s="2" t="n"/>
-      <c r="G402" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -5422,11 +3437,6 @@
       </c>
       <c r="D403" s="2" t="n"/>
       <c r="E403" s="2" t="n"/>
-      <c r="G403" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -5434,11 +3444,6 @@
       </c>
       <c r="D404" s="2" t="n"/>
       <c r="E404" s="2" t="n"/>
-      <c r="G404" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -5446,11 +3451,6 @@
       </c>
       <c r="D405" s="2" t="n"/>
       <c r="E405" s="2" t="n"/>
-      <c r="G405" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -5458,11 +3458,6 @@
       </c>
       <c r="D406" s="2" t="n"/>
       <c r="E406" s="2" t="n"/>
-      <c r="G406" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -5470,11 +3465,6 @@
       </c>
       <c r="D407" s="2" t="n"/>
       <c r="E407" s="2" t="n"/>
-      <c r="G407" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -5482,11 +3472,6 @@
       </c>
       <c r="D408" s="2" t="n"/>
       <c r="E408" s="2" t="n"/>
-      <c r="G408" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -5494,11 +3479,6 @@
       </c>
       <c r="D409" s="2" t="n"/>
       <c r="E409" s="2" t="n"/>
-      <c r="G409" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -5506,11 +3486,6 @@
       </c>
       <c r="D410" s="2" t="n"/>
       <c r="E410" s="2" t="n"/>
-      <c r="G410" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -5518,11 +3493,6 @@
       </c>
       <c r="D411" s="2" t="n"/>
       <c r="E411" s="2" t="n"/>
-      <c r="G411" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -5530,11 +3500,6 @@
       </c>
       <c r="D412" s="2" t="n"/>
       <c r="E412" s="2" t="n"/>
-      <c r="G412" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -5542,11 +3507,6 @@
       </c>
       <c r="D413" s="2" t="n"/>
       <c r="E413" s="2" t="n"/>
-      <c r="G413" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -5554,11 +3514,6 @@
       </c>
       <c r="D414" s="2" t="n"/>
       <c r="E414" s="2" t="n"/>
-      <c r="G414" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -5566,11 +3521,6 @@
       </c>
       <c r="D415" s="2" t="n"/>
       <c r="E415" s="2" t="n"/>
-      <c r="G415" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -5578,11 +3528,6 @@
       </c>
       <c r="D416" s="2" t="n"/>
       <c r="E416" s="2" t="n"/>
-      <c r="G416" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -5590,11 +3535,6 @@
       </c>
       <c r="D417" s="2" t="n"/>
       <c r="E417" s="2" t="n"/>
-      <c r="G417" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -5602,11 +3542,6 @@
       </c>
       <c r="D418" s="2" t="n"/>
       <c r="E418" s="2" t="n"/>
-      <c r="G418" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -5614,11 +3549,6 @@
       </c>
       <c r="D419" s="2" t="n"/>
       <c r="E419" s="2" t="n"/>
-      <c r="G419" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -5626,11 +3556,6 @@
       </c>
       <c r="D420" s="2" t="n"/>
       <c r="E420" s="2" t="n"/>
-      <c r="G420" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -5638,11 +3563,6 @@
       </c>
       <c r="D421" s="2" t="n"/>
       <c r="E421" s="2" t="n"/>
-      <c r="G421" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -5650,11 +3570,6 @@
       </c>
       <c r="D422" s="2" t="n"/>
       <c r="E422" s="2" t="n"/>
-      <c r="G422" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -5662,11 +3577,6 @@
       </c>
       <c r="D423" s="2" t="n"/>
       <c r="E423" s="2" t="n"/>
-      <c r="G423" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -5674,11 +3584,6 @@
       </c>
       <c r="D424" s="2" t="n"/>
       <c r="E424" s="2" t="n"/>
-      <c r="G424" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -5686,11 +3591,6 @@
       </c>
       <c r="D425" s="2" t="n"/>
       <c r="E425" s="2" t="n"/>
-      <c r="G425" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -5698,11 +3598,6 @@
       </c>
       <c r="D426" s="2" t="n"/>
       <c r="E426" s="2" t="n"/>
-      <c r="G426" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -5710,11 +3605,6 @@
       </c>
       <c r="D427" s="2" t="n"/>
       <c r="E427" s="2" t="n"/>
-      <c r="G427" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -5722,11 +3612,6 @@
       </c>
       <c r="D428" s="2" t="n"/>
       <c r="E428" s="2" t="n"/>
-      <c r="G428" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -5734,11 +3619,6 @@
       </c>
       <c r="D429" s="2" t="n"/>
       <c r="E429" s="2" t="n"/>
-      <c r="G429" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -5746,11 +3626,6 @@
       </c>
       <c r="D430" s="2" t="n"/>
       <c r="E430" s="2" t="n"/>
-      <c r="G430" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -5758,11 +3633,6 @@
       </c>
       <c r="D431" s="2" t="n"/>
       <c r="E431" s="2" t="n"/>
-      <c r="G431" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -5770,11 +3640,6 @@
       </c>
       <c r="D432" s="2" t="n"/>
       <c r="E432" s="2" t="n"/>
-      <c r="G432" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -5782,11 +3647,6 @@
       </c>
       <c r="D433" s="2" t="n"/>
       <c r="E433" s="2" t="n"/>
-      <c r="G433" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -5794,11 +3654,6 @@
       </c>
       <c r="D434" s="2" t="n"/>
       <c r="E434" s="2" t="n"/>
-      <c r="G434" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -5806,11 +3661,6 @@
       </c>
       <c r="D435" s="2" t="n"/>
       <c r="E435" s="2" t="n"/>
-      <c r="G435" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -5818,11 +3668,6 @@
       </c>
       <c r="D436" s="2" t="n"/>
       <c r="E436" s="2" t="n"/>
-      <c r="G436" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -5830,11 +3675,6 @@
       </c>
       <c r="D437" s="2" t="n"/>
       <c r="E437" s="2" t="n"/>
-      <c r="G437" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -5842,11 +3682,6 @@
       </c>
       <c r="D438" s="2" t="n"/>
       <c r="E438" s="2" t="n"/>
-      <c r="G438" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -5854,11 +3689,6 @@
       </c>
       <c r="D439" s="2" t="n"/>
       <c r="E439" s="2" t="n"/>
-      <c r="G439" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -5866,11 +3696,6 @@
       </c>
       <c r="D440" s="2" t="n"/>
       <c r="E440" s="2" t="n"/>
-      <c r="G440" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -5878,11 +3703,6 @@
       </c>
       <c r="D441" s="2" t="n"/>
       <c r="E441" s="2" t="n"/>
-      <c r="G441" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -5890,11 +3710,6 @@
       </c>
       <c r="D442" s="2" t="n"/>
       <c r="E442" s="2" t="n"/>
-      <c r="G442" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -5902,11 +3717,6 @@
       </c>
       <c r="D443" s="2" t="n"/>
       <c r="E443" s="2" t="n"/>
-      <c r="G443" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -5914,11 +3724,6 @@
       </c>
       <c r="D444" s="2" t="n"/>
       <c r="E444" s="2" t="n"/>
-      <c r="G444" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -5926,11 +3731,6 @@
       </c>
       <c r="D445" s="2" t="n"/>
       <c r="E445" s="2" t="n"/>
-      <c r="G445" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -5938,11 +3738,6 @@
       </c>
       <c r="D446" s="2" t="n"/>
       <c r="E446" s="2" t="n"/>
-      <c r="G446" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -5950,11 +3745,6 @@
       </c>
       <c r="D447" s="2" t="n"/>
       <c r="E447" s="2" t="n"/>
-      <c r="G447" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -5962,11 +3752,6 @@
       </c>
       <c r="D448" s="2" t="n"/>
       <c r="E448" s="2" t="n"/>
-      <c r="G448" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -5974,11 +3759,6 @@
       </c>
       <c r="D449" s="2" t="n"/>
       <c r="E449" s="2" t="n"/>
-      <c r="G449" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -5986,11 +3766,6 @@
       </c>
       <c r="D450" s="2" t="n"/>
       <c r="E450" s="2" t="n"/>
-      <c r="G450" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -5998,11 +3773,6 @@
       </c>
       <c r="D451" s="2" t="n"/>
       <c r="E451" s="2" t="n"/>
-      <c r="G451" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -6010,11 +3780,6 @@
       </c>
       <c r="D452" s="2" t="n"/>
       <c r="E452" s="2" t="n"/>
-      <c r="G452" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -6022,11 +3787,6 @@
       </c>
       <c r="D453" s="2" t="n"/>
       <c r="E453" s="2" t="n"/>
-      <c r="G453" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -6034,11 +3794,6 @@
       </c>
       <c r="D454" s="2" t="n"/>
       <c r="E454" s="2" t="n"/>
-      <c r="G454" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -6046,11 +3801,6 @@
       </c>
       <c r="D455" s="2" t="n"/>
       <c r="E455" s="2" t="n"/>
-      <c r="G455" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -6058,11 +3808,6 @@
       </c>
       <c r="D456" s="2" t="n"/>
       <c r="E456" s="2" t="n"/>
-      <c r="G456" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -6070,11 +3815,6 @@
       </c>
       <c r="D457" s="2" t="n"/>
       <c r="E457" s="2" t="n"/>
-      <c r="G457" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -6082,11 +3822,6 @@
       </c>
       <c r="D458" s="2" t="n"/>
       <c r="E458" s="2" t="n"/>
-      <c r="G458" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -6094,11 +3829,6 @@
       </c>
       <c r="D459" s="2" t="n"/>
       <c r="E459" s="2" t="n"/>
-      <c r="G459" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -6106,11 +3836,6 @@
       </c>
       <c r="D460" s="2" t="n"/>
       <c r="E460" s="2" t="n"/>
-      <c r="G460" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -6118,11 +3843,6 @@
       </c>
       <c r="D461" s="2" t="n"/>
       <c r="E461" s="2" t="n"/>
-      <c r="G461" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -6130,11 +3850,6 @@
       </c>
       <c r="D462" s="2" t="n"/>
       <c r="E462" s="2" t="n"/>
-      <c r="G462" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -6142,11 +3857,6 @@
       </c>
       <c r="D463" s="2" t="n"/>
       <c r="E463" s="2" t="n"/>
-      <c r="G463" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -6154,11 +3864,6 @@
       </c>
       <c r="D464" s="2" t="n"/>
       <c r="E464" s="2" t="n"/>
-      <c r="G464" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -6166,11 +3871,6 @@
       </c>
       <c r="D465" s="2" t="n"/>
       <c r="E465" s="2" t="n"/>
-      <c r="G465" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -6178,11 +3878,6 @@
       </c>
       <c r="D466" s="2" t="n"/>
       <c r="E466" s="2" t="n"/>
-      <c r="G466" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -6190,11 +3885,6 @@
       </c>
       <c r="D467" s="2" t="n"/>
       <c r="E467" s="2" t="n"/>
-      <c r="G467" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -6202,11 +3892,6 @@
       </c>
       <c r="D468" s="2" t="n"/>
       <c r="E468" s="2" t="n"/>
-      <c r="G468" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -6214,11 +3899,6 @@
       </c>
       <c r="D469" s="2" t="n"/>
       <c r="E469" s="2" t="n"/>
-      <c r="G469" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -6226,11 +3906,6 @@
       </c>
       <c r="D470" s="2" t="n"/>
       <c r="E470" s="2" t="n"/>
-      <c r="G470" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -6238,11 +3913,6 @@
       </c>
       <c r="D471" s="2" t="n"/>
       <c r="E471" s="2" t="n"/>
-      <c r="G471" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -6250,11 +3920,6 @@
       </c>
       <c r="D472" s="2" t="n"/>
       <c r="E472" s="2" t="n"/>
-      <c r="G472" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -6262,11 +3927,6 @@
       </c>
       <c r="D473" s="2" t="n"/>
       <c r="E473" s="2" t="n"/>
-      <c r="G473" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -6274,11 +3934,6 @@
       </c>
       <c r="D474" s="2" t="n"/>
       <c r="E474" s="2" t="n"/>
-      <c r="G474" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -6286,11 +3941,6 @@
       </c>
       <c r="D475" s="2" t="n"/>
       <c r="E475" s="2" t="n"/>
-      <c r="G475" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -6298,11 +3948,6 @@
       </c>
       <c r="D476" s="2" t="n"/>
       <c r="E476" s="2" t="n"/>
-      <c r="G476" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -6310,11 +3955,6 @@
       </c>
       <c r="D477" s="2" t="n"/>
       <c r="E477" s="2" t="n"/>
-      <c r="G477" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
@@ -6322,11 +3962,6 @@
       </c>
       <c r="D478" s="2" t="n"/>
       <c r="E478" s="2" t="n"/>
-      <c r="G478" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -6334,11 +3969,6 @@
       </c>
       <c r="D479" s="2" t="n"/>
       <c r="E479" s="2" t="n"/>
-      <c r="G479" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -6346,11 +3976,6 @@
       </c>
       <c r="D480" s="2" t="n"/>
       <c r="E480" s="2" t="n"/>
-      <c r="G480" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -6358,11 +3983,6 @@
       </c>
       <c r="D481" s="2" t="n"/>
       <c r="E481" s="2" t="n"/>
-      <c r="G481" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -6370,11 +3990,6 @@
       </c>
       <c r="D482" s="2" t="n"/>
       <c r="E482" s="2" t="n"/>
-      <c r="G482" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -6382,11 +3997,6 @@
       </c>
       <c r="D483" s="2" t="n"/>
       <c r="E483" s="2" t="n"/>
-      <c r="G483" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -6394,11 +4004,6 @@
       </c>
       <c r="D484" s="2" t="n"/>
       <c r="E484" s="2" t="n"/>
-      <c r="G484" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
@@ -6406,11 +4011,6 @@
       </c>
       <c r="D485" s="2" t="n"/>
       <c r="E485" s="2" t="n"/>
-      <c r="G485" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
@@ -6418,11 +4018,6 @@
       </c>
       <c r="D486" s="2" t="n"/>
       <c r="E486" s="2" t="n"/>
-      <c r="G486" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -6430,11 +4025,6 @@
       </c>
       <c r="D487" s="2" t="n"/>
       <c r="E487" s="2" t="n"/>
-      <c r="G487" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -6442,11 +4032,6 @@
       </c>
       <c r="D488" s="2" t="n"/>
       <c r="E488" s="2" t="n"/>
-      <c r="G488" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -6454,11 +4039,6 @@
       </c>
       <c r="D489" s="2" t="n"/>
       <c r="E489" s="2" t="n"/>
-      <c r="G489" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -6466,11 +4046,6 @@
       </c>
       <c r="D490" s="2" t="n"/>
       <c r="E490" s="2" t="n"/>
-      <c r="G490" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -6478,11 +4053,6 @@
       </c>
       <c r="D491" s="2" t="n"/>
       <c r="E491" s="2" t="n"/>
-      <c r="G491" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -6490,11 +4060,6 @@
       </c>
       <c r="D492" s="2" t="n"/>
       <c r="E492" s="2" t="n"/>
-      <c r="G492" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -6502,11 +4067,6 @@
       </c>
       <c r="D493" s="2" t="n"/>
       <c r="E493" s="2" t="n"/>
-      <c r="G493" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -6514,11 +4074,6 @@
       </c>
       <c r="D494" s="2" t="n"/>
       <c r="E494" s="2" t="n"/>
-      <c r="G494" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -6526,11 +4081,6 @@
       </c>
       <c r="D495" s="2" t="n"/>
       <c r="E495" s="2" t="n"/>
-      <c r="G495" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -6538,11 +4088,6 @@
       </c>
       <c r="D496" s="2" t="n"/>
       <c r="E496" s="2" t="n"/>
-      <c r="G496" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -6550,11 +4095,6 @@
       </c>
       <c r="D497" s="2" t="n"/>
       <c r="E497" s="2" t="n"/>
-      <c r="G497" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -6562,11 +4102,6 @@
       </c>
       <c r="D498" s="2" t="n"/>
       <c r="E498" s="2" t="n"/>
-      <c r="G498" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -6574,11 +4109,6 @@
       </c>
       <c r="D499" s="2" t="n"/>
       <c r="E499" s="2" t="n"/>
-      <c r="G499" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
@@ -6586,11 +4116,6 @@
       </c>
       <c r="D500" s="2" t="n"/>
       <c r="E500" s="2" t="n"/>
-      <c r="G500" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2:G500">

--- a/terminboard/vorlagen/termine_modell2.xlsx
+++ b/terminboard/vorlagen/termine_modell2.xlsx
@@ -22,10 +22,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="DD.MM.YYYY"/>
-    <numFmt numFmtId="166" formatCode="DD.MM.YYYY HH:MM"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="167" formatCode="DD.MM.YYYY HH:MM"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -76,7 +77,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -552,7 +553,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kalibrierung Hycom (Kristin + Glen) 07:00 - 14:00</t>
+          <t>Hycom, Kristin + Glen</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -583,7 +584,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kalibrierung (Sven + Glen) 15:00 - 22:00</t>
+          <t>Belastungsbank, Sven + Glen</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -612,7 +613,7 @@
       <c r="E4" s="2" t="n"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kalibrierung (Kristin) 07:00 - 13:00</t>
+          <t>Low-Pressure, Kristin</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -643,7 +644,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kalibrierung (Bernd + Tommy) 08:00 - 15:00</t>
+          <t>THSA, Bernd + Tommy</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -4182,80 +4183,232 @@
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>46314.29166666666</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>46314.58333333334</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>46315.29166666666</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>46315.58333333334</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>46316.29166666666</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>46316.58333333334</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>46317.29166666666</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>46317.58333333334</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>46318.29166666666</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>46318.58333333334</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
+      <c r="A7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>46321.29166666666</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>46321.58333333334</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
+      <c r="A8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>46321.625</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>46321.91666666666</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>46322.625</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>46322.91666666666</v>
+      </c>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
+      <c r="A10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>46331.29166666666</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>46331.54166666666</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n"/>
+      <c r="A11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>46335.33333333334</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>46335.625</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
+      <c r="A12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>46336.33333333334</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>46336.625</v>
+      </c>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
+      <c r="A13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>46337.33333333334</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>46337.625</v>
+      </c>
+      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
+      <c r="A14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>46338.33333333334</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>46338.625</v>
+      </c>
+      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
+      <c r="A15" t="n">
+        <v>4</v>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>46339.33333333334</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>46339.625</v>
+      </c>
+      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
+      <c r="A16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>46342.33333333334</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>46342.625</v>
+      </c>
+      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
+      <c r="A17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>46343.33333333334</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>46343.625</v>
+      </c>
+      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n"/>
+      <c r="A18" t="n">
+        <v>4</v>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>46344.33333333334</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>46344.625</v>
+      </c>
+      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
+      <c r="A19" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>46345.33333333334</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>46345.625</v>
+      </c>
+      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n"/>
+      <c r="A20" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>46346.33333333334</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>46346.625</v>
+      </c>
+      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="B21" s="3" t="n"/>
